--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -453,7 +453,7 @@
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C2" t="n">
-        <v>334.17999268</v>
+        <v>334.57901001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>12.07333373999999</v>
+        <v>11.8607954991482</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6067481210509929</v>
+        <v>0.4880706692182213</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -745,7 +745,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.438384134924214</v>
+        <v>7.54877267609978</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,14 +776,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" t="n">
-        <v>512.0443725600001</v>
+        <v>492.80999756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -807,13 +807,17 @@
         <v>16.90717447700184</v>
       </c>
       <c r="K3" t="n">
-        <v>16.24162827695801</v>
+        <v>11.87514133030647</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>74.07407407407408</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.49920667937732</v>
+      </c>
       <c r="O3" t="n">
         <v>6</v>
       </c>
@@ -836,31 +840,31 @@
         <v>56.43279073180463</v>
       </c>
       <c r="V3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W3" t="n">
-        <v>68.08510638297872</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="X3" t="n">
         <v>19.58909830419979</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.799143128186132</v>
+        <v>6.450384761887962</v>
       </c>
       <c r="Z3" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>43.39622641509434</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.48418530648395</v>
+        <v>13.19543715763684</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.264236080466153</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -891,10 +895,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C4" t="n">
-        <v>255.46499634</v>
+        <v>253.40499878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,43 +926,43 @@
         <v>13.09888885119279</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3579591581254</v>
+        <v>1.532573492248535</v>
       </c>
       <c r="L4" t="n">
         <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>42.5</v>
+        <v>55</v>
       </c>
       <c r="N4" t="n">
-        <v>12.71421142423889</v>
+        <v>11.03343980421643</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.604214127929149</v>
+        <v>6.369804571382431</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
-        <v>39.28571428571428</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="S4" t="n">
-        <v>45.29288172145316</v>
+        <v>41.12723098792893</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.007167435738872</v>
+        <v>-6.344622292276753</v>
       </c>
       <c r="U4" t="n">
-        <v>23.56568654157959</v>
+        <v>18.81127593879773</v>
       </c>
       <c r="V4" t="n">
         <v>38</v>
       </c>
       <c r="W4" t="n">
-        <v>42.10526315789474</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -1000,19 +1004,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C5" t="n">
-        <v>364.73440552</v>
+        <v>346.29998779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1022,7 +1026,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %93.75: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1035,22 +1039,22 @@
         <v>20.89062975160487</v>
       </c>
       <c r="K5" t="n">
-        <v>6.544684903149345</v>
+        <v>1.159700106840678</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>93.75</v>
       </c>
       <c r="N5" t="n">
-        <v>15.98815539256542</v>
+        <v>13.16398977669445</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.819202598678804</v>
       </c>
       <c r="Q5" t="n">
         <v>45</v>
@@ -1113,10 +1117,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>209.68009949</v>
+        <v>210.13989258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,22 +1148,22 @@
         <v>15.10639127416894</v>
       </c>
       <c r="K6" t="n">
-        <v>2.447892394975537</v>
+        <v>2.67254334240854</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>58.13953488372093</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N6" t="n">
-        <v>10.45822777129368</v>
+        <v>10.33168989683851</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>5.41944541291195</v>
+        <v>5.188784152180426</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1168,10 +1172,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="S6" t="n">
-        <v>39.56854928918239</v>
+        <v>39.65188262251572</v>
       </c>
       <c r="T6" t="n">
-        <v>7.098117377484272</v>
+        <v>7.014784044150943</v>
       </c>
       <c r="U6" t="n">
         <v>30.23238890769975</v>
@@ -1222,10 +1226,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C7" t="n">
-        <v>62.74499893</v>
+        <v>61.89500046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1325,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C8" t="n">
-        <v>138.36749268</v>
+        <v>135.38999939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,10 +1370,10 @@
         <v>57.69230769230769</v>
       </c>
       <c r="S8" t="n">
-        <v>31.09258967782676</v>
+        <v>30.99643583167292</v>
       </c>
       <c r="T8" t="n">
-        <v>26.59971801448093</v>
+        <v>26.69587186063478</v>
       </c>
       <c r="U8" t="n">
         <v>38.94861374659171</v>
@@ -1420,19 +1424,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C9" t="n">
-        <v>821.59002686</v>
+        <v>785.51000977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1451,22 +1455,22 @@
         <v>17.49839415508021</v>
       </c>
       <c r="K9" t="n">
-        <v>6.507734253311148</v>
+        <v>1.830461226077262</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M9" t="n">
-        <v>58.8235294117647</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>8.608721268647214</v>
+        <v>9.209861197941871</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.094588911529939</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1475,10 +1479,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="S9" t="n">
-        <v>33.13920704025206</v>
+        <v>33.22541393680378</v>
       </c>
       <c r="T9" t="n">
-        <v>18.58493089078242</v>
+        <v>18.4987239942307</v>
       </c>
       <c r="U9" t="n">
         <v>34.43102188199472</v>
@@ -1529,10 +1533,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C10" t="n">
-        <v>136.94999695</v>
+        <v>138.71000671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,25 +1593,25 @@
         <v>63.26530612244898</v>
       </c>
       <c r="X10" t="n">
-        <v>21.07924374852153</v>
+        <v>21.88562772325671</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.396790588609997</v>
+        <v>0.7903270112048277</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>27.27272727272727</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.48118419918245</v>
+        <v>11.95977359310978</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>8.725080514870353</v>
+        <v>9.283039356288691</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C11" t="n">
-        <v>248.86000061</v>
+        <v>257.23001099</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,25 +1702,25 @@
         <v>60.8695652173913</v>
       </c>
       <c r="X11" t="n">
-        <v>23.62430486264277</v>
+        <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.235244043371736</v>
+        <v>4.115248992532116</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>42.85714285714285</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.05852079543693</v>
+        <v>10.34409543203857</v>
       </c>
       <c r="AC11" t="n">
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.980394793385654</v>
+        <v>6.13731687847795</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1747,10 +1751,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C12" t="n">
-        <v>111.44999695</v>
+        <v>110.97000122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,13 +1782,13 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>3.809609087892496</v>
+        <v>3.362519177988665</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N12" t="n">
         <v>12.1620108159896</v>
@@ -1793,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.036611782787491</v>
+        <v>4.48661744981822</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1834,10 +1838,10 @@
         <v>26.66666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.854497354497354</v>
+        <v>6.687830687830687</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.81216931216931</v>
+        <v>19.97883597883598</v>
       </c>
       <c r="AI12" t="n">
         <v>10.89745332569237</v>
@@ -1856,19 +1860,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>94.1867981</v>
+        <v>95.85500336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1884,25 +1888,25 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>12.68790639719547</v>
+        <v>12.62182199075366</v>
       </c>
       <c r="K13" t="n">
-        <v>1.988954694565259</v>
+        <v>3.79534915871016</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>48.71794871794872</v>
+        <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>9.760564659793181</v>
+        <v>8.799430895124942</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01082990355947278</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>36</v>
@@ -1965,10 +1969,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C14" t="n">
-        <v>214.11019897</v>
+        <v>215.28999329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,10 +2014,10 @@
         <v>36.36363636363637</v>
       </c>
       <c r="S14" t="n">
-        <v>23.52874184112325</v>
+        <v>23.64237820475961</v>
       </c>
       <c r="T14" t="n">
-        <v>12.83489452251312</v>
+        <v>12.72125815887676</v>
       </c>
       <c r="U14" t="n">
         <v>19.73320467036612</v>
@@ -2025,25 +2029,25 @@
         <v>48.38709677419355</v>
       </c>
       <c r="X14" t="n">
-        <v>16.96346888030198</v>
+        <v>17.09797149318395</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.513245180454437</v>
+        <v>1.08430998214698</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.89220626203184</v>
+        <v>19.84582265015259</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>8.617153479262873</v>
+        <v>9.013423468252457</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2052,10 +2056,10 @@
         <v>50</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.80534055727554</v>
+        <v>12.8231658692185</v>
       </c>
       <c r="AH14" t="n">
-        <v>37.19465944272446</v>
+        <v>37.1768341307815</v>
       </c>
       <c r="AI14" t="n">
         <v>29.92980081982123</v>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C15" t="n">
-        <v>106.62000275</v>
+        <v>108.90499878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,25 +2138,25 @@
         <v>55.55555555555556</v>
       </c>
       <c r="X15" t="n">
-        <v>17.01883320124282</v>
+        <v>15.08075692700643</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.692947055460762</v>
+        <v>2.650401266750657</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.66666666666667</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.26648462295025</v>
+        <v>10.42999878940044</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.568373777780645</v>
+        <v>7.54969597089784</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -2183,19 +2187,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C16" t="n">
-        <v>14.02499962</v>
+        <v>13.89999962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2214,22 +2218,22 @@
         <v>12.68260788003351</v>
       </c>
       <c r="K16" t="n">
-        <v>6.653992587719948</v>
+        <v>5.703422218045651</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="N16" t="n">
-        <v>15.96538157465413</v>
+        <v>13.88774541267856</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.28057538320998</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2270,10 +2274,10 @@
         <v>38.46153846153846</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.2785690793731</v>
+        <v>17.3756941764982</v>
       </c>
       <c r="AH16" t="n">
-        <v>21.18296938216536</v>
+        <v>21.08584428504026</v>
       </c>
       <c r="AI16" t="n">
         <v>24.89137346556135</v>
@@ -2292,10 +2296,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C17" t="n">
-        <v>324.10159302</v>
+        <v>316.93991089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,25 +2324,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>17.40561498741013</v>
+        <v>19.74055820196081</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9159264312109672</v>
+        <v>1.557000679226794</v>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M17" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="N17" t="n">
-        <v>13.51539026952484</v>
+        <v>13.82142119397245</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.019777570607633</v>
+        <v>6.344219775772797</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2401,10 +2405,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C18" t="n">
-        <v>86.01000214</v>
+        <v>86.69999695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,10 +2482,10 @@
         <v>48.48484848484848</v>
       </c>
       <c r="AG18" t="n">
-        <v>27.43188693793001</v>
+        <v>27.47618961381163</v>
       </c>
       <c r="AH18" t="n">
-        <v>21.05296154691848</v>
+        <v>21.00865887103686</v>
       </c>
       <c r="AI18" t="n">
         <v>32.5040421081337</v>
@@ -2500,19 +2504,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C19" t="n">
-        <v>340.22000122</v>
+        <v>346.05999756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2531,22 +2535,22 @@
         <v>14.75759965099349</v>
       </c>
       <c r="K19" t="n">
-        <v>3.807899970107953</v>
+        <v>5.589799193300604</v>
       </c>
       <c r="L19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>34.78260869565217</v>
+        <v>40</v>
       </c>
       <c r="N19" t="n">
-        <v>11.15736896344867</v>
+        <v>9.285175638317453</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.148371203189091</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>23</v>
@@ -2587,10 +2591,10 @@
         <v>55</v>
       </c>
       <c r="AG19" t="n">
-        <v>19.73878029472659</v>
+        <v>19.83401838996468</v>
       </c>
       <c r="AH19" t="n">
-        <v>35.26121970527341</v>
+        <v>35.16598161003532</v>
       </c>
       <c r="AI19" t="n">
         <v>34.20853424503424</v>
@@ -2609,10 +2613,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>1028.60998535</v>
+        <v>998.90997314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2712,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C21" t="n">
-        <v>35.70500183</v>
+        <v>34.95500183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,10 +2757,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S21" t="n">
-        <v>35.86874293564107</v>
+        <v>35.56596061158216</v>
       </c>
       <c r="T21" t="n">
-        <v>25.83338472393339</v>
+        <v>26.13616704799231</v>
       </c>
       <c r="U21" t="n">
         <v>47.42656695641357</v>
@@ -2771,16 +2775,16 @@
         <v>21.98718090672251</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.187597097293541</v>
+        <v>8.158169806182535</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>54.54545454545455</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.51179069827537</v>
+        <v>14.36277581346553</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -2817,10 +2821,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C22" t="n">
-        <v>309.48498535</v>
+        <v>311.29998779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,22 +2852,22 @@
         <v>15.08538893012877</v>
       </c>
       <c r="K22" t="n">
-        <v>1.703909881054022</v>
+        <v>2.30036157767799</v>
       </c>
       <c r="L22" t="n">
         <v>19</v>
       </c>
       <c r="M22" t="n">
-        <v>47.36842105263158</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N22" t="n">
-        <v>9.268289662533006</v>
+        <v>9.733572734950815</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>8.157100477895618</v>
+        <v>7.526501669767405</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2926,10 +2930,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C23" t="n">
-        <v>102.51000214</v>
+        <v>98.02999878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,7 +2950,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -2957,13 +2965,17 @@
         <v>20.85153887202731</v>
       </c>
       <c r="K23" t="n">
-        <v>20.40169470806945</v>
+        <v>15.13976918293705</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.35994594923866</v>
+      </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
@@ -2995,16 +3007,16 @@
         <v>25.31125581911988</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.917893152501084</v>
+        <v>8.116977656711732</v>
       </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>52.94117647058823</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.01950653633058</v>
+        <v>9.356344946747415</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
@@ -3013,25 +3025,25 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF23" t="n">
-        <v>45.65217391304348</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.66086830789348</v>
+        <v>19.48711053269496</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.99130560515</v>
+        <v>25.19374053113482</v>
       </c>
       <c r="AI23" t="n">
-        <v>32.15473378228458</v>
+        <v>31.41096626549528</v>
       </c>
       <c r="AJ23" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AK23" t="n">
-        <v>49.18032786885246</v>
+        <v>48.38709677419355</v>
       </c>
     </row>
     <row r="24">
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C24" t="n">
-        <v>266</v>
+        <v>268.06500244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,7 +3116,7 @@
         <v>12.23047619452817</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.361656145275829</v>
+        <v>4.626962870924078</v>
       </c>
       <c r="Z24" t="n">
         <v>12</v>
@@ -3113,13 +3125,13 @@
         <v>16.66666666666667</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.32145774201913</v>
+        <v>6.430932275361045</v>
       </c>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.6745086914285769</v>
+        <v>1.439649161237977</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3150,10 +3162,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C25" t="n">
-        <v>356.26501465</v>
+        <v>351.9750061</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3249,10 +3261,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C26" t="n">
-        <v>30.99500084</v>
+        <v>30.98500061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3360,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C27" t="n">
-        <v>88.29499817</v>
+        <v>89.08000183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,10 +3459,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C28" t="n">
-        <v>568.77001953</v>
+        <v>575.82501221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,10 +3558,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C29" t="n">
-        <v>252.88000488</v>
+        <v>257.30999756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,10 +3657,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C30" t="n">
-        <v>648.98498535</v>
+        <v>660.60498047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,22 +3720,22 @@
         <v>23.63243175397585</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.296610427613344</v>
+        <v>0.5472434381346591</v>
       </c>
       <c r="Z30" t="n">
         <v>20</v>
       </c>
       <c r="AA30" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.10925358061076</v>
+        <v>10.2356136366264</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.790441241184261</v>
+        <v>5.482760609529624</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3754,10 +3766,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C31" t="n">
-        <v>213.8999939</v>
+        <v>209.38499451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,14 +3865,14 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C32" t="n">
-        <v>495.37869263</v>
+        <v>505.23999023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3870,7 +3882,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3912,27 +3924,17 @@
       <c r="W32" t="n">
         <v>52.17391304347826</v>
       </c>
-      <c r="X32" t="n">
-        <v>15.2338025005897</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>4.326419599513132</v>
-      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>35</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>9.51560993328431</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>10</v>
       </c>
-      <c r="AD32" t="n">
-        <v>5.930143281705802</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
         <v>16</v>
       </c>
@@ -3962,10 +3964,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C33" t="n">
-        <v>971.52001953</v>
+        <v>919.3099975600001</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3976,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3989,17 +3991,27 @@
       <c r="I33" t="n">
         <v>10</v>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>13.41136277305126</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.851320897618813</v>
+      </c>
       <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="M33" t="n">
+        <v>68.23529411764706</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13.89179737264407</v>
+      </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>4.073269807223667</v>
+      </c>
       <c r="Q33" t="n">
         <v>55</v>
       </c>
@@ -4025,16 +4037,16 @@
         <v>35.35905174018239</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.799693325037881</v>
+        <v>11.80832923710541</v>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="n">
-        <v>44.44444444444444</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.561326334185281</v>
+        <v>7.308475867796361</v>
       </c>
       <c r="AC33" t="n">
         <v>4</v>
@@ -4071,10 +4083,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>76.75499725</v>
+        <v>80.71499634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4102,22 +4114,22 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>2.299078366051921</v>
+        <v>7.576966083485259</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="M34" t="n">
-        <v>55</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N34" t="n">
-        <v>10.71281442913421</v>
+        <v>11.68643474899504</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>7.527850452759943</v>
+        <v>2.252372422024207</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4126,10 +4138,10 @@
         <v>60</v>
       </c>
       <c r="S34" t="n">
-        <v>46.55435131972062</v>
+        <v>46.38164587390593</v>
       </c>
       <c r="T34" t="n">
-        <v>13.44564868027938</v>
+        <v>13.61835412609407</v>
       </c>
       <c r="U34" t="n">
         <v>43.5727090128925</v>
@@ -4141,25 +4153,25 @@
         <v>65.11627906976744</v>
       </c>
       <c r="X34" t="n">
-        <v>17.56433378267131</v>
+        <v>15.82155460093264</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.187800652240851</v>
+        <v>3.450959548803456</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="AA34" t="n">
-        <v>37.5</v>
+        <v>30.3030303030303</v>
       </c>
       <c r="AB34" t="n">
-        <v>12.87844361751754</v>
+        <v>10.44044289477803</v>
       </c>
       <c r="AC34" t="n">
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.973811062836039</v>
+        <v>6.783123292154247</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4190,19 +4202,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C35" t="n">
-        <v>36.88000107</v>
+        <v>37.31999969</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4221,22 +4233,22 @@
         <v>15.41309877759897</v>
       </c>
       <c r="K35" t="n">
-        <v>0.902877802631652</v>
+        <v>2.10670442137062</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M35" t="n">
-        <v>44</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N35" t="n">
-        <v>10.25955150494271</v>
+        <v>14.2445891002565</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.087305160427987</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4245,10 +4257,10 @@
         <v>37.93103448275862</v>
       </c>
       <c r="S35" t="n">
-        <v>29.36647249527574</v>
+        <v>29.3692092221504</v>
       </c>
       <c r="T35" t="n">
-        <v>8.564561987482879</v>
+        <v>8.561825260608217</v>
       </c>
       <c r="U35" t="n">
         <v>22.68802210080984</v>
@@ -4277,10 +4289,10 @@
         <v>48.14814814814815</v>
       </c>
       <c r="AG35" t="n">
-        <v>12.98543438188132</v>
+        <v>12.99655661522578</v>
       </c>
       <c r="AH35" t="n">
-        <v>35.16271376626683</v>
+        <v>35.15159153292237</v>
       </c>
       <c r="AI35" t="n">
         <v>30.74322697621846</v>
@@ -4299,10 +4311,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C36" t="n">
-        <v>219.16000366</v>
+        <v>211.77380371</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4311,7 +4323,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4319,24 +4331,38 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>5</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>11.0027272252725</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.361131062860665</v>
+      </c>
       <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="M36" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13.09038498587369</v>
+      </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0.6302898659873213</v>
+      </c>
       <c r="Q36" t="n">
         <v>49</v>
       </c>
@@ -4344,10 +4370,10 @@
         <v>63.26530612244898</v>
       </c>
       <c r="S36" t="n">
-        <v>62.95905244284938</v>
+        <v>63.65790793687295</v>
       </c>
       <c r="T36" t="n">
-        <v>0.3062536795995925</v>
+        <v>-0.3926018144239762</v>
       </c>
       <c r="U36" t="n">
         <v>49.26706756079243</v>
@@ -4359,19 +4385,19 @@
         <v>69.73684210526316</v>
       </c>
       <c r="X36" t="n">
-        <v>20.42061973984555</v>
+        <v>19.25831203212749</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.645080599256659</v>
+        <v>9.791357700436842</v>
       </c>
       <c r="Z36" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="AB36" t="n">
-        <v>14.26255828977072</v>
+        <v>13.69584238822664</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4408,10 +4434,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C37" t="n">
-        <v>151.6499939</v>
+        <v>143.96499634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4436,25 +4462,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>11.8037506971379</v>
+        <v>17.39308902782027</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7299845683178319</v>
+        <v>2.095597436386276</v>
       </c>
       <c r="L37" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M37" t="n">
-        <v>50</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N37" t="n">
-        <v>9.902261401013666</v>
+        <v>9.257798206011573</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>7.21733003617353</v>
+        <v>5.783209767975195</v>
       </c>
       <c r="Q37" t="n">
         <v>33</v>
@@ -4463,10 +4489,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S37" t="n">
-        <v>25.3896059713994</v>
+        <v>25.46536354715698</v>
       </c>
       <c r="T37" t="n">
-        <v>38.24675766496423</v>
+        <v>38.17100008920665</v>
       </c>
       <c r="U37" t="n">
         <v>46.6161783022664</v>
@@ -4478,17 +4504,15 @@
         <v>65.78947368421052</v>
       </c>
       <c r="X37" t="n">
-        <v>35.79952354167501</v>
+        <v>31.09591287417577</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.15993168739188</v>
+        <v>15.66198071920939</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>10</v>
@@ -4525,10 +4549,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C38" t="n">
-        <v>61.27999878</v>
+        <v>62.65000153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4585,25 +4609,25 @@
         <v>69.62025316455696</v>
       </c>
       <c r="X38" t="n">
-        <v>15.9895673760424</v>
+        <v>17.34998396575658</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.542421070191713</v>
+        <v>0.5081779955538046</v>
       </c>
       <c r="Z38" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA38" t="n">
-        <v>39.58333333333334</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.94235975724232</v>
+        <v>10.89005815116391</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>8.590074041773665</v>
+        <v>9.540303728704469</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4634,10 +4658,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C39" t="n">
-        <v>137.19999695</v>
+        <v>136.53999329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,10 +4703,10 @@
         <v>31.25</v>
       </c>
       <c r="S39" t="n">
-        <v>16.12152777777778</v>
+        <v>16.1328502415459</v>
       </c>
       <c r="T39" t="n">
-        <v>15.12847222222222</v>
+        <v>15.1171497584541</v>
       </c>
       <c r="U39" t="n">
         <v>14.16464385478204</v>
@@ -4733,10 +4757,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C40" t="n">
-        <v>27.55999947</v>
+        <v>27.83499908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,25 +4817,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X40" t="n">
-        <v>18.40291441134037</v>
+        <v>18.25910194830291</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.648749270689802</v>
+        <v>4.707292171540867</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>30.76923076923077</v>
+        <v>25</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.024442601027385</v>
+        <v>7.917880425252678</v>
       </c>
       <c r="AC40" t="n">
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.611757338324807</v>
+        <v>5.554158286683153</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4842,10 +4866,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>166.46000671</v>
+        <v>173.33999634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4862,7 +4886,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.40: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -4873,22 +4901,22 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>1.160743618716076</v>
+        <v>5.341837208796107</v>
       </c>
       <c r="L41" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="M41" t="n">
-        <v>67.69230769230769</v>
+        <v>81.3953488372093</v>
       </c>
       <c r="N41" t="n">
-        <v>17.55900602968539</v>
+        <v>19.24691857538625</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>8.737832547573877</v>
+        <v>4.421949450123064</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4915,16 +4943,16 @@
         <v>31.46984695975164</v>
       </c>
       <c r="Y41" t="n">
-        <v>11.63135795381976</v>
+        <v>7.97897710324047</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA41" t="n">
-        <v>16.66666666666667</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB41" t="n">
-        <v>22.98194067748828</v>
+        <v>17.15255780364066</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -4961,10 +4989,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C42" t="n">
-        <v>183.6499939</v>
+        <v>179.33999634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,10 +5034,10 @@
         <v>46.34146341463415</v>
       </c>
       <c r="S42" t="n">
-        <v>44.23735053070403</v>
+        <v>44.54745506032076</v>
       </c>
       <c r="T42" t="n">
-        <v>2.104112883930114</v>
+        <v>1.794008354313391</v>
       </c>
       <c r="U42" t="n">
         <v>32.05623397633605</v>
@@ -5021,25 +5049,25 @@
         <v>51.02040816326531</v>
       </c>
       <c r="X42" t="n">
-        <v>29.62418784429108</v>
+        <v>29.7921530560096</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.8476445900327922</v>
+        <v>3.299908416141561</v>
       </c>
       <c r="Z42" t="n">
         <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>41.66666666666666</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.855953484901036</v>
+        <v>10.96385939172265</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>9.230598075179131</v>
+        <v>6.928733441837654</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5070,10 +5098,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C43" t="n">
-        <v>55.86500168</v>
+        <v>53.97999954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,7 +5110,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5097,17 +5125,27 @@
       <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>11.54482243832677</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.9349289534418048</v>
+      </c>
       <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="M43" t="n">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="N43" t="n">
+        <v>11.83834137200701</v>
+      </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>3.036680243736067</v>
+      </c>
       <c r="Q43" t="n">
         <v>43</v>
       </c>
@@ -5115,10 +5153,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S43" t="n">
-        <v>36.38598429296103</v>
+        <v>36.44412382784476</v>
       </c>
       <c r="T43" t="n">
-        <v>14.77680640471338</v>
+        <v>14.71866686982966</v>
       </c>
       <c r="U43" t="n">
         <v>36.75230846944931</v>
@@ -5133,16 +5171,16 @@
         <v>25.17598350173391</v>
       </c>
       <c r="Y43" t="n">
-        <v>7.600061974728045</v>
+        <v>10.71782937248434</v>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="n">
-        <v>44.44444444444444</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.08344150974317</v>
+        <v>10.03974720938522</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5157,10 +5195,10 @@
         <v>47.22222222222222</v>
       </c>
       <c r="AG43" t="n">
-        <v>32.49141240095187</v>
+        <v>32.56085684539632</v>
       </c>
       <c r="AH43" t="n">
-        <v>14.73080982127035</v>
+        <v>14.6613653768259</v>
       </c>
       <c r="AI43" t="n">
         <v>31.98604151517905</v>
@@ -5179,24 +5217,24 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C44" t="n">
-        <v>39.27000046</v>
+        <v>37.81499863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5210,16 +5248,16 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>15.19507271108063</v>
+        <v>10.92695354534927</v>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>60</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N44" t="n">
-        <v>19.9152360837106</v>
+        <v>19.34901320079606</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
@@ -5234,10 +5272,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="S44" t="n">
-        <v>48.59030815813367</v>
+        <v>48.6312745446883</v>
       </c>
       <c r="T44" t="n">
-        <v>22.83826327043776</v>
+        <v>22.79729688388313</v>
       </c>
       <c r="U44" t="n">
         <v>59.94980341827974</v>
@@ -5249,10 +5287,10 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X44" t="n">
-        <v>55.49431385721313</v>
+        <v>54.19096411365851</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.185064551086318</v>
+        <v>10.62397209749843</v>
       </c>
       <c r="Z44" t="n">
         <v>4</v>
@@ -5261,13 +5299,13 @@
         <v>50</v>
       </c>
       <c r="AB44" t="n">
-        <v>15.75808927979525</v>
+        <v>26.99088785794874</v>
       </c>
       <c r="AC44" t="n">
         <v>8</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.878021888365399</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>77</v>
@@ -5298,10 +5336,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C45" t="n">
-        <v>26.19499969</v>
+        <v>26.41500092</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,25 +5396,25 @@
         <v>43.47826086956522</v>
       </c>
       <c r="X45" t="n">
-        <v>17.25056062573953</v>
+        <v>17.47228675294625</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.9266294821817844</v>
+        <v>0.2831213690116186</v>
       </c>
       <c r="Z45" t="n">
         <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>50</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.923365812762649</v>
+        <v>10.83363306638135</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>7.139527484376917</v>
+        <v>7.738788795771889</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5385,10 +5423,10 @@
         <v>29.41176470588235</v>
       </c>
       <c r="AG45" t="n">
-        <v>15.14163570391944</v>
+        <v>14.75378825724847</v>
       </c>
       <c r="AH45" t="n">
-        <v>14.27012900196291</v>
+        <v>14.65797644863389</v>
       </c>
       <c r="AI45" t="n">
         <v>13.27998961029523</v>
@@ -5407,10 +5445,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C46" t="n">
-        <v>365</v>
+        <v>363.27999878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,10 +5490,10 @@
         <v>67.12328767123287</v>
       </c>
       <c r="S46" t="n">
-        <v>72.47786164702568</v>
+        <v>72.45070715600723</v>
       </c>
       <c r="T46" t="n">
-        <v>-5.354573975792803</v>
+        <v>-5.327419484774353</v>
       </c>
       <c r="U46" t="n">
         <v>55.72900614018867</v>
@@ -5467,19 +5505,19 @@
         <v>75.22935779816514</v>
       </c>
       <c r="X46" t="n">
-        <v>27.17819882386527</v>
+        <v>23.71227574517236</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.957819007551878</v>
+        <v>5.405689328807961</v>
       </c>
       <c r="Z46" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>27.27272727272727</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.86431866808767</v>
+        <v>13.22405888697484</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5516,10 +5554,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C47" t="n">
-        <v>71.57800293</v>
+        <v>72.44490051</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5528,7 +5566,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5536,11 +5574,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5551,22 +5585,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>3.376668316378817</v>
+        <v>4.628686812613947</v>
       </c>
       <c r="L47" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M47" t="n">
-        <v>74.19354838709677</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N47" t="n">
-        <v>15.18584596772699</v>
+        <v>14.83997524742984</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0.6029713413799653</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5593,13 +5627,13 @@
         <v>23.42098914682247</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.09657647091209</v>
+        <v>12.04406921355319</v>
       </c>
       <c r="Z47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA47" t="n">
-        <v>83.33333333333333</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AB47" t="n">
         <v>13.43868584457045</v>
@@ -5639,10 +5673,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>377.35998535</v>
+        <v>385.82000732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,25 +5701,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.90087665996108</v>
+        <v>10.35913645708599</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1698832363366432</v>
+        <v>2.639003346895241</v>
       </c>
       <c r="L48" t="n">
         <v>26</v>
       </c>
       <c r="M48" t="n">
-        <v>53.84615384615385</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N48" t="n">
-        <v>11.57772343413499</v>
+        <v>12.99734936520743</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>7.816837267534105</v>
+        <v>5.22315735567489</v>
       </c>
       <c r="Q48" t="n">
         <v>26</v>
@@ -5748,10 +5782,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C49" t="n">
-        <v>370.1000061</v>
+        <v>376.20001221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5847,10 +5881,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C50" t="n">
-        <v>50.72000122</v>
+        <v>51.31999969</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,23 +5916,23 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R50" t="n">
-        <v>38.88888888888889</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="S50" t="n">
-        <v>13.77425267227899</v>
+        <v>13.70622279382667</v>
       </c>
       <c r="T50" t="n">
-        <v>25.1146362166099</v>
+        <v>23.13588246933123</v>
       </c>
       <c r="U50" t="n">
-        <v>20.30524657216362</v>
+        <v>19.14951274513507</v>
       </c>
       <c r="V50" t="n">
         <v>20</v>
@@ -5907,25 +5941,25 @@
         <v>35</v>
       </c>
       <c r="X50" t="n">
-        <v>12.95187434147744</v>
+        <v>14.10512439308564</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.4123288606357245</v>
+        <v>0.2526745735270564</v>
       </c>
       <c r="Z50" t="n">
         <v>24</v>
       </c>
       <c r="AA50" t="n">
-        <v>41.66666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.634191932247624</v>
+        <v>9.976199754602384</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.594244670248857</v>
+        <v>1.751751657502798</v>
       </c>
       <c r="AE50" t="n">
         <v>19</v>
@@ -5956,10 +5990,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C51" t="n">
-        <v>28.01000023</v>
+        <v>28.09499931</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6001,10 +6035,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S51" t="n">
-        <v>35.70748998671556</v>
+        <v>35.78295972973849</v>
       </c>
       <c r="T51" t="n">
-        <v>30.24995682179508</v>
+        <v>30.17448707877215</v>
       </c>
       <c r="U51" t="n">
         <v>51.67092456194193</v>
@@ -6019,16 +6053,16 @@
         <v>14.13385906971916</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.380474466281791</v>
+        <v>3.087273084169473</v>
       </c>
       <c r="Z51" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA51" t="n">
-        <v>49.01960784313726</v>
+        <v>49.0566037735849</v>
       </c>
       <c r="AB51" t="n">
-        <v>13.75474128913363</v>
+        <v>14.08684353074138</v>
       </c>
       <c r="AC51" t="n">
         <v>3</v>
@@ -6065,10 +6099,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C52" t="n">
-        <v>90.08999634</v>
+        <v>88.58499908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,10 +6198,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C53" t="n">
-        <v>106.54000092</v>
+        <v>109.47499847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6195,16 +6229,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>4.297600904793653</v>
+        <v>7.170824111880947</v>
       </c>
       <c r="L53" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>46.15384615384615</v>
+        <v>20</v>
       </c>
       <c r="N53" t="n">
-        <v>10.30700197623545</v>
+        <v>7.058549906036282</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -6273,10 +6307,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C54" t="n">
-        <v>166.13000488</v>
+        <v>166.17500305</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6318,10 +6352,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S54" t="n">
-        <v>26.24768366127813</v>
+        <v>26.36673128032575</v>
       </c>
       <c r="T54" t="n">
-        <v>30.89517348157901</v>
+        <v>30.77612586253139</v>
       </c>
       <c r="U54" t="n">
         <v>36.54655436930671</v>
@@ -6333,25 +6367,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X54" t="n">
-        <v>13.11288720231516</v>
+        <v>13.6561815747644</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.488374359036471</v>
+        <v>1.932719952167594</v>
       </c>
       <c r="Z54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA54" t="n">
-        <v>40.625</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.46119185333322</v>
+        <v>12.5679160943793</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.564681445580886</v>
+        <v>3.127730315693822</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6382,10 +6416,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>29381.31054688</v>
+        <v>29174.43554688</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -453,7 +453,7 @@
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C2" t="n">
-        <v>334.57901001</v>
+        <v>330.36999512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>11.8607954991482</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4880706692182213</v>
+        <v>1.739933995233112</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -739,13 +739,13 @@
         <v>17.85714285714286</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.20753016674198</v>
+        <v>10.83217609155666</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.54877267609978</v>
+        <v>6.370915733420324</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,14 +776,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" t="n">
-        <v>492.80999756</v>
+        <v>503.07998657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -793,10 +793,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>5</v>
       </c>
@@ -807,16 +811,16 @@
         <v>16.90717447700184</v>
       </c>
       <c r="K3" t="n">
-        <v>11.87514133030647</v>
+        <v>14.20658037911464</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>74.07407407407408</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N3" t="n">
-        <v>13.49920667937732</v>
+        <v>15.01741392173222</v>
       </c>
       <c r="O3" t="n">
         <v>6</v>
@@ -849,22 +853,22 @@
         <v>19.58909830419979</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.450384761887962</v>
+        <v>4.500843305460489</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>50</v>
+        <v>52.27272727272727</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.19543715763684</v>
+        <v>13.80284927037375</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.5226817825586649</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -895,10 +899,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C4" t="n">
-        <v>253.40499878</v>
+        <v>249.33000183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,25 +927,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>13.09888885119279</v>
+        <v>12.14859434297889</v>
       </c>
       <c r="K4" t="n">
-        <v>1.532573492248535</v>
+        <v>0.3602569198342565</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>55</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N4" t="n">
-        <v>11.03343980421643</v>
+        <v>9.913216619903212</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>6.369804571382431</v>
+        <v>7.612319173583049</v>
       </c>
       <c r="Q4" t="n">
         <v>23</v>
@@ -950,10 +954,10 @@
         <v>34.78260869565217</v>
       </c>
       <c r="S4" t="n">
-        <v>41.12723098792893</v>
+        <v>41.18369626178551</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.344622292276753</v>
+        <v>-6.401087566133334</v>
       </c>
       <c r="U4" t="n">
         <v>18.81127593879773</v>
@@ -1004,10 +1008,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C5" t="n">
-        <v>346.29998779</v>
+        <v>339.95999146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,7 +1030,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %93.75: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1036,25 +1040,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>20.89062975160487</v>
+        <v>21.61625174459222</v>
       </c>
       <c r="K5" t="n">
-        <v>1.159700106840678</v>
+        <v>0.2270081707777427</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>13.16398977669445</v>
+        <v>11.82285042520303</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.819202598678804</v>
+        <v>2.766711168807245</v>
       </c>
       <c r="Q5" t="n">
         <v>45</v>
@@ -1063,10 +1067,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S5" t="n">
-        <v>43.95780042606945</v>
+        <v>42.58173659407056</v>
       </c>
       <c r="T5" t="n">
-        <v>11.5977551294861</v>
+        <v>12.97381896148499</v>
       </c>
       <c r="U5" t="n">
         <v>41.17613449352105</v>
@@ -1117,10 +1121,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C6" t="n">
-        <v>210.13989258</v>
+        <v>211.30000305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,22 +1152,22 @@
         <v>15.10639127416894</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67254334240854</v>
+        <v>3.239363335750389</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>59.52380952380953</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N6" t="n">
-        <v>10.33168989683851</v>
+        <v>11.14052084727848</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>5.188784152180426</v>
+        <v>4.611261160888103</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1172,10 +1176,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="S6" t="n">
-        <v>39.65188262251572</v>
+        <v>39.75658347721659</v>
       </c>
       <c r="T6" t="n">
-        <v>7.014784044150943</v>
+        <v>6.910083189450077</v>
       </c>
       <c r="U6" t="n">
         <v>30.23238890769975</v>
@@ -1204,10 +1208,10 @@
         <v>54.28571428571428</v>
       </c>
       <c r="AG6" t="n">
-        <v>20.70838556867968</v>
+        <v>20.72391351899025</v>
       </c>
       <c r="AH6" t="n">
-        <v>33.5773287170346</v>
+        <v>33.56180076672403</v>
       </c>
       <c r="AI6" t="n">
         <v>38.18972506848375</v>
@@ -1226,10 +1230,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>61.89500046</v>
+        <v>59.04999924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,10 +1275,10 @@
         <v>54.16666666666666</v>
       </c>
       <c r="S7" t="n">
-        <v>40.6484885620915</v>
+        <v>40.75265522875817</v>
       </c>
       <c r="T7" t="n">
-        <v>13.51817810457516</v>
+        <v>13.4140114379085</v>
       </c>
       <c r="U7" t="n">
         <v>35.07486535891948</v>
@@ -1325,10 +1329,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C8" t="n">
-        <v>135.38999939</v>
+        <v>135.11500549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1428,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C9" t="n">
-        <v>785.51000977</v>
+        <v>781.0599975600001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,22 +1459,22 @@
         <v>17.49839415508021</v>
       </c>
       <c r="K9" t="n">
-        <v>1.830461226077262</v>
+        <v>1.253578958289681</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M9" t="n">
-        <v>58.33333333333334</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N9" t="n">
-        <v>9.209861197941871</v>
+        <v>11.14817914289122</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.094588911529939</v>
+        <v>4.687657552989366</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1479,10 +1483,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="S9" t="n">
-        <v>33.22541393680378</v>
+        <v>33.31162083335551</v>
       </c>
       <c r="T9" t="n">
-        <v>18.4987239942307</v>
+        <v>18.41251709767897</v>
       </c>
       <c r="U9" t="n">
         <v>34.43102188199472</v>
@@ -1533,10 +1537,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C10" t="n">
-        <v>138.71000671</v>
+        <v>140.38000488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,25 +1597,25 @@
         <v>63.26530612244898</v>
       </c>
       <c r="X10" t="n">
-        <v>21.88562772325671</v>
+        <v>22.7181635419816</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7903270112048277</v>
+        <v>0.2770472246715006</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.80952380952381</v>
+        <v>25</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.95977359310978</v>
+        <v>12.32988127814506</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.283039356288691</v>
+        <v>9.749964782163934</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1642,10 +1646,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C11" t="n">
-        <v>257.23001099</v>
+        <v>262.01998901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,22 +1709,22 @@
         <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.115248992532116</v>
+        <v>2.329742519118316</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>48.27586206896552</v>
+        <v>46.875</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.34409543203857</v>
+        <v>12.31497854465687</v>
       </c>
       <c r="AC11" t="n">
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.13731687847795</v>
+        <v>7.853217221612308</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1751,10 +1755,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C12" t="n">
-        <v>110.97000122</v>
+        <v>110.37999725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,22 +1786,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>3.362519177988665</v>
+        <v>2.812962577161815</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>40.90909090909091</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N12" t="n">
-        <v>12.1620108159896</v>
+        <v>10.71931863751676</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.48661744981822</v>
+        <v>5.045120082932431</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1838,10 +1842,10 @@
         <v>26.66666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.687830687830687</v>
+        <v>6.521164021164021</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.97883597883598</v>
+        <v>20.14550264550265</v>
       </c>
       <c r="AI12" t="n">
         <v>10.89745332569237</v>
@@ -1860,10 +1864,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C13" t="n">
-        <v>95.85500336</v>
+        <v>94.78289795000001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,19 +1892,19 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>12.62182199075366</v>
+        <v>12.0476205047619</v>
       </c>
       <c r="K13" t="n">
-        <v>3.79534915871016</v>
+        <v>2.634433698220717</v>
       </c>
       <c r="L13" t="n">
         <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N13" t="n">
-        <v>8.799430895124942</v>
+        <v>9.383714203196007</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1969,10 +1973,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>215.28999329</v>
+        <v>216.08000183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,10 +2018,10 @@
         <v>36.36363636363637</v>
       </c>
       <c r="S14" t="n">
-        <v>23.64237820475961</v>
+        <v>23.75601456839597</v>
       </c>
       <c r="T14" t="n">
-        <v>12.72125815887676</v>
+        <v>12.60762179524039</v>
       </c>
       <c r="U14" t="n">
         <v>19.73320467036612</v>
@@ -2032,22 +2036,22 @@
         <v>17.09797149318395</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08430998214698</v>
+        <v>0.7213379802442632</v>
       </c>
       <c r="Z14" t="n">
         <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.05263157894737</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.84582265015259</v>
+        <v>17.69688484665765</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>9.013423468252457</v>
+        <v>9.346078836063832</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2056,10 +2060,10 @@
         <v>50</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.8231658692185</v>
+        <v>12.8421052631579</v>
       </c>
       <c r="AH14" t="n">
-        <v>37.1768341307815</v>
+        <v>37.1578947368421</v>
       </c>
       <c r="AI14" t="n">
         <v>29.92980081982123</v>
@@ -2078,10 +2082,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C15" t="n">
-        <v>108.90499878</v>
+        <v>107.18000031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,25 +2142,25 @@
         <v>55.55555555555556</v>
       </c>
       <c r="X15" t="n">
-        <v>15.08075692700643</v>
+        <v>14.87985819387563</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.650401266750657</v>
+        <v>4.192368217314623</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.72727272727273</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.42999878940044</v>
+        <v>9.820484006419468</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>7.54969597089784</v>
+        <v>6.061763217212668</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -2187,10 +2191,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C16" t="n">
-        <v>13.89999962</v>
+        <v>13.56999969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,25 +2219,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>12.68260788003351</v>
+        <v>10.17760031008306</v>
       </c>
       <c r="K16" t="n">
-        <v>5.703422218045651</v>
+        <v>3.193916974424971</v>
       </c>
       <c r="L16" t="n">
         <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>58.97435897435897</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N16" t="n">
-        <v>13.88774541267856</v>
+        <v>12.63396783499991</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>0.28057538320998</v>
+        <v>2.719232981795305</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2242,10 +2246,10 @@
         <v>55</v>
       </c>
       <c r="S16" t="n">
-        <v>41.86616124976899</v>
+        <v>41.99116124976899</v>
       </c>
       <c r="T16" t="n">
-        <v>13.13383875023101</v>
+        <v>13.00883875023101</v>
       </c>
       <c r="U16" t="n">
         <v>39.82909179893205</v>
@@ -2274,10 +2278,10 @@
         <v>38.46153846153846</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.3756941764982</v>
+        <v>17.50186930267333</v>
       </c>
       <c r="AH16" t="n">
-        <v>21.08584428504026</v>
+        <v>20.95966915886513</v>
       </c>
       <c r="AI16" t="n">
         <v>24.89137346556135</v>
@@ -2296,10 +2300,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C17" t="n">
-        <v>316.93991089</v>
+        <v>309.48001099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,25 +2328,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>19.74055820196081</v>
+        <v>20.85433522869784</v>
       </c>
       <c r="K17" t="n">
-        <v>1.557000679226794</v>
+        <v>0.5621481689683128</v>
       </c>
       <c r="L17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M17" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N17" t="n">
-        <v>13.82142119397245</v>
+        <v>14.79358930761215</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.344219775772797</v>
+        <v>7.396273813218812</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C18" t="n">
-        <v>86.69999695</v>
+        <v>85.29000092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,10 +2454,10 @@
         <v>55</v>
       </c>
       <c r="S18" t="n">
-        <v>30.58408750119277</v>
+        <v>30.64658750119277</v>
       </c>
       <c r="T18" t="n">
-        <v>24.41591249880723</v>
+        <v>24.35341249880723</v>
       </c>
       <c r="U18" t="n">
         <v>39.82909179893205</v>
@@ -2482,10 +2486,10 @@
         <v>48.48484848484848</v>
       </c>
       <c r="AG18" t="n">
-        <v>27.47618961381163</v>
+        <v>27.52570436920874</v>
       </c>
       <c r="AH18" t="n">
-        <v>21.00865887103686</v>
+        <v>20.95914411563975</v>
       </c>
       <c r="AI18" t="n">
         <v>32.5040421081337</v>
@@ -2504,10 +2508,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C19" t="n">
-        <v>346.05999756</v>
+        <v>344.29998779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,16 +2539,16 @@
         <v>14.75759965099349</v>
       </c>
       <c r="K19" t="n">
-        <v>5.589799193300604</v>
+        <v>5.052785150929728</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
-        <v>9.285175638317453</v>
+        <v>10.55470572399957</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -2591,10 +2595,10 @@
         <v>55</v>
       </c>
       <c r="AG19" t="n">
-        <v>19.83401838996468</v>
+        <v>19.93928154785942</v>
       </c>
       <c r="AH19" t="n">
-        <v>35.16598161003532</v>
+        <v>35.06071845214058</v>
       </c>
       <c r="AI19" t="n">
         <v>34.20853424503424</v>
@@ -2613,19 +2617,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C20" t="n">
-        <v>998.90997314</v>
+        <v>959.6799926800001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2640,17 +2644,27 @@
       <c r="I20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>11.3923910063839</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.543746137007628</v>
+      </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="M20" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.6954880576206</v>
+      </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>9.405113919374619</v>
+      </c>
       <c r="Q20" t="n">
         <v>30</v>
       </c>
@@ -2658,10 +2672,10 @@
         <v>40</v>
       </c>
       <c r="S20" t="n">
-        <v>34.00855897914722</v>
+        <v>33.92522564581388</v>
       </c>
       <c r="T20" t="n">
-        <v>5.991441020852783</v>
+        <v>6.074774354186118</v>
       </c>
       <c r="U20" t="n">
         <v>24.59062811680185</v>
@@ -2712,10 +2726,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>34.95500183</v>
+        <v>35.65999985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,10 +2771,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S21" t="n">
-        <v>35.56596061158216</v>
+        <v>35.26124013608901</v>
       </c>
       <c r="T21" t="n">
-        <v>26.13616704799231</v>
+        <v>26.44088752348546</v>
       </c>
       <c r="U21" t="n">
         <v>47.42656695641357</v>
@@ -2772,19 +2786,19 @@
         <v>71.23287671232876</v>
       </c>
       <c r="X21" t="n">
-        <v>21.98718090672251</v>
+        <v>21.05598196057028</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.158169806182535</v>
+        <v>6.305836662138842</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
-        <v>52.63157894736842</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB21" t="n">
-        <v>14.36277581346553</v>
+        <v>10.52757656519848</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -2821,10 +2835,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C22" t="n">
-        <v>311.29998779</v>
+        <v>305.64001465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,22 +2866,22 @@
         <v>15.08538893012877</v>
       </c>
       <c r="K22" t="n">
-        <v>2.30036157767799</v>
+        <v>0.4403637574000863</v>
       </c>
       <c r="L22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>42.10526315789474</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N22" t="n">
-        <v>9.733572734950815</v>
+        <v>7.944935520626509</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>7.526501669767405</v>
+        <v>9.517723637172315</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2930,10 +2944,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C23" t="n">
-        <v>98.02999878</v>
+        <v>98.21140289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2966,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2965,16 +2979,16 @@
         <v>20.85153887202731</v>
       </c>
       <c r="K23" t="n">
-        <v>15.13976918293705</v>
+        <v>15.35283485277461</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>10.35994594923866</v>
+        <v>11.41843203785392</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
@@ -3007,7 +3021,7 @@
         <v>25.31125581911988</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.116977656711732</v>
+        <v>7.946948501353878</v>
       </c>
       <c r="Z23" t="n">
         <v>15</v>
@@ -3031,10 +3045,10 @@
         <v>44.68085106382978</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.48711053269496</v>
+        <v>19.57436553741145</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.19374053113482</v>
+        <v>25.10648552641833</v>
       </c>
       <c r="AI23" t="n">
         <v>31.41096626549528</v>
@@ -3053,10 +3067,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C24" t="n">
-        <v>268.06500244</v>
+        <v>264.54998779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,22 +3130,22 @@
         <v>12.23047619452817</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.626962870924078</v>
+        <v>5.877546198371808</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.66666666666667</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.430932275361045</v>
+        <v>8.752793166477732</v>
       </c>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.439649161237977</v>
+        <v>0.1301005197827498</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3162,10 +3176,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C25" t="n">
-        <v>351.9750061</v>
+        <v>344.83999634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,10 +3275,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C26" t="n">
-        <v>30.98500061</v>
+        <v>30.71500015</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,10 +3374,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C27" t="n">
-        <v>89.08000183</v>
+        <v>88.18000031</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3437,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>8.87037037037037</v>
+        <v>9.12037037037037</v>
       </c>
       <c r="AH27" t="n">
-        <v>-8.87037037037037</v>
+        <v>-9.12037037037037</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3459,10 +3473,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>575.82501221</v>
+        <v>572.79998779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,10 +3572,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C29" t="n">
-        <v>257.30999756</v>
+        <v>254.53500366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,10 +3671,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C30" t="n">
-        <v>660.60498047</v>
+        <v>665.16998291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,19 +3710,19 @@
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>60.8695652173913</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="S30" t="n">
-        <v>59.88411548194156</v>
+        <v>62.60612073112073</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9854497354497411</v>
+        <v>1.030242905242908</v>
       </c>
       <c r="U30" t="n">
-        <v>40.78552239138171</v>
+        <v>42.95170809013101</v>
       </c>
       <c r="V30" t="n">
         <v>37</v>
@@ -3717,25 +3731,25 @@
         <v>59.45945945945946</v>
       </c>
       <c r="X30" t="n">
-        <v>23.63243175397585</v>
+        <v>26.35545823194651</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5472434381346591</v>
+        <v>2.018061235358959</v>
       </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>40</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="AB30" t="n">
-        <v>10.2356136366264</v>
+        <v>12.6667902740774</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.482760609529624</v>
+        <v>4.063951800551657</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3766,10 +3780,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C31" t="n">
-        <v>209.38499451</v>
+        <v>202.38499451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3811,10 +3825,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="S31" t="n">
-        <v>33.53631553631553</v>
+        <v>33.61964886964887</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.2029822029821986</v>
+        <v>-0.2863155363155343</v>
       </c>
       <c r="U31" t="n">
         <v>19.23049808367614</v>
@@ -3865,10 +3879,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C32" t="n">
-        <v>505.23999023</v>
+        <v>500.25500488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,10 +3978,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C33" t="n">
-        <v>919.3099975600001</v>
+        <v>924.03497314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,22 +4009,22 @@
         <v>13.41136277305126</v>
       </c>
       <c r="K33" t="n">
-        <v>1.851320897618813</v>
+        <v>2.374805908452271</v>
       </c>
       <c r="L33" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M33" t="n">
-        <v>68.23529411764706</v>
+        <v>71.08433734939759</v>
       </c>
       <c r="N33" t="n">
-        <v>13.89179737264407</v>
+        <v>13.89558125827143</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.073269807223667</v>
+        <v>3.541099843246132</v>
       </c>
       <c r="Q33" t="n">
         <v>55</v>
@@ -4034,19 +4048,19 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X33" t="n">
-        <v>35.35905174018239</v>
+        <v>26.04595216565901</v>
       </c>
       <c r="Y33" t="n">
-        <v>11.80832923710541</v>
+        <v>11.35505070013738</v>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.33333333333334</v>
+        <v>31.25</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.308475867796361</v>
+        <v>11.77119477123058</v>
       </c>
       <c r="AC33" t="n">
         <v>4</v>
@@ -4070,10 +4084,10 @@
         <v>39.01038392417698</v>
       </c>
       <c r="AJ33" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK33" t="n">
-        <v>50.66666666666666</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -4083,10 +4097,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C34" t="n">
-        <v>80.71499634</v>
+        <v>78.02500153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4114,22 +4128,22 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>7.576966083485259</v>
+        <v>3.991740368784802</v>
       </c>
       <c r="L34" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M34" t="n">
-        <v>46.66666666666666</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N34" t="n">
-        <v>11.68643474899504</v>
+        <v>10.32512463612697</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>2.252372422024207</v>
+        <v>5.77763157911213</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4138,10 +4152,10 @@
         <v>60</v>
       </c>
       <c r="S34" t="n">
-        <v>46.38164587390593</v>
+        <v>46.82427187535546</v>
       </c>
       <c r="T34" t="n">
-        <v>13.61835412609407</v>
+        <v>13.17572812464454</v>
       </c>
       <c r="U34" t="n">
         <v>43.5727090128925</v>
@@ -4153,25 +4167,25 @@
         <v>65.11627906976744</v>
       </c>
       <c r="X34" t="n">
-        <v>15.82155460093264</v>
+        <v>15.629315274282</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.450959548803456</v>
+        <v>6.668656748840252</v>
       </c>
       <c r="Z34" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>30.3030303030303</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.44044289477803</v>
+        <v>9.446413475488416</v>
       </c>
       <c r="AC34" t="n">
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>6.783123292154247</v>
+        <v>3.569372447790575</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4202,19 +4216,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>37.31999969</v>
+        <v>36.24509811</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4230,25 +4244,25 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>15.41309877759897</v>
+        <v>15.07973827857974</v>
       </c>
       <c r="K35" t="n">
-        <v>2.10670442137062</v>
+        <v>0.09693187211203824</v>
       </c>
       <c r="L35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M35" t="n">
-        <v>46.15384615384615</v>
+        <v>48</v>
       </c>
       <c r="N35" t="n">
-        <v>14.2445891002565</v>
+        <v>10.113440319783</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.90122523467493</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4257,10 +4271,10 @@
         <v>37.93103448275862</v>
       </c>
       <c r="S35" t="n">
-        <v>29.3692092221504</v>
+        <v>29.45831382951058</v>
       </c>
       <c r="T35" t="n">
-        <v>8.561825260608217</v>
+        <v>8.472720653248036</v>
       </c>
       <c r="U35" t="n">
         <v>22.68802210080984</v>
@@ -4289,10 +4303,10 @@
         <v>48.14814814814815</v>
       </c>
       <c r="AG35" t="n">
-        <v>12.99655661522578</v>
+        <v>13.00831440476134</v>
       </c>
       <c r="AH35" t="n">
-        <v>35.15159153292237</v>
+        <v>35.1398337433868</v>
       </c>
       <c r="AI35" t="n">
         <v>30.74322697621846</v>
@@ -4311,10 +4325,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C36" t="n">
-        <v>211.77380371</v>
+        <v>211.94999695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4331,11 +4345,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>5</v>
       </c>
@@ -4346,37 +4356,37 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K36" t="n">
-        <v>1.361131062860665</v>
+        <v>1.44546229637097</v>
       </c>
       <c r="L36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M36" t="n">
-        <v>68.18181818181819</v>
+        <v>68.65671641791045</v>
       </c>
       <c r="N36" t="n">
-        <v>13.09038498587369</v>
+        <v>13.01337979812925</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6302898659873213</v>
+        <v>0.5466362822705184</v>
       </c>
       <c r="Q36" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R36" t="n">
-        <v>63.26530612244898</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="S36" t="n">
-        <v>63.65790793687295</v>
+        <v>64.92311001269151</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.3926018144239762</v>
+        <v>-0.3397766793581809</v>
       </c>
       <c r="U36" t="n">
-        <v>49.26706756079243</v>
+        <v>50.43905701034311</v>
       </c>
       <c r="V36" t="n">
         <v>76</v>
@@ -4385,19 +4395,19 @@
         <v>69.73684210526316</v>
       </c>
       <c r="X36" t="n">
-        <v>19.25831203212749</v>
+        <v>13.27382123522316</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.791357700436842</v>
+        <v>9.716305202515397</v>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AA36" t="n">
-        <v>75</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB36" t="n">
-        <v>13.69584238822664</v>
+        <v>10.78701223636375</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4434,10 +4444,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C37" t="n">
-        <v>143.96499634</v>
+        <v>143.58999634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4462,25 +4472,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>17.39308902782027</v>
+        <v>17.744577522677</v>
       </c>
       <c r="K37" t="n">
-        <v>2.095597436386276</v>
+        <v>2.264790682364981</v>
       </c>
       <c r="L37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M37" t="n">
-        <v>65.21739130434783</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N37" t="n">
-        <v>9.257798206011573</v>
+        <v>10.83396361990318</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.783209767975195</v>
+        <v>5.608195430085638</v>
       </c>
       <c r="Q37" t="n">
         <v>33</v>
@@ -4504,13 +4514,13 @@
         <v>65.78947368421052</v>
       </c>
       <c r="X37" t="n">
-        <v>31.09591287417577</v>
+        <v>24.2086924558512</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.66198071920939</v>
+        <v>15.88166437867064</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
@@ -4549,10 +4559,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C38" t="n">
-        <v>62.65000153</v>
+        <v>63.38999939</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4609,25 +4619,25 @@
         <v>69.62025316455696</v>
       </c>
       <c r="X38" t="n">
-        <v>17.34998396575658</v>
+        <v>18.2538240912798</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.5081779955538046</v>
+        <v>0.1024386386027532</v>
       </c>
       <c r="Z38" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AA38" t="n">
-        <v>39.47368421052632</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.89005815116391</v>
+        <v>9.955781127293166</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.540303728704469</v>
+        <v>9.90771068534001</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4658,10 +4668,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C39" t="n">
-        <v>136.53999329</v>
+        <v>135.3500061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4703,10 +4713,10 @@
         <v>31.25</v>
       </c>
       <c r="S39" t="n">
-        <v>16.1328502415459</v>
+        <v>16.14520202020202</v>
       </c>
       <c r="T39" t="n">
-        <v>15.1171497584541</v>
+        <v>15.10479797979798</v>
       </c>
       <c r="U39" t="n">
         <v>14.16464385478204</v>
@@ -4757,10 +4767,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C40" t="n">
-        <v>27.83499908</v>
+        <v>27.53000069</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,10 +4812,10 @@
         <v>47.36842105263158</v>
       </c>
       <c r="S40" t="n">
-        <v>24.67874231032126</v>
+        <v>24.81032125768968</v>
       </c>
       <c r="T40" t="n">
-        <v>22.68967874231032</v>
+        <v>22.5580997949419</v>
       </c>
       <c r="U40" t="n">
         <v>27.32980516117956</v>
@@ -4820,22 +4830,22 @@
         <v>18.25910194830291</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.707292171540867</v>
+        <v>5.751449650507823</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.917880425252678</v>
+        <v>8.205280914877466</v>
       </c>
       <c r="AC40" t="n">
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.554158286683153</v>
+        <v>4.507815063189524</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4866,10 +4876,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C41" t="n">
-        <v>173.33999634</v>
+        <v>174.21000671</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,7 +4898,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.40: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4901,22 +4911,22 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>5.341837208796107</v>
+        <v>5.870558177422036</v>
       </c>
       <c r="L41" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M41" t="n">
-        <v>81.3953488372093</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N41" t="n">
-        <v>19.24691857538625</v>
+        <v>19.01433689832987</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>4.421949450123064</v>
+        <v>3.900462880017774</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4943,7 +4953,7 @@
         <v>31.46984695975164</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.97897710324047</v>
+        <v>7.517114602556251</v>
       </c>
       <c r="Z41" t="n">
         <v>11</v>
@@ -4989,10 +4999,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>179.33999634</v>
+        <v>188.08999634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,10 +5044,10 @@
         <v>46.34146341463415</v>
       </c>
       <c r="S42" t="n">
-        <v>44.54745506032076</v>
+        <v>44.84420302780043</v>
       </c>
       <c r="T42" t="n">
-        <v>1.794008354313391</v>
+        <v>1.497260386833716</v>
       </c>
       <c r="U42" t="n">
         <v>32.05623397633605</v>
@@ -5049,25 +5059,25 @@
         <v>51.02040816326531</v>
       </c>
       <c r="X42" t="n">
-        <v>29.7921530560096</v>
+        <v>22.24584364682432</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.299908416141561</v>
+        <v>0.8748372384716707</v>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="n">
-        <v>33.33333333333334</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB42" t="n">
-        <v>10.96385939172265</v>
+        <v>11.08490925847598</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.928733441837654</v>
+        <v>9.205697632478349</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5098,10 +5108,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C43" t="n">
-        <v>53.97999954</v>
+        <v>54.22999954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,25 +5136,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>11.54482243832677</v>
+        <v>12.18987602075233</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9349289534418048</v>
+        <v>2.147295887698353</v>
       </c>
       <c r="L43" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M43" t="n">
-        <v>54.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>11.83834137200701</v>
+        <v>13.25564778464197</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.036680243736067</v>
+        <v>1.813757374780178</v>
       </c>
       <c r="Q43" t="n">
         <v>43</v>
@@ -5168,19 +5178,19 @@
         <v>60</v>
       </c>
       <c r="X43" t="n">
-        <v>25.17598350173391</v>
+        <v>23.84268632509694</v>
       </c>
       <c r="Y43" t="n">
-        <v>10.71782937248434</v>
+        <v>10.30433283956312</v>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA43" t="n">
-        <v>28.57142857142857</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.03974720938522</v>
+        <v>8.372267648678688</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5195,10 +5205,10 @@
         <v>47.22222222222222</v>
       </c>
       <c r="AG43" t="n">
-        <v>32.56085684539632</v>
+        <v>32.63030128984077</v>
       </c>
       <c r="AH43" t="n">
-        <v>14.6613653768259</v>
+        <v>14.59192093238146</v>
       </c>
       <c r="AI43" t="n">
         <v>31.98604151517905</v>
@@ -5217,27 +5227,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C44" t="n">
-        <v>37.81499863</v>
+        <v>36.13000107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %82.05: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5248,22 +5262,22 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>10.92695354534927</v>
+        <v>5.984162249996339</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M44" t="n">
-        <v>61.29032258064516</v>
+        <v>82.05128205128206</v>
       </c>
       <c r="N44" t="n">
-        <v>19.34901320079606</v>
+        <v>17.88973188241306</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>0.01494350633852726</v>
       </c>
       <c r="Q44" t="n">
         <v>70</v>
@@ -5272,10 +5286,10 @@
         <v>71.42857142857143</v>
       </c>
       <c r="S44" t="n">
-        <v>48.6312745446883</v>
+        <v>48.69161534767615</v>
       </c>
       <c r="T44" t="n">
-        <v>22.79729688388313</v>
+        <v>22.73695608089528</v>
       </c>
       <c r="U44" t="n">
         <v>59.94980341827974</v>
@@ -5287,20 +5301,16 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X44" t="n">
-        <v>54.19096411365851</v>
+        <v>45.54524190295925</v>
       </c>
       <c r="Y44" t="n">
-        <v>10.62397209749843</v>
+        <v>14.60647624649322</v>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>26.99088785794874</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>8</v>
       </c>
@@ -5336,10 +5346,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C45" t="n">
-        <v>26.41500092</v>
+        <v>26.77499962</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5396,25 +5406,25 @@
         <v>43.47826086956522</v>
       </c>
       <c r="X45" t="n">
-        <v>17.47228675294625</v>
+        <v>18.80266883769528</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.2831213690116186</v>
+        <v>0.05599589206733979</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>38.88888888888889</v>
+        <v>43.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>10.83363306638135</v>
+        <v>9.374067093461447</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>7.738788795771889</v>
+        <v>7.948454916168535</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5423,10 +5433,10 @@
         <v>29.41176470588235</v>
       </c>
       <c r="AG45" t="n">
-        <v>14.75378825724847</v>
+        <v>14.00718192240684</v>
       </c>
       <c r="AH45" t="n">
-        <v>14.65797644863389</v>
+        <v>15.40458278347552</v>
       </c>
       <c r="AI45" t="n">
         <v>13.27998961029523</v>
@@ -5445,10 +5455,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C46" t="n">
-        <v>363.27999878</v>
+        <v>361.1499939</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5490,10 +5500,10 @@
         <v>67.12328767123287</v>
       </c>
       <c r="S46" t="n">
-        <v>72.45070715600723</v>
+        <v>72.7374037697431</v>
       </c>
       <c r="T46" t="n">
-        <v>-5.327419484774353</v>
+        <v>-5.614116098510223</v>
       </c>
       <c r="U46" t="n">
         <v>55.72900614018867</v>
@@ -5505,19 +5515,19 @@
         <v>75.22935779816514</v>
       </c>
       <c r="X46" t="n">
-        <v>23.71227574517236</v>
+        <v>21.71653838636141</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.405689328807961</v>
+        <v>5.960320313245648</v>
       </c>
       <c r="Z46" t="n">
         <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>23.07692307692308</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.22405888697484</v>
+        <v>12.81943638748685</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5554,10 +5564,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C47" t="n">
-        <v>72.44490051</v>
+        <v>71.79000092</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,7 +5576,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5574,7 +5584,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5585,22 +5599,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>4.628686812613947</v>
+        <v>3.682846820931429</v>
       </c>
       <c r="L47" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M47" t="n">
-        <v>71.42857142857143</v>
+        <v>74.19354838709677</v>
       </c>
       <c r="N47" t="n">
-        <v>14.83997524742984</v>
+        <v>14.5652771198515</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.3058877999524201</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5627,13 +5641,13 @@
         <v>23.42098914682247</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.04406921355319</v>
+        <v>12.83918802253218</v>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA47" t="n">
-        <v>71.42857142857143</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="AB47" t="n">
         <v>13.43868584457045</v>
@@ -5673,19 +5687,19 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C48" t="n">
-        <v>385.82000732</v>
+        <v>376.96499634</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5700,27 +5714,17 @@
       <c r="I48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
-        <v>10.35913645708599</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.639003346895241</v>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>26</v>
-      </c>
-      <c r="M48" t="n">
-        <v>46.15384615384615</v>
-      </c>
-      <c r="N48" t="n">
-        <v>12.99734936520743</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>8</v>
       </c>
-      <c r="P48" t="n">
-        <v>5.22315735567489</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>26</v>
       </c>
@@ -5782,10 +5786,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>376.20001221</v>
+        <v>374.77999878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5881,10 +5885,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C50" t="n">
-        <v>51.31999969</v>
+        <v>51.49499893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5926,10 +5930,10 @@
         <v>36.8421052631579</v>
       </c>
       <c r="S50" t="n">
-        <v>13.70622279382667</v>
+        <v>13.71949125910752</v>
       </c>
       <c r="T50" t="n">
-        <v>23.13588246933123</v>
+        <v>23.12261400405038</v>
       </c>
       <c r="U50" t="n">
         <v>19.14951274513507</v>
@@ -5941,25 +5945,25 @@
         <v>35</v>
       </c>
       <c r="X50" t="n">
-        <v>14.10512439308564</v>
+        <v>14.32689968620457</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.2526745735270564</v>
+        <v>0.1066931344536615</v>
       </c>
       <c r="Z50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA50" t="n">
-        <v>37.5</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.976199754602384</v>
+        <v>10.27292042944566</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.751751657502798</v>
+        <v>1.895329051519612</v>
       </c>
       <c r="AE50" t="n">
         <v>19</v>
@@ -5990,10 +5994,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C51" t="n">
-        <v>28.09499931</v>
+        <v>27.87000084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6035,10 +6039,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S51" t="n">
-        <v>35.78295972973849</v>
+        <v>35.80848542230262</v>
       </c>
       <c r="T51" t="n">
-        <v>30.17448707877215</v>
+        <v>30.14896138620801</v>
       </c>
       <c r="U51" t="n">
         <v>51.67092456194193</v>
@@ -6053,16 +6057,16 @@
         <v>14.13385906971916</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.087273084169473</v>
+        <v>3.863397512541622</v>
       </c>
       <c r="Z51" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AA51" t="n">
-        <v>49.0566037735849</v>
+        <v>52</v>
       </c>
       <c r="AB51" t="n">
-        <v>14.08684353074138</v>
+        <v>13.00698474437825</v>
       </c>
       <c r="AC51" t="n">
         <v>3</v>
@@ -6099,14 +6103,14 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C52" t="n">
-        <v>88.58499908</v>
+        <v>88.86000061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6116,7 +6120,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6158,17 +6162,27 @@
       <c r="W52" t="n">
         <v>58.33333333333334</v>
       </c>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
+      <c r="X52" t="n">
+        <v>10.19405145840906</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>3.402540844455237</v>
+      </c>
       <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>40.74074074074074</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>8.368858389096365</v>
+      </c>
       <c r="AC52" t="n">
         <v>6</v>
       </c>
-      <c r="AD52" t="inlineStr"/>
+      <c r="AD52" t="n">
+        <v>2.688951840195142</v>
+      </c>
       <c r="AE52" t="n">
         <v>28</v>
       </c>
@@ -6198,10 +6212,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C53" t="n">
-        <v>109.47499847</v>
+        <v>108.44000244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6229,16 +6243,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>7.170824111880947</v>
+        <v>6.157612154467484</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M53" t="n">
-        <v>20</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N53" t="n">
-        <v>7.058549906036282</v>
+        <v>9.139762072655046</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -6307,10 +6321,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C54" t="n">
-        <v>166.17500305</v>
+        <v>168.69000244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,10 +6366,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S54" t="n">
-        <v>26.36673128032575</v>
+        <v>26.48577889937337</v>
       </c>
       <c r="T54" t="n">
-        <v>30.77612586253139</v>
+        <v>30.65707824348377</v>
       </c>
       <c r="U54" t="n">
         <v>36.54655436930671</v>
@@ -6370,22 +6384,22 @@
         <v>13.6561815747644</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.932719952167594</v>
+        <v>0.4485066531008997</v>
       </c>
       <c r="Z54" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA54" t="n">
-        <v>43.33333333333334</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.5679160943793</v>
+        <v>12.68473811409051</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.127730315693822</v>
+        <v>4.57199906689384</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6416,10 +6430,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C55" t="n">
-        <v>29174.43554688</v>
+        <v>28977.31640625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6493,10 +6507,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.58707067056213</v>
+        <v>12.60616921907245</v>
       </c>
       <c r="AH55" t="n">
-        <v>44.55578647229501</v>
+        <v>44.5366879237847</v>
       </c>
       <c r="AI55" t="n">
         <v>32.59064457965074</v>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>330.36999512</v>
+        <v>332.70999146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         <v>65</v>
       </c>
       <c r="S2" t="n">
-        <v>34.07696123321124</v>
+        <v>33.62893143649723</v>
       </c>
       <c r="T2" t="n">
-        <v>30.92303876678876</v>
+        <v>31.37106856350277</v>
       </c>
       <c r="U2" t="n">
         <v>43.28542766852362</v>
@@ -730,22 +730,22 @@
         <v>11.8607954991482</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.739933995233112</v>
+        <v>1.043962211428118</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.85714285714286</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.83217609155666</v>
+        <v>9.81050995120604</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.370915733420324</v>
+        <v>7.029422301076826</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>503.07998657</v>
+        <v>523.52001953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -796,38 +796,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" t="n">
-        <v>16.90717447700184</v>
-      </c>
-      <c r="K3" t="n">
-        <v>14.20658037911464</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M3" t="n">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="N3" t="n">
-        <v>15.01741392173222</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>42</v>
       </c>
@@ -850,25 +836,25 @@
         <v>67.74193548387096</v>
       </c>
       <c r="X3" t="n">
-        <v>19.58909830419979</v>
+        <v>19.69353007945516</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.500843305460489</v>
+        <v>0.707440582266472</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="AA3" t="n">
-        <v>52.27272727272727</v>
+        <v>48.21428571428572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.80284927037375</v>
+        <v>14.13239990401026</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5226817825586649</v>
+        <v>4.323143086355863</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -899,10 +885,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>249.33000183</v>
+        <v>247.88000488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>12.14859434297889</v>
+        <v>12.76565826578477</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3602569198342565</v>
+        <v>0.4823877855728798</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>59.45945945945946</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N4" t="n">
-        <v>9.913216619903212</v>
+        <v>9.812507235896533</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>7.612319173583049</v>
+        <v>7.481522264846596</v>
       </c>
       <c r="Q4" t="n">
         <v>23</v>
@@ -954,10 +940,10 @@
         <v>34.78260869565217</v>
       </c>
       <c r="S4" t="n">
-        <v>41.18369626178551</v>
+        <v>41.29239191395942</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.401087566133334</v>
+        <v>-6.509783218307248</v>
       </c>
       <c r="U4" t="n">
         <v>18.81127593879773</v>
@@ -1008,10 +994,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>339.95999146</v>
+        <v>341.67498779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %93.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1040,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>21.61625174459222</v>
+        <v>21.91436107540768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2270081707777427</v>
+        <v>1.117192648164766</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="N5" t="n">
-        <v>11.82285042520303</v>
+        <v>12.5406638374357</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.766711168807245</v>
+        <v>1.862005167001057</v>
       </c>
       <c r="Q5" t="n">
         <v>45</v>
@@ -1067,10 +1053,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S5" t="n">
-        <v>42.58173659407056</v>
+        <v>42.71754788026136</v>
       </c>
       <c r="T5" t="n">
-        <v>12.97381896148499</v>
+        <v>12.8380076752942</v>
       </c>
       <c r="U5" t="n">
         <v>41.17613449352105</v>
@@ -1121,10 +1107,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>211.30000305</v>
+        <v>210.75999451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,22 +1138,22 @@
         <v>15.10639127416894</v>
       </c>
       <c r="K6" t="n">
-        <v>3.239363335750389</v>
+        <v>2.975519809670213</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>53.84615384615385</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="N6" t="n">
-        <v>11.14052084727848</v>
+        <v>10.71945499829607</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.611261160888103</v>
+        <v>4.879295777886372</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1176,10 +1162,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="S6" t="n">
-        <v>39.75658347721659</v>
+        <v>39.83991681054992</v>
       </c>
       <c r="T6" t="n">
-        <v>6.910083189450077</v>
+        <v>6.826749856116749</v>
       </c>
       <c r="U6" t="n">
         <v>30.23238890769975</v>
@@ -1208,10 +1194,10 @@
         <v>54.28571428571428</v>
       </c>
       <c r="AG6" t="n">
-        <v>20.72391351899025</v>
+        <v>20.74085310114722</v>
       </c>
       <c r="AH6" t="n">
-        <v>33.56180076672403</v>
+        <v>33.54486118456707</v>
       </c>
       <c r="AI6" t="n">
         <v>38.18972506848375</v>
@@ -1230,19 +1216,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>59.04999924</v>
+        <v>58.36000061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1257,17 +1243,27 @@
       <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>10.86923747477177</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3783990751775601</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10.25737454686742</v>
+      </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>2.611718207279856</v>
+      </c>
       <c r="Q7" t="n">
         <v>24</v>
       </c>
@@ -1275,10 +1271,10 @@
         <v>54.16666666666666</v>
       </c>
       <c r="S7" t="n">
-        <v>40.75265522875817</v>
+        <v>41.22617967332123</v>
       </c>
       <c r="T7" t="n">
-        <v>13.4140114379085</v>
+        <v>12.94048699334543</v>
       </c>
       <c r="U7" t="n">
         <v>35.07486535891948</v>
@@ -1329,10 +1325,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>135.11500549</v>
+        <v>135.02999878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,10 +1424,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>781.0599975600001</v>
+        <v>790.06011963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,25 +1452,25 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>17.49839415508021</v>
+        <v>14.83129006708122</v>
       </c>
       <c r="K9" t="n">
-        <v>1.253578958289681</v>
+        <v>2.420319763728229</v>
       </c>
       <c r="L9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>60.8695652173913</v>
+        <v>46.875</v>
       </c>
       <c r="N9" t="n">
-        <v>11.14817914289122</v>
+        <v>11.34759150973013</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.687657552989366</v>
+        <v>3.495087932286944</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1483,10 +1479,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="S9" t="n">
-        <v>33.31162083335551</v>
+        <v>33.65644841956241</v>
       </c>
       <c r="T9" t="n">
-        <v>18.41251709767897</v>
+        <v>18.06768951147208</v>
       </c>
       <c r="U9" t="n">
         <v>34.43102188199472</v>
@@ -1537,10 +1533,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>140.38000488</v>
+        <v>134.67500305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,25 +1593,25 @@
         <v>63.26530612244898</v>
       </c>
       <c r="X10" t="n">
-        <v>22.7181635419816</v>
+        <v>23.45915461234785</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2770472246715006</v>
+        <v>4.903962935541173</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>25</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.32988127814506</v>
+        <v>13.39485170604108</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.749964782163934</v>
+        <v>5.358832209805531</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1646,10 +1642,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>262.01998901</v>
+        <v>250.75999451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,22 +1705,22 @@
         <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.329742519118316</v>
+        <v>6.527004591388453</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>46.875</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.31497854465687</v>
+        <v>8.615392882506303</v>
       </c>
       <c r="AC11" t="n">
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.853217221612308</v>
+        <v>3.715506701619598</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1755,10 +1751,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>110.37999725</v>
+        <v>110.65249634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,22 +1782,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>2.812962577161815</v>
+        <v>3.066780655078838</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>10.71931863751676</v>
+        <v>10.9048699535845</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>5.045120082932431</v>
+        <v>4.786430034552636</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1842,10 +1838,10 @@
         <v>26.66666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.521164021164021</v>
+        <v>6.687830687830687</v>
       </c>
       <c r="AH12" t="n">
-        <v>20.14550264550265</v>
+        <v>19.97883597883598</v>
       </c>
       <c r="AI12" t="n">
         <v>10.89745332569237</v>
@@ -1864,19 +1860,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>94.78289795000001</v>
+        <v>93.29000092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1891,27 +1887,17 @@
       <c r="I13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="n">
-        <v>12.0476205047619</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.634433698220717</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>34</v>
-      </c>
-      <c r="M13" t="n">
-        <v>55.88235294117647</v>
-      </c>
-      <c r="N13" t="n">
-        <v>9.383714203196007</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>36</v>
       </c>
@@ -1973,10 +1959,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>216.08000183</v>
+        <v>212.91999817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,10 +2019,10 @@
         <v>48.38709677419355</v>
       </c>
       <c r="X14" t="n">
-        <v>17.09797149318395</v>
+        <v>17.16791547737358</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.7213379802442632</v>
+        <v>2.231610174132437</v>
       </c>
       <c r="Z14" t="n">
         <v>19</v>
@@ -2045,13 +2031,13 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.69688484665765</v>
+        <v>10.70170648627307</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>9.346078836063832</v>
+        <v>7.945707032409565</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2060,10 +2046,10 @@
         <v>50</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.8421052631579</v>
+        <v>12.86226655348048</v>
       </c>
       <c r="AH14" t="n">
-        <v>37.1578947368421</v>
+        <v>37.13773344651953</v>
       </c>
       <c r="AI14" t="n">
         <v>29.92980081982123</v>
@@ -2082,10 +2068,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>107.18000031</v>
+        <v>107.63999939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,25 +2128,25 @@
         <v>55.55555555555556</v>
       </c>
       <c r="X15" t="n">
-        <v>14.87985819387563</v>
+        <v>12.21787542570352</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.192368217314623</v>
+        <v>3.781177488171639</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>27.77777777777778</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.820484006419468</v>
+        <v>10.6323326448617</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.061763217212668</v>
+        <v>6.463207872933452</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -2191,10 +2177,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>13.56999969</v>
+        <v>13.41499996</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,22 +2208,22 @@
         <v>10.17760031008306</v>
       </c>
       <c r="K16" t="n">
-        <v>3.193916974424971</v>
+        <v>2.015211769260872</v>
       </c>
       <c r="L16" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>46.15384615384615</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N16" t="n">
-        <v>12.63396783499991</v>
+        <v>13.33090069265678</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.719232981795305</v>
+        <v>3.9060725960673</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2246,10 +2232,10 @@
         <v>55</v>
       </c>
       <c r="S16" t="n">
-        <v>41.99116124976899</v>
+        <v>42.05366124976899</v>
       </c>
       <c r="T16" t="n">
-        <v>13.00883875023101</v>
+        <v>12.94633875023101</v>
       </c>
       <c r="U16" t="n">
         <v>39.82909179893205</v>
@@ -2272,19 +2258,19 @@
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF16" t="n">
-        <v>38.46153846153846</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.50186930267333</v>
+        <v>16.65709811055487</v>
       </c>
       <c r="AH16" t="n">
-        <v>20.95966915886513</v>
+        <v>22.81658609997145</v>
       </c>
       <c r="AI16" t="n">
-        <v>24.89137346556135</v>
+        <v>25.5980757481601</v>
       </c>
       <c r="AJ16" t="n">
         <v>50</v>
@@ -2300,10 +2286,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>309.48001099</v>
+        <v>317.36999512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,25 +2314,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>20.85433522869784</v>
+        <v>21.09865479945756</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5621481689683128</v>
+        <v>3.445243725770619</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>43.75</v>
       </c>
       <c r="N17" t="n">
-        <v>14.79358930761215</v>
+        <v>15.64398184173933</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.396273813218812</v>
+        <v>4.403060121646463</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2409,10 +2395,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>85.29000092</v>
+        <v>84.55500031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,10 +2440,10 @@
         <v>55</v>
       </c>
       <c r="S18" t="n">
-        <v>30.64658750119277</v>
+        <v>30.70908750119277</v>
       </c>
       <c r="T18" t="n">
-        <v>24.35341249880723</v>
+        <v>24.29091249880723</v>
       </c>
       <c r="U18" t="n">
         <v>39.82909179893205</v>
@@ -2486,10 +2472,10 @@
         <v>48.48484848484848</v>
       </c>
       <c r="AG18" t="n">
-        <v>27.52570436920874</v>
+        <v>27.58140846903048</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.95914411563975</v>
+        <v>20.903440015818</v>
       </c>
       <c r="AI18" t="n">
         <v>32.5040421081337</v>
@@ -2508,10 +2494,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>344.29998779</v>
+        <v>345.6000061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,16 +2525,16 @@
         <v>14.75759965099349</v>
       </c>
       <c r="K19" t="n">
-        <v>5.052785150929728</v>
+        <v>5.449446635262989</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N19" t="n">
-        <v>10.55470572399957</v>
+        <v>9.876250008421708</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -2595,10 +2581,10 @@
         <v>55</v>
       </c>
       <c r="AG19" t="n">
-        <v>19.93928154785942</v>
+        <v>20.0562406121869</v>
       </c>
       <c r="AH19" t="n">
-        <v>35.06071845214058</v>
+        <v>34.9437593878131</v>
       </c>
       <c r="AI19" t="n">
         <v>34.20853424503424</v>
@@ -2617,10 +2603,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>959.6799926800001</v>
+        <v>978</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,22 +2634,22 @@
         <v>11.3923910063839</v>
       </c>
       <c r="K20" t="n">
-        <v>0.543746137007628</v>
+        <v>2.463096523865582</v>
       </c>
       <c r="L20" t="n">
         <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>10.6954880576206</v>
+        <v>9.826113369739431</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>9.405113919374619</v>
+        <v>7.355724872494895</v>
       </c>
       <c r="Q20" t="n">
         <v>30</v>
@@ -2672,10 +2658,10 @@
         <v>40</v>
       </c>
       <c r="S20" t="n">
-        <v>33.92522564581388</v>
+        <v>33.84189231248055</v>
       </c>
       <c r="T20" t="n">
-        <v>6.074774354186118</v>
+        <v>6.158107687519454</v>
       </c>
       <c r="U20" t="n">
         <v>24.59062811680185</v>
@@ -2726,10 +2712,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>35.65999985</v>
+        <v>35.09000015</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,10 +2757,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S21" t="n">
-        <v>35.26124013608901</v>
+        <v>35.11399882983314</v>
       </c>
       <c r="T21" t="n">
-        <v>26.44088752348546</v>
+        <v>26.58812882974133</v>
       </c>
       <c r="U21" t="n">
         <v>47.42656695641357</v>
@@ -2786,19 +2772,19 @@
         <v>71.23287671232876</v>
       </c>
       <c r="X21" t="n">
-        <v>21.05598196057028</v>
+        <v>19.98739658862876</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.305836662138842</v>
+        <v>7.803471132665385</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>45.83333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.52757656519848</v>
+        <v>16.59119965274705</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -2835,10 +2821,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>305.64001465</v>
+        <v>307.7250061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,22 +2852,22 @@
         <v>15.08538893012877</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4403637574000863</v>
+        <v>1.125540074738218</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M22" t="n">
-        <v>41.1764705882353</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N22" t="n">
-        <v>7.944935520626509</v>
+        <v>9.253020532007756</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.517723637172315</v>
+        <v>8.77568606180299</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2922,10 +2908,10 @@
         <v>50</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.09672619047619</v>
+        <v>14.22172619047619</v>
       </c>
       <c r="AH22" t="n">
-        <v>35.90327380952381</v>
+        <v>35.77827380952381</v>
       </c>
       <c r="AI22" t="n">
         <v>29.92980081982123</v>
@@ -2944,10 +2930,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>98.21140289</v>
+        <v>102.44680023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2964,11 +2950,7 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -2979,17 +2961,13 @@
         <v>20.85153887202731</v>
       </c>
       <c r="K23" t="n">
-        <v>15.35283485277461</v>
+        <v>20.32746178529188</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" t="n">
-        <v>11.41843203785392</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>10</v>
       </c>
@@ -3021,16 +2999,16 @@
         <v>25.31125581911988</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.946948501353878</v>
+        <v>3.977131983276772</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA23" t="n">
-        <v>40</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.356344946747415</v>
+        <v>8.94571731336895</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
@@ -3045,10 +3023,10 @@
         <v>44.68085106382978</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.57436553741145</v>
+        <v>19.62755702677315</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.10648552641833</v>
+        <v>25.05329403705663</v>
       </c>
       <c r="AI23" t="n">
         <v>31.41096626549528</v>
@@ -3067,10 +3045,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>264.54998779</v>
+        <v>267.82470703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3127,25 +3105,23 @@
         <v>40</v>
       </c>
       <c r="X24" t="n">
-        <v>12.23047619452817</v>
+        <v>10.45310094410821</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.877546198371808</v>
+        <v>4.712455952271045</v>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA24" t="n">
-        <v>27.27272727272727</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.752793166477732</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.1301005197827498</v>
+        <v>1.351219679965765</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3154,10 +3130,10 @@
         <v>35.71428571428572</v>
       </c>
       <c r="AG24" t="n">
-        <v>5.424991674991675</v>
+        <v>5.603563103563104</v>
       </c>
       <c r="AH24" t="n">
-        <v>30.28929403929404</v>
+        <v>30.11072261072261</v>
       </c>
       <c r="AI24" t="n">
         <v>16.34473175355414</v>
@@ -3176,10 +3152,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>344.83999634</v>
+        <v>350.54000854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3253,10 +3229,10 @@
         <v>38.09523809523809</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.1530612244898</v>
+        <v>15.27210884353742</v>
       </c>
       <c r="AH25" t="n">
-        <v>22.9421768707483</v>
+        <v>22.82312925170068</v>
       </c>
       <c r="AI25" t="n">
         <v>20.75101136856449</v>
@@ -3275,10 +3251,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>30.71500015</v>
+        <v>31.09499931</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3296,10 @@
         <v>44.44444444444444</v>
       </c>
       <c r="S26" t="n">
-        <v>22.48449727378026</v>
+        <v>22.50823896418862</v>
       </c>
       <c r="T26" t="n">
-        <v>21.95994717066418</v>
+        <v>21.93620548025582</v>
       </c>
       <c r="U26" t="n">
         <v>24.55951812700564</v>
@@ -3374,10 +3350,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C27" t="n">
-        <v>88.18000031</v>
+        <v>88.40499878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3419,10 +3395,10 @@
         <v>20</v>
       </c>
       <c r="S27" t="n">
-        <v>9.704545454545455</v>
+        <v>9.726190476190476</v>
       </c>
       <c r="T27" t="n">
-        <v>10.29545454545454</v>
+        <v>10.27380952380952</v>
       </c>
       <c r="U27" t="n">
         <v>5.668215145437519</v>
@@ -3473,10 +3449,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>572.79998779</v>
+        <v>569.42498779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,19 +3548,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>254.53500366</v>
+        <v>251.94000244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3599,17 +3575,27 @@
       <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>10.971007588959</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.658395101340182</v>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7.552551706909805</v>
+      </c>
       <c r="O29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0.33603215781568</v>
+      </c>
       <c r="Q29" t="n">
         <v>16</v>
       </c>
@@ -3617,10 +3603,10 @@
         <v>37.5</v>
       </c>
       <c r="S29" t="n">
-        <v>19.05016915954416</v>
+        <v>19.11747685185185</v>
       </c>
       <c r="T29" t="n">
-        <v>18.44983084045584</v>
+        <v>18.38252314814815</v>
       </c>
       <c r="U29" t="n">
         <v>18.48123255886363</v>
@@ -3671,10 +3657,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>665.16998291</v>
+        <v>676.40002441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,25 +3717,25 @@
         <v>59.45945945945946</v>
       </c>
       <c r="X30" t="n">
-        <v>26.35545823194651</v>
+        <v>27.55411108915111</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.018061235358959</v>
+        <v>1.300137628478115</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>15.78947368421053</v>
+        <v>29.41176470588235</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.6667902740774</v>
+        <v>10.74156720706106</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.063951800551657</v>
+        <v>4.761771960563498</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3780,10 +3766,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>202.38499451</v>
+        <v>207.36000061</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,10 +3865,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>500.25500488</v>
+        <v>493.58499146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,10 +3964,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>924.03497314</v>
+        <v>928.85498047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,22 +3995,22 @@
         <v>13.41136277305126</v>
       </c>
       <c r="K33" t="n">
-        <v>2.374805908452271</v>
+        <v>2.90881958675413</v>
       </c>
       <c r="L33" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M33" t="n">
-        <v>71.08433734939759</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="N33" t="n">
-        <v>13.89558125827143</v>
+        <v>14.09056122916454</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.541099843246132</v>
+        <v>3.003805140957772</v>
       </c>
       <c r="Q33" t="n">
         <v>55</v>
@@ -4051,7 +4037,7 @@
         <v>26.04595216565901</v>
       </c>
       <c r="Y33" t="n">
-        <v>11.35505070013738</v>
+        <v>10.89265553349029</v>
       </c>
       <c r="Z33" t="n">
         <v>16</v>
@@ -4097,10 +4083,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>78.02500153</v>
+        <v>77.31999969</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4128,37 +4114,37 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>3.991740368784802</v>
+        <v>3.052113750814067</v>
       </c>
       <c r="L34" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M34" t="n">
-        <v>58.62068965517241</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N34" t="n">
-        <v>10.32512463612697</v>
+        <v>10.7819821585961</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>5.77763157911213</v>
+        <v>6.742109401061214</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R34" t="n">
-        <v>60</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="S34" t="n">
-        <v>46.82427187535546</v>
+        <v>44.63817137303297</v>
       </c>
       <c r="T34" t="n">
-        <v>13.17572812464454</v>
+        <v>17.12653450931997</v>
       </c>
       <c r="U34" t="n">
-        <v>43.5727090128925</v>
+        <v>45.0410173444307</v>
       </c>
       <c r="V34" t="n">
         <v>43</v>
@@ -4167,25 +4153,25 @@
         <v>65.11627906976744</v>
       </c>
       <c r="X34" t="n">
-        <v>15.629315274282</v>
+        <v>14.39517840252906</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.668656748840252</v>
+        <v>7.511960400637552</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA34" t="n">
-        <v>38.46153846153846</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.446413475488416</v>
+        <v>12.03053678919745</v>
       </c>
       <c r="AC34" t="n">
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.569372447790575</v>
+        <v>2.690120376796912</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4216,10 +4202,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C35" t="n">
-        <v>36.24509811</v>
+        <v>36.35689926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4244,25 +4230,25 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>15.07973827857974</v>
+        <v>15.17354904446212</v>
       </c>
       <c r="K35" t="n">
-        <v>0.09693187211203824</v>
+        <v>0.5167296086705964</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M35" t="n">
-        <v>48</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N35" t="n">
-        <v>10.113440319783</v>
+        <v>10.06015990587838</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.90122523467493</v>
+        <v>1.475645295170303</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4271,10 +4257,10 @@
         <v>37.93103448275862</v>
       </c>
       <c r="S35" t="n">
-        <v>29.45831382951058</v>
+        <v>29.46138715915592</v>
       </c>
       <c r="T35" t="n">
-        <v>8.472720653248036</v>
+        <v>8.469647323602697</v>
       </c>
       <c r="U35" t="n">
         <v>22.68802210080984</v>
@@ -4303,10 +4289,10 @@
         <v>48.14814814814815</v>
       </c>
       <c r="AG35" t="n">
-        <v>13.00831440476134</v>
+        <v>13.12799556664199</v>
       </c>
       <c r="AH35" t="n">
-        <v>35.1398337433868</v>
+        <v>35.02015258150615</v>
       </c>
       <c r="AI35" t="n">
         <v>30.74322697621846</v>
@@ -4325,10 +4311,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>211.94999695</v>
+        <v>215.88000488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4337,7 +4323,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4356,22 +4342,22 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K36" t="n">
-        <v>1.44546229637097</v>
+        <v>3.326478937203015</v>
       </c>
       <c r="L36" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="M36" t="n">
-        <v>68.65671641791045</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N36" t="n">
-        <v>13.01337979812925</v>
+        <v>12.88073307750389</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5466362822705184</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>48</v>
@@ -4380,10 +4366,10 @@
         <v>64.58333333333333</v>
       </c>
       <c r="S36" t="n">
-        <v>64.92311001269151</v>
+        <v>65.71674320102495</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.3397766793581809</v>
+        <v>-1.133409867691626</v>
       </c>
       <c r="U36" t="n">
         <v>50.43905701034311</v>
@@ -4398,16 +4384,16 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.716305202515397</v>
+        <v>8.04225169173608</v>
       </c>
       <c r="Z36" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="n">
-        <v>28.57142857142857</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.78701223636375</v>
+        <v>12.06041554360705</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4444,10 +4430,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>143.58999634</v>
+        <v>143.85499573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,25 +4458,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>17.744577522677</v>
+        <v>18.57059022636381</v>
       </c>
       <c r="K37" t="n">
-        <v>2.264790682364981</v>
+        <v>3.492802683453244</v>
       </c>
       <c r="L37" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M37" t="n">
-        <v>54.16666666666666</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N37" t="n">
-        <v>10.83396361990318</v>
+        <v>12.46676894596764</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.608195430085638</v>
+        <v>4.355082865358906</v>
       </c>
       <c r="Q37" t="n">
         <v>33</v>
@@ -4517,10 +4503,10 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.88166437867064</v>
+        <v>15.72642161667009</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
@@ -4559,10 +4545,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>63.38999939</v>
+        <v>60.38029861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4619,25 +4605,25 @@
         <v>69.62025316455696</v>
       </c>
       <c r="X38" t="n">
-        <v>18.2538240912798</v>
+        <v>18.84085098446007</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1024386386027532</v>
+        <v>5.315511722673117</v>
       </c>
       <c r="Z38" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA38" t="n">
-        <v>33.33333333333334</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.955781127293166</v>
+        <v>13.58947825042231</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.90771068534001</v>
+        <v>4.947471716387386</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4668,10 +4654,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>135.3500061</v>
+        <v>135.27000427</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,10 +4699,10 @@
         <v>31.25</v>
       </c>
       <c r="S39" t="n">
-        <v>16.14520202020202</v>
+        <v>16.15873015873016</v>
       </c>
       <c r="T39" t="n">
-        <v>15.10479797979798</v>
+        <v>15.09126984126984</v>
       </c>
       <c r="U39" t="n">
         <v>14.16464385478204</v>
@@ -4767,10 +4753,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>27.53000069</v>
+        <v>27.54000092</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4827,25 +4813,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X40" t="n">
-        <v>18.25910194830291</v>
+        <v>15.45454528638159</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.751449650507823</v>
+        <v>5.717214010949567</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>33.33333333333334</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.205280914877466</v>
+        <v>8.67005836806079</v>
       </c>
       <c r="AC40" t="n">
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.507815063189524</v>
+        <v>4.542489855515952</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4876,10 +4862,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C41" t="n">
-        <v>174.21000671</v>
+        <v>171.91499329</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4896,11 +4882,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -4911,22 +4893,22 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>5.870558177422036</v>
+        <v>4.475837194461851</v>
       </c>
       <c r="L41" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>85.71428571428571</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="N41" t="n">
-        <v>19.01433689832987</v>
+        <v>20.41113424164209</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>3.900462880017774</v>
+        <v>5.287502789047749</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4950,19 +4932,19 @@
         <v>79.24528301886792</v>
       </c>
       <c r="X41" t="n">
-        <v>31.46984695975164</v>
+        <v>23.35952775538022</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.517114602556251</v>
+        <v>8.735468628916953</v>
       </c>
       <c r="Z41" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AA41" t="n">
-        <v>27.27272727272727</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.15255780364066</v>
+        <v>13.47052463739631</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -4999,10 +4981,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>188.08999634</v>
+        <v>188.94500732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5044,10 +5026,10 @@
         <v>46.34146341463415</v>
       </c>
       <c r="S42" t="n">
-        <v>44.84420302780043</v>
+        <v>45.26235839664509</v>
       </c>
       <c r="T42" t="n">
-        <v>1.497260386833716</v>
+        <v>1.079105017989058</v>
       </c>
       <c r="U42" t="n">
         <v>32.05623397633605</v>
@@ -5059,25 +5041,25 @@
         <v>51.02040816326531</v>
       </c>
       <c r="X42" t="n">
-        <v>22.24584364682432</v>
+        <v>23.23057719146176</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.8748372384716707</v>
+        <v>1.219946861920085</v>
       </c>
       <c r="Z42" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA42" t="n">
-        <v>42.85714285714285</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.08490925847598</v>
+        <v>10.24757937337741</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>9.205697632478349</v>
+        <v>8.888487968119129</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5108,10 +5090,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>54.22999954</v>
+        <v>53.29499817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,25 +5118,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>12.18987602075233</v>
+        <v>12.90936225399626</v>
       </c>
       <c r="K43" t="n">
-        <v>2.147295887698353</v>
+        <v>1.215457990368596</v>
       </c>
       <c r="L43" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M43" t="n">
-        <v>50</v>
+        <v>62.26415094339622</v>
       </c>
       <c r="N43" t="n">
-        <v>13.25564778464197</v>
+        <v>13.31719995476874</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.813757374780178</v>
+        <v>2.751103502289509</v>
       </c>
       <c r="Q43" t="n">
         <v>43</v>
@@ -5163,10 +5145,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S43" t="n">
-        <v>36.44412382784476</v>
+        <v>36.50226336272848</v>
       </c>
       <c r="T43" t="n">
-        <v>14.71866686982966</v>
+        <v>14.66052733494594</v>
       </c>
       <c r="U43" t="n">
         <v>36.75230846944931</v>
@@ -5178,19 +5160,19 @@
         <v>60</v>
       </c>
       <c r="X43" t="n">
-        <v>23.84268632509694</v>
+        <v>21.13804700802859</v>
       </c>
       <c r="Y43" t="n">
-        <v>10.30433283956312</v>
+        <v>11.85081213864948</v>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA43" t="n">
-        <v>44.44444444444444</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.372267648678688</v>
+        <v>8.722883500149905</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5227,31 +5209,27 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>36.13000107</v>
+        <v>36.71500015</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.05: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5262,22 +5240,22 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>5.984162249996339</v>
+        <v>7.700205304927232</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M44" t="n">
-        <v>82.05128205128206</v>
+        <v>72.97297297297297</v>
       </c>
       <c r="N44" t="n">
-        <v>17.88973188241306</v>
+        <v>17.9931486750642</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>0.01494350633852726</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>70</v>
@@ -5301,13 +5279,13 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X44" t="n">
-        <v>45.54524190295925</v>
+        <v>44.25503404501885</v>
       </c>
       <c r="Y44" t="n">
-        <v>14.60647624649322</v>
+        <v>13.22382661033697</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
@@ -5346,10 +5324,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C45" t="n">
-        <v>26.77499962</v>
+        <v>26.375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5381,50 +5359,50 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R45" t="n">
-        <v>45.83333333333334</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="S45" t="n">
-        <v>12.23970926702756</v>
+        <v>13.32722311531995</v>
       </c>
       <c r="T45" t="n">
-        <v>33.59362406630578</v>
+        <v>34.49886384120179</v>
       </c>
       <c r="U45" t="n">
-        <v>27.89133373121099</v>
+        <v>29.23715741664665</v>
       </c>
       <c r="V45" t="n">
         <v>23</v>
       </c>
       <c r="W45" t="n">
-        <v>43.47826086956522</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="X45" t="n">
-        <v>18.80266883769528</v>
+        <v>19.42350872558167</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.05599589206733979</v>
+        <v>2.060899753476464</v>
       </c>
       <c r="Z45" t="n">
         <v>16</v>
       </c>
       <c r="AA45" t="n">
-        <v>43.75</v>
+        <v>25</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.374067093461447</v>
+        <v>9.737221561477718</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>7.948454916168535</v>
+        <v>6.06407474805687</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5433,10 +5411,10 @@
         <v>29.41176470588235</v>
       </c>
       <c r="AG45" t="n">
-        <v>14.00718192240684</v>
+        <v>14.01159810329361</v>
       </c>
       <c r="AH45" t="n">
-        <v>15.40458278347552</v>
+        <v>15.40016660258875</v>
       </c>
       <c r="AI45" t="n">
         <v>13.27998961029523</v>
@@ -5455,10 +5433,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C46" t="n">
-        <v>361.1499939</v>
+        <v>360.99990845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,16 +5496,16 @@
         <v>21.71653838636141</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.960320313245648</v>
+        <v>5.999400994076431</v>
       </c>
       <c r="Z46" t="n">
         <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>30.76923076923077</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.81943638748685</v>
+        <v>11.70050568701519</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5564,10 +5542,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>71.79000092</v>
+        <v>71.83000183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5599,7 +5577,7 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>3.682846820931429</v>
+        <v>3.740618212087266</v>
       </c>
       <c r="L47" t="n">
         <v>31</v>
@@ -5608,13 +5586,13 @@
         <v>74.19354838709677</v>
       </c>
       <c r="N47" t="n">
-        <v>14.5652771198515</v>
+        <v>14.53212474585712</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3058877999524201</v>
+        <v>0.2500291519204723</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5641,7 +5619,7 @@
         <v>23.42098914682247</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.83918802253218</v>
+        <v>12.79062259906432</v>
       </c>
       <c r="Z47" t="n">
         <v>6</v>
@@ -5687,19 +5665,19 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>376.96499634</v>
+        <v>378.82998657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5714,17 +5692,27 @@
       <c r="I48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>10.39403223569868</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.391746278961215</v>
+      </c>
       <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="N48" t="n">
+        <v>11.93885027906669</v>
+      </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>6.517546016869424</v>
+      </c>
       <c r="Q48" t="n">
         <v>26</v>
       </c>
@@ -5786,10 +5774,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>374.77999878</v>
+        <v>370.69500732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5885,14 +5873,14 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>51.49499893</v>
+        <v>50.57500076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5902,7 +5890,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5930,10 +5918,10 @@
         <v>36.8421052631579</v>
       </c>
       <c r="S50" t="n">
-        <v>13.71949125910752</v>
+        <v>13.86514282116775</v>
       </c>
       <c r="T50" t="n">
-        <v>23.12261400405038</v>
+        <v>22.97696244199015</v>
       </c>
       <c r="U50" t="n">
         <v>19.14951274513507</v>
@@ -5945,25 +5933,25 @@
         <v>35</v>
       </c>
       <c r="X50" t="n">
-        <v>14.32689968620457</v>
+        <v>14.59303171015847</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1066931344536615</v>
+        <v>2.119213177436807</v>
       </c>
       <c r="Z50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA50" t="n">
-        <v>31.81818181818182</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB50" t="n">
-        <v>10.27292042944566</v>
+        <v>12.51837670917653</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.895329051519612</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>19</v>
@@ -5994,10 +5982,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>27.87000084</v>
+        <v>28.05500031</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6039,10 +6027,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S51" t="n">
-        <v>35.80848542230262</v>
+        <v>35.84136221329811</v>
       </c>
       <c r="T51" t="n">
-        <v>30.14896138620801</v>
+        <v>30.11608459521253</v>
       </c>
       <c r="U51" t="n">
         <v>51.67092456194193</v>
@@ -6054,19 +6042,19 @@
         <v>68.65671641791045</v>
       </c>
       <c r="X51" t="n">
-        <v>14.13385906971916</v>
+        <v>13.33072658586623</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.863397512541622</v>
+        <v>3.225248249113732</v>
       </c>
       <c r="Z51" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA51" t="n">
         <v>50</v>
       </c>
-      <c r="AA51" t="n">
-        <v>52</v>
-      </c>
       <c r="AB51" t="n">
-        <v>13.00698474437825</v>
+        <v>14.04164998977432</v>
       </c>
       <c r="AC51" t="n">
         <v>3</v>
@@ -6103,10 +6091,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>88.86000061</v>
+        <v>88.23999786</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,22 +6154,22 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.402540844455237</v>
+        <v>4.076530152448898</v>
       </c>
       <c r="Z52" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA52" t="n">
-        <v>40.74074074074074</v>
+        <v>26.08695652173913</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.368858389096365</v>
+        <v>9.937568094511763</v>
       </c>
       <c r="AC52" t="n">
         <v>6</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.688951840195142</v>
+        <v>2.005212958421987</v>
       </c>
       <c r="AE52" t="n">
         <v>28</v>
@@ -6212,10 +6200,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>108.44000244</v>
+        <v>108.19999695</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6243,7 +6231,7 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>6.157612154467484</v>
+        <v>5.922658178544626</v>
       </c>
       <c r="L53" t="n">
         <v>11</v>
@@ -6267,10 +6255,10 @@
         <v>30.76923076923077</v>
       </c>
       <c r="S53" t="n">
-        <v>25.42329797724123</v>
+        <v>25.45659801054126</v>
       </c>
       <c r="T53" t="n">
-        <v>5.34593279198954</v>
+        <v>5.31263275868951</v>
       </c>
       <c r="U53" t="n">
         <v>12.68070365571051</v>
@@ -6299,10 +6287,10 @@
         <v>23.07692307692308</v>
       </c>
       <c r="AG53" t="n">
-        <v>10.44178794178794</v>
+        <v>10.24948024948025</v>
       </c>
       <c r="AH53" t="n">
-        <v>12.63513513513513</v>
+        <v>12.82744282744283</v>
       </c>
       <c r="AI53" t="n">
         <v>8.179528718498569</v>
@@ -6321,10 +6309,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>168.69000244</v>
+        <v>164.58000183</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6366,10 +6354,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S54" t="n">
-        <v>26.48577889937337</v>
+        <v>26.60482651842099</v>
       </c>
       <c r="T54" t="n">
-        <v>30.65707824348377</v>
+        <v>30.53803062443615</v>
       </c>
       <c r="U54" t="n">
         <v>36.54655436930671</v>
@@ -6381,25 +6369,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X54" t="n">
-        <v>13.6561815747644</v>
+        <v>12.2328853696368</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.4485066531008997</v>
+        <v>2.982785650904873</v>
       </c>
       <c r="Z54" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA54" t="n">
-        <v>40.74074074074074</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.68473811409051</v>
+        <v>14.33019873573315</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.57199906689384</v>
+        <v>2.079233425355453</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6408,10 +6396,10 @@
         <v>40.90909090909091</v>
       </c>
       <c r="AG54" t="n">
-        <v>21.98241573241573</v>
+        <v>22.20968845968846</v>
       </c>
       <c r="AH54" t="n">
-        <v>18.92667517667518</v>
+        <v>18.69940244940245</v>
       </c>
       <c r="AI54" t="n">
         <v>23.25581619647187</v>
@@ -6430,10 +6418,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>28977.31640625</v>
+        <v>29176.00195312</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,10 +6495,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.60616921907245</v>
+        <v>12.62646142686465</v>
       </c>
       <c r="AH55" t="n">
-        <v>44.5366879237847</v>
+        <v>44.51639571599249</v>
       </c>
       <c r="AI55" t="n">
         <v>32.59064457965074</v>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>332.70999146</v>
+        <v>332.41000366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>11.8607954991482</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.043962211428118</v>
+        <v>1.133185874182119</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -739,13 +739,13 @@
         <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.81050995120604</v>
+        <v>9.803360299429047</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.029422301076826</v>
+        <v>6.945519774794374</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -779,7 +779,7 @@
         <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>523.52001953</v>
+        <v>512.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         <v>19.69353007945516</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.707440582266472</v>
+        <v>2.797534376481747</v>
       </c>
       <c r="Z3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AA3" t="n">
-        <v>48.21428571428572</v>
+        <v>42.5925925925926</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.13239990401026</v>
+        <v>14.48418530648395</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.323143086355863</v>
+        <v>2.265853658536587</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -888,7 +888,7 @@
         <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>247.88000488</v>
+        <v>245.96000671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>12.76565826578477</v>
+        <v>13.61080813594433</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4823877855728798</v>
+        <v>0.6794939170181813</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>60.52631578947368</v>
+        <v>62.16216216216216</v>
       </c>
       <c r="N4" t="n">
-        <v>9.812507235896533</v>
+        <v>10.7409930297991</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>7.481522264846596</v>
+        <v>7.271099404825687</v>
       </c>
       <c r="Q4" t="n">
         <v>23</v>
@@ -997,7 +997,7 @@
         <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>341.67498779</v>
+        <v>339.51000977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %93.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %92.31: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1026,25 +1026,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>21.91436107540768</v>
+        <v>22.39625430606883</v>
       </c>
       <c r="K5" t="n">
-        <v>1.117192648164766</v>
+        <v>1.100402254588917</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>93.33333333333333</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5406638374357</v>
+        <v>13.10451646294336</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.862005167001057</v>
+        <v>1.878922044867393</v>
       </c>
       <c r="Q5" t="n">
         <v>45</v>
@@ -1110,7 +1110,7 @@
         <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>210.75999451</v>
+        <v>201.96000671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>15.10639127416894</v>
+        <v>18.27947768013144</v>
       </c>
       <c r="K6" t="n">
-        <v>2.975519809670213</v>
+        <v>2.507360843028983</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M6" t="n">
-        <v>53.65853658536585</v>
+        <v>65.625</v>
       </c>
       <c r="N6" t="n">
-        <v>10.71945499829607</v>
+        <v>13.31625689221774</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.879295777886372</v>
+        <v>5.358287553009955</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1219,7 +1219,7 @@
         <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>58.36000061</v>
+        <v>57.90000153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>10.86923747477177</v>
+        <v>12.34095145691251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3783990751775601</v>
+        <v>1.259183658790719</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>48.57142857142857</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N7" t="n">
-        <v>10.25737454686742</v>
+        <v>11.12502980176296</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.611718207279856</v>
+        <v>1.719168848008135</v>
       </c>
       <c r="Q7" t="n">
         <v>24</v>
@@ -1328,7 +1328,7 @@
         <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>135.02999878</v>
+        <v>132.94999695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>790.06011963</v>
+        <v>782.7199707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,22 +1455,22 @@
         <v>14.83129006708122</v>
       </c>
       <c r="K9" t="n">
-        <v>2.420319763728229</v>
+        <v>1.468771417159287</v>
       </c>
       <c r="L9" t="n">
         <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>46.875</v>
+        <v>56.25</v>
       </c>
       <c r="N9" t="n">
-        <v>11.34759150973013</v>
+        <v>10.64486250369917</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>3.495087932286944</v>
+        <v>4.465638560076668</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1536,7 +1536,7 @@
         <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>134.67500305</v>
+        <v>132.53999329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,22 +1596,22 @@
         <v>23.45915461234785</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.903962935541173</v>
+        <v>6.411525309195332</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.38461538461539</v>
+        <v>25</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.39485170604108</v>
+        <v>11.90839610674435</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.358832209805531</v>
+        <v>3.834312614518165</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1645,7 +1645,7 @@
         <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>250.75999451</v>
+        <v>250.53999329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.527004591388453</v>
+        <v>6.609011982827163</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB11" t="n">
         <v>8.615392882506303</v>
@@ -1720,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.715506701619598</v>
+        <v>3.630958499496006</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1754,7 +1754,7 @@
         <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>110.65249634</v>
+        <v>107.73999786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,22 +1782,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>3.066780655078838</v>
+        <v>0.3539467658727036</v>
       </c>
       <c r="L12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N12" t="n">
-        <v>10.9048699535845</v>
+        <v>8.710752460045491</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.786430034552636</v>
+        <v>7.619085726608898</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1863,7 +1863,7 @@
         <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>93.29000092</v>
+        <v>91.72000122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>212.91999817</v>
+        <v>211.53999329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,22 +2022,22 @@
         <v>17.16791547737358</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.231610174132437</v>
+        <v>2.865279421873634</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.31578947368421</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.70170648627307</v>
+        <v>9.736178955181336</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.945707032409565</v>
+        <v>7.345180524185313</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2071,7 +2071,7 @@
         <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>107.63999939</v>
+        <v>106.98999786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,22 +2131,22 @@
         <v>12.21787542570352</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.781177488171639</v>
+        <v>4.362210396030397</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>26.31578947368421</v>
+        <v>31.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.6323326448617</v>
+        <v>12.14919448128582</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.463207872933452</v>
+        <v>5.894939257081699</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -2180,7 +2180,7 @@
         <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>13.41499996</v>
+        <v>13.35000038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,22 +2208,22 @@
         <v>10.17760031008306</v>
       </c>
       <c r="K16" t="n">
-        <v>2.015211769260872</v>
+        <v>1.5209183709467</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>52.17391304347826</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="N16" t="n">
-        <v>13.33090069265678</v>
+        <v>12.30838893360362</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9060725960673</v>
+        <v>4.411979029471746</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2289,7 +2289,7 @@
         <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>317.36999512</v>
+        <v>312.8999939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2317,22 +2317,22 @@
         <v>21.09865479945756</v>
       </c>
       <c r="K17" t="n">
-        <v>3.445243725770619</v>
+        <v>1.988268041971186</v>
       </c>
       <c r="L17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>43.75</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N17" t="n">
-        <v>15.64398184173933</v>
+        <v>14.45597755919411</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.403060121646463</v>
+        <v>5.89453284524335</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2398,7 +2398,7 @@
         <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>84.55500031</v>
+        <v>84.29000092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,16 +2497,16 @@
         <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>345.6000061</v>
+        <v>342.86999512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2525,22 +2525,22 @@
         <v>14.75759965099349</v>
       </c>
       <c r="K19" t="n">
-        <v>5.449446635262989</v>
+        <v>4.61646590011251</v>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M19" t="n">
-        <v>35</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="N19" t="n">
-        <v>9.876250008421708</v>
+        <v>10.74288699811014</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3666096886255854</v>
       </c>
       <c r="Q19" t="n">
         <v>23</v>
@@ -2606,7 +2606,7 @@
         <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>978</v>
+        <v>937.97998047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>11.3923910063839</v>
+        <v>13.4458321963166</v>
       </c>
       <c r="K20" t="n">
-        <v>2.463096523865582</v>
+        <v>0.6016777218157854</v>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N20" t="n">
-        <v>9.826113369739431</v>
+        <v>11.4634541192612</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.355724872494895</v>
+        <v>9.342112866320695</v>
       </c>
       <c r="Q20" t="n">
         <v>30</v>
@@ -2715,7 +2715,7 @@
         <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>35.09000015</v>
+        <v>34.50999832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2739,17 +2739,27 @@
       <c r="I21" t="n">
         <v>10</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>10.36521163425277</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.157838547701351</v>
+      </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.39027390591968</v>
+      </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>6.763847024145542</v>
+      </c>
       <c r="Q21" t="n">
         <v>47</v>
       </c>
@@ -2775,16 +2785,16 @@
         <v>19.98739658862876</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.803471132665385</v>
+        <v>9.327385502403629</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
-        <v>44.44444444444444</v>
+        <v>37.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>16.59119965274705</v>
+        <v>18.20433957561407</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -2824,7 +2834,7 @@
         <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>307.7250061</v>
+        <v>302.47000122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,25 +2859,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>15.08538893012877</v>
+        <v>15.59604487521503</v>
       </c>
       <c r="K22" t="n">
-        <v>1.125540074738218</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>47.36842105263158</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N22" t="n">
-        <v>9.253020532007756</v>
+        <v>8.655085078351195</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>8.77568606180299</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2933,7 +2943,7 @@
         <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>102.44680023</v>
+        <v>101.05000305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,7 +2971,7 @@
         <v>20.85153887202731</v>
       </c>
       <c r="K23" t="n">
-        <v>20.32746178529188</v>
+        <v>18.68687311955595</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2999,16 +3009,16 @@
         <v>25.31125581911988</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.977131983276772</v>
+        <v>5.286342919686227</v>
       </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>58.8235294117647</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.94571731336895</v>
+        <v>10.86213491611809</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
@@ -3048,7 +3058,7 @@
         <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>267.82470703</v>
+        <v>267.27999878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,20 +3118,22 @@
         <v>10.45310094410821</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.712455952271045</v>
+        <v>4.906254022436462</v>
       </c>
       <c r="Z24" t="n">
         <v>9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="inlineStr"/>
+        <v>11.11111111111111</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.966186301970189</v>
+      </c>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.351219679965765</v>
+        <v>1.15017656137093</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3155,7 +3167,7 @@
         <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>350.54000854</v>
+        <v>348.92001343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3254,7 +3266,7 @@
         <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>31.09499931</v>
+        <v>30.72999954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3365,7 @@
         <v>46281</v>
       </c>
       <c r="C27" t="n">
-        <v>88.40499878</v>
+        <v>87.87000275</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3464,7 @@
         <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>569.42498779</v>
+        <v>567.75</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3563,7 @@
         <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>251.94000244</v>
+        <v>248.55999756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3579,22 +3591,22 @@
         <v>10.971007588959</v>
       </c>
       <c r="K29" t="n">
-        <v>1.658395101340182</v>
+        <v>0.2945550274824127</v>
       </c>
       <c r="L29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>31.25</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="N29" t="n">
-        <v>7.552551706909805</v>
+        <v>8.138531162827295</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0.33603215781568</v>
+        <v>1.700436252048054</v>
       </c>
       <c r="Q29" t="n">
         <v>16</v>
@@ -3660,7 +3672,7 @@
         <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>676.40002441</v>
+        <v>673.3099975600001</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,22 +3732,22 @@
         <v>27.55411108915111</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.300137628478115</v>
+        <v>1.751032385741513</v>
       </c>
       <c r="Z30" t="n">
         <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>29.41176470588235</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="AB30" t="n">
-        <v>10.74156720706106</v>
+        <v>14.37174574117448</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.761771960563498</v>
+        <v>4.324694414032559</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3769,7 +3781,7 @@
         <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>207.36000061</v>
+        <v>202.41999817</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3868,7 +3880,7 @@
         <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>493.58499146</v>
+        <v>490.29998779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3979,7 @@
         <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>928.85498047</v>
+        <v>926.54998779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,22 +4007,22 @@
         <v>13.41136277305126</v>
       </c>
       <c r="K33" t="n">
-        <v>2.90881958675413</v>
+        <v>2.65344702500625</v>
       </c>
       <c r="L33" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M33" t="n">
-        <v>68.35443037974683</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N33" t="n">
-        <v>14.09056122916454</v>
+        <v>14.34329319244495</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.003805140957772</v>
+        <v>3.260049293988665</v>
       </c>
       <c r="Q33" t="n">
         <v>55</v>
@@ -4037,7 +4049,7 @@
         <v>26.04595216565901</v>
       </c>
       <c r="Y33" t="n">
-        <v>10.89265553349029</v>
+        <v>11.11377915455933</v>
       </c>
       <c r="Z33" t="n">
         <v>16</v>
@@ -4086,7 +4098,7 @@
         <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>77.31999969</v>
+        <v>76.41000366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4114,22 +4126,22 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>3.052113750814067</v>
+        <v>1.839270828254169</v>
       </c>
       <c r="L34" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M34" t="n">
-        <v>54.05405405405406</v>
+        <v>56.81818181818182</v>
       </c>
       <c r="N34" t="n">
-        <v>10.7819821585961</v>
+        <v>10.813648521222</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>6.742109401061214</v>
+        <v>8.013342107985455</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4156,22 +4168,22 @@
         <v>14.39517840252906</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.511960400637552</v>
+        <v>8.600472418166538</v>
       </c>
       <c r="Z34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
-        <v>42.85714285714285</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB34" t="n">
-        <v>12.03053678919745</v>
+        <v>10.35058875984423</v>
       </c>
       <c r="AC34" t="n">
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.690120376796912</v>
+        <v>1.531219710715037</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4205,7 +4217,7 @@
         <v>46281</v>
       </c>
       <c r="C35" t="n">
-        <v>36.35689926</v>
+        <v>35.77999878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4230,25 +4242,25 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>15.17354904446212</v>
+        <v>16.1350871679738</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5167296086705964</v>
+        <v>0.05592970061414348</v>
       </c>
       <c r="L35" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M35" t="n">
-        <v>53.84615384615385</v>
+        <v>50</v>
       </c>
       <c r="N35" t="n">
-        <v>10.06015990587838</v>
+        <v>8.99945789332031</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.475645295170303</v>
+        <v>1.942983594478487</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4314,7 +4326,7 @@
         <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>215.88000488</v>
+        <v>213.8999939</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4342,16 +4354,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K36" t="n">
-        <v>3.326478937203015</v>
+        <v>2.378787820862138</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M36" t="n">
-        <v>63.1578947368421</v>
+        <v>65.15151515151516</v>
       </c>
       <c r="N36" t="n">
-        <v>12.88073307750389</v>
+        <v>12.75720590321936</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4384,16 +4396,16 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.04225169173608</v>
+        <v>8.885670939607838</v>
       </c>
       <c r="Z36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="n">
-        <v>44.11764705882353</v>
+        <v>34.375</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.06041554360705</v>
+        <v>11.57975726743594</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4433,7 +4445,7 @@
         <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>143.85499573</v>
+        <v>143.16000366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4461,22 +4473,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K37" t="n">
-        <v>3.492802683453244</v>
+        <v>2.99280838848921</v>
       </c>
       <c r="L37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M37" t="n">
-        <v>52.63157894736842</v>
+        <v>50</v>
       </c>
       <c r="N37" t="n">
-        <v>12.46676894596764</v>
+        <v>11.83848525057088</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.355082865358906</v>
+        <v>4.861690529520901</v>
       </c>
       <c r="Q37" t="n">
         <v>33</v>
@@ -4503,10 +4515,10 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.72642161667009</v>
+        <v>16.13356401996117</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
@@ -4548,7 +4560,7 @@
         <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>60.38029861</v>
+        <v>59.36000061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4608,22 +4620,22 @@
         <v>18.84085098446007</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.315511722673117</v>
+        <v>6.915477212151178</v>
       </c>
       <c r="Z38" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>42.30769230769231</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB38" t="n">
-        <v>13.58947825042231</v>
+        <v>10.07875313925385</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.947471716387386</v>
+        <v>3.31367954141939</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4657,7 +4669,7 @@
         <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>135.27000427</v>
+        <v>134.33999634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,7 +4768,7 @@
         <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>27.54000092</v>
+        <v>27.45999908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,22 +4828,22 @@
         <v>15.45454528638159</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.717214010949567</v>
+        <v>5.991099127415655</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA40" t="n">
-        <v>15.38461538461539</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.67005836806079</v>
+        <v>9.792296222678097</v>
       </c>
       <c r="AC40" t="n">
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.542489855515952</v>
+        <v>4.264384367197138</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4865,7 +4877,7 @@
         <v>46281</v>
       </c>
       <c r="C41" t="n">
-        <v>171.91499329</v>
+        <v>174.33999634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,7 +4894,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.29: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -4893,22 +4909,22 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>4.475837194461851</v>
+        <v>5.949555216371061</v>
       </c>
       <c r="L41" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M41" t="n">
-        <v>73.91304347826087</v>
+        <v>85.29411764705883</v>
       </c>
       <c r="N41" t="n">
-        <v>20.41113424164209</v>
+        <v>18.73144017189489</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>5.287502789047749</v>
+        <v>3.822993664633234</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4935,16 +4951,16 @@
         <v>23.35952775538022</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.735468628916953</v>
+        <v>7.448106993400017</v>
       </c>
       <c r="Z41" t="n">
         <v>19</v>
       </c>
       <c r="AA41" t="n">
-        <v>57.89473684210526</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="AB41" t="n">
-        <v>13.47052463739631</v>
+        <v>15.59078289161739</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -4984,7 +5000,7 @@
         <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>188.94500732</v>
+        <v>184.83999634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5044,22 +5060,22 @@
         <v>23.23057719146176</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.219946861920085</v>
+        <v>3.366037983820191</v>
       </c>
       <c r="Z42" t="n">
         <v>18</v>
       </c>
       <c r="AA42" t="n">
-        <v>38.88888888888889</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB42" t="n">
-        <v>10.24757937337741</v>
+        <v>9.671932415068611</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>8.888487968119129</v>
+        <v>6.865041935328131</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5093,7 +5109,7 @@
         <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>53.29499817</v>
+        <v>52.29999924</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,25 +5134,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>12.90936225399626</v>
+        <v>14.7204727843671</v>
       </c>
       <c r="K43" t="n">
-        <v>1.215457990368596</v>
+        <v>1.435216932384642</v>
       </c>
       <c r="L43" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>62.26415094339622</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>13.31719995476874</v>
+        <v>13.73733484516358</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.751103502289509</v>
+        <v>2.528493697928424</v>
       </c>
       <c r="Q43" t="n">
         <v>43</v>
@@ -5163,16 +5179,16 @@
         <v>21.13804700802859</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.85081213864948</v>
+        <v>13.49652656991076</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>33.33333333333334</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.722883500149905</v>
+        <v>13.55932437400208</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5212,7 +5228,7 @@
         <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>36.71500015</v>
+        <v>36.84999847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,16 +5256,16 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>7.700205304927232</v>
+        <v>8.096210935334947</v>
       </c>
       <c r="L44" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M44" t="n">
-        <v>72.97297297297297</v>
+        <v>73.52941176470588</v>
       </c>
       <c r="N44" t="n">
-        <v>17.9931486750642</v>
+        <v>18.54090843862751</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
@@ -5282,7 +5298,7 @@
         <v>44.25503404501885</v>
       </c>
       <c r="Y44" t="n">
-        <v>13.22382661033697</v>
+        <v>12.90475708627943</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -5327,7 +5343,7 @@
         <v>46281</v>
       </c>
       <c r="C45" t="n">
-        <v>26.375</v>
+        <v>25.86000061</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5387,22 +5403,22 @@
         <v>19.42350872558167</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.060899753476464</v>
+        <v>3.973262858087212</v>
       </c>
       <c r="Z45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA45" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.737221561477718</v>
+        <v>8.42106677079321</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>6.06407474805687</v>
+        <v>4.193349958316173</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5436,7 +5452,7 @@
         <v>46281</v>
       </c>
       <c r="C46" t="n">
-        <v>360.99990845</v>
+        <v>358.07998657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,16 +5512,16 @@
         <v>21.71653838636141</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.999400994076431</v>
+        <v>6.759718100385381</v>
       </c>
       <c r="Z46" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA46" t="n">
-        <v>26.92307692307692</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.70050568701519</v>
+        <v>13.2367251271195</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5545,7 +5561,7 @@
         <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>71.83000183</v>
+        <v>70.97000122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5564,7 +5580,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.38: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -5577,22 +5593,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>3.740618212087266</v>
+        <v>2.498560678031758</v>
       </c>
       <c r="L47" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M47" t="n">
-        <v>74.19354838709677</v>
+        <v>78.37837837837837</v>
       </c>
       <c r="N47" t="n">
-        <v>14.53212474585712</v>
+        <v>13.751570603264</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2500291519204723</v>
+        <v>1.464839420218356</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5619,17 +5635,13 @@
         <v>23.42098914682247</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.79062259906432</v>
+        <v>13.83475619020674</v>
       </c>
       <c r="Z47" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>13.43868584457045</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>4</v>
       </c>
@@ -5668,7 +5680,7 @@
         <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>378.82998657</v>
+        <v>375.26000977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5696,22 +5708,22 @@
         <v>10.39403223569868</v>
       </c>
       <c r="K48" t="n">
-        <v>1.391746278961215</v>
+        <v>0.4362617746729303</v>
       </c>
       <c r="L48" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M48" t="n">
-        <v>46.42857142857143</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N48" t="n">
-        <v>11.93885027906669</v>
+        <v>11.43449717362419</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>6.517546016869424</v>
+        <v>7.530883857760662</v>
       </c>
       <c r="Q48" t="n">
         <v>26</v>
@@ -5777,7 +5789,7 @@
         <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>370.69500732</v>
+        <v>370.92999268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5876,7 +5888,7 @@
         <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>50.57500076</v>
+        <v>49.75999832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5936,16 +5948,16 @@
         <v>14.59303171015847</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.119213177436807</v>
+        <v>3.696535547990321</v>
       </c>
       <c r="Z50" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="n">
-        <v>34.78260869565217</v>
+        <v>40</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.51837670917653</v>
+        <v>9.198215711733816</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
@@ -5985,7 +5997,7 @@
         <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>28.05500031</v>
+        <v>28.06999969</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6045,16 +6057,16 @@
         <v>13.33072658586623</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.225248249113732</v>
+        <v>3.173508407378645</v>
       </c>
       <c r="Z51" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA51" t="n">
-        <v>50</v>
+        <v>49.0566037735849</v>
       </c>
       <c r="AB51" t="n">
-        <v>14.04164998977432</v>
+        <v>14.27494710745987</v>
       </c>
       <c r="AC51" t="n">
         <v>3</v>
@@ -6094,7 +6106,7 @@
         <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>88.23999786</v>
+        <v>87.05000305</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6154,22 +6166,22 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.076530152448898</v>
+        <v>5.370143412241624</v>
       </c>
       <c r="Z52" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>26.08695652173913</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.937568094511763</v>
+        <v>9.913514658355945</v>
       </c>
       <c r="AC52" t="n">
         <v>6</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.005212958421987</v>
+        <v>0.6656002771960878</v>
       </c>
       <c r="AE52" t="n">
         <v>28</v>
@@ -6203,7 +6215,7 @@
         <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>108.19999695</v>
+        <v>107.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6231,16 +6243,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>5.922658178544626</v>
+        <v>5.237394410051754</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>45.45454545454545</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N53" t="n">
-        <v>9.139762072655046</v>
+        <v>10.22726737744266</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -6312,7 +6324,7 @@
         <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>164.58000183</v>
+        <v>163.32000732</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6372,22 +6384,22 @@
         <v>12.2328853696368</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.982785650904873</v>
+        <v>3.725531768878654</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="n">
-        <v>41.66666666666666</v>
+        <v>35</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.33019873573315</v>
+        <v>12.58665447699926</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.079233425355453</v>
+        <v>1.32378631067771</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6421,7 +6433,7 @@
         <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>29176.00195312</v>
+        <v>28945.06054688</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>332.41000366</v>
+        <v>335.98001099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         <v>65</v>
       </c>
       <c r="S2" t="n">
-        <v>33.62893143649723</v>
+        <v>33.68741096866097</v>
       </c>
       <c r="T2" t="n">
-        <v>31.37106856350277</v>
+        <v>31.31258903133903</v>
       </c>
       <c r="U2" t="n">
         <v>43.28542766852362</v>
@@ -727,25 +727,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>11.8607954991482</v>
+        <v>11.92067927850626</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.133185874182119</v>
+        <v>0.1248462894220204</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.803360299429047</v>
+        <v>11.26791998397711</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.945519774794374</v>
+        <v>7.884997837799479</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" t="n">
-        <v>512.5</v>
+        <v>550.2620239300001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,25 +836,25 @@
         <v>67.74193548387096</v>
       </c>
       <c r="X3" t="n">
-        <v>19.69353007945516</v>
+        <v>25.18047285130534</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.797534376481747</v>
+        <v>0.2099958318320438</v>
       </c>
       <c r="Z3" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>42.5925925925926</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.48418530648395</v>
+        <v>12.82985053283794</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.265853658536587</v>
+        <v>4.800084144796468</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>245.96000671</v>
+        <v>251.28999329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>13.61080813594433</v>
+        <v>12.7936066701423</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6794939170181813</v>
+        <v>2.861232154208948</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>62.16216216216216</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="N4" t="n">
-        <v>10.7409930297991</v>
+        <v>12.48992280296793</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>7.271099404825687</v>
+        <v>4.995825675203891</v>
       </c>
       <c r="Q4" t="n">
         <v>23</v>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>339.51000977</v>
+        <v>348.1000061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1026,10 +1026,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>22.39625430606883</v>
+        <v>22.3973403666333</v>
       </c>
       <c r="K5" t="n">
-        <v>1.100402254588917</v>
+        <v>3.65981019901116</v>
       </c>
       <c r="L5" t="n">
         <v>13</v>
@@ -1038,13 +1038,13 @@
         <v>92.30769230769231</v>
       </c>
       <c r="N5" t="n">
-        <v>13.10451646294336</v>
+        <v>13.18405045400497</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.878922044867393</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>45</v>
@@ -1053,10 +1053,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="S5" t="n">
-        <v>42.71754788026136</v>
+        <v>43.11818591325233</v>
       </c>
       <c r="T5" t="n">
-        <v>12.8380076752942</v>
+        <v>12.43736964230322</v>
       </c>
       <c r="U5" t="n">
         <v>41.17613449352105</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>201.96000671</v>
+        <v>199.72000122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>18.27947768013144</v>
+        <v>18.03885738249209</v>
       </c>
       <c r="K6" t="n">
-        <v>2.507360843028983</v>
+        <v>1.375568136398497</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>65.625</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="N6" t="n">
-        <v>13.31625689221774</v>
+        <v>13.19831138342355</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>5.358287553009955</v>
+        <v>6.534544748186755</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1162,10 +1162,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="S6" t="n">
-        <v>39.83991681054992</v>
+        <v>39.94574227163854</v>
       </c>
       <c r="T6" t="n">
-        <v>6.826749856116749</v>
+        <v>6.720924395028128</v>
       </c>
       <c r="U6" t="n">
         <v>30.23238890769975</v>
@@ -1194,10 +1194,10 @@
         <v>54.28571428571428</v>
       </c>
       <c r="AG6" t="n">
-        <v>20.74085310114722</v>
+        <v>20.77380689850194</v>
       </c>
       <c r="AH6" t="n">
-        <v>33.54486118456707</v>
+        <v>33.51190738721235</v>
       </c>
       <c r="AI6" t="n">
         <v>38.18972506848375</v>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>57.90000153</v>
+        <v>58.47499847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,22 +1247,22 @@
         <v>12.34095145691251</v>
       </c>
       <c r="K7" t="n">
-        <v>1.259183658790719</v>
+        <v>2.26477466418189</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>52.63157894736842</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="N7" t="n">
-        <v>11.12502980176296</v>
+        <v>11.38047269758389</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.719168848008135</v>
+        <v>0.7189428991873914</v>
       </c>
       <c r="Q7" t="n">
         <v>24</v>
@@ -1271,10 +1271,10 @@
         <v>54.16666666666666</v>
       </c>
       <c r="S7" t="n">
-        <v>41.22617967332123</v>
+        <v>41.45667989417989</v>
       </c>
       <c r="T7" t="n">
-        <v>12.94048699334543</v>
+        <v>12.70998677248677</v>
       </c>
       <c r="U7" t="n">
         <v>35.07486535891948</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>132.94999695</v>
+        <v>133.63000488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         <v>57.69230769230769</v>
       </c>
       <c r="S8" t="n">
-        <v>30.99643583167292</v>
+        <v>31.09258967782676</v>
       </c>
       <c r="T8" t="n">
-        <v>26.69587186063478</v>
+        <v>26.59971801448093</v>
       </c>
       <c r="U8" t="n">
         <v>38.94861374659171</v>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>782.7199707</v>
+        <v>800.85998535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>14.83129006708122</v>
+        <v>13.12294737246159</v>
       </c>
       <c r="K9" t="n">
-        <v>1.468771417159287</v>
+        <v>3.820372333101996</v>
       </c>
       <c r="L9" t="n">
         <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>56.25</v>
+        <v>37.5</v>
       </c>
       <c r="N9" t="n">
-        <v>10.64486250369917</v>
+        <v>12.21480014003237</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.465638560076668</v>
+        <v>2.099421932243506</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1479,10 +1479,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="S9" t="n">
-        <v>33.65644841956241</v>
+        <v>33.82886221266585</v>
       </c>
       <c r="T9" t="n">
-        <v>18.06768951147208</v>
+        <v>17.89527571836863</v>
       </c>
       <c r="U9" t="n">
         <v>34.43102188199472</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>132.53999329</v>
+        <v>131.80999756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         <v>63.26530612244898</v>
       </c>
       <c r="X10" t="n">
-        <v>23.45915461234785</v>
+        <v>23.26572884665414</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.411525309195332</v>
+        <v>6.926986229372211</v>
       </c>
       <c r="Z10" t="n">
         <v>8</v>
@@ -1611,7 +1611,7 @@
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.834312614518165</v>
+        <v>3.30172371789853</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>250.53999329</v>
+        <v>243.25999451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,22 +1705,22 @@
         <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.609011982827163</v>
+        <v>9.322695614330435</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.38095238095238</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.615392882506303</v>
+        <v>9.182546694266328</v>
       </c>
       <c r="AC11" t="n">
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.630958499496006</v>
+        <v>0.7469392592316715</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>107.73999786</v>
+        <v>110.80999756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,22 +1782,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3539467658727036</v>
+        <v>3.213484473172268</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>47.05882352941177</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N12" t="n">
-        <v>8.710752460045491</v>
+        <v>11.35023269647337</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>7.619085726608898</v>
+        <v>4.637490489987162</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1838,10 +1838,10 @@
         <v>26.66666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.687830687830687</v>
+        <v>6.521164021164021</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.97883597883598</v>
+        <v>20.14550264550265</v>
       </c>
       <c r="AI12" t="n">
         <v>10.89745332569237</v>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>91.72000122</v>
+        <v>91.36000061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>211.53999329</v>
+        <v>210.25540161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>36.36363636363637</v>
       </c>
       <c r="S14" t="n">
-        <v>23.75601456839597</v>
+        <v>23.86965093203234</v>
       </c>
       <c r="T14" t="n">
-        <v>12.60762179524039</v>
+        <v>12.49398543160403</v>
       </c>
       <c r="U14" t="n">
         <v>19.73320467036612</v>
@@ -2022,22 +2022,22 @@
         <v>17.16791547737358</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.865279421873634</v>
+        <v>3.455136932754466</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>27.77777777777778</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.736178955181336</v>
+        <v>8.216864098805654</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.345180524185313</v>
+        <v>6.779089906302826</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2046,10 +2046,10 @@
         <v>50</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.86226655348048</v>
+        <v>13.13377192982456</v>
       </c>
       <c r="AH14" t="n">
-        <v>37.13773344651953</v>
+        <v>36.86622807017544</v>
       </c>
       <c r="AI14" t="n">
         <v>29.92980081982123</v>
@@ -2068,14 +2068,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>106.98999786</v>
+        <v>105.625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2127,27 +2127,17 @@
       <c r="W15" t="n">
         <v>55.55555555555556</v>
       </c>
-      <c r="X15" t="n">
-        <v>12.21787542570352</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>4.362210396030397</v>
-      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12.14919448128582</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" t="n">
-        <v>5.894939257081699</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>13.35000038</v>
+        <v>13.72999954</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,22 +2198,22 @@
         <v>10.17760031008306</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5209183709467</v>
+        <v>4.410645906923616</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>59.57446808510638</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>12.30838893360362</v>
+        <v>13.99715724409568</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.411979029471746</v>
+        <v>1.522214597248261</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2232,10 +2222,10 @@
         <v>55</v>
       </c>
       <c r="S16" t="n">
-        <v>42.05366124976899</v>
+        <v>42.24116124976899</v>
       </c>
       <c r="T16" t="n">
-        <v>12.94633875023101</v>
+        <v>12.75883875023101</v>
       </c>
       <c r="U16" t="n">
         <v>39.82909179893205</v>
@@ -2264,10 +2254,10 @@
         <v>39.47368421052632</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.65709811055487</v>
+        <v>16.393387363098</v>
       </c>
       <c r="AH16" t="n">
-        <v>22.81658609997145</v>
+        <v>23.08029684742832</v>
       </c>
       <c r="AI16" t="n">
         <v>25.5980757481601</v>
@@ -2286,10 +2276,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C17" t="n">
-        <v>312.8999939</v>
+        <v>317.20001221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2317,22 +2307,22 @@
         <v>21.09865479945756</v>
       </c>
       <c r="K17" t="n">
-        <v>1.988268041971186</v>
+        <v>3.389838602965889</v>
       </c>
       <c r="L17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>55.55555555555556</v>
+        <v>43.75</v>
       </c>
       <c r="N17" t="n">
-        <v>14.45597755919411</v>
+        <v>15.64398184173933</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.89453284524335</v>
+        <v>4.459008215244342</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2395,10 +2385,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>84.29000092</v>
+        <v>87.23500061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,10 +2462,10 @@
         <v>48.48484848484848</v>
       </c>
       <c r="AG18" t="n">
-        <v>27.58140846903048</v>
+        <v>27.36676200438402</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.903440015818</v>
+        <v>21.11808648046447</v>
       </c>
       <c r="AI18" t="n">
         <v>32.5040421081337</v>
@@ -2494,19 +2484,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>342.86999512</v>
+        <v>345.30999756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2521,27 +2511,17 @@
       <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
-        <v>14.75759965099349</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.61646590011251</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>22</v>
-      </c>
-      <c r="M19" t="n">
-        <v>31.81818181818182</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10.74288699811014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>5</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.3666096886255854</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>23</v>
       </c>
@@ -2581,10 +2561,10 @@
         <v>55</v>
       </c>
       <c r="AG19" t="n">
-        <v>20.0562406121869</v>
+        <v>20.18695956643527</v>
       </c>
       <c r="AH19" t="n">
-        <v>34.9437593878131</v>
+        <v>34.81304043356473</v>
       </c>
       <c r="AI19" t="n">
         <v>34.20853424503424</v>
@@ -2603,10 +2583,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>937.97998047</v>
+        <v>953.34997559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,25 +2611,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>13.4458321963166</v>
+        <v>13.67364833892672</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6016777218157854</v>
+        <v>3.40021427223427</v>
       </c>
       <c r="L20" t="n">
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>62.85714285714285</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N20" t="n">
-        <v>11.4634541192612</v>
+        <v>11.07561194828861</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>9.342112866320695</v>
+        <v>6.382758270103461</v>
       </c>
       <c r="Q20" t="n">
         <v>30</v>
@@ -2658,10 +2638,10 @@
         <v>40</v>
       </c>
       <c r="S20" t="n">
-        <v>33.84189231248055</v>
+        <v>33.75855897914722</v>
       </c>
       <c r="T20" t="n">
-        <v>6.158107687519454</v>
+        <v>6.241441020852783</v>
       </c>
       <c r="U20" t="n">
         <v>24.59062811680185</v>
@@ -2712,10 +2692,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>34.50999832</v>
+        <v>33.92499924</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,25 +2720,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>10.36521163425277</v>
+        <v>11.15344873147072</v>
       </c>
       <c r="K21" t="n">
-        <v>1.157838547701351</v>
+        <v>0.3253012404454525</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M21" t="n">
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>12.39027390591968</v>
+        <v>13.01999238341612</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.763847024145542</v>
+        <v>7.64981382030534</v>
       </c>
       <c r="Q21" t="n">
         <v>47</v>
@@ -2767,10 +2747,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S21" t="n">
-        <v>35.11399882983314</v>
+        <v>34.91129612713043</v>
       </c>
       <c r="T21" t="n">
-        <v>26.58812882974133</v>
+        <v>26.79083153244403</v>
       </c>
       <c r="U21" t="n">
         <v>47.42656695641357</v>
@@ -2782,19 +2762,19 @@
         <v>71.23287671232876</v>
       </c>
       <c r="X21" t="n">
-        <v>19.98739658862876</v>
+        <v>19.79855467084246</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.327385502403629</v>
+        <v>10.86442979810119</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
-        <v>37.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB21" t="n">
-        <v>18.20433957561407</v>
+        <v>17.49852906802476</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -2831,10 +2811,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>302.47000122</v>
+        <v>304.29998779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,22 +2842,22 @@
         <v>15.59604487521503</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.6050142369883993</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>41.1764705882353</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>8.655085078351195</v>
+        <v>8.29913836654338</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>10.00000000000001</v>
+        <v>9.338486589625127</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2886,10 +2866,10 @@
         <v>17.39130434782609</v>
       </c>
       <c r="S22" t="n">
-        <v>26.91599626382235</v>
+        <v>27.02469191599626</v>
       </c>
       <c r="T22" t="n">
-        <v>-9.524691915996268</v>
+        <v>-9.633387568170178</v>
       </c>
       <c r="U22" t="n">
         <v>6.978653563062565</v>
@@ -2940,24 +2920,24 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>101.05000305</v>
+        <v>111.09500122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2967,12 +2947,8 @@
       <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
-        <v>20.85153887202731</v>
-      </c>
-      <c r="K23" t="n">
-        <v>18.68687311955595</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
@@ -2981,9 +2957,7 @@
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
         <v>36</v>
       </c>
@@ -3006,25 +2980,25 @@
         <v>68.96551724137932</v>
       </c>
       <c r="X23" t="n">
-        <v>25.31125581911988</v>
+        <v>30.53793773347595</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.286342919686227</v>
+        <v>0.04048782638741422</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>47.36842105263158</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.86213491611809</v>
+        <v>13.40755227567588</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.960305858845379</v>
       </c>
       <c r="AE23" t="n">
         <v>47</v>
@@ -3033,10 +3007,10 @@
         <v>44.68085106382978</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.62755702677315</v>
+        <v>19.42576709094066</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.05329403705663</v>
+        <v>25.25508397288912</v>
       </c>
       <c r="AI23" t="n">
         <v>31.41096626549528</v>
@@ -3055,10 +3029,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C24" t="n">
-        <v>267.27999878</v>
+        <v>268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,25 +3089,25 @@
         <v>40</v>
       </c>
       <c r="X24" t="n">
-        <v>10.45310094410821</v>
+        <v>10.17168889008249</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.906254022436462</v>
+        <v>4.650089650127532</v>
       </c>
       <c r="Z24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>11.11111111111111</v>
+        <v>12.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.966186301970189</v>
+        <v>6.300018693230369</v>
       </c>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.15017656137093</v>
+        <v>1.415743701194028</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3164,10 +3138,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>348.92001343</v>
+        <v>350.33999634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,10 +3237,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>30.72999954</v>
+        <v>31.23010063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,10 +3336,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C27" t="n">
-        <v>87.87000275</v>
+        <v>88.08999634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3407,10 +3381,10 @@
         <v>20</v>
       </c>
       <c r="S27" t="n">
-        <v>9.726190476190476</v>
+        <v>9.75</v>
       </c>
       <c r="T27" t="n">
-        <v>10.27380952380952</v>
+        <v>10.25</v>
       </c>
       <c r="U27" t="n">
         <v>5.668215145437519</v>
@@ -3461,10 +3435,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>567.75</v>
+        <v>566.76898193</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,10 +3534,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>248.55999756</v>
+        <v>249.21499634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,7 +3565,7 @@
         <v>10.971007588959</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2945550274824127</v>
+        <v>0.5588486058076381</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
@@ -3606,7 +3580,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.700436252048054</v>
+        <v>1.433142298438295</v>
       </c>
       <c r="Q29" t="n">
         <v>16</v>
@@ -3615,10 +3589,10 @@
         <v>37.5</v>
       </c>
       <c r="S29" t="n">
-        <v>19.11747685185185</v>
+        <v>19.19039351851852</v>
       </c>
       <c r="T29" t="n">
-        <v>18.38252314814815</v>
+        <v>18.30960648148148</v>
       </c>
       <c r="U29" t="n">
         <v>18.48123255886363</v>
@@ -3669,10 +3643,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>673.3099975600001</v>
+        <v>679.47357178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,46 +3682,46 @@
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>63.63636363636363</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="S30" t="n">
-        <v>62.60612073112073</v>
+        <v>62.49281113411548</v>
       </c>
       <c r="T30" t="n">
-        <v>1.030242905242908</v>
+        <v>2.72458017023235</v>
       </c>
       <c r="U30" t="n">
-        <v>42.95170809013101</v>
+        <v>44.890335377263</v>
       </c>
       <c r="V30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W30" t="n">
-        <v>59.45945945945946</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="X30" t="n">
         <v>27.55411108915111</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.751032385741513</v>
+        <v>0.851647546479728</v>
       </c>
       <c r="Z30" t="n">
         <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>11.76470588235294</v>
+        <v>29.41176470588235</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.37174574117448</v>
+        <v>8.863991608210943</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.324694414032559</v>
+        <v>5.192574890171542</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3778,10 +3752,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>202.41999817</v>
+        <v>203.67500305</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,10 +3851,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>490.29998779</v>
+        <v>495.72750854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,24 +3950,24 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>926.54998779</v>
+        <v>975.63201904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -4007,22 +3981,22 @@
         <v>13.41136277305126</v>
       </c>
       <c r="K33" t="n">
-        <v>2.65344702500625</v>
+        <v>8.091296856313491</v>
       </c>
       <c r="L33" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>70.37037037037037</v>
+        <v>62</v>
       </c>
       <c r="N33" t="n">
-        <v>14.34329319244495</v>
+        <v>12.32856328088578</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.260049293988665</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>55</v>
@@ -4049,16 +4023,16 @@
         <v>26.04595216565901</v>
       </c>
       <c r="Y33" t="n">
-        <v>11.11377915455933</v>
+        <v>6.405219091182457</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>31.25</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.77119477123058</v>
+        <v>12.30544998332289</v>
       </c>
       <c r="AC33" t="n">
         <v>4</v>
@@ -4095,10 +4069,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>76.41000366</v>
+        <v>75.68499756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4126,22 +4100,22 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>1.839270828254169</v>
+        <v>0.8729825278560366</v>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M34" t="n">
-        <v>56.81818181818182</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N34" t="n">
-        <v>10.813648521222</v>
+        <v>10.19718509946021</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>8.013342107985455</v>
+        <v>9.048029753282606</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4150,10 +4124,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="S34" t="n">
-        <v>44.63817137303297</v>
+        <v>44.1753221501577</v>
       </c>
       <c r="T34" t="n">
-        <v>17.12653450931997</v>
+        <v>17.58938373219524</v>
       </c>
       <c r="U34" t="n">
         <v>45.0410173444307</v>
@@ -4168,13 +4142,13 @@
         <v>14.39517840252906</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.600472418166538</v>
+        <v>9.467704611071637</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA34" t="n">
-        <v>41.66666666666666</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
         <v>10.35058875984423</v>
@@ -4183,7 +4157,7 @@
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.531219710715037</v>
+        <v>0.5879618832612232</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4214,10 +4188,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C35" t="n">
-        <v>35.77999878</v>
+        <v>35.85499954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,10 +4216,10 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>16.1350871679738</v>
+        <v>16.20544078061254</v>
       </c>
       <c r="K35" t="n">
-        <v>0.05592970061414348</v>
+        <v>0.3498460722342278</v>
       </c>
       <c r="L35" t="n">
         <v>22</v>
@@ -4254,13 +4228,13 @@
         <v>50</v>
       </c>
       <c r="N35" t="n">
-        <v>8.99945789332031</v>
+        <v>8.707038735216463</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.942983594478487</v>
+        <v>1.644401055262157</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4269,10 +4243,10 @@
         <v>37.93103448275862</v>
       </c>
       <c r="S35" t="n">
-        <v>29.46138715915592</v>
+        <v>29.4646525719041</v>
       </c>
       <c r="T35" t="n">
-        <v>8.469647323602697</v>
+        <v>8.466381910854523</v>
       </c>
       <c r="U35" t="n">
         <v>22.68802210080984</v>
@@ -4301,10 +4275,10 @@
         <v>48.14814814814815</v>
       </c>
       <c r="AG35" t="n">
-        <v>13.12799556664199</v>
+        <v>13.24982544337383</v>
       </c>
       <c r="AH35" t="n">
-        <v>35.02015258150615</v>
+        <v>34.89832270477432</v>
       </c>
       <c r="AI35" t="n">
         <v>30.74322697621846</v>
@@ -4323,10 +4297,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>213.8999939</v>
+        <v>218.8999939</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,16 +4328,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K36" t="n">
-        <v>2.378787820862138</v>
+        <v>4.771933934478323</v>
       </c>
       <c r="L36" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>65.15151515151516</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N36" t="n">
-        <v>12.75720590321936</v>
+        <v>11.43839929995689</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4372,19 +4346,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R36" t="n">
-        <v>64.58333333333333</v>
+        <v>63.82978723404256</v>
       </c>
       <c r="S36" t="n">
-        <v>65.71674320102495</v>
+        <v>67.34353935322912</v>
       </c>
       <c r="T36" t="n">
-        <v>-1.133409867691626</v>
+        <v>-3.513752119186563</v>
       </c>
       <c r="U36" t="n">
-        <v>50.43905701034311</v>
+        <v>49.53589653479511</v>
       </c>
       <c r="V36" t="n">
         <v>76</v>
@@ -4396,16 +4370,16 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.885670939607838</v>
+        <v>6.755836164975049</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>34.375</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.57975726743594</v>
+        <v>11.49356344987565</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4442,24 +4416,24 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>143.16000366</v>
+        <v>150.99299622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4473,22 +4447,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K37" t="n">
-        <v>2.99280838848921</v>
+        <v>8.628054834532373</v>
       </c>
       <c r="L37" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M37" t="n">
-        <v>50</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N37" t="n">
-        <v>11.83848525057088</v>
+        <v>9.514910927130867</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.861690529520901</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>33</v>
@@ -4497,10 +4471,10 @@
         <v>63.63636363636363</v>
       </c>
       <c r="S37" t="n">
-        <v>25.46536354715698</v>
+        <v>25.46730604909948</v>
       </c>
       <c r="T37" t="n">
-        <v>38.17100008920665</v>
+        <v>38.16905758726415</v>
       </c>
       <c r="U37" t="n">
         <v>46.6161783022664</v>
@@ -4515,13 +4489,17 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y37" t="n">
-        <v>16.13356401996117</v>
+        <v>11.54481609965841</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>10.3153604625776</v>
+      </c>
       <c r="AC37" t="n">
         <v>10</v>
       </c>
@@ -4557,10 +4535,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>59.36000061</v>
+        <v>58.875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4617,25 +4595,25 @@
         <v>69.62025316455696</v>
       </c>
       <c r="X38" t="n">
-        <v>18.84085098446007</v>
+        <v>15.6720464761638</v>
       </c>
       <c r="Y38" t="n">
-        <v>6.915477212151178</v>
+        <v>7.676023874377114</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AA38" t="n">
-        <v>46.66666666666666</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.07875313925385</v>
+        <v>12.40972030963657</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.31367954141939</v>
+        <v>2.517196749044592</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4666,10 +4644,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>134.33999634</v>
+        <v>133.625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,10 +4689,10 @@
         <v>31.25</v>
       </c>
       <c r="S39" t="n">
-        <v>16.15873015873016</v>
+        <v>16.17361111111111</v>
       </c>
       <c r="T39" t="n">
-        <v>15.09126984126984</v>
+        <v>15.07638888888889</v>
       </c>
       <c r="U39" t="n">
         <v>14.16464385478204</v>
@@ -4765,10 +4743,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>27.45999908</v>
+        <v>27.69499969</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,25 +4803,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X40" t="n">
-        <v>15.45454528638159</v>
+        <v>13.1731874460205</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.991099127415655</v>
+        <v>5.186578013408139</v>
       </c>
       <c r="Z40" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>36.36363636363637</v>
+        <v>20</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.792296222678097</v>
+        <v>11.43386932212815</v>
       </c>
       <c r="AC40" t="n">
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.264384367197138</v>
+        <v>5.076730578580479</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4874,10 +4852,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C41" t="n">
-        <v>174.33999634</v>
+        <v>176.72000122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,7 +4887,7 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>5.949555216371061</v>
+        <v>7.395927040063355</v>
       </c>
       <c r="L41" t="n">
         <v>34</v>
@@ -4918,13 +4896,13 @@
         <v>85.29411764705883</v>
       </c>
       <c r="N41" t="n">
-        <v>18.73144017189489</v>
+        <v>20.2111712418399</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>3.822993664633234</v>
+        <v>2.424740892608734</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4951,16 +4929,16 @@
         <v>23.35952775538022</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.448106993400017</v>
+        <v>6.184633541333606</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA41" t="n">
-        <v>63.1578947368421</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.59078289161739</v>
+        <v>15.4096485600858</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -4997,10 +4975,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>184.83999634</v>
+        <v>190.16499329</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,10 +5020,10 @@
         <v>46.34146341463415</v>
       </c>
       <c r="S42" t="n">
-        <v>45.26235839664509</v>
+        <v>45.5986295839237</v>
       </c>
       <c r="T42" t="n">
-        <v>1.079105017989058</v>
+        <v>0.7428338307104454</v>
       </c>
       <c r="U42" t="n">
         <v>32.05623397633605</v>
@@ -5057,25 +5035,25 @@
         <v>51.02040816326531</v>
       </c>
       <c r="X42" t="n">
-        <v>23.23057719146176</v>
+        <v>23.63097048814724</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.366037983820191</v>
+        <v>0.9041170740756277</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>44.44444444444444</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.671932415068611</v>
+        <v>10.41975609405634</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.865041935328131</v>
+        <v>9.178870662794015</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5106,10 +5084,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>52.29999924</v>
+        <v>52.20999908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,22 +5115,22 @@
         <v>14.7204727843671</v>
       </c>
       <c r="K43" t="n">
-        <v>1.435216932384642</v>
+        <v>1.260662708938942</v>
       </c>
       <c r="L43" t="n">
         <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>64.58333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="N43" t="n">
-        <v>13.73733484516358</v>
+        <v>13.86208026393347</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.528493697928424</v>
+        <v>2.705233422118658</v>
       </c>
       <c r="Q43" t="n">
         <v>43</v>
@@ -5161,10 +5139,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S43" t="n">
-        <v>36.50226336272848</v>
+        <v>36.2697052231936</v>
       </c>
       <c r="T43" t="n">
-        <v>14.66052733494594</v>
+        <v>14.89308547448082</v>
       </c>
       <c r="U43" t="n">
         <v>36.75230846944931</v>
@@ -5176,16 +5154,16 @@
         <v>60</v>
       </c>
       <c r="X43" t="n">
-        <v>21.13804700802859</v>
+        <v>20.24662002189492</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.49652656991076</v>
+        <v>13.64538558640017</v>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="n">
-        <v>16.66666666666667</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB43" t="n">
         <v>13.55932437400208</v>
@@ -5225,24 +5203,24 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C44" t="n">
-        <v>36.84999847</v>
+        <v>40.68500137</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5256,17 +5234,13 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>8.096210935334947</v>
+        <v>19.34585271628402</v>
       </c>
       <c r="L44" t="n">
-        <v>34</v>
-      </c>
-      <c r="M44" t="n">
-        <v>73.52941176470588</v>
-      </c>
-      <c r="N44" t="n">
-        <v>18.54090843862751</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>6</v>
       </c>
@@ -5298,18 +5272,22 @@
         <v>44.25503404501885</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.90475708627943</v>
+        <v>3.84069947384168</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>8.837765829123923</v>
+      </c>
       <c r="AC44" t="n">
         <v>8</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>4.325427185305763</v>
       </c>
       <c r="AE44" t="n">
         <v>77</v>
@@ -5340,10 +5318,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C45" t="n">
-        <v>25.86000061</v>
+        <v>25.44499969</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5400,25 +5378,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X45" t="n">
-        <v>19.42350872558167</v>
+        <v>16.02758025615572</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.973262858087212</v>
+        <v>5.514298562590703</v>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>33.33333333333334</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.42106677079321</v>
+        <v>13.30536041648421</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.193349958316173</v>
+        <v>2.630769946769052</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5449,10 +5427,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>358.07998657</v>
+        <v>367.73901367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5503,25 +5481,25 @@
         <v>55.72900614018867</v>
       </c>
       <c r="V46" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W46" t="n">
-        <v>75.22935779816514</v>
+        <v>75</v>
       </c>
       <c r="X46" t="n">
         <v>21.71653838636141</v>
       </c>
       <c r="Y46" t="n">
-        <v>6.759718100385381</v>
+        <v>4.244608506278091</v>
       </c>
       <c r="Z46" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="AA46" t="n">
-        <v>34.78260869565217</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB46" t="n">
-        <v>13.2367251271195</v>
+        <v>12.82889531085061</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5558,10 +5536,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>70.97000122</v>
+        <v>70.94000244</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5580,7 +5558,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.38: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.68: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -5593,22 +5571,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>2.498560678031758</v>
+        <v>2.455234882354174</v>
       </c>
       <c r="L47" t="n">
         <v>37</v>
       </c>
       <c r="M47" t="n">
-        <v>78.37837837837837</v>
+        <v>75.67567567567568</v>
       </c>
       <c r="N47" t="n">
-        <v>13.751570603264</v>
+        <v>14.04937287242685</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.464839420218356</v>
+        <v>1.507746402045362</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5632,16 +5610,20 @@
         <v>57.89473684210526</v>
       </c>
       <c r="X47" t="n">
-        <v>23.42098914682247</v>
+        <v>20.8229427476307</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.83475619020674</v>
+        <v>13.87117794796723</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>9.57591789254208</v>
+      </c>
       <c r="AC47" t="n">
         <v>4</v>
       </c>
@@ -5677,10 +5659,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>375.26000977</v>
+        <v>377.95999146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,22 +5690,22 @@
         <v>10.39403223569868</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4362617746729303</v>
+        <v>1.158896909628737</v>
       </c>
       <c r="L48" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M48" t="n">
-        <v>57.69230769230769</v>
+        <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>11.43449717362419</v>
+        <v>11.54383792842054</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>7.530883857760662</v>
+        <v>6.762730021149621</v>
       </c>
       <c r="Q48" t="n">
         <v>26</v>
@@ -5786,10 +5768,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>370.92999268</v>
+        <v>370.92001343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5885,10 +5867,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>49.75999832</v>
+        <v>48.625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5930,10 +5912,10 @@
         <v>36.8421052631579</v>
       </c>
       <c r="S50" t="n">
-        <v>13.86514282116775</v>
+        <v>13.8800949742778</v>
       </c>
       <c r="T50" t="n">
-        <v>22.97696244199015</v>
+        <v>22.96201028888009</v>
       </c>
       <c r="U50" t="n">
         <v>19.14951274513507</v>
@@ -5945,19 +5927,19 @@
         <v>35</v>
       </c>
       <c r="X50" t="n">
-        <v>14.59303171015847</v>
+        <v>12.10674333226271</v>
       </c>
       <c r="Y50" t="n">
-        <v>3.696535547990321</v>
+        <v>5.893164849709532</v>
       </c>
       <c r="Z50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>40</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.198215711733816</v>
+        <v>8.125876846070605</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
@@ -5994,14 +5976,14 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C51" t="n">
-        <v>28.06999969</v>
+        <v>28.22500038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6011,7 +5993,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -6039,10 +6021,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S51" t="n">
-        <v>35.84136221329811</v>
+        <v>35.88210851239791</v>
       </c>
       <c r="T51" t="n">
-        <v>30.11608459521253</v>
+        <v>30.07533829611273</v>
       </c>
       <c r="U51" t="n">
         <v>51.67092456194193</v>
@@ -6054,25 +6036,25 @@
         <v>68.65671641791045</v>
       </c>
       <c r="X51" t="n">
-        <v>13.33072658586623</v>
+        <v>10.73338207305774</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.173508407378645</v>
+        <v>2.638838896410245</v>
       </c>
       <c r="Z51" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AA51" t="n">
-        <v>49.0566037735849</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB51" t="n">
-        <v>14.27494710745987</v>
+        <v>13.84894258070201</v>
       </c>
       <c r="AC51" t="n">
         <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>0.3709498731280458</v>
       </c>
       <c r="AE51" t="n">
         <v>47</v>
@@ -6103,10 +6085,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>87.05000305</v>
+        <v>87.58999634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,22 +6148,22 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.370143412241624</v>
+        <v>4.783130364560273</v>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>31.57894736842105</v>
+        <v>25</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.913514658355945</v>
+        <v>10.51833461074082</v>
       </c>
       <c r="AC52" t="n">
         <v>6</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.6656002771960878</v>
+        <v>1.277997943115339</v>
       </c>
       <c r="AE52" t="n">
         <v>28</v>
@@ -6212,10 +6194,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>107.5</v>
+        <v>106.58499908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6243,16 +6225,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>5.237394410051754</v>
+        <v>4.341651966297344</v>
       </c>
       <c r="L53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M53" t="n">
-        <v>41.66666666666666</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N53" t="n">
-        <v>10.22726737744266</v>
+        <v>10.30700197623545</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -6267,10 +6249,10 @@
         <v>30.76923076923077</v>
       </c>
       <c r="S53" t="n">
-        <v>25.45659801054126</v>
+        <v>25.4932280471713</v>
       </c>
       <c r="T53" t="n">
-        <v>5.31263275868951</v>
+        <v>5.276002722059474</v>
       </c>
       <c r="U53" t="n">
         <v>12.68070365571051</v>
@@ -6299,10 +6281,10 @@
         <v>23.07692307692308</v>
       </c>
       <c r="AG53" t="n">
-        <v>10.24948024948025</v>
+        <v>10.05717255717256</v>
       </c>
       <c r="AH53" t="n">
-        <v>12.82744282744283</v>
+        <v>13.01975051975052</v>
       </c>
       <c r="AI53" t="n">
         <v>8.179528718498569</v>
@@ -6321,10 +6303,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C54" t="n">
-        <v>163.32000732</v>
+        <v>162.16499329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6381,25 +6363,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X54" t="n">
-        <v>12.2328853696368</v>
+        <v>11.95142925876556</v>
       </c>
       <c r="Y54" t="n">
-        <v>3.725531768878654</v>
+        <v>4.406393614052706</v>
       </c>
       <c r="Z54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>35</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.58665447699926</v>
+        <v>14.78362049164532</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32378631067771</v>
+        <v>0.6209687116005336</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6408,10 +6390,10 @@
         <v>40.90909090909091</v>
       </c>
       <c r="AG54" t="n">
-        <v>22.20968845968846</v>
+        <v>22.32332482332482</v>
       </c>
       <c r="AH54" t="n">
-        <v>18.69940244940245</v>
+        <v>18.58576608576608</v>
       </c>
       <c r="AI54" t="n">
         <v>23.25581619647187</v>
@@ -6430,10 +6412,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>28945.06054688</v>
+        <v>29442.78515625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6507,10 +6489,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.62646142686465</v>
+        <v>12.64806280935314</v>
       </c>
       <c r="AH55" t="n">
-        <v>44.51639571599249</v>
+        <v>44.49479433350401</v>
       </c>
       <c r="AI55" t="n">
         <v>32.59064457965074</v>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>335.98001099</v>
+        <v>337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>11.92067927850626</v>
+        <v>12.56612040461789</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1248462894220204</v>
+        <v>0.3960502318660075</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -739,13 +739,13 @@
         <v>17.85714285714286</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.26791998397711</v>
+        <v>11.20753016674198</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.884997837799479</v>
+        <v>7.634184975430259</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -779,7 +779,7 @@
         <v>46282</v>
       </c>
       <c r="C3" t="n">
-        <v>550.2620239300001</v>
+        <v>545.09002686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
         <v>25.18047285130534</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2099958318320438</v>
+        <v>1.147937370095853</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>54.76190476190476</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.82985053283794</v>
+        <v>13.20277503821869</v>
       </c>
       <c r="AC3" t="n">
         <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.800084144796468</v>
+        <v>3.896795400543163</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -888,7 +888,7 @@
         <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>251.28999329</v>
+        <v>251.19000244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,22 +916,22 @@
         <v>12.7936066701423</v>
       </c>
       <c r="K4" t="n">
-        <v>2.861232154208948</v>
+        <v>2.820302621359305</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
-        <v>39.47368421052632</v>
+        <v>41.02564102564103</v>
       </c>
       <c r="N4" t="n">
-        <v>12.48992280296793</v>
+        <v>12.03005755399682</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.995825675203891</v>
+        <v>5.037621215447285</v>
       </c>
       <c r="Q4" t="n">
         <v>23</v>
@@ -997,7 +997,7 @@
         <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>348.1000061</v>
+        <v>347.29998779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>22.3973403666333</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65981019901116</v>
+        <v>3.421574793331472</v>
       </c>
       <c r="L5" t="n">
         <v>13</v>
@@ -1110,7 +1110,7 @@
         <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>199.72000122</v>
+        <v>197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1127,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1135,25 +1139,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>18.03885738249209</v>
+        <v>18.04301535154102</v>
       </c>
       <c r="K6" t="n">
-        <v>1.375568136398497</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M6" t="n">
-        <v>68.57142857142857</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>13.19831138342355</v>
+        <v>13.11151380613315</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>6.534544748186755</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q6" t="n">
         <v>30</v>
@@ -1219,7 +1223,7 @@
         <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>58.47499847</v>
+        <v>58.18000031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,7 +1251,7 @@
         <v>12.34095145691251</v>
       </c>
       <c r="K7" t="n">
-        <v>2.26477466418189</v>
+        <v>1.7488632294133</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
@@ -1256,13 +1260,13 @@
         <v>44.73684210526316</v>
       </c>
       <c r="N7" t="n">
-        <v>11.38047269758389</v>
+        <v>11.86301762781457</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7189428991873914</v>
+        <v>1.229632185438545</v>
       </c>
       <c r="Q7" t="n">
         <v>24</v>
@@ -1328,7 +1332,7 @@
         <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>133.63000488</v>
+        <v>132.69999695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1431,7 @@
         <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>800.85998535</v>
+        <v>798.5700073199999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,22 +1459,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K9" t="n">
-        <v>3.820372333101996</v>
+        <v>3.523508491658678</v>
       </c>
       <c r="L9" t="n">
         <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>37.5</v>
+        <v>40.625</v>
       </c>
       <c r="N9" t="n">
-        <v>12.21480014003237</v>
+        <v>10.32318483007037</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.099421932243506</v>
+        <v>2.392202065428317</v>
       </c>
       <c r="Q9" t="n">
         <v>29</v>
@@ -1536,7 +1540,7 @@
         <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>131.80999756</v>
+        <v>133.19000244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,22 +1600,22 @@
         <v>23.26572884665414</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.926986229372211</v>
+        <v>5.952544111343139</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>25</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.90839610674435</v>
+        <v>12.27461935461157</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.30172371789853</v>
+        <v>4.30363144905127</v>
       </c>
       <c r="AE10" t="n">
         <v>35</v>
@@ -1645,7 +1649,7 @@
         <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>243.25999451</v>
+        <v>242.8500061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1709,7 @@
         <v>19.5913144208306</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.322695614330435</v>
+        <v>9.475522403310066</v>
       </c>
       <c r="Z11" t="n">
         <v>18</v>
@@ -1720,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7469392592316715</v>
+        <v>0.5793765516401206</v>
       </c>
       <c r="AE11" t="n">
         <v>27</v>
@@ -1754,7 +1758,7 @@
         <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>110.80999756</v>
+        <v>110.23999786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,22 +1786,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K12" t="n">
-        <v>3.213484473172268</v>
+        <v>2.682560761583819</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>45.45454545454545</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N12" t="n">
-        <v>11.35023269647337</v>
+        <v>10.55625114125625</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.637490489987162</v>
+        <v>5.178522232964777</v>
       </c>
       <c r="Q12" t="n">
         <v>17</v>
@@ -1863,16 +1867,16 @@
         <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>91.36000061</v>
+        <v>90.26999664</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1887,17 +1891,27 @@
       <c r="I13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>10.72772186138614</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1164484211486405</v>
+      </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>54.54545454545455</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10.18953108880514</v>
+      </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1.881360763945628</v>
+      </c>
       <c r="Q13" t="n">
         <v>36</v>
       </c>
@@ -1962,7 +1976,7 @@
         <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>210.25540161</v>
+        <v>211.57000732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,22 +2036,22 @@
         <v>17.16791547737358</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.455136932754466</v>
+        <v>2.851497609876141</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.52941176470588</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.216864098805654</v>
+        <v>9.736178955181336</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.779089906302826</v>
+        <v>7.358324847270703</v>
       </c>
       <c r="AE14" t="n">
         <v>20</v>
@@ -2071,7 +2085,7 @@
         <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>105.625</v>
+        <v>105.34999847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2184,7 @@
         <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>13.72999954</v>
+        <v>13.60999966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,22 +2212,22 @@
         <v>10.17760031008306</v>
       </c>
       <c r="K16" t="n">
-        <v>4.410645906923616</v>
+        <v>3.498099264583865</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
         <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>13.99715724409568</v>
+        <v>12.25933510733132</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.522214597248261</v>
+        <v>2.417339789999673</v>
       </c>
       <c r="Q16" t="n">
         <v>40</v>
@@ -2279,7 +2293,7 @@
         <v>46282</v>
       </c>
       <c r="C17" t="n">
-        <v>317.20001221</v>
+        <v>313.47000122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,22 +2321,22 @@
         <v>21.09865479945756</v>
       </c>
       <c r="K17" t="n">
-        <v>3.389838602965889</v>
+        <v>2.174059222768121</v>
       </c>
       <c r="L17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>15.64398184173933</v>
+        <v>14.87370911888632</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.459008215244342</v>
+        <v>5.701976432716349</v>
       </c>
       <c r="Q17" t="n">
         <v>31</v>
@@ -2388,7 +2402,7 @@
         <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>87.23500061</v>
+        <v>86.62000275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2501,7 @@
         <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>345.30999756</v>
+        <v>347.32998657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2600,7 @@
         <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>953.34997559</v>
+        <v>951.4699707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,22 +2628,22 @@
         <v>13.67364833892672</v>
       </c>
       <c r="K20" t="n">
-        <v>3.40021427223427</v>
+        <v>3.196309186550983</v>
       </c>
       <c r="L20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>57.14285714285715</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="N20" t="n">
-        <v>11.07561194828861</v>
+        <v>12.23562624438321</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>6.382758270103461</v>
+        <v>6.592959445041591</v>
       </c>
       <c r="Q20" t="n">
         <v>30</v>
@@ -2695,7 +2709,7 @@
         <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>33.92499924</v>
+        <v>34.02999878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,22 +2737,22 @@
         <v>11.15344873147072</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3253012404454525</v>
+        <v>0.6358129785912769</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N21" t="n">
-        <v>13.01999238341612</v>
+        <v>13.44924978730225</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.64981382030534</v>
+        <v>7.317660386939329</v>
       </c>
       <c r="Q21" t="n">
         <v>47</v>
@@ -2765,7 +2779,7 @@
         <v>19.79855467084246</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.86442979810119</v>
+        <v>10.58855082747466</v>
       </c>
       <c r="Z21" t="n">
         <v>11</v>
@@ -2814,7 +2828,7 @@
         <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>304.29998779</v>
+        <v>302.51000977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2842,22 +2856,22 @@
         <v>15.59604487521503</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6050142369883993</v>
+        <v>0.01322727868504625</v>
       </c>
       <c r="L22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>44.44444444444444</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="N22" t="n">
-        <v>8.29913836654338</v>
+        <v>8.655085078351195</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.338486589625127</v>
+        <v>9.985451917761834</v>
       </c>
       <c r="Q22" t="n">
         <v>23</v>
@@ -2923,11 +2937,11 @@
         <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>111.09500122</v>
+        <v>108.80000305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2937,7 +2951,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2980,25 +2994,25 @@
         <v>68.96551724137932</v>
       </c>
       <c r="X23" t="n">
-        <v>30.53793773347595</v>
+        <v>30.80808497525172</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.04048782638741422</v>
+        <v>2.307622911502527</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
-        <v>23.07692307692308</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.40755227567588</v>
+        <v>11.96117844271113</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.960305858845379</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>47</v>
@@ -3032,7 +3046,7 @@
         <v>46282</v>
       </c>
       <c r="C24" t="n">
-        <v>268</v>
+        <v>270.22000122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,22 +3106,20 @@
         <v>10.17168889008249</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.650089650127532</v>
+        <v>3.860250406457355</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>6.300018693230369</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.415743701194028</v>
+        <v>2.225665869309035</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -3141,7 +3153,7 @@
         <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>350.33999634</v>
+        <v>349.30999756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3252,7 @@
         <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>31.23010063</v>
+        <v>31.30999947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3339,7 +3351,7 @@
         <v>46282</v>
       </c>
       <c r="C27" t="n">
-        <v>88.08999634</v>
+        <v>88.05999756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
         <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>566.76898193</v>
+        <v>565.72998047</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3549,7 @@
         <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>249.21499634</v>
+        <v>248.47999573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,7 +3577,7 @@
         <v>10.971007588959</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5588486058076381</v>
+        <v>0.2622740972442417</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
@@ -3580,7 +3592,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.433142298438295</v>
+        <v>1.73318021998019</v>
       </c>
       <c r="Q29" t="n">
         <v>16</v>
@@ -3646,7 +3658,7 @@
         <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>679.47357178</v>
+        <v>682.3099975600001</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,22 +3718,22 @@
         <v>27.55411108915111</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.851647546479728</v>
+        <v>0.4377580964353811</v>
       </c>
       <c r="Z30" t="n">
         <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>29.41176470588235</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.863991608210943</v>
+        <v>9.296077668789271</v>
       </c>
       <c r="AC30" t="n">
         <v>6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.192574890171542</v>
+        <v>5.586698126938705</v>
       </c>
       <c r="AE30" t="n">
         <v>31</v>
@@ -3755,7 +3767,7 @@
         <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>203.67500305</v>
+        <v>203.52000427</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,7 +3866,7 @@
         <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>495.72750854</v>
+        <v>497.75</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3953,7 +3965,7 @@
         <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>975.63201904</v>
+        <v>977.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,16 +3993,16 @@
         <v>13.41136277305126</v>
       </c>
       <c r="K33" t="n">
-        <v>8.091296856313491</v>
+        <v>8.298252430268494</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M33" t="n">
-        <v>62</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N33" t="n">
-        <v>12.32856328088578</v>
+        <v>12.24756570819475</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
@@ -4023,16 +4035,16 @@
         <v>26.04595216565901</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.405219091182457</v>
+        <v>6.226019080029621</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
-        <v>42.10526315789474</v>
+        <v>45</v>
       </c>
       <c r="AB33" t="n">
-        <v>12.30544998332289</v>
+        <v>11.96356508612536</v>
       </c>
       <c r="AC33" t="n">
         <v>4</v>
@@ -4072,7 +4084,7 @@
         <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>75.68499756</v>
+        <v>75.30999756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4100,22 +4112,22 @@
         <v>10.25119598904701</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8729825278560366</v>
+        <v>0.3731824397611883</v>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M34" t="n">
-        <v>58.53658536585366</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="N34" t="n">
-        <v>10.19718509946021</v>
+        <v>11.01887258905039</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>9.048029753282606</v>
+        <v>9.591025537141196</v>
       </c>
       <c r="Q34" t="n">
         <v>34</v>
@@ -4142,7 +4154,7 @@
         <v>14.39517840252906</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.467704611071637</v>
+        <v>9.91626921258244</v>
       </c>
       <c r="Z34" t="n">
         <v>10</v>
@@ -4157,7 +4169,7 @@
         <v>10</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.5879618832612232</v>
+        <v>0.0929477350523511</v>
       </c>
       <c r="AE34" t="n">
         <v>25</v>
@@ -4191,7 +4203,7 @@
         <v>46282</v>
       </c>
       <c r="C35" t="n">
-        <v>35.85499954</v>
+        <v>36.36000061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,22 +4231,22 @@
         <v>16.20544078061254</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3498460722342278</v>
+        <v>1.763227198742912</v>
       </c>
       <c r="L35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M35" t="n">
-        <v>50</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="N35" t="n">
-        <v>8.707038735216463</v>
+        <v>11.42908879249151</v>
       </c>
       <c r="O35" t="n">
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.644401055262157</v>
+        <v>0.2326702953264981</v>
       </c>
       <c r="Q35" t="n">
         <v>29</v>
@@ -4300,7 +4312,7 @@
         <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>218.8999939</v>
+        <v>219.33999634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4328,7 +4340,7 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K36" t="n">
-        <v>4.771933934478323</v>
+        <v>4.982531960331849</v>
       </c>
       <c r="L36" t="n">
         <v>46</v>
@@ -4337,7 +4349,7 @@
         <v>65.21739130434783</v>
       </c>
       <c r="N36" t="n">
-        <v>11.43839929995689</v>
+        <v>11.42019995364024</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4370,16 +4382,16 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.755836164975049</v>
+        <v>6.568409665447994</v>
       </c>
       <c r="Z36" t="n">
         <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>47.36842105263158</v>
+        <v>50</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.49356344987565</v>
+        <v>11.46961297183301</v>
       </c>
       <c r="AC36" t="n">
         <v>6</v>
@@ -4419,7 +4431,7 @@
         <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>150.99299622</v>
+        <v>150.58999634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4436,7 +4448,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>5</v>
       </c>
@@ -4447,7 +4463,7 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K37" t="n">
-        <v>8.628054834532373</v>
+        <v>8.338126863309348</v>
       </c>
       <c r="L37" t="n">
         <v>13</v>
@@ -4456,7 +4472,7 @@
         <v>61.53846153846154</v>
       </c>
       <c r="N37" t="n">
-        <v>9.514910927130867</v>
+        <v>9.999584585022177</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
@@ -4489,13 +4505,13 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.54481609965841</v>
+        <v>11.78090273539399</v>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="AB37" t="n">
         <v>10.3153604625776</v>
@@ -4538,7 +4554,7 @@
         <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>58.875</v>
+        <v>59.29000092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4598,7 +4614,7 @@
         <v>15.6720464761638</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.676023874377114</v>
+        <v>7.02524620932079</v>
       </c>
       <c r="Z38" t="n">
         <v>26</v>
@@ -4607,13 +4623,13 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AB38" t="n">
-        <v>12.40972030963657</v>
+        <v>10.04796355838424</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.517196749044592</v>
+        <v>3.199528548767638</v>
       </c>
       <c r="AE38" t="n">
         <v>33</v>
@@ -4647,7 +4663,7 @@
         <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>133.625</v>
+        <v>133.66000366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4746,7 +4762,7 @@
         <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>27.69499969</v>
+        <v>27.63999939</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,13 +4822,13 @@
         <v>13.1731874460205</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.186578013408139</v>
+        <v>5.37487072731534</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>20</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB40" t="n">
         <v>11.43386932212815</v>
@@ -4821,7 +4837,7 @@
         <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.076730578580479</v>
+        <v>4.887844601359815</v>
       </c>
       <c r="AE40" t="n">
         <v>17</v>
@@ -4855,7 +4871,7 @@
         <v>46282</v>
       </c>
       <c r="C41" t="n">
-        <v>176.72000122</v>
+        <v>176.24000549</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4890,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.29: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4887,22 +4903,22 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K41" t="n">
-        <v>7.395927040063355</v>
+        <v>7.104224991383257</v>
       </c>
       <c r="L41" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M41" t="n">
-        <v>85.29411764705883</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N41" t="n">
-        <v>20.2111712418399</v>
+        <v>19.98901470157656</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>2.424740892608734</v>
+        <v>2.703698205042548</v>
       </c>
       <c r="Q41" t="n">
         <v>27</v>
@@ -4929,16 +4945,16 @@
         <v>23.35952775538022</v>
       </c>
       <c r="Y41" t="n">
-        <v>6.184633541333606</v>
+        <v>6.439448927241664</v>
       </c>
       <c r="Z41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>54.54545454545455</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB41" t="n">
-        <v>15.4096485600858</v>
+        <v>15.57487031324569</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -4978,7 +4994,7 @@
         <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>190.16499329</v>
+        <v>188.71000671</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,22 +5054,22 @@
         <v>23.63097048814724</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.9041170740756277</v>
+        <v>1.662317504638555</v>
       </c>
       <c r="Z42" t="n">
         <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>35.29411764705883</v>
+        <v>29.41176470588235</v>
       </c>
       <c r="AB42" t="n">
-        <v>10.41975609405634</v>
+        <v>10.71303653994351</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>9.178870662794015</v>
+        <v>8.478624148738433</v>
       </c>
       <c r="AE42" t="n">
         <v>36</v>
@@ -5087,7 +5103,7 @@
         <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>52.20999908</v>
+        <v>52.08000183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5115,22 +5131,22 @@
         <v>14.7204727843671</v>
       </c>
       <c r="K43" t="n">
-        <v>1.260662708938942</v>
+        <v>1.008534612457468</v>
       </c>
       <c r="L43" t="n">
         <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>62.5</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>13.86208026393347</v>
+        <v>13.86917594453042</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.705233422118658</v>
+        <v>2.961596660143595</v>
       </c>
       <c r="Q43" t="n">
         <v>43</v>
@@ -5157,13 +5173,13 @@
         <v>20.24662002189492</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.64538558640017</v>
+        <v>13.86039923505735</v>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>14.28571428571429</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB43" t="n">
         <v>13.55932437400208</v>
@@ -5206,7 +5222,7 @@
         <v>46282</v>
       </c>
       <c r="C44" t="n">
-        <v>40.68500137</v>
+        <v>40.34999847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5223,7 +5239,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5234,13 +5254,17 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K44" t="n">
-        <v>19.34585271628402</v>
+        <v>18.36315134190458</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>100</v>
+      </c>
+      <c r="N44" t="n">
+        <v>14.73687195807274</v>
+      </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
@@ -5272,22 +5296,22 @@
         <v>44.25503404501885</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.84069947384168</v>
+        <v>4.632481296466572</v>
       </c>
       <c r="Z44" t="n">
         <v>10</v>
       </c>
       <c r="AA44" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.837765829123923</v>
+        <v>8.686067454850765</v>
       </c>
       <c r="AC44" t="n">
         <v>8</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.325427185305763</v>
+        <v>3.531096068465345</v>
       </c>
       <c r="AE44" t="n">
         <v>77</v>
@@ -5321,7 +5345,7 @@
         <v>46282</v>
       </c>
       <c r="C45" t="n">
-        <v>25.44499969</v>
+        <v>25.38999939</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5381,22 +5405,22 @@
         <v>16.02758025615572</v>
       </c>
       <c r="Y45" t="n">
-        <v>5.514298562590703</v>
+        <v>5.718532871416815</v>
       </c>
       <c r="Z45" t="n">
         <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>35.71428571428572</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.30536041648421</v>
+        <v>15.35012986685182</v>
       </c>
       <c r="AC45" t="n">
         <v>8</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.630769946769052</v>
+        <v>2.419846867117226</v>
       </c>
       <c r="AE45" t="n">
         <v>17</v>
@@ -5430,7 +5454,7 @@
         <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>367.73901367</v>
+        <v>366.20001221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5490,16 +5514,16 @@
         <v>21.71653838636141</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.244608506278091</v>
+        <v>4.6453483838369</v>
       </c>
       <c r="Z46" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA46" t="n">
-        <v>36.36363636363637</v>
+        <v>31.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.82889531085061</v>
+        <v>14.16877540372585</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5539,7 +5563,7 @@
         <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>70.94000244</v>
+        <v>70.87000275</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,7 +5595,7 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K47" t="n">
-        <v>2.455234882354174</v>
+        <v>2.354137695520708</v>
       </c>
       <c r="L47" t="n">
         <v>37</v>
@@ -5580,13 +5604,13 @@
         <v>75.67567567567568</v>
       </c>
       <c r="N47" t="n">
-        <v>14.04937287242685</v>
+        <v>14.04876797151395</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.507746402045362</v>
+        <v>1.608007591618188</v>
       </c>
       <c r="Q47" t="n">
         <v>28</v>
@@ -5613,7 +5637,7 @@
         <v>20.8229427476307</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.87117794796723</v>
+        <v>13.95616512919558</v>
       </c>
       <c r="Z47" t="n">
         <v>3</v>
@@ -5662,7 +5686,7 @@
         <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>377.95999146</v>
+        <v>375.20999146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5690,22 +5714,22 @@
         <v>10.39403223569868</v>
       </c>
       <c r="K48" t="n">
-        <v>1.158896909628737</v>
+        <v>0.4228746512227932</v>
       </c>
       <c r="L48" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M48" t="n">
-        <v>50</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N48" t="n">
-        <v>11.54383792842054</v>
+        <v>11.43449717362419</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>6.762730021149621</v>
+        <v>7.545218532225073</v>
       </c>
       <c r="Q48" t="n">
         <v>26</v>
@@ -5771,7 +5795,7 @@
         <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>370.92001343</v>
+        <v>369.92999268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5894,7 @@
         <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>48.625</v>
+        <v>48.33000183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5930,16 +5954,16 @@
         <v>12.10674333226271</v>
       </c>
       <c r="Y50" t="n">
-        <v>5.893164849709532</v>
+        <v>6.464092235906493</v>
       </c>
       <c r="Z50" t="n">
         <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>53.33333333333334</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB50" t="n">
-        <v>8.125876846070605</v>
+        <v>8.768821837136917</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
@@ -5979,7 +6003,7 @@
         <v>46282</v>
       </c>
       <c r="C51" t="n">
-        <v>28.22500038</v>
+        <v>28.23999977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6039,13 +6063,13 @@
         <v>10.73338207305774</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.638838896410245</v>
+        <v>2.587099020180506</v>
       </c>
       <c r="Z51" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA51" t="n">
-        <v>45.45454545454545</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB51" t="n">
         <v>13.84894258070201</v>
@@ -6054,7 +6078,7 @@
         <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.3709498731280458</v>
+        <v>0.4238668345428298</v>
       </c>
       <c r="AE51" t="n">
         <v>47</v>
@@ -6088,7 +6112,7 @@
         <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>87.58999634</v>
+        <v>86.88999939</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,22 +6172,22 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.783130364560273</v>
+        <v>5.544079344106212</v>
       </c>
       <c r="Z52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>25</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.51833461074082</v>
+        <v>9.247029805985685</v>
       </c>
       <c r="AC52" t="n">
         <v>6</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.277997943115339</v>
+        <v>0.4826808660885584</v>
       </c>
       <c r="AE52" t="n">
         <v>28</v>
@@ -6197,7 +6221,7 @@
         <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>106.58499908</v>
+        <v>106.79000092</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6225,7 +6249,7 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K53" t="n">
-        <v>4.341651966297344</v>
+        <v>4.542339031328657</v>
       </c>
       <c r="L53" t="n">
         <v>13</v>
@@ -6234,7 +6258,7 @@
         <v>46.15384615384615</v>
       </c>
       <c r="N53" t="n">
-        <v>10.30700197623545</v>
+        <v>10.24442328542791</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -6306,7 +6330,7 @@
         <v>46282</v>
       </c>
       <c r="C54" t="n">
-        <v>162.16499329</v>
+        <v>163.27000427</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6366,22 +6390,22 @@
         <v>11.95142925876556</v>
       </c>
       <c r="Y54" t="n">
-        <v>4.406393614052706</v>
+        <v>3.75500774752745</v>
       </c>
       <c r="Z54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="n">
-        <v>42.10526315789474</v>
+        <v>35</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.78362049164532</v>
+        <v>12.58665447699926</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.6209687116005336</v>
+        <v>1.293565746471936</v>
       </c>
       <c r="AE54" t="n">
         <v>22</v>
@@ -6415,7 +6439,7 @@
         <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>29442.78515625</v>
+        <v>29446.98046875</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -1708,10 +1708,10 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X11" t="n">
-        <v>13.04313716172454</v>
+        <v>13.04296880513336</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.627111462047271</v>
+        <v>2.626966443141965</v>
       </c>
       <c r="Z11" t="n">
         <v>60</v>
@@ -1726,7 +1726,7 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.517848570198824</v>
+        <v>5.517989283676384</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -3523,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10.72772186138614</v>
+        <v>10.72277408910891</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1164484211486405</v>
+        <v>0.1108999357097407</v>
       </c>
       <c r="L28" t="n">
         <v>33</v>
@@ -3541,7 +3541,7 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.881360763945628</v>
+        <v>1.8870073743253</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -4583,10 +4583,10 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>11.15344873147072</v>
+        <v>11.14030879500202</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6358129785912769</v>
+        <v>0.6209316733438275</v>
       </c>
       <c r="L38" t="n">
         <v>50</v>
@@ -4601,7 +4601,7 @@
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>7.317660386939329</v>
+        <v>7.333532103053475</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -5986,10 +5986,10 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>15.05752993064056</v>
+        <v>15.06813824398204</v>
       </c>
       <c r="K51" t="n">
-        <v>3.382430234401768</v>
+        <v>3.395343094090175</v>
       </c>
       <c r="L51" t="n">
         <v>17</v>
@@ -7734,10 +7734,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>16.20544078061254</v>
+        <v>16.22888899858401</v>
       </c>
       <c r="K67" t="n">
-        <v>1.763227198742912</v>
+        <v>1.791711556946018</v>
       </c>
       <c r="L67" t="n">
         <v>23</v>
@@ -7752,7 +7752,7 @@
         <v>2</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2326702953264981</v>
+        <v>0.2046222033878164</v>
       </c>
       <c r="Q67" t="n">
         <v>29</v>
@@ -8884,10 +8884,10 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>23.63097048814724</v>
+        <v>23.63741924470009</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.662317504638555</v>
+        <v>1.667446661962102</v>
       </c>
       <c r="Z77" t="n">
         <v>17</v>
@@ -8902,7 +8902,7 @@
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>8.478624148738433</v>
+        <v>8.473850271530193</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8965,10 +8965,10 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>15.4354740465219</v>
+        <v>15.44429116110657</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8756346683303828</v>
+        <v>0.8861535563142287</v>
       </c>
       <c r="L78" t="n">
         <v>18</v>
@@ -8983,7 +8983,7 @@
         <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>1.114605459848095</v>
+        <v>1.104062752341961</v>
       </c>
       <c r="Q78" t="n">
         <v>13</v>
@@ -9415,10 +9415,10 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>11.26330171400214</v>
+        <v>11.26352308918246</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1062684620418031</v>
+        <v>0.1065182019909683</v>
       </c>
       <c r="L82" t="n">
         <v>21</v>
@@ -9433,7 +9433,7 @@
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>9.883228782730736</v>
+        <v>9.882954652409715</v>
       </c>
       <c r="Q82" t="n">
         <v>20</v>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -437,14 +437,14 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C2" t="n">
-        <v>337</v>
+        <v>338.42498779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,25 +727,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>12.56612040461789</v>
+        <v>12.78570440965048</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3960502318660075</v>
+        <v>0.1696201209439585</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.85714285714286</v>
+        <v>24.13793103448276</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.20753016674198</v>
+        <v>10.52967967438215</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.634184975430259</v>
+        <v>7.843684345930068</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,14 +776,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C3" t="n">
-        <v>264.01998901</v>
+        <v>264.60998535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -835,27 +835,17 @@
       <c r="W3" t="n">
         <v>44</v>
       </c>
-      <c r="X3" t="n">
-        <v>10.6840815074065</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.104997638880389</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>17.39130434782609</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17.37015054625821</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>1.916176061354369</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>18</v>
       </c>
@@ -885,10 +875,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C4" t="n">
-        <v>102.23000336</v>
+        <v>102.77999878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,22 +906,22 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>1.893752113370217</v>
+        <v>2.441938508235353</v>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>63.1578947368421</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N4" t="n">
-        <v>8.825614182024168</v>
+        <v>7.536245754264848</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>4.029930983463093</v>
+        <v>3.473246937316232</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -972,10 +962,10 @@
         <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.06372549019608</v>
+        <v>12.81372549019608</v>
       </c>
       <c r="AH4" t="n">
-        <v>26.93627450980392</v>
+        <v>27.18627450980392</v>
       </c>
       <c r="AI4" t="n">
         <v>21.88065323728171</v>
@@ -994,10 +984,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C5" t="n">
-        <v>190.28999329</v>
+        <v>187.02000427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,19 +1044,19 @@
         <v>48.27586206896552</v>
       </c>
       <c r="X5" t="n">
-        <v>25.27257337567461</v>
+        <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.714016803499454</v>
+        <v>5.368618300871042</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.208739707267471</v>
+        <v>8.04076975353742</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1103,10 +1093,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C6" t="n">
-        <v>362.6499939</v>
+        <v>379.60998535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,22 +1124,22 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>4.209768362068966</v>
+        <v>9.083329123563221</v>
       </c>
       <c r="L6" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="M6" t="n">
-        <v>61.76470588235294</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N6" t="n">
-        <v>9.910078620979149</v>
+        <v>8.711758247621066</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>5.55632329765221</v>
+        <v>0.8403400261083327</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1158,10 +1148,10 @@
         <v>41.1764705882353</v>
       </c>
       <c r="S6" t="n">
-        <v>35.60252777798417</v>
+        <v>35.74958660151358</v>
       </c>
       <c r="T6" t="n">
-        <v>5.573942810251125</v>
+        <v>5.426883986721712</v>
       </c>
       <c r="U6" t="n">
         <v>26.36596836387115</v>
@@ -1212,10 +1202,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C7" t="n">
-        <v>272.23999023</v>
+        <v>270.47000122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1247,10 @@
         <v>25</v>
       </c>
       <c r="S7" t="n">
-        <v>21.04858120483121</v>
+        <v>21.11160641491524</v>
       </c>
       <c r="T7" t="n">
-        <v>3.951418795168792</v>
+        <v>3.888393585084764</v>
       </c>
       <c r="U7" t="n">
         <v>10.18206749121305</v>
@@ -1311,24 +1301,24 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C8" t="n">
-        <v>417.3999939</v>
+        <v>461.48001099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1342,22 +1332,22 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>1.431310050827683</v>
+        <v>12.14308280081184</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>15.27907757850019</v>
+        <v>9.043238964344949</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.518331713732215</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>46</v>
@@ -1380,17 +1370,27 @@
       <c r="W8" t="n">
         <v>65.71428571428571</v>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>12.52459886669746</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3390512561058601</v>
+      </c>
       <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>37.73584905660378</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.03615909163916</v>
+      </c>
       <c r="AC8" t="n">
         <v>10</v>
       </c>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>9.693815747952161</v>
+      </c>
       <c r="AE8" t="n">
         <v>42</v>
       </c>
@@ -1398,10 +1398,10 @@
         <v>40.47619047619047</v>
       </c>
       <c r="AG8" t="n">
-        <v>19.92335225232889</v>
+        <v>19.68525701423366</v>
       </c>
       <c r="AH8" t="n">
-        <v>20.55283822386158</v>
+        <v>20.79093346195682</v>
       </c>
       <c r="AI8" t="n">
         <v>27.04286114748132</v>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C9" t="n">
-        <v>545.09002686</v>
+        <v>612.63500977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,31 +1474,31 @@
         <v>56.43279073180463</v>
       </c>
       <c r="V9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W9" t="n">
-        <v>67.74193548387096</v>
+        <v>67.39130434782609</v>
       </c>
       <c r="X9" t="n">
-        <v>25.18047285130534</v>
+        <v>39.83881730533485</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.147937370095853</v>
+        <v>0.5446485354002717</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>47.72727272727273</v>
+        <v>43.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.20277503821869</v>
+        <v>15.37366925134289</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.908408080537452</v>
+        <v>5.485226671328514</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C10" t="n">
-        <v>251.19000244</v>
+        <v>257.86499023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,22 +1560,22 @@
         <v>12.7936066701423</v>
       </c>
       <c r="K10" t="n">
-        <v>2.820302621359305</v>
+        <v>5.552593946232465</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>41.02564102564103</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="N10" t="n">
-        <v>12.03005755399682</v>
+        <v>11.47379342580538</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>5.037621215447285</v>
+        <v>2.318660264298411</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
@@ -1584,10 +1584,10 @@
         <v>39.1304347826087</v>
       </c>
       <c r="S10" t="n">
-        <v>44.73585934305574</v>
+        <v>44.91320488081318</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.605424560447048</v>
+        <v>-5.782770098204487</v>
       </c>
       <c r="U10" t="n">
         <v>22.15762279247795</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C11" t="n">
-        <v>199.52999878</v>
+        <v>202.74989319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,16 +1669,16 @@
         <v>14.2728744929405</v>
       </c>
       <c r="K11" t="n">
-        <v>10.07336794829106</v>
+        <v>11.84966536879755</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N11" t="n">
-        <v>14.3463833123371</v>
+        <v>13.46029151457658</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1711,22 +1711,22 @@
         <v>13.04296880513336</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.626966443141965</v>
+        <v>1.055619335681879</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA11" t="n">
-        <v>31.66666666666667</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.79667279957727</v>
+        <v>11.09075118217421</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.517989283676384</v>
+        <v>7.018468979939185</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C12" t="n">
-        <v>78.37000275</v>
+        <v>80.69999695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,19 +1785,19 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>14.08155253269405</v>
+        <v>12.33653883634149</v>
       </c>
       <c r="K12" t="n">
-        <v>3.458749504950487</v>
+        <v>6.534649438943885</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
       </c>
       <c r="M12" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>11.30156957148062</v>
+        <v>9.577328043969082</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1812,10 +1812,10 @@
         <v>52.38095238095238</v>
       </c>
       <c r="S12" t="n">
-        <v>19.68712596293248</v>
+        <v>19.69653684190857</v>
       </c>
       <c r="T12" t="n">
-        <v>32.6938264180199</v>
+        <v>32.68441553904381</v>
       </c>
       <c r="U12" t="n">
         <v>32.36953458284443</v>
@@ -1830,22 +1830,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.232481495014942</v>
+        <v>4.474439227815862</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>18.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.077320691973259</v>
+        <v>9.111428899320011</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.983283965751804</v>
+        <v>5.784379309075049</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1876,24 +1876,24 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C13" t="n">
-        <v>264.8999939</v>
+        <v>319.05999756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1903,12 +1903,8 @@
       <c r="I13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="n">
-        <v>24.66712198980348</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17.49311896398995</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1917,9 +1913,7 @@
       <c r="O13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>14</v>
       </c>
@@ -1942,25 +1936,25 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>21.88413892112759</v>
+        <v>42.19817109842221</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.602618023973658</v>
+        <v>0.480351999594042</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>46.66666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.24734568739429</v>
+        <v>8.627526536685187</v>
       </c>
       <c r="AC13" t="n">
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.531809598437973</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -1991,10 +1985,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C14" t="n">
-        <v>1629.67004395</v>
+        <v>1701.94494629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,22 +2016,22 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>3.613214272589493</v>
+        <v>8.208399028231138</v>
       </c>
       <c r="L14" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>58.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
-        <v>11.43494090652927</v>
+        <v>8.880447662134857</v>
       </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>6.164064856252716</v>
+        <v>1.655694925586548</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2078,10 +2072,10 @@
         <v>48.57142857142857</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.72360775945168</v>
+        <v>14.6521791880231</v>
       </c>
       <c r="AH14" t="n">
-        <v>33.8478208119769</v>
+        <v>33.91924938340546</v>
       </c>
       <c r="AI14" t="n">
         <v>32.99423600250972</v>
@@ -2100,10 +2094,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C15" t="n">
-        <v>347.29998779</v>
+        <v>360.79989624</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,11 +2114,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %92.31: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>5</v>
       </c>
@@ -2135,16 +2125,16 @@
         <v>22.3973403666333</v>
       </c>
       <c r="K15" t="n">
-        <v>3.421574793331472</v>
+        <v>7.441677990999951</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>92.30769230769231</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N15" t="n">
-        <v>13.18405045400497</v>
+        <v>13.83351318357871</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -2159,10 +2149,10 @@
         <v>56.81818181818182</v>
       </c>
       <c r="S15" t="n">
-        <v>43.99184563130525</v>
+        <v>44.30251814592512</v>
       </c>
       <c r="T15" t="n">
-        <v>12.82633618687657</v>
+        <v>12.5156636722567</v>
       </c>
       <c r="U15" t="n">
         <v>42.22414699362943</v>
@@ -2213,10 +2203,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C16" t="n">
-        <v>311.17001343</v>
+        <v>312.58999634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,25 +2231,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>11.54571533142856</v>
+        <v>11.07429159124881</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5103579278009862</v>
+        <v>1.269959095294171</v>
       </c>
       <c r="L16" t="n">
         <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>63.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>10.19567638618513</v>
+        <v>9.629107580588869</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.471922838744357</v>
+        <v>0.7208859480419827</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2268,10 +2258,10 @@
         <v>47.61904761904762</v>
       </c>
       <c r="S16" t="n">
-        <v>27.51497751497751</v>
+        <v>31.75799717350371</v>
       </c>
       <c r="T16" t="n">
-        <v>20.10407010407011</v>
+        <v>15.86105044554391</v>
       </c>
       <c r="U16" t="n">
         <v>28.34400610153417</v>
@@ -2280,7 +2270,7 @@
         <v>35</v>
       </c>
       <c r="W16" t="n">
-        <v>57.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -2300,10 +2290,10 @@
         <v>31.81818181818182</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.392010163749294</v>
+        <v>7.553493417337811</v>
       </c>
       <c r="AH16" t="n">
-        <v>24.42617165443252</v>
+        <v>24.264688400844</v>
       </c>
       <c r="AI16" t="n">
         <v>16.36059318135624</v>
@@ -2322,10 +2312,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C17" t="n">
-        <v>197</v>
+        <v>201.07499695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,11 +2332,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>5</v>
       </c>
@@ -2354,25 +2340,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>18.04301535154102</v>
+        <v>17.56568419419229</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.872705437041589</v>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>76.66666666666667</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N17" t="n">
-        <v>13.11151380613315</v>
+        <v>13.19522740948047</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>6.000000000000005</v>
+        <v>3.039965314096205</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2381,10 +2367,10 @@
         <v>46.875</v>
       </c>
       <c r="S17" t="n">
-        <v>38.98586658895805</v>
+        <v>39.09706037202684</v>
       </c>
       <c r="T17" t="n">
-        <v>7.889133411041946</v>
+        <v>7.777939627973161</v>
       </c>
       <c r="U17" t="n">
         <v>30.86938710806884</v>
@@ -2413,10 +2399,10 @@
         <v>55.55555555555556</v>
       </c>
       <c r="AG17" t="n">
-        <v>21.20760100593262</v>
+        <v>21.25521231816381</v>
       </c>
       <c r="AH17" t="n">
-        <v>34.34795454962294</v>
+        <v>34.30034323739174</v>
       </c>
       <c r="AI17" t="n">
         <v>39.5810617556973</v>
@@ -2435,10 +2421,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C18" t="n">
-        <v>58.18000031</v>
+        <v>57.95999908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,22 +2452,22 @@
         <v>12.34095145691251</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7488632294133</v>
+        <v>1.364111167840609</v>
       </c>
       <c r="L18" t="n">
         <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>44.73684210526316</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N18" t="n">
-        <v>11.86301762781457</v>
+        <v>11.12502980176296</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.229632185438545</v>
+        <v>1.613873799426568</v>
       </c>
       <c r="Q18" t="n">
         <v>24</v>
@@ -2490,10 +2476,10 @@
         <v>50</v>
       </c>
       <c r="S18" t="n">
-        <v>38.78816316316317</v>
+        <v>38.92361111111111</v>
       </c>
       <c r="T18" t="n">
-        <v>11.21183683683683</v>
+        <v>11.07638888888889</v>
       </c>
       <c r="U18" t="n">
         <v>31.42742581957335</v>
@@ -2544,10 +2530,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C19" t="n">
-        <v>170.52000427</v>
+        <v>167.86999512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,7 +2550,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2572,25 +2562,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>22.5243928544149</v>
+        <v>23.56732248521627</v>
       </c>
       <c r="K19" t="n">
-        <v>1.276955046810824</v>
+        <v>1.063490381638599</v>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N19" t="n">
-        <v>10.28253339768669</v>
+        <v>8.637758974740988</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>6.638277138251003</v>
+        <v>6.863516777589584</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2653,10 +2643,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C20" t="n">
-        <v>62.84000015</v>
+        <v>62.89500046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,10 +2720,10 @@
         <v>50</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.74878691355084</v>
+        <v>14.27272697203038</v>
       </c>
       <c r="AH20" t="n">
-        <v>35.25121308644916</v>
+        <v>35.72727302796962</v>
       </c>
       <c r="AI20" t="n">
         <v>27.99956361032602</v>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C21" t="n">
-        <v>132.69999695</v>
+        <v>134.25500488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,10 +2787,10 @@
         <v>57.69230769230769</v>
       </c>
       <c r="S21" t="n">
-        <v>31.71079211401792</v>
+        <v>31.93515108837689</v>
       </c>
       <c r="T21" t="n">
-        <v>25.98151557828977</v>
+        <v>25.7571566039308</v>
       </c>
       <c r="U21" t="n">
         <v>38.94861374659171</v>
@@ -2851,10 +2841,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C22" t="n">
-        <v>798.5700073199999</v>
+        <v>820.39501953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,37 +2872,37 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>3.523508491658678</v>
+        <v>6.352818152855511</v>
       </c>
       <c r="L22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M22" t="n">
-        <v>40.625</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="N22" t="n">
-        <v>10.32318483007037</v>
+        <v>10.91990640416717</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>6.256058747142612</v>
+        <v>3.429323181547095</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R22" t="n">
-        <v>53.57142857142857</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="S22" t="n">
-        <v>32.42611233682663</v>
+        <v>33.92710170487948</v>
       </c>
       <c r="T22" t="n">
-        <v>21.14531623460194</v>
+        <v>17.92475014697237</v>
       </c>
       <c r="U22" t="n">
-        <v>35.8126892344679</v>
+        <v>33.98561575495229</v>
       </c>
       <c r="V22" t="n">
         <v>34</v>
@@ -2960,10 +2950,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C23" t="n">
-        <v>22.90999985</v>
+        <v>23.02499962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,25 +2978,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>16.48994576723293</v>
+        <v>18.24497148325086</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3064785443970264</v>
+        <v>2.974056314214013</v>
       </c>
       <c r="L23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M23" t="n">
-        <v>63.1578947368421</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>8.950019722099126</v>
+        <v>8.906984238639312</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.685291612954788</v>
+        <v>0.02519439042667493</v>
       </c>
       <c r="Q23" t="n">
         <v>27</v>
@@ -3069,19 +3059,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C24" t="n">
-        <v>133.19000244</v>
+        <v>127.55999756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3096,17 +3086,27 @@
       <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>10.13804453095366</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.233769269918449</v>
+      </c>
       <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.27862100052214</v>
+      </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>9.74345352989987</v>
+      </c>
       <c r="Q24" t="n">
         <v>35</v>
       </c>
@@ -3129,25 +3129,25 @@
         <v>55.10204081632653</v>
       </c>
       <c r="X24" t="n">
-        <v>23.26572884665414</v>
+        <v>18.83863161428796</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.952544111343139</v>
+        <v>9.927974893719227</v>
       </c>
       <c r="Z24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
-        <v>22.22222222222222</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.27461935461157</v>
+        <v>12.51331360108521</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.30363144905127</v>
+        <v>0.07996390243895091</v>
       </c>
       <c r="AE24" t="n">
         <v>36</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C25" t="n">
-        <v>893.9299926800001</v>
+        <v>896.1849975600001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
         <v>41.66666666666666</v>
       </c>
       <c r="S25" t="n">
-        <v>27.41178678678679</v>
+        <v>27.43055555555556</v>
       </c>
       <c r="T25" t="n">
-        <v>14.25487987987988</v>
+        <v>14.23611111111111</v>
       </c>
       <c r="U25" t="n">
         <v>19.32603136587566</v>
@@ -3277,24 +3277,24 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C26" t="n">
-        <v>242.8500061</v>
+        <v>237.95500183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3304,17 +3304,27 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>11.82390399949569</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5939542430287048</v>
+      </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="M26" t="n">
+        <v>55.81395348837209</v>
+      </c>
+      <c r="N26" t="n">
+        <v>11.49687307178913</v>
+      </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>7.362316962984439</v>
+      </c>
       <c r="Q26" t="n">
         <v>35</v>
       </c>
@@ -3337,25 +3347,25 @@
         <v>60.8695652173913</v>
       </c>
       <c r="X26" t="n">
-        <v>19.5913144208306</v>
+        <v>16.61377328984133</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.475522403310066</v>
+        <v>11.30017833596363</v>
       </c>
       <c r="Z26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>55.55555555555556</v>
+        <v>40</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.182546694266328</v>
+        <v>8.204579259374766</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5793765516401206</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>28</v>
@@ -3386,10 +3396,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C27" t="n">
-        <v>110.23999786</v>
+        <v>109.55999756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3427,7 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K27" t="n">
-        <v>2.682560761583819</v>
+        <v>2.049177475316699</v>
       </c>
       <c r="L27" t="n">
         <v>22</v>
@@ -3426,13 +3436,13 @@
         <v>54.54545454545455</v>
       </c>
       <c r="N27" t="n">
-        <v>10.55625114125625</v>
+        <v>10.77081897375242</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5.178522232964777</v>
+        <v>5.831328259478297</v>
       </c>
       <c r="Q27" t="n">
         <v>16</v>
@@ -3473,10 +3483,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AG27" t="n">
-        <v>8.042950513538749</v>
+        <v>7.709617180205415</v>
       </c>
       <c r="AH27" t="n">
-        <v>25.29038281979459</v>
+        <v>25.62371615312792</v>
       </c>
       <c r="AI27" t="n">
         <v>15.17632443971473</v>
@@ -3495,10 +3505,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C28" t="n">
-        <v>90.26999664</v>
+        <v>87.72709656000001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3523,25 +3533,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10.72277408910891</v>
+        <v>11.48223102538071</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1108999357097407</v>
+        <v>0.6160042493055462</v>
       </c>
       <c r="L28" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>54.54545454545455</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N28" t="n">
-        <v>10.18953108880514</v>
+        <v>10.3587507096946</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8870073743253</v>
+        <v>1.375522473805657</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3604,14 +3614,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C29" t="n">
-        <v>211.57000732</v>
+        <v>205</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3621,7 +3631,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3649,10 +3659,10 @@
         <v>36.36363636363637</v>
       </c>
       <c r="S29" t="n">
-        <v>23.8007467014644</v>
+        <v>23.91438306510077</v>
       </c>
       <c r="T29" t="n">
-        <v>12.56288966217196</v>
+        <v>12.4492532985356</v>
       </c>
       <c r="U29" t="n">
         <v>19.73320467036612</v>
@@ -3664,25 +3674,25 @@
         <v>48.38709677419355</v>
       </c>
       <c r="X29" t="n">
-        <v>17.16791547737358</v>
+        <v>15.3007164090031</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.851497609876141</v>
+        <v>5.868306938926137</v>
       </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.77777777777778</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.736178955181336</v>
+        <v>7.711745261131634</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.1528612242806537</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -3691,10 +3701,10 @@
         <v>47.61904761904762</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.80026455026455</v>
+        <v>11.03835978835979</v>
       </c>
       <c r="AH29" t="n">
-        <v>36.81878306878307</v>
+        <v>36.58068783068784</v>
       </c>
       <c r="AI29" t="n">
         <v>28.34400610153417</v>
@@ -3713,10 +3723,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C30" t="n">
-        <v>685.63000488</v>
+        <v>690.59997559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,22 +3786,22 @@
         <v>21.84840721774197</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.868759542699117</v>
+        <v>2.164678016711585</v>
       </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>30</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.792696363972778</v>
+        <v>8.527482308059199</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.194186388711661</v>
+        <v>2.898055554795154</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3822,14 +3832,14 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C31" t="n">
-        <v>212.5</v>
+        <v>213.75500488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3839,7 +3849,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3881,27 +3891,17 @@
       <c r="W31" t="n">
         <v>44.44444444444444</v>
       </c>
-      <c r="X31" t="n">
-        <v>12.31168717717277</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.702360192936605</v>
-      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>45.83333333333334</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>10.75710521276845</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
         <v>26</v>
       </c>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C32" t="n">
-        <v>105.34999847</v>
+        <v>104.30500031</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C33" t="n">
-        <v>13.60999966</v>
+        <v>13.20499992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4058,46 +4058,46 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10.17760031008306</v>
+        <v>11.61202677950211</v>
       </c>
       <c r="K33" t="n">
-        <v>3.498099264583865</v>
+        <v>2.047916140658801</v>
       </c>
       <c r="L33" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="M33" t="n">
-        <v>50</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="N33" t="n">
-        <v>12.25933510733132</v>
+        <v>12.92016468574718</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.417339789999673</v>
+        <v>3.872772721682827</v>
       </c>
       <c r="Q33" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R33" t="n">
-        <v>56.09756097560975</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="S33" t="n">
-        <v>42.69832699892816</v>
+        <v>43.22931921323939</v>
       </c>
       <c r="T33" t="n">
-        <v>13.39923397668159</v>
+        <v>11.53258554866537</v>
       </c>
       <c r="U33" t="n">
-        <v>41.04052722210609</v>
+        <v>39.94911903473349</v>
       </c>
       <c r="V33" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W33" t="n">
-        <v>63.82978723404256</v>
+        <v>62.5</v>
       </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         <v>42.10526315789474</v>
       </c>
       <c r="AG33" t="n">
-        <v>17.94491781666803</v>
+        <v>17.81278601657957</v>
       </c>
       <c r="AH33" t="n">
-        <v>24.16034534122671</v>
+        <v>24.29247714131517</v>
       </c>
       <c r="AI33" t="n">
         <v>27.85250115775871</v>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C34" t="n">
-        <v>313.47000122</v>
+        <v>320.88000488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,25 +4167,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>21.09865479945756</v>
+        <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>2.174059222768121</v>
+        <v>4.589314749137996</v>
       </c>
       <c r="L34" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M34" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N34" t="n">
-        <v>14.87370911888632</v>
+        <v>12.27193608235259</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>5.701976432716349</v>
+        <v>3.261026481570029</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C35" t="n">
-        <v>86.62000275</v>
+        <v>84.0911026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AG35" t="n">
-        <v>29.12745271272138</v>
+        <v>28.81071063127341</v>
       </c>
       <c r="AH35" t="n">
-        <v>17.93137081669039</v>
+        <v>18.24811289813836</v>
       </c>
       <c r="AI35" t="n">
         <v>31.45150447508847</v>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C36" t="n">
-        <v>347.32998657</v>
+        <v>356.45001221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
         <v>55</v>
       </c>
       <c r="AG36" t="n">
-        <v>20.84830896153892</v>
+        <v>21.162034451735</v>
       </c>
       <c r="AH36" t="n">
-        <v>34.15169103846108</v>
+        <v>33.837965548265</v>
       </c>
       <c r="AI36" t="n">
         <v>34.20853424503424</v>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C37" t="n">
-        <v>951.4699707</v>
+        <v>950.95001221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>13.67364833892672</v>
+        <v>13.30675651903024</v>
       </c>
       <c r="K37" t="n">
-        <v>3.196309186550983</v>
+        <v>3.139914556399126</v>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>52.77777777777778</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="N37" t="n">
-        <v>12.23562624438321</v>
+        <v>11.32105074789215</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>6.592959445041591</v>
+        <v>6.651242123969037</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4501,10 +4501,10 @@
         <v>38.70967741935484</v>
       </c>
       <c r="S37" t="n">
-        <v>35.90937995224922</v>
+        <v>35.8287347909589</v>
       </c>
       <c r="T37" t="n">
-        <v>2.800297467105615</v>
+        <v>2.880942628395943</v>
       </c>
       <c r="U37" t="n">
         <v>23.73310142038025</v>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C38" t="n">
-        <v>34.02999878</v>
+        <v>33.29000092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,25 +4583,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>11.14030879500202</v>
+        <v>13.72832922207538</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6209316733438275</v>
+        <v>1.385722103696163</v>
       </c>
       <c r="L38" t="n">
+        <v>54</v>
+      </c>
+      <c r="M38" t="n">
         <v>50</v>
       </c>
-      <c r="M38" t="n">
-        <v>52</v>
-      </c>
       <c r="N38" t="n">
-        <v>13.44924978730225</v>
+        <v>15.28007428190196</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>7.333532103053475</v>
+        <v>6.52387511679291</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4610,10 +4610,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S38" t="n">
-        <v>33.17488391270135</v>
+        <v>32.69616050844603</v>
       </c>
       <c r="T38" t="n">
-        <v>28.52724374687312</v>
+        <v>29.00596715112844</v>
       </c>
       <c r="U38" t="n">
         <v>47.42656695641357</v>
@@ -4625,19 +4625,19 @@
         <v>71.23287671232876</v>
       </c>
       <c r="X38" t="n">
-        <v>19.79855467084246</v>
+        <v>18.08874313747508</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.58855082747466</v>
+        <v>12.53284361087769</v>
       </c>
       <c r="Z38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA38" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB38" t="n">
-        <v>17.49852906802476</v>
+        <v>10.72916620710978</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C39" t="n">
-        <v>302.51000977</v>
+        <v>298.4750061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>15.59604487521503</v>
+        <v>17.57170813546579</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01322727868504625</v>
+        <v>1.044379057178113</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M39" t="n">
-        <v>41.1764705882353</v>
+        <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>8.655085078351195</v>
+        <v>6.738192314882714</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>9.985451917761834</v>
+        <v>8.863057031360611</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4729,10 +4729,10 @@
         <v>17.39130434782609</v>
       </c>
       <c r="S39" t="n">
-        <v>25.97116651464477</v>
+        <v>26.07986216681869</v>
       </c>
       <c r="T39" t="n">
-        <v>-8.579862166818689</v>
+        <v>-8.688557818992599</v>
       </c>
       <c r="U39" t="n">
         <v>6.978653563062565</v>
@@ -4761,10 +4761,10 @@
         <v>50</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.05555555555555</v>
+        <v>13.06130268199234</v>
       </c>
       <c r="AH39" t="n">
-        <v>36.94444444444444</v>
+        <v>36.93869731800766</v>
       </c>
       <c r="AI39" t="n">
         <v>29.92980081982123</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C40" t="n">
-        <v>206.49000549</v>
+        <v>206.61999512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4803,11 +4803,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4815,25 +4811,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>21.20800170799999</v>
+        <v>20.00812356142131</v>
       </c>
       <c r="K40" t="n">
-        <v>4.827906369251478</v>
+        <v>4.89389765406103</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M40" t="n">
-        <v>75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N40" t="n">
-        <v>7.907752766764631</v>
+        <v>8.436049077843947</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>3.026001129484523</v>
+        <v>2.96118498349911</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4874,10 +4870,10 @@
         <v>37.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>15.05787037037037</v>
+        <v>14.96394230769231</v>
       </c>
       <c r="AH40" t="n">
-        <v>22.44212962962963</v>
+        <v>22.53605769230769</v>
       </c>
       <c r="AI40" t="n">
         <v>18.48123255886363</v>
@@ -4896,10 +4892,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C41" t="n">
-        <v>237.75</v>
+        <v>229.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4959,16 +4955,16 @@
         <v>10.73879246924641</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.58732702367074</v>
+        <v>8.863476559126958</v>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>44.44444444444444</v>
+        <v>60</v>
       </c>
       <c r="AB41" t="n">
-        <v>12.54868625712967</v>
+        <v>12.79361125189371</v>
       </c>
       <c r="AC41" t="n">
         <v>4</v>
@@ -4983,10 +4979,10 @@
         <v>38.46153846153846</v>
       </c>
       <c r="AG41" t="n">
-        <v>12.14516821487488</v>
+        <v>11.67813524784191</v>
       </c>
       <c r="AH41" t="n">
-        <v>26.31637024666358</v>
+        <v>26.78340321369655</v>
       </c>
       <c r="AI41" t="n">
         <v>22.4285944357128</v>
@@ -5005,14 +5001,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C42" t="n">
-        <v>108.80000305</v>
+        <v>122.95500183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5022,7 +5018,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5044,46 +5040,46 @@
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R42" t="n">
-        <v>70</v>
+        <v>70.73170731707317</v>
       </c>
       <c r="S42" t="n">
-        <v>38.63851461038961</v>
+        <v>38.91562401013621</v>
       </c>
       <c r="T42" t="n">
-        <v>31.36148538961039</v>
+        <v>31.81608330693697</v>
       </c>
       <c r="U42" t="n">
-        <v>54.56998118185506</v>
+        <v>55.52053227700284</v>
       </c>
       <c r="V42" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W42" t="n">
-        <v>68.96551724137932</v>
+        <v>69.49152542372882</v>
       </c>
       <c r="X42" t="n">
-        <v>30.80808497525172</v>
+        <v>46.49635691053297</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.307622911502527</v>
+        <v>1.420699276998827</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>28.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.96117844271113</v>
+        <v>16.93665027209175</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.5876494545532962</v>
       </c>
       <c r="AE42" t="n">
         <v>48</v>
@@ -5092,10 +5088,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG42" t="n">
-        <v>18.56101448932331</v>
+        <v>18.370996174305</v>
       </c>
       <c r="AH42" t="n">
-        <v>27.27231884401002</v>
+        <v>27.46233715902834</v>
       </c>
       <c r="AI42" t="n">
         <v>32.57524229286744</v>
@@ -5114,10 +5110,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C43" t="n">
-        <v>383.54000854</v>
+        <v>398.6000061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5145,17 +5141,13 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>11.09051659377263</v>
+        <v>15.45257236784938</v>
       </c>
       <c r="L43" t="n">
-        <v>11</v>
-      </c>
-      <c r="M43" t="n">
-        <v>54.54545454545455</v>
-      </c>
-      <c r="N43" t="n">
-        <v>9.656999603963261</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>10</v>
       </c>
@@ -5184,25 +5176,25 @@
         <v>50</v>
       </c>
       <c r="X43" t="n">
-        <v>12.4402642172339</v>
+        <v>15.53801274728459</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.200413066313655</v>
+        <v>0.07395001645223997</v>
       </c>
       <c r="Z43" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AA43" t="n">
-        <v>32.25806451612903</v>
+        <v>50</v>
       </c>
       <c r="AB43" t="n">
-        <v>14.63087841067424</v>
+        <v>11.18712625632929</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.882201783141239</v>
+        <v>7.931915636465902</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5233,10 +5225,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C44" t="n">
-        <v>270.22000122</v>
+        <v>271.33999634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5293,23 +5285,25 @@
         <v>40</v>
       </c>
       <c r="X44" t="n">
-        <v>10.17168889008249</v>
+        <v>10.11126434424055</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.860250406457355</v>
+        <v>3.461774905396542</v>
       </c>
       <c r="Z44" t="n">
         <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="inlineStr"/>
+        <v>7.692307692307693</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>5.203064942090774</v>
+      </c>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.225665869309035</v>
+        <v>2.629243589382457</v>
       </c>
       <c r="AE44" t="n">
         <v>14</v>
@@ -5340,10 +5334,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C45" t="n">
-        <v>349.30999756</v>
+        <v>351.01919556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,10 +5411,10 @@
         <v>38.09523809523809</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.2034632034632</v>
+        <v>13.44155844155844</v>
       </c>
       <c r="AH45" t="n">
-        <v>24.89177489177489</v>
+        <v>24.65367965367965</v>
       </c>
       <c r="AI45" t="n">
         <v>20.75101136856449</v>
@@ -5439,31 +5433,27 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C46" t="n">
-        <v>168.97999573</v>
+        <v>182.63999939</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %89.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>5</v>
       </c>
@@ -5474,55 +5464,65 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>1.862677889783804</v>
+        <v>10.09705230067637</v>
       </c>
       <c r="L46" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>89.47368421052632</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N46" t="n">
-        <v>14.60438544233544</v>
+        <v>10.19275247602296</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>7.988521683104444</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R46" t="n">
-        <v>67.39130434782609</v>
+        <v>65.95744680851064</v>
       </c>
       <c r="S46" t="n">
-        <v>40.42955857725679</v>
+        <v>40.6864804710499</v>
       </c>
       <c r="T46" t="n">
-        <v>26.9617457705693</v>
+        <v>25.27096633746074</v>
       </c>
       <c r="U46" t="n">
-        <v>52.96773241932241</v>
+        <v>51.67092456194193</v>
       </c>
       <c r="V46" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W46" t="n">
-        <v>66.07142857142857</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+        <v>64.91228070175438</v>
+      </c>
+      <c r="X46" t="n">
+        <v>10.3743485281111</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.2512324929955234</v>
+      </c>
       <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>44.68085106382978</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>11.70810393479271</v>
+      </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="n">
+        <v>7.768283960461309</v>
+      </c>
       <c r="AE46" t="n">
         <v>43</v>
       </c>
@@ -5530,10 +5530,10 @@
         <v>41.86046511627907</v>
       </c>
       <c r="AG46" t="n">
-        <v>20.94364836769188</v>
+        <v>21.0017879025756</v>
       </c>
       <c r="AH46" t="n">
-        <v>20.91681674858719</v>
+        <v>20.85867721370348</v>
       </c>
       <c r="AI46" t="n">
         <v>28.38455092784919</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C47" t="n">
-        <v>31.30999947</v>
+        <v>31.76499939</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C48" t="n">
-        <v>88.05999756</v>
+        <v>87.89499664</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C49" t="n">
-        <v>458.48001099</v>
+        <v>458.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C50" t="n">
-        <v>1152.43994141</v>
+        <v>1157.23999023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5880,16 +5880,16 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>3.516595044994397</v>
+        <v>3.947753921081421</v>
       </c>
       <c r="L50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M50" t="n">
-        <v>62.96296296296296</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N50" t="n">
-        <v>9.908479677567916</v>
+        <v>9.226715679892591</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5898,19 +5898,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R50" t="n">
-        <v>60</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="S50" t="n">
-        <v>25.04918300653595</v>
+        <v>25.91294793779581</v>
       </c>
       <c r="T50" t="n">
-        <v>34.95081699346405</v>
+        <v>32.70774171737661</v>
       </c>
       <c r="U50" t="n">
-        <v>42.32036025332248</v>
+        <v>40.73783598787858</v>
       </c>
       <c r="V50" t="n">
         <v>32</v>
@@ -5936,10 +5936,10 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AG50" t="n">
-        <v>16.78481844242714</v>
+        <v>16.93866459627329</v>
       </c>
       <c r="AH50" t="n">
-        <v>22.50089584328715</v>
+        <v>22.34704968944099</v>
       </c>
       <c r="AI50" t="n">
         <v>23.56568654157959</v>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C51" t="n">
-        <v>538.09002686</v>
+        <v>536.9450073199999</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,16 +5989,16 @@
         <v>15.06813824398204</v>
       </c>
       <c r="K51" t="n">
-        <v>3.395343094090175</v>
+        <v>3.175324728615903</v>
       </c>
       <c r="L51" t="n">
         <v>17</v>
       </c>
       <c r="M51" t="n">
-        <v>29.41176470588235</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="N51" t="n">
-        <v>12.38602575436714</v>
+        <v>11.2031956956144</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C52" t="n">
-        <v>194.19000244</v>
+        <v>192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6095,25 +6095,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>14.36732723063363</v>
+        <v>16.63935213539153</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4344433997925723</v>
+        <v>2.008287512219153</v>
       </c>
       <c r="L52" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M52" t="n">
-        <v>57.14285714285715</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="N52" t="n">
-        <v>8.979590422454168</v>
+        <v>9.770564092829414</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>2.554458922020308</v>
+        <v>0.97218815447917</v>
       </c>
       <c r="Q52" t="n">
         <v>24</v>
@@ -6122,10 +6122,10 @@
         <v>41.66666666666666</v>
       </c>
       <c r="S52" t="n">
-        <v>36.51960784313726</v>
+        <v>36.58958001063264</v>
       </c>
       <c r="T52" t="n">
-        <v>5.147058823529406</v>
+        <v>5.07708665603402</v>
       </c>
       <c r="U52" t="n">
         <v>24.46760260981176</v>
@@ -6176,31 +6176,27 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C53" t="n">
-        <v>269.30999756</v>
+        <v>299.76998901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6211,55 +6207,65 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>1.48472039509151</v>
+        <v>12.96303068266793</v>
       </c>
       <c r="L53" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M53" t="n">
-        <v>82.35294117647059</v>
+        <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>12.41457297963144</v>
+        <v>11.79551441110968</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>8.390701153589974</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R53" t="n">
-        <v>57.14285714285715</v>
+        <v>62.5</v>
       </c>
       <c r="S53" t="n">
-        <v>55.65410543482242</v>
+        <v>61.5021706108263</v>
       </c>
       <c r="T53" t="n">
-        <v>1.488751708034727</v>
+        <v>0.9978293891736953</v>
       </c>
       <c r="U53" t="n">
-        <v>42.20623987810458</v>
+        <v>48.36276351921527</v>
       </c>
       <c r="V53" t="n">
         <v>64</v>
       </c>
       <c r="W53" t="n">
-        <v>60.9375</v>
-      </c>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
+        <v>68.75</v>
+      </c>
+      <c r="X53" t="n">
+        <v>12.96303068266793</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
       <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>12.54970589597803</v>
+      </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
-      <c r="AD53" t="inlineStr"/>
+      <c r="AD53" t="n">
+        <v>9.999999999999998</v>
+      </c>
       <c r="AE53" t="n">
         <v>35</v>
       </c>
@@ -6289,10 +6295,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C54" t="n">
-        <v>565.72998047</v>
+        <v>564.47998047</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,10 +6394,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C55" t="n">
-        <v>248.47999573</v>
+        <v>248.42999268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6416,25 +6422,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>10.971007588959</v>
+        <v>11.44128000083862</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2622740972442417</v>
+        <v>0.7744122728911229</v>
       </c>
       <c r="L55" t="n">
         <v>14</v>
       </c>
       <c r="M55" t="n">
-        <v>28.57142857142857</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N55" t="n">
-        <v>8.138531162827295</v>
+        <v>7.525232615082142</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>2.730564339783914</v>
+        <v>2.208484948621803</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6497,10 +6503,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C56" t="n">
-        <v>92.76999664</v>
+        <v>91.70999908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6557,25 +6563,25 @@
         <v>36.8421052631579</v>
       </c>
       <c r="X56" t="n">
-        <v>12.29991136200468</v>
+        <v>10.02075913024301</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.767012806547875</v>
+        <v>3.878004861193818</v>
       </c>
       <c r="Z56" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AA56" t="n">
-        <v>38.88888888888889</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB56" t="n">
-        <v>7.533028523046828</v>
+        <v>8.784158376605012</v>
       </c>
       <c r="AC56" t="n">
         <v>4</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.268074990845458</v>
+        <v>0.1269169856805585</v>
       </c>
       <c r="AE56" t="n">
         <v>19</v>
@@ -6606,10 +6612,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C57" t="n">
-        <v>682.3099975600001</v>
+        <v>726.6295166</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6666,25 +6672,25 @@
         <v>60.52631578947368</v>
       </c>
       <c r="X57" t="n">
-        <v>27.55411108915111</v>
+        <v>35.57429187044519</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.4377580964353811</v>
+        <v>0.2430680602233837</v>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="n">
-        <v>35.29411764705883</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB57" t="n">
-        <v>9.296077668789271</v>
+        <v>12.23736859190473</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.586698126938705</v>
+        <v>5.770959298600009</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6715,14 +6721,14 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C58" t="n">
-        <v>49.38000107</v>
+        <v>50.16949844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6732,7 +6738,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6743,25 +6749,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>23.35521028504311</v>
+        <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>3.132832010189435</v>
+        <v>6.15636949519045</v>
       </c>
       <c r="L58" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="M58" t="n">
-        <v>70.96774193548387</v>
+        <v>68.75</v>
       </c>
       <c r="N58" t="n">
-        <v>15.86076361200199</v>
+        <v>16.43157808826553</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>4.719319633663988</v>
+        <v>1.736712091395587</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6784,12 +6790,8 @@
       <c r="W58" t="n">
         <v>61.19402985074627</v>
       </c>
-      <c r="X58" t="n">
-        <v>33.48291075741479</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>20.95405777871058</v>
-      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
         <v>0</v>
       </c>
@@ -6798,9 +6800,7 @@
       <c r="AC58" t="n">
         <v>10</v>
       </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
         <v>19</v>
       </c>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C59" t="n">
-        <v>147.1499939</v>
+        <v>148.86999512</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6869,19 +6869,19 @@
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R59" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="S59" t="n">
-        <v>13.66666666666667</v>
+        <v>14.64285714285714</v>
       </c>
       <c r="T59" t="n">
-        <v>39.66666666666667</v>
+        <v>35.35714285714286</v>
       </c>
       <c r="U59" t="n">
-        <v>30.1169800254984</v>
+        <v>26.79920245241363</v>
       </c>
       <c r="V59" t="n">
         <v>22</v>
@@ -6890,23 +6890,25 @@
         <v>40.90909090909091</v>
       </c>
       <c r="X59" t="n">
-        <v>23.871169707925</v>
+        <v>22.36431024033017</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.2261052663381</v>
+        <v>5.130004552561241</v>
       </c>
       <c r="Z59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="inlineStr"/>
+        <v>14.28571428571429</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>14.09380874649435</v>
+      </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.024461972471737</v>
+        <v>5.133335808092143</v>
       </c>
       <c r="AE59" t="n">
         <v>19</v>
@@ -6915,10 +6917,10 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AG59" t="n">
-        <v>11.18648894964685</v>
+        <v>11.70412920412921</v>
       </c>
       <c r="AH59" t="n">
-        <v>15.12930052403736</v>
+        <v>14.611660269555</v>
       </c>
       <c r="AI59" t="n">
         <v>11.80641234678251</v>
@@ -6937,19 +6939,19 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C60" t="n">
-        <v>240.75999451</v>
+        <v>254.72999573</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6964,12 +6966,8 @@
       <c r="I60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
-        <v>21.20188911495867</v>
-      </c>
-      <c r="K60" t="n">
-        <v>20.00797545927087</v>
-      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>0</v>
       </c>
@@ -6978,9 +6976,7 @@
       <c r="O60" t="n">
         <v>5</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
         <v>48</v>
       </c>
@@ -6988,40 +6984,40 @@
         <v>62.5</v>
       </c>
       <c r="S60" t="n">
-        <v>44.93651486140802</v>
+        <v>45.04068152807469</v>
       </c>
       <c r="T60" t="n">
-        <v>17.56348513859198</v>
+        <v>17.45931847192531</v>
       </c>
       <c r="U60" t="n">
         <v>48.36276351921527</v>
       </c>
       <c r="V60" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W60" t="n">
-        <v>69.14893617021276</v>
+        <v>69.47368421052632</v>
       </c>
       <c r="X60" t="n">
-        <v>23.56196063195279</v>
+        <v>27.33027772092391</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.876277743170474</v>
+        <v>0.2818560299849726</v>
       </c>
       <c r="Z60" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AA60" t="n">
-        <v>44.44444444444444</v>
+        <v>48</v>
       </c>
       <c r="AB60" t="n">
-        <v>11.54336144532113</v>
+        <v>12.92183659638986</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.186615388579993</v>
+        <v>4.731479931509519</v>
       </c>
       <c r="AE60" t="n">
         <v>53</v>
@@ -7052,10 +7048,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C61" t="n">
-        <v>203.52000427</v>
+        <v>204.96499634</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,10 +7093,10 @@
         <v>40.625</v>
       </c>
       <c r="S61" t="n">
-        <v>40.21348148890225</v>
+        <v>40.76035648890225</v>
       </c>
       <c r="T61" t="n">
-        <v>0.4115185110977535</v>
+        <v>-0.1353564889022465</v>
       </c>
       <c r="U61" t="n">
         <v>25.51963484266544</v>
@@ -7151,10 +7147,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C62" t="n">
-        <v>497.75</v>
+        <v>494.38000488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,24 +7246,24 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C63" t="n">
-        <v>977.5</v>
+        <v>1043.8449707</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7277,27 +7273,17 @@
       <c r="I63" t="n">
         <v>10</v>
       </c>
-      <c r="J63" t="n">
-        <v>13.41136277305126</v>
-      </c>
-      <c r="K63" t="n">
-        <v>8.298252430268494</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>49</v>
-      </c>
-      <c r="M63" t="n">
-        <v>61.22448979591837</v>
-      </c>
-      <c r="N63" t="n">
-        <v>12.24756570819475</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>4</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>59</v>
       </c>
@@ -7320,25 +7306,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X63" t="n">
-        <v>26.04595216565901</v>
+        <v>26.03182453415183</v>
       </c>
       <c r="Y63" t="n">
-        <v>6.226019080029621</v>
+        <v>1.939428244462815</v>
       </c>
       <c r="Z63" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AA63" t="n">
-        <v>45</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.96356508612536</v>
+        <v>11.76137818193657</v>
       </c>
       <c r="AC63" t="n">
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2.101325454917957</v>
       </c>
       <c r="AE63" t="n">
         <v>54</v>
@@ -7369,10 +7355,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C64" t="n">
-        <v>81.27999878</v>
+        <v>80.05999756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7414,10 +7400,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S64" t="n">
-        <v>26.28593958951101</v>
+        <v>25.93309063355146</v>
       </c>
       <c r="T64" t="n">
-        <v>30.85691755334613</v>
+        <v>31.20976650930568</v>
       </c>
       <c r="U64" t="n">
         <v>36.54655436930671</v>
@@ -7446,10 +7432,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AG64" t="n">
-        <v>9.676402593069261</v>
+        <v>9.685220935220935</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.65693074026407</v>
+        <v>23.6481123981124</v>
       </c>
       <c r="AI64" t="n">
         <v>16.27877475083369</v>
@@ -7468,10 +7454,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C65" t="n">
-        <v>124.38999939</v>
+        <v>122.06999969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7499,22 +7485,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>3.65833282500001</v>
+        <v>1.724999741666666</v>
       </c>
       <c r="L65" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M65" t="n">
-        <v>56.75675675675676</v>
+        <v>55</v>
       </c>
       <c r="N65" t="n">
-        <v>12.31882085729384</v>
+        <v>11.67895108850531</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.117855653443938</v>
+        <v>8.134677099383559</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7538,19 +7524,19 @@
         <v>67.44186046511628</v>
       </c>
       <c r="X65" t="n">
-        <v>31.22210989107497</v>
+        <v>19.61980116727053</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.056762835840637</v>
+        <v>9.771597498465667</v>
       </c>
       <c r="Z65" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA65" t="n">
-        <v>33.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB65" t="n">
-        <v>7.375932098061977</v>
+        <v>9.67392877385792</v>
       </c>
       <c r="AC65" t="n">
         <v>6</v>
@@ -7587,10 +7573,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C66" t="n">
-        <v>75.30999756</v>
+        <v>73.625</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7604,7 +7590,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7615,25 +7601,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>10.25119598904701</v>
+        <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3731824397611883</v>
+        <v>5.013549221819069</v>
       </c>
       <c r="L66" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M66" t="n">
-        <v>56.41025641025641</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N66" t="n">
-        <v>11.01887258905039</v>
+        <v>14.72246063738556</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>9.591025537141196</v>
+        <v>4.748388008149407</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7642,10 +7628,10 @@
         <v>59.375</v>
       </c>
       <c r="S66" t="n">
-        <v>42.71979243790606</v>
+        <v>41.63020375686206</v>
       </c>
       <c r="T66" t="n">
-        <v>16.65520756209394</v>
+        <v>17.74479624313794</v>
       </c>
       <c r="U66" t="n">
         <v>42.26002487538288</v>
@@ -7656,27 +7642,17 @@
       <c r="W66" t="n">
         <v>65.11627906976744</v>
       </c>
-      <c r="X66" t="n">
-        <v>14.39517840252906</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>9.91626921258244</v>
-      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>10.35058875984423</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
         <v>10</v>
       </c>
-      <c r="AD66" t="n">
-        <v>0.0929477350523511</v>
-      </c>
+      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="n">
         <v>26</v>
       </c>
@@ -7706,10 +7682,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C67" t="n">
-        <v>36.36000061</v>
+        <v>36.23500061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,46 +7710,46 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>16.22888899858401</v>
+        <v>16.29173844409661</v>
       </c>
       <c r="K67" t="n">
-        <v>1.791711556946018</v>
+        <v>2.503542229997713</v>
       </c>
       <c r="L67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M67" t="n">
-        <v>47.82608695652174</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N67" t="n">
-        <v>11.42908879249151</v>
+        <v>11.76148344880915</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2046222033878164</v>
+        <v>7.313364598836714</v>
       </c>
       <c r="Q67" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R67" t="n">
-        <v>37.93103448275862</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="S67" t="n">
-        <v>29.17463433944165</v>
+        <v>24.18883404177522</v>
       </c>
       <c r="T67" t="n">
-        <v>8.756400143316974</v>
+        <v>9.144499291558116</v>
       </c>
       <c r="U67" t="n">
-        <v>22.68802210080984</v>
+        <v>19.75022767922068</v>
       </c>
       <c r="V67" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W67" t="n">
-        <v>54.05405405405406</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -7793,10 +7769,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="AG67" t="n">
-        <v>15.21740612511404</v>
+        <v>15.32491511193337</v>
       </c>
       <c r="AH67" t="n">
-        <v>36.50673180592045</v>
+        <v>36.39922281910111</v>
       </c>
       <c r="AI67" t="n">
         <v>34.43102188199472</v>
@@ -7815,10 +7791,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C68" t="n">
-        <v>138.47000122</v>
+        <v>137.24499512</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7846,22 +7822,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>6.196795665158716</v>
+        <v>5.257301757856836</v>
       </c>
       <c r="L68" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M68" t="n">
-        <v>69.56521739130434</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="N68" t="n">
-        <v>11.7935395396623</v>
+        <v>12.72095128489728</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>3.581279746738208</v>
+        <v>4.505814003339825</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7870,10 +7846,10 @@
         <v>48.93617021276596</v>
       </c>
       <c r="S68" t="n">
-        <v>51.51842850001017</v>
+        <v>52.54195353519956</v>
       </c>
       <c r="T68" t="n">
-        <v>-2.582258287244215</v>
+        <v>-3.605783322433602</v>
       </c>
       <c r="U68" t="n">
         <v>35.27555503368215</v>
@@ -7885,19 +7861,19 @@
         <v>60</v>
       </c>
       <c r="X68" t="n">
-        <v>33.81037747655053</v>
+        <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>7.439842530862039</v>
+        <v>8.258696842392709</v>
       </c>
       <c r="Z68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AB68" t="n">
-        <v>5.328808636891286</v>
+        <v>11.28626210482051</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7934,14 +7910,14 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C69" t="n">
-        <v>219.33999634</v>
+        <v>225.60499573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7951,7 +7927,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -7965,16 +7941,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>4.982531960331849</v>
+        <v>7.981143748729114</v>
       </c>
       <c r="L69" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M69" t="n">
-        <v>65.21739130434783</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N69" t="n">
-        <v>11.42019995364024</v>
+        <v>11.35964129165207</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -7989,10 +7965,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S69" t="n">
-        <v>67.92284635192532</v>
+        <v>68.9327301854474</v>
       </c>
       <c r="T69" t="n">
-        <v>-6.22071869235085</v>
+        <v>-7.230602525872932</v>
       </c>
       <c r="U69" t="n">
         <v>47.42656695641357</v>
@@ -8007,22 +7983,22 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>6.568409665447994</v>
+        <v>3.899726952672944</v>
       </c>
       <c r="Z69" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AA69" t="n">
-        <v>50</v>
+        <v>40.42553191489362</v>
       </c>
       <c r="AB69" t="n">
-        <v>11.46961297183301</v>
+        <v>12.61345573411901</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>2.185501643988808</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8053,10 +8029,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C70" t="n">
-        <v>227.94999695</v>
+        <v>229.94000244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8084,22 +8060,22 @@
         <v>10.65198616240091</v>
       </c>
       <c r="K70" t="n">
-        <v>5.210926382017966</v>
+        <v>6.129418700112277</v>
       </c>
       <c r="L70" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M70" t="n">
-        <v>39.28571428571428</v>
+        <v>40</v>
       </c>
       <c r="N70" t="n">
-        <v>13.04868169814502</v>
+        <v>11.72424633069284</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>4.551878576368629</v>
+        <v>3.647039008877218</v>
       </c>
       <c r="Q70" t="n">
         <v>32</v>
@@ -8108,10 +8084,10 @@
         <v>59.375</v>
       </c>
       <c r="S70" t="n">
-        <v>41.77919823232323</v>
+        <v>41.93110795454545</v>
       </c>
       <c r="T70" t="n">
-        <v>17.59580176767677</v>
+        <v>17.44389204545455</v>
       </c>
       <c r="U70" t="n">
         <v>42.26002487538288</v>
@@ -8162,29 +8138,29 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C71" t="n">
-        <v>150.58999634</v>
+        <v>148.99000549</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -8197,22 +8173,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K71" t="n">
-        <v>8.338126863309348</v>
+        <v>7.187054309352514</v>
       </c>
       <c r="L71" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M71" t="n">
-        <v>61.53846153846154</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>9.999584585022177</v>
+        <v>10.88869311955713</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.7584364510113684</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8221,10 +8197,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="S71" t="n">
-        <v>25.18511272517829</v>
+        <v>25.18709732468611</v>
       </c>
       <c r="T71" t="n">
-        <v>39.52076962776289</v>
+        <v>39.51878502825507</v>
       </c>
       <c r="U71" t="n">
         <v>47.91396311978173</v>
@@ -8239,16 +8215,16 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y71" t="n">
-        <v>11.78090273539399</v>
+        <v>12.71821432214737</v>
       </c>
       <c r="Z71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA71" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB71" t="n">
-        <v>10.3153604625776</v>
+        <v>10.31728732748828</v>
       </c>
       <c r="AC71" t="n">
         <v>10</v>
@@ -8285,24 +8261,24 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C72" t="n">
-        <v>59.29000092</v>
+        <v>57.13000107</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8312,17 +8288,27 @@
       <c r="I72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>10.6162778911167</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.2280720526315783</v>
+      </c>
       <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="M72" t="n">
+        <v>51.72413793103448</v>
+      </c>
+      <c r="N72" t="n">
+        <v>17.2639723534175</v>
+      </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>2.765620340290331</v>
+      </c>
       <c r="Q72" t="n">
         <v>30</v>
       </c>
@@ -8345,25 +8331,25 @@
         <v>69.62025316455696</v>
       </c>
       <c r="X72" t="n">
-        <v>15.6720464761638</v>
+        <v>12.66784838130402</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.02524620932079</v>
+        <v>10.41241860138447</v>
       </c>
       <c r="Z72" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA72" t="n">
-        <v>53.84615384615385</v>
+        <v>56</v>
       </c>
       <c r="AB72" t="n">
-        <v>10.04796355838424</v>
+        <v>11.82984176474623</v>
       </c>
       <c r="AC72" t="n">
         <v>10</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.199528548767638</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
         <v>33</v>
@@ -8394,19 +8380,19 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C73" t="n">
-        <v>133.66000366</v>
+        <v>129.41070557</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8421,17 +8407,27 @@
       <c r="I73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>12.28237922496582</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.117910745771367</v>
+      </c>
       <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="M73" t="n">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="N73" t="n">
+        <v>8.176251134453048</v>
+      </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>0.8723373017925251</v>
+      </c>
       <c r="Q73" t="n">
         <v>16</v>
       </c>
@@ -8493,10 +8489,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C74" t="n">
-        <v>27.63999939</v>
+        <v>27.60499954</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8538,10 +8534,10 @@
         <v>44.44444444444444</v>
       </c>
       <c r="S74" t="n">
-        <v>24.87433862433862</v>
+        <v>25.1521164021164</v>
       </c>
       <c r="T74" t="n">
-        <v>19.57010582010582</v>
+        <v>19.29232804232804</v>
       </c>
       <c r="U74" t="n">
         <v>24.55951812700564</v>
@@ -8553,25 +8549,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X74" t="n">
-        <v>13.1731874460205</v>
+        <v>11.57371556196134</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.37487072731534</v>
+        <v>5.494692196340867</v>
       </c>
       <c r="Z74" t="n">
         <v>14</v>
       </c>
       <c r="AA74" t="n">
-        <v>21.42857142857143</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB74" t="n">
-        <v>11.43386932212815</v>
+        <v>9.635841473093306</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.887844601359815</v>
+        <v>4.767253721895914</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8580,10 +8576,10 @@
         <v>41.1764705882353</v>
       </c>
       <c r="AG74" t="n">
-        <v>21.31907308377897</v>
+        <v>21.46613190730838</v>
       </c>
       <c r="AH74" t="n">
-        <v>19.85739750445633</v>
+        <v>19.71033868092692</v>
       </c>
       <c r="AI74" t="n">
         <v>21.61105679021481</v>
@@ -8602,31 +8598,27 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C75" t="n">
-        <v>176.24000549</v>
+        <v>182.8999939</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8637,85 +8629,85 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K75" t="n">
-        <v>7.104224991383257</v>
+        <v>11.1516198783808</v>
       </c>
       <c r="L75" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M75" t="n">
-        <v>85.71428571428571</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>19.98901470157656</v>
+        <v>17.76304101843429</v>
       </c>
       <c r="O75" t="n">
         <v>10</v>
       </c>
       <c r="P75" t="n">
-        <v>2.703698205042548</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R75" t="n">
-        <v>76.66666666666667</v>
+        <v>74.19354838709677</v>
       </c>
       <c r="S75" t="n">
-        <v>72.32736958805967</v>
+        <v>72.87129925261223</v>
       </c>
       <c r="T75" t="n">
-        <v>4.339297078607004</v>
+        <v>1.322249134484537</v>
       </c>
       <c r="U75" t="n">
-        <v>59.07167384187784</v>
+        <v>56.7538641905662</v>
       </c>
       <c r="V75" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W75" t="n">
-        <v>79.24528301886792</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="X75" t="n">
-        <v>23.35952775538022</v>
+        <v>11.44333119476051</v>
       </c>
       <c r="Y75" t="n">
-        <v>6.439448927241664</v>
+        <v>0.2617575347509171</v>
       </c>
       <c r="Z75" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AA75" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AB75" t="n">
-        <v>15.57487031324568</v>
+        <v>14.9208019071865</v>
       </c>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.745428832078278</v>
       </c>
       <c r="AE75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF75" t="n">
-        <v>77.77777777777777</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="AG75" t="n">
-        <v>17.10497654022461</v>
+        <v>17.65208303810752</v>
       </c>
       <c r="AH75" t="n">
-        <v>60.67280123755316</v>
+        <v>61.29528538294511</v>
       </c>
       <c r="AI75" t="n">
-        <v>54.78541568378738</v>
+        <v>56.66572155618583</v>
       </c>
       <c r="AJ75" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AK75" t="n">
-        <v>52.94117647058823</v>
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="76">
@@ -8725,10 +8717,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C76" t="n">
-        <v>190.47999573</v>
+        <v>187.77999878</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8770,10 +8762,10 @@
         <v>39.1304347826087</v>
       </c>
       <c r="S76" t="n">
-        <v>19.41476458352889</v>
+        <v>19.44263526357348</v>
       </c>
       <c r="T76" t="n">
-        <v>19.71567019907981</v>
+        <v>19.68779951903522</v>
       </c>
       <c r="U76" t="n">
         <v>22.15762279247795</v>
@@ -8802,10 +8794,10 @@
         <v>30</v>
       </c>
       <c r="AG76" t="n">
-        <v>12.06944444444444</v>
+        <v>12.19345238095238</v>
       </c>
       <c r="AH76" t="n">
-        <v>17.93055555555556</v>
+        <v>17.80654761904762</v>
       </c>
       <c r="AI76" t="n">
         <v>14.54772448676043</v>
@@ -8824,10 +8816,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C77" t="n">
-        <v>188.71000671</v>
+        <v>192.55000305</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8869,10 +8861,10 @@
         <v>45.94594594594594</v>
       </c>
       <c r="S77" t="n">
-        <v>43.45862567636761</v>
+        <v>43.74503262661158</v>
       </c>
       <c r="T77" t="n">
-        <v>2.487320269578333</v>
+        <v>2.200913319334369</v>
       </c>
       <c r="U77" t="n">
         <v>31.03856980437303</v>
@@ -8884,25 +8876,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>23.63741924470009</v>
+        <v>23.29898876327645</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.667446661962102</v>
+        <v>0.04153134401354563</v>
       </c>
       <c r="Z77" t="n">
         <v>17</v>
       </c>
       <c r="AA77" t="n">
-        <v>29.41176470588235</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB77" t="n">
-        <v>10.71303653994351</v>
+        <v>8.03450545973401</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>8.473850271530193</v>
+        <v>9.962606260265117</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8933,10 +8925,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C78" t="n">
-        <v>193.53999329</v>
+        <v>194.83000183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8955,7 +8947,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -8965,40 +8957,40 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>15.44429116110657</v>
+        <v>15.7351954478678</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8861535563142287</v>
+        <v>1.909200381710141</v>
       </c>
       <c r="L78" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M78" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N78" t="n">
-        <v>10.78993917435211</v>
+        <v>13.08999219944563</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>1.104062752341961</v>
+        <v>0.08909854846250731</v>
       </c>
       <c r="Q78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R78" t="n">
-        <v>46.15384615384615</v>
+        <v>50</v>
       </c>
       <c r="S78" t="n">
-        <v>22.87740646099779</v>
+        <v>25.04092327621739</v>
       </c>
       <c r="T78" t="n">
-        <v>23.27643969284836</v>
+        <v>24.95907672378261</v>
       </c>
       <c r="U78" t="n">
-        <v>23.2060678095383</v>
+        <v>25.37815976337061</v>
       </c>
       <c r="V78" t="n">
         <v>29</v>
@@ -9046,10 +9038,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C79" t="n">
-        <v>104.62999725</v>
+        <v>106.81999969</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9091,10 +9083,10 @@
         <v>44.44444444444444</v>
       </c>
       <c r="S79" t="n">
-        <v>47.90623728123728</v>
+        <v>48.09142246642246</v>
       </c>
       <c r="T79" t="n">
-        <v>-3.461792836792839</v>
+        <v>-3.646978021978022</v>
       </c>
       <c r="U79" t="n">
         <v>27.585858177023</v>
@@ -9145,14 +9137,14 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C80" t="n">
-        <v>52.08000183</v>
+        <v>51.36999893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9162,7 +9154,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9173,25 +9165,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>14.7204727843671</v>
+        <v>16.51637120732817</v>
       </c>
       <c r="K80" t="n">
-        <v>1.008534612457468</v>
+        <v>1.774763559804482</v>
       </c>
       <c r="L80" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="M80" t="n">
-        <v>64.58333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N80" t="n">
-        <v>13.86917594453042</v>
+        <v>14.06499869375114</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>2.961596660143595</v>
+        <v>2.186432434095442</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9214,27 +9206,17 @@
       <c r="W80" t="n">
         <v>60</v>
       </c>
-      <c r="X80" t="n">
-        <v>20.24662002189492</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>13.86039923505735</v>
-      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>13.55932437400208</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>2</v>
       </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="n">
         <v>38</v>
       </c>
@@ -9264,10 +9246,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C81" t="n">
-        <v>40.34999847</v>
+        <v>40.91500092</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9284,11 +9266,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>5</v>
       </c>
@@ -9299,17 +9277,13 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K81" t="n">
-        <v>18.36315134190458</v>
+        <v>20.02053605153766</v>
       </c>
       <c r="L81" t="n">
-        <v>5</v>
-      </c>
-      <c r="M81" t="n">
-        <v>100</v>
-      </c>
-      <c r="N81" t="n">
-        <v>14.73687195807274</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>6</v>
       </c>
@@ -9338,25 +9312,25 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X81" t="n">
-        <v>44.25503404501885</v>
+        <v>36.83700278308666</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.632481296466572</v>
+        <v>3.297093842660881</v>
       </c>
       <c r="Z81" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AA81" t="n">
-        <v>20</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB81" t="n">
-        <v>8.686067454850761</v>
+        <v>13.78032059620465</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.531096068465345</v>
+        <v>4.863252144343333</v>
       </c>
       <c r="AE81" t="n">
         <v>76</v>
@@ -9387,14 +9361,14 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C82" t="n">
-        <v>404.10998535</v>
+        <v>406.48001099</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9404,7 +9378,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9415,66 +9389,58 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>11.26352308918246</v>
+        <v>11.8900081911483</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1065182019909683</v>
+        <v>1.409581271188975</v>
       </c>
       <c r="L82" t="n">
+        <v>22</v>
+      </c>
+      <c r="M82" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="N82" t="n">
+        <v>10.64662700539032</v>
+      </c>
+      <c r="O82" t="n">
+        <v>10</v>
+      </c>
+      <c r="P82" t="n">
+        <v>8.471012917249476</v>
+      </c>
+      <c r="Q82" t="n">
         <v>21</v>
       </c>
-      <c r="M82" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="N82" t="n">
-        <v>11.19424651929636</v>
-      </c>
-      <c r="O82" t="n">
-        <v>10</v>
-      </c>
-      <c r="P82" t="n">
-        <v>9.882954652409715</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>20</v>
-      </c>
       <c r="R82" t="n">
-        <v>25</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="S82" t="n">
-        <v>24.17752100840336</v>
+        <v>24.69287715086034</v>
       </c>
       <c r="T82" t="n">
-        <v>0.8224789915966362</v>
+        <v>-0.8833533413365302</v>
       </c>
       <c r="U82" t="n">
-        <v>11.18617014076657</v>
+        <v>10.62801302263647</v>
       </c>
       <c r="V82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W82" t="n">
-        <v>27.27272727272727</v>
-      </c>
-      <c r="X82" t="n">
-        <v>12.75746676473251</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>11.16900258946693</v>
-      </c>
+        <v>26.08695652173913</v>
+      </c>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
         <v>8</v>
       </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="n">
         <v>20</v>
       </c>
@@ -9504,10 +9470,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C83" t="n">
-        <v>280.13000488</v>
+        <v>273.73999023</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9535,13 +9501,17 @@
         <v>23.66411973888177</v>
       </c>
       <c r="K83" t="n">
-        <v>4.917604823970034</v>
+        <v>2.524340910112355</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N83" t="n">
+        <v>7.952586279424212</v>
+      </c>
       <c r="O83" t="n">
         <v>2</v>
       </c>
@@ -9609,10 +9579,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C84" t="n">
-        <v>25.38999939</v>
+        <v>25.69000053</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9669,19 +9639,19 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X84" t="n">
-        <v>16.02758025615572</v>
+        <v>14.74222881006126</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.718532871416815</v>
+        <v>4.604529393709466</v>
       </c>
       <c r="Z84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA84" t="n">
-        <v>28.57142857142857</v>
+        <v>20</v>
       </c>
       <c r="AB84" t="n">
-        <v>15.35012986685182</v>
+        <v>11.83959366477939</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9696,10 +9666,10 @@
         <v>25</v>
       </c>
       <c r="AG84" t="n">
-        <v>11.95075757575758</v>
+        <v>12.20678275972394</v>
       </c>
       <c r="AH84" t="n">
-        <v>13.04924242424242</v>
+        <v>12.79321724027606</v>
       </c>
       <c r="AI84" t="n">
         <v>11.18617014076657</v>
@@ -9718,10 +9688,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C85" t="n">
-        <v>126.55000305</v>
+        <v>129.77999878</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9746,10 +9716,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>24.44307767384616</v>
+        <v>23.66801733058809</v>
       </c>
       <c r="K85" t="n">
-        <v>3.070536168317761</v>
+        <v>5.701254332591055</v>
       </c>
       <c r="L85" t="n">
         <v>2</v>
@@ -9823,14 +9793,14 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C86" t="n">
-        <v>366.20001221</v>
+        <v>374.79998779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9840,7 +9810,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9883,25 +9853,25 @@
         <v>75</v>
       </c>
       <c r="X86" t="n">
-        <v>21.71653838636141</v>
+        <v>18.66270892223245</v>
       </c>
       <c r="Y86" t="n">
-        <v>4.6453483838369</v>
+        <v>2.406004724645139</v>
       </c>
       <c r="Z86" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="AA86" t="n">
-        <v>31.25</v>
+        <v>43.10344827586207</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.16877540372585</v>
+        <v>13.51480539732798</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>0.6086391623572163</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9932,10 +9902,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C87" t="n">
-        <v>430.26000977</v>
+        <v>441.42001343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9977,10 +9947,10 @@
         <v>62.85714285714285</v>
       </c>
       <c r="S87" t="n">
-        <v>38.38684469652211</v>
+        <v>38.53446374414116</v>
       </c>
       <c r="T87" t="n">
-        <v>24.47029816062074</v>
+        <v>24.32267911300169</v>
       </c>
       <c r="U87" t="n">
         <v>46.33693684359532</v>
@@ -10031,14 +10001,14 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C88" t="n">
-        <v>258.14001465</v>
+        <v>268.91500854</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10048,7 +10018,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10062,22 +10032,22 @@
         <v>14.3256649882924</v>
       </c>
       <c r="K88" t="n">
-        <v>4.034179491851875</v>
+        <v>8.37665870762061</v>
       </c>
       <c r="L88" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M88" t="n">
-        <v>60.71428571428572</v>
+        <v>30</v>
       </c>
       <c r="N88" t="n">
-        <v>8.97708126089338</v>
+        <v>6.999718865000822</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>5.734481241922418</v>
+        <v>1.497869847380007</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10104,22 +10074,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>5.557374845920848</v>
+        <v>1.615255642237912</v>
       </c>
       <c r="Z88" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>23.07692307692308</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.03178436035473</v>
+        <v>11.25813856665627</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.423896482456989</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10128,10 +10098,10 @@
         <v>37.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>14.92101648351648</v>
+        <v>14.49900793650794</v>
       </c>
       <c r="AH88" t="n">
-        <v>22.57898351648352</v>
+        <v>23.00099206349206</v>
       </c>
       <c r="AI88" t="n">
         <v>21.15936755954878</v>
@@ -10150,14 +10120,14 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C89" t="n">
-        <v>70.87000275</v>
+        <v>70.85500336</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10167,7 +10137,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -10185,7 +10155,7 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K89" t="n">
-        <v>2.354137695520708</v>
+        <v>2.332474797681905</v>
       </c>
       <c r="L89" t="n">
         <v>37</v>
@@ -10194,13 +10164,13 @@
         <v>75.67567567567568</v>
       </c>
       <c r="N89" t="n">
-        <v>14.04876797151395</v>
+        <v>14.04258870465226</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>1.608007591618188</v>
+        <v>1.629517126029545</v>
       </c>
       <c r="Q89" t="n">
         <v>28</v>
@@ -10223,27 +10193,17 @@
       <c r="W89" t="n">
         <v>57.89473684210526</v>
       </c>
-      <c r="X89" t="n">
-        <v>20.8229427476307</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>13.95616512919558</v>
-      </c>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>9.57591789254208</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
         <v>4</v>
       </c>
-      <c r="AD89" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="n">
         <v>29</v>
       </c>
@@ -10273,19 +10233,19 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C90" t="n">
-        <v>375.20999146</v>
+        <v>374.5</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10300,27 +10260,17 @@
       <c r="I90" t="n">
         <v>10</v>
       </c>
-      <c r="J90" t="n">
-        <v>10.39403223569868</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.4228746512227932</v>
-      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>26</v>
-      </c>
-      <c r="M90" t="n">
-        <v>57.69230769230769</v>
-      </c>
-      <c r="N90" t="n">
-        <v>11.43449717362419</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="P90" t="n">
-        <v>7.545218532225073</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>26</v>
       </c>
@@ -10382,10 +10332,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C91" t="n">
-        <v>282.48001099</v>
+        <v>272.3999939</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10410,25 +10360,25 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>11.20483284211199</v>
+        <v>13.62406131818169</v>
       </c>
       <c r="K91" t="n">
-        <v>1.265459267068425</v>
+        <v>0.3869496135603834</v>
       </c>
       <c r="L91" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M91" t="n">
-        <v>33.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N91" t="n">
-        <v>9.288571954097206</v>
+        <v>9.297602702674224</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0.7253615776277256</v>
+        <v>1.606832753310128</v>
       </c>
       <c r="Q91" t="n">
         <v>17</v>
@@ -10469,10 +10419,10 @@
         <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>18.49697931276879</v>
+        <v>18.37197931276879</v>
       </c>
       <c r="AH91" t="n">
-        <v>21.50302068723121</v>
+        <v>21.62802068723121</v>
       </c>
       <c r="AI91" t="n">
         <v>21.88065323728171</v>
@@ -10491,10 +10441,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C92" t="n">
-        <v>369.92999268</v>
+        <v>367.66000366</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10590,31 +10540,27 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C93" t="n">
-        <v>241.49000549</v>
+        <v>254.57000732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>5</v>
       </c>
@@ -10625,64 +10571,64 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>6.411387544532543</v>
+        <v>12.17502625492612</v>
       </c>
       <c r="L93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M93" t="n">
-        <v>88.88888888888889</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N93" t="n">
-        <v>13.64163435046833</v>
+        <v>11.87404846679999</v>
       </c>
       <c r="O93" t="n">
         <v>10</v>
       </c>
       <c r="P93" t="n">
-        <v>3.372395133900175</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R93" t="n">
-        <v>76.47058823529412</v>
+        <v>77.14285714285714</v>
       </c>
       <c r="S93" t="n">
-        <v>67.45538721973514</v>
+        <v>67.26722087681105</v>
       </c>
       <c r="T93" t="n">
-        <v>9.015201015558972</v>
+        <v>9.875636266046087</v>
       </c>
       <c r="U93" t="n">
-        <v>60.00386207746361</v>
+        <v>60.98268310800976</v>
       </c>
       <c r="V93" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W93" t="n">
-        <v>74.07407407407408</v>
+        <v>74.39024390243902</v>
       </c>
       <c r="X93" t="n">
-        <v>11.19238284432267</v>
+        <v>12.3097290736065</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.299750736058849</v>
+        <v>0.1199386907897337</v>
       </c>
       <c r="Z93" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AA93" t="n">
-        <v>44.82758620689656</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB93" t="n">
-        <v>12.92177121046226</v>
+        <v>15.23592640207823</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>3.884720592229429</v>
       </c>
       <c r="AE93" t="n">
         <v>31</v>
@@ -10713,10 +10659,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C94" t="n">
-        <v>48.33000183</v>
+        <v>48.11500168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10773,19 +10719,19 @@
         <v>35</v>
       </c>
       <c r="X94" t="n">
-        <v>12.10674333226271</v>
+        <v>12.08242925132574</v>
       </c>
       <c r="Y94" t="n">
-        <v>6.464092235906493</v>
+        <v>6.880194727903167</v>
       </c>
       <c r="Z94" t="n">
         <v>15</v>
       </c>
       <c r="AA94" t="n">
-        <v>46.66666666666666</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB94" t="n">
-        <v>8.768821837136917</v>
+        <v>8.721012058594662</v>
       </c>
       <c r="AC94" t="n">
         <v>2</v>
@@ -10794,19 +10740,19 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF94" t="n">
-        <v>42.10526315789474</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AG94" t="n">
-        <v>9.162066004171269</v>
+        <v>9.67106967106967</v>
       </c>
       <c r="AH94" t="n">
-        <v>32.94319715372347</v>
+        <v>34.77337477337477</v>
       </c>
       <c r="AI94" t="n">
-        <v>23.14189128245424</v>
+        <v>24.55951812700564</v>
       </c>
       <c r="AJ94" t="n">
         <v>19</v>
@@ -10822,10 +10768,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C95" t="n">
-        <v>28.23999977</v>
+        <v>30.64999962</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10882,25 +10828,25 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X95" t="n">
-        <v>10.73338207305774</v>
+        <v>15.71428665520944</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.587099020180506</v>
+        <v>0.4223556435534404</v>
       </c>
       <c r="Z95" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA95" t="n">
-        <v>44.44444444444444</v>
+        <v>48.97959183673469</v>
       </c>
       <c r="AB95" t="n">
-        <v>13.84894258070201</v>
+        <v>13.00064432445259</v>
       </c>
       <c r="AC95" t="n">
         <v>8</v>
       </c>
       <c r="AD95" t="n">
-        <v>5.556657203896275</v>
+        <v>7.609784711638423</v>
       </c>
       <c r="AE95" t="n">
         <v>51</v>
@@ -10931,10 +10877,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C96" t="n">
-        <v>86.88999939</v>
+        <v>86.52500153</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10994,22 +10940,22 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y96" t="n">
-        <v>5.544079344106212</v>
+        <v>5.940859285938027</v>
       </c>
       <c r="Z96" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA96" t="n">
-        <v>31.57894736842105</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB96" t="n">
-        <v>9.247029805985685</v>
+        <v>8.444925214768407</v>
       </c>
       <c r="AC96" t="n">
         <v>6</v>
       </c>
       <c r="AD96" t="n">
-        <v>0.4826808660885584</v>
+        <v>0.06287609435191577</v>
       </c>
       <c r="AE96" t="n">
         <v>29</v>
@@ -11040,10 +10986,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C97" t="n">
-        <v>106.79000092</v>
+        <v>107.57499695</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11071,16 +11017,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>4.542339031328657</v>
+        <v>5.310812862207115</v>
       </c>
       <c r="L97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M97" t="n">
-        <v>46.15384615384615</v>
+        <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>10.24442328542791</v>
+        <v>9.865823559457239</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -11149,14 +11095,14 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C98" t="n">
-        <v>163.27000427</v>
+        <v>158.46499634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11166,7 +11112,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -11194,10 +11140,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S98" t="n">
-        <v>25.813135322779</v>
+        <v>25.93218294182662</v>
       </c>
       <c r="T98" t="n">
-        <v>31.32972182007815</v>
+        <v>31.21067420103053</v>
       </c>
       <c r="U98" t="n">
         <v>36.54655436930671</v>
@@ -11208,27 +11154,17 @@
       <c r="W98" t="n">
         <v>55.17241379310344</v>
       </c>
-      <c r="X98" t="n">
-        <v>11.95142925876556</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>3.75500774752745</v>
-      </c>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA98" t="n">
-        <v>35</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>12.58665447699926</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
         <v>4</v>
       </c>
-      <c r="AD98" t="n">
-        <v>0.2545506490663763</v>
-      </c>
+      <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="n">
         <v>24</v>
       </c>
@@ -11236,10 +11172,10 @@
         <v>50</v>
       </c>
       <c r="AG98" t="n">
-        <v>23.0822870083706</v>
+        <v>23.29596222204581</v>
       </c>
       <c r="AH98" t="n">
-        <v>26.9177129916294</v>
+        <v>26.70403777795419</v>
       </c>
       <c r="AI98" t="n">
         <v>31.42742581957335</v>
@@ -11258,10 +11194,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C99" t="n">
-        <v>29446.98046875</v>
+        <v>30375.44726562</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -436,7 +436,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -670,7 +670,7 @@
         <v>46286</v>
       </c>
       <c r="C2" t="n">
-        <v>338.42498779</v>
+        <v>338.98001099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>12.78570440965048</v>
+        <v>12.9986380472102</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1696201209439585</v>
+        <v>0.1943244704780023</v>
       </c>
       <c r="Z2" t="n">
         <v>29</v>
@@ -745,7 +745,7 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.843684345930068</v>
+        <v>7.820873400343964</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -779,7 +779,7 @@
         <v>46286</v>
       </c>
       <c r="C3" t="n">
-        <v>264.60998535</v>
+        <v>264.48001099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46286</v>
       </c>
       <c r="C4" t="n">
-        <v>102.77999878</v>
+        <v>102.98000336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>2.441938508235353</v>
+        <v>2.641285240371261</v>
       </c>
       <c r="L4" t="n">
         <v>17</v>
@@ -915,13 +915,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N4" t="n">
-        <v>7.536245754264848</v>
+        <v>7.395298426209745</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.473246937316232</v>
+        <v>3.272284394883718</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -987,7 +987,7 @@
         <v>46286</v>
       </c>
       <c r="C5" t="n">
-        <v>187.02000427</v>
+        <v>186.11000061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.368618300871042</v>
+        <v>5.829076549886702</v>
       </c>
       <c r="Z5" t="n">
         <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.04076975353742</v>
+        <v>9.876429880880892</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1096,21 +1096,21 @@
         <v>46286</v>
       </c>
       <c r="C6" t="n">
-        <v>379.60998535</v>
+        <v>383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1124,22 +1124,22 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>9.083329123563221</v>
+        <v>10.05747126436782</v>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>45.45454545454545</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="N6" t="n">
-        <v>8.711758247621066</v>
+        <v>8.762970374522952</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8403400261083327</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1162,17 +1162,27 @@
       <c r="W6" t="n">
         <v>42.5</v>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>10.37930894252874</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.2915742825754464</v>
+      </c>
       <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.745915768792873</v>
+      </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>3.719270152689302</v>
+      </c>
       <c r="AE6" t="n">
         <v>29</v>
       </c>
@@ -1205,7 +1215,7 @@
         <v>46286</v>
       </c>
       <c r="C7" t="n">
-        <v>270.47000122</v>
+        <v>269.94000244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1314,7 @@
         <v>46286</v>
       </c>
       <c r="C8" t="n">
-        <v>461.48001099</v>
+        <v>464.23999023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,7 +1342,7 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>12.14308280081184</v>
+        <v>12.81377833056154</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -1371,25 +1381,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X8" t="n">
-        <v>12.52459886669746</v>
+        <v>13.85142490989666</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3390512561058601</v>
+        <v>0.9114041217809343</v>
       </c>
       <c r="Z8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AA8" t="n">
-        <v>37.73584905660378</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.03615909163916</v>
+        <v>13.3937646430881</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.693815747952161</v>
+        <v>9.172191610615865</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -1423,7 +1433,7 @@
         <v>46286</v>
       </c>
       <c r="C9" t="n">
-        <v>612.63500977</v>
+        <v>615.52001953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,25 +1490,25 @@
         <v>67.39130434782609</v>
       </c>
       <c r="X9" t="n">
-        <v>39.83881730533485</v>
+        <v>39.99545804313283</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5446485354002717</v>
+        <v>0.188099689266541</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>43.75</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.37366925134289</v>
+        <v>16.29358770374292</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.485226671328514</v>
+        <v>5.822853079282043</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1532,7 +1542,7 @@
         <v>46286</v>
       </c>
       <c r="C10" t="n">
-        <v>257.86499023</v>
+        <v>258.45001221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,22 +1570,22 @@
         <v>12.7936066701423</v>
       </c>
       <c r="K10" t="n">
-        <v>5.552593946232465</v>
+        <v>5.792062621097882</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
-        <v>41.93548387096774</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>11.47379342580538</v>
+        <v>11.39134211987505</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.318660264298411</v>
+        <v>2.087053909526282</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
@@ -1641,7 +1651,7 @@
         <v>46286</v>
       </c>
       <c r="C11" t="n">
-        <v>202.74989319</v>
+        <v>205.41999817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,16 +1679,16 @@
         <v>14.2728744929405</v>
       </c>
       <c r="K11" t="n">
-        <v>11.84966536879755</v>
+        <v>13.32266416457344</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>62.96296296296296</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N11" t="n">
-        <v>13.46029151457658</v>
+        <v>14.60517234197607</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1708,25 +1718,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X11" t="n">
-        <v>13.04296880513336</v>
+        <v>13.61504501497082</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.055619335681879</v>
+        <v>0.2573434269720676</v>
       </c>
       <c r="Z11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AA11" t="n">
-        <v>39.34426229508197</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.09075118217421</v>
+        <v>10.75711369972829</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.018468979939185</v>
+        <v>7.762633199326341</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1760,7 +1770,7 @@
         <v>46286</v>
       </c>
       <c r="C12" t="n">
-        <v>80.69999695</v>
+        <v>80.72000122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,7 +1798,7 @@
         <v>12.33653883634149</v>
       </c>
       <c r="K12" t="n">
-        <v>6.534649438943885</v>
+        <v>6.561057716171614</v>
       </c>
       <c r="L12" t="n">
         <v>22</v>
@@ -1830,22 +1840,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.474439227815862</v>
+        <v>4.450759931882653</v>
       </c>
       <c r="Z12" t="n">
         <v>16</v>
       </c>
       <c r="AA12" t="n">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.111428899320011</v>
+        <v>8.787538517092495</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.784379309075049</v>
+        <v>5.807728103500642</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1879,7 +1889,7 @@
         <v>46286</v>
       </c>
       <c r="C13" t="n">
-        <v>319.05999756</v>
+        <v>322.8999939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,10 +1946,10 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>42.19817109842221</v>
+        <v>43.77716402579273</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.480351999594042</v>
+        <v>0.388699946252935</v>
       </c>
       <c r="Z13" t="n">
         <v>3</v>
@@ -1954,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.531809598437973</v>
+        <v>2.621489783125097</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -1988,7 +1998,7 @@
         <v>46286</v>
       </c>
       <c r="C14" t="n">
-        <v>1701.94494629</v>
+        <v>1711.31994629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,22 +2026,22 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>8.208399028231138</v>
+        <v>8.804454584023969</v>
       </c>
       <c r="L14" t="n">
         <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N14" t="n">
-        <v>8.880447662134857</v>
+        <v>8.992220128437165</v>
       </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>1.655694925586548</v>
+        <v>1.098801901582802</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2097,7 +2107,7 @@
         <v>46286</v>
       </c>
       <c r="C15" t="n">
-        <v>360.79989624</v>
+        <v>362.66000366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,16 +2135,16 @@
         <v>22.3973403666333</v>
       </c>
       <c r="K15" t="n">
-        <v>7.441677990999951</v>
+        <v>7.995594620497459</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M15" t="n">
-        <v>66.66666666666667</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N15" t="n">
-        <v>13.83351318357871</v>
+        <v>14.47003005101384</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -2206,7 +2216,7 @@
         <v>46286</v>
       </c>
       <c r="C16" t="n">
-        <v>312.58999634</v>
+        <v>313.58999634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,22 +2244,22 @@
         <v>11.07429159124881</v>
       </c>
       <c r="K16" t="n">
-        <v>1.269959095294171</v>
+        <v>1.593929664669491</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="N16" t="n">
-        <v>9.629107580588869</v>
+        <v>9.294492093603905</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7208859480419827</v>
+        <v>0.3996994078985017</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2315,7 +2325,7 @@
         <v>46286</v>
       </c>
       <c r="C17" t="n">
-        <v>201.07499695</v>
+        <v>201.1499939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2353,7 @@
         <v>17.56568419419229</v>
       </c>
       <c r="K17" t="n">
-        <v>2.872705437041589</v>
+        <v>2.911074897506838</v>
       </c>
       <c r="L17" t="n">
         <v>34</v>
@@ -2352,13 +2362,13 @@
         <v>58.8235294117647</v>
       </c>
       <c r="N17" t="n">
-        <v>13.19522740948047</v>
+        <v>13.46609029588345</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.039965314096205</v>
+        <v>3.001547798008675</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2533,7 +2543,7 @@
         <v>46286</v>
       </c>
       <c r="C19" t="n">
-        <v>167.86999512</v>
+        <v>168.52000427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2565,7 +2575,7 @@
         <v>23.56732248521627</v>
       </c>
       <c r="K19" t="n">
-        <v>1.063490381638599</v>
+        <v>1.454818167357796</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
@@ -2574,13 +2584,13 @@
         <v>75</v>
       </c>
       <c r="N19" t="n">
-        <v>8.637758974740988</v>
+        <v>8.341748246093617</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>6.863516777589584</v>
+        <v>6.451326758917864</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2646,7 +2656,7 @@
         <v>46286</v>
       </c>
       <c r="C20" t="n">
-        <v>62.89500046</v>
+        <v>62.61999893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,7 +2755,7 @@
         <v>46286</v>
       </c>
       <c r="C21" t="n">
-        <v>134.25500488</v>
+        <v>135.05000305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2854,7 @@
         <v>46286</v>
       </c>
       <c r="C22" t="n">
-        <v>820.39501953</v>
+        <v>816.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,22 +2882,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>6.352818152855511</v>
+        <v>5.847882976611718</v>
       </c>
       <c r="L22" t="n">
         <v>27</v>
       </c>
       <c r="M22" t="n">
-        <v>40.74074074074074</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N22" t="n">
-        <v>10.91990640416717</v>
+        <v>9.752072580897003</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>3.429323181547095</v>
+        <v>3.922720895897136</v>
       </c>
       <c r="Q22" t="n">
         <v>27</v>
@@ -2953,7 +2963,7 @@
         <v>46286</v>
       </c>
       <c r="C23" t="n">
-        <v>23.02499962</v>
+        <v>22.93000031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,22 +2991,22 @@
         <v>18.24497148325086</v>
       </c>
       <c r="K23" t="n">
-        <v>2.974056314214013</v>
+        <v>2.549193579829701</v>
       </c>
       <c r="L23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M23" t="n">
-        <v>50</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N23" t="n">
-        <v>8.906984238639312</v>
+        <v>7.912202245602368</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>0.02519439042667493</v>
+        <v>0.4396001610869504</v>
       </c>
       <c r="Q23" t="n">
         <v>27</v>
@@ -3062,7 +3072,7 @@
         <v>46286</v>
       </c>
       <c r="C24" t="n">
-        <v>127.55999756</v>
+        <v>127.52999878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,13 +3100,13 @@
         <v>10.13804453095366</v>
       </c>
       <c r="K24" t="n">
-        <v>0.233769269918449</v>
+        <v>0.2101969051456765</v>
       </c>
       <c r="L24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>39.02439024390244</v>
+        <v>40</v>
       </c>
       <c r="N24" t="n">
         <v>12.27862100052214</v>
@@ -3105,7 +3115,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.74345352989987</v>
+        <v>9.769268395032604</v>
       </c>
       <c r="Q24" t="n">
         <v>35</v>
@@ -3132,13 +3142,13 @@
         <v>18.83863161428796</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.927974893719227</v>
+        <v>9.949157481654346</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>14.28571428571429</v>
+        <v>12.5</v>
       </c>
       <c r="AB24" t="n">
         <v>12.51331360108521</v>
@@ -3147,7 +3157,7 @@
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.07996390243895091</v>
+        <v>0.05645979196173823</v>
       </c>
       <c r="AE24" t="n">
         <v>36</v>
@@ -3181,7 +3191,7 @@
         <v>46286</v>
       </c>
       <c r="C25" t="n">
-        <v>896.1849975600001</v>
+        <v>898.47998047</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,7 +3290,7 @@
         <v>46286</v>
       </c>
       <c r="C26" t="n">
-        <v>237.95500183</v>
+        <v>236.41999817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3305,25 +3315,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>11.82390399949569</v>
+        <v>11.92082492641692</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5939542430287048</v>
+        <v>0.05501920677632999</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>55.81395348837209</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N26" t="n">
-        <v>11.49687307178913</v>
+        <v>11.21256438173759</v>
       </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>7.362316962984439</v>
+        <v>7.940611931525754</v>
       </c>
       <c r="Q26" t="n">
         <v>35</v>
@@ -3350,16 +3360,16 @@
         <v>16.61377328984133</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.30017833596363</v>
+        <v>11.8723644629563</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.204579259374766</v>
+        <v>8.021609374416245</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
@@ -3399,7 +3409,7 @@
         <v>46286</v>
       </c>
       <c r="C27" t="n">
-        <v>109.55999756</v>
+        <v>111.45999908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,22 +3437,22 @@
         <v>13.9122753572231</v>
       </c>
       <c r="K27" t="n">
-        <v>2.049177475316699</v>
+        <v>3.818925527854478</v>
       </c>
       <c r="L27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M27" t="n">
-        <v>54.54545454545455</v>
+        <v>45</v>
       </c>
       <c r="N27" t="n">
-        <v>10.77081897375242</v>
+        <v>12.1620108159896</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>5.831328259478297</v>
+        <v>4.027275808227992</v>
       </c>
       <c r="Q27" t="n">
         <v>16</v>
@@ -3508,7 +3518,7 @@
         <v>46286</v>
       </c>
       <c r="C28" t="n">
-        <v>87.72709656000001</v>
+        <v>87.59999847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,22 +3546,22 @@
         <v>11.48223102538071</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6160042493055462</v>
+        <v>0.4702328461134497</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>55.55555555555556</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N28" t="n">
-        <v>10.3587507096946</v>
+        <v>9.955292196253463</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.375522473805657</v>
+        <v>1.522607353990746</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3617,7 +3627,7 @@
         <v>46286</v>
       </c>
       <c r="C29" t="n">
-        <v>205</v>
+        <v>203.66999817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,16 +3687,16 @@
         <v>15.3007164090031</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.868306938926137</v>
+        <v>6.479015836644308</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>35.71428571428572</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.711745261131634</v>
+        <v>8.109641567169778</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
@@ -3726,7 +3736,7 @@
         <v>46286</v>
       </c>
       <c r="C30" t="n">
-        <v>690.59997559</v>
+        <v>684.72998047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,22 +3796,22 @@
         <v>21.84840721774197</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.164678016711585</v>
+        <v>2.996263424913914</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>34.78260869565217</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.527482308059199</v>
+        <v>9.428164700328242</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.898055554795154</v>
+        <v>2.06562823849068</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3835,7 +3845,7 @@
         <v>46286</v>
       </c>
       <c r="C31" t="n">
-        <v>213.75500488</v>
+        <v>215.83999634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3944,7 @@
         <v>46286</v>
       </c>
       <c r="C32" t="n">
-        <v>104.30500031</v>
+        <v>104.23000336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,7 +4043,7 @@
         <v>46286</v>
       </c>
       <c r="C33" t="n">
-        <v>13.20499992</v>
+        <v>13.17000008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4061,22 +4071,22 @@
         <v>11.61202677950211</v>
       </c>
       <c r="K33" t="n">
-        <v>2.047916140658801</v>
+        <v>1.777438233889028</v>
       </c>
       <c r="L33" t="n">
         <v>51</v>
       </c>
       <c r="M33" t="n">
-        <v>54.90196078431372</v>
+        <v>56.86274509803921</v>
       </c>
       <c r="N33" t="n">
-        <v>12.92016468574718</v>
+        <v>12.55058230874586</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.872772721682827</v>
+        <v>4.148819069711052</v>
       </c>
       <c r="Q33" t="n">
         <v>42</v>
@@ -4142,7 +4152,7 @@
         <v>46286</v>
       </c>
       <c r="C34" t="n">
-        <v>320.88000488</v>
+        <v>319.01000977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,22 +4180,22 @@
         <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>4.589314749137996</v>
+        <v>3.979798717709726</v>
       </c>
       <c r="L34" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M34" t="n">
-        <v>57.14285714285715</v>
+        <v>48</v>
       </c>
       <c r="N34" t="n">
-        <v>12.27193608235259</v>
+        <v>12.69421011751322</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.261026481570029</v>
+        <v>3.86632916380667</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4251,7 +4261,7 @@
         <v>46286</v>
       </c>
       <c r="C35" t="n">
-        <v>84.0911026</v>
+        <v>83.94999695</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4350,7 +4360,7 @@
         <v>46286</v>
       </c>
       <c r="C36" t="n">
-        <v>356.45001221</v>
+        <v>354.97000122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4449,7 +4459,7 @@
         <v>46286</v>
       </c>
       <c r="C37" t="n">
-        <v>950.95001221</v>
+        <v>959.39001465</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4477,22 +4487,22 @@
         <v>13.30675651903024</v>
       </c>
       <c r="K37" t="n">
-        <v>3.139914556399126</v>
+        <v>4.055316122559649</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>56.41025641025641</v>
+        <v>55.26315789473684</v>
       </c>
       <c r="N37" t="n">
-        <v>11.32105074789215</v>
+        <v>9.954193227163939</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>6.651242123969037</v>
+        <v>5.71300352443167</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4558,7 +4568,7 @@
         <v>46286</v>
       </c>
       <c r="C38" t="n">
-        <v>33.29000092</v>
+        <v>33.38999939</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4586,22 +4596,22 @@
         <v>13.72832922207538</v>
       </c>
       <c r="K38" t="n">
-        <v>1.385722103696163</v>
+        <v>1.690270520939507</v>
       </c>
       <c r="L38" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M38" t="n">
-        <v>50</v>
+        <v>50.90909090909091</v>
       </c>
       <c r="N38" t="n">
-        <v>15.28007428190196</v>
+        <v>15.3206344232693</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>6.52387511679291</v>
+        <v>6.204850716530674</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4628,16 +4638,16 @@
         <v>18.08874313747508</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.53284361087769</v>
+        <v>12.27010460299414</v>
       </c>
       <c r="Z38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AA38" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.72916620710978</v>
+        <v>10.11727802990801</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
@@ -4677,7 +4687,7 @@
         <v>46286</v>
       </c>
       <c r="C39" t="n">
-        <v>298.4750061</v>
+        <v>297.20001221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4715,7 @@
         <v>17.57170813546579</v>
       </c>
       <c r="K39" t="n">
-        <v>1.044379057178113</v>
+        <v>0.6127483903423769</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -4714,13 +4724,13 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>6.738192314882714</v>
+        <v>6.997009141765651</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>8.863057031360611</v>
+        <v>9.330081684319346</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4786,7 +4796,7 @@
         <v>46286</v>
       </c>
       <c r="C40" t="n">
-        <v>206.61999512</v>
+        <v>206.47999573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4814,7 +4824,7 @@
         <v>20.00812356142131</v>
       </c>
       <c r="K40" t="n">
-        <v>4.89389765406103</v>
+        <v>4.822824756794919</v>
       </c>
       <c r="L40" t="n">
         <v>7</v>
@@ -4829,7 +4839,7 @@
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.96118498349911</v>
+        <v>3.030995635327161</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4895,7 +4905,7 @@
         <v>46286</v>
       </c>
       <c r="C41" t="n">
-        <v>229.5</v>
+        <v>231.92999268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,16 +4965,16 @@
         <v>10.73879246924641</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.863476559126958</v>
+        <v>7.898504511885262</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB41" t="n">
-        <v>12.79361125189371</v>
+        <v>10.80125222495703</v>
       </c>
       <c r="AC41" t="n">
         <v>4</v>
@@ -5004,11 +5014,11 @@
         <v>46286</v>
       </c>
       <c r="C42" t="n">
-        <v>122.95500183</v>
+        <v>121.77999878</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5018,7 +5028,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5064,22 +5074,22 @@
         <v>46.49635691053297</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.420699276998827</v>
+        <v>2.362759195606634</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA42" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB42" t="n">
-        <v>16.93665027209175</v>
+        <v>16.46136610268062</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5876494545532962</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>48</v>
@@ -5113,7 +5123,7 @@
         <v>46286</v>
       </c>
       <c r="C43" t="n">
-        <v>398.6000061</v>
+        <v>401.6499939</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,7 +5151,7 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>15.45257236784938</v>
+        <v>16.335986647357</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5176,25 +5186,25 @@
         <v>50</v>
       </c>
       <c r="X43" t="n">
-        <v>15.53801274728459</v>
+        <v>16.86604228530051</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.07395001645223997</v>
+        <v>0.4535583028040802</v>
       </c>
       <c r="Z43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="n">
-        <v>50</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB43" t="n">
-        <v>11.18712625632929</v>
+        <v>9.415358728982806</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>7.931915636465902</v>
+        <v>7.580825159126192</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5228,7 +5238,7 @@
         <v>46286</v>
       </c>
       <c r="C44" t="n">
-        <v>271.33999634</v>
+        <v>269.47000122</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,22 +5298,22 @@
         <v>10.11126434424055</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.461774905396542</v>
+        <v>4.127087842137978</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
-        <v>7.692307692307693</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.203064942090774</v>
+        <v>5.290252104904014</v>
       </c>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.629243589382457</v>
+        <v>1.953536317722504</v>
       </c>
       <c r="AE44" t="n">
         <v>14</v>
@@ -5337,7 +5347,7 @@
         <v>46286</v>
       </c>
       <c r="C45" t="n">
-        <v>351.01919556</v>
+        <v>352.04000854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,7 +5446,7 @@
         <v>46286</v>
       </c>
       <c r="C46" t="n">
-        <v>182.63999939</v>
+        <v>183.97000122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5464,7 +5474,7 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>10.09705230067637</v>
+        <v>10.89878949694532</v>
       </c>
       <c r="L46" t="n">
         <v>12</v>
@@ -5473,7 +5483,7 @@
         <v>58.33333333333334</v>
       </c>
       <c r="N46" t="n">
-        <v>10.19275247602296</v>
+        <v>9.298386782800609</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5503,25 +5513,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X46" t="n">
-        <v>10.3743485281111</v>
+        <v>12.08632414475048</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.2512324929955234</v>
+        <v>1.059482195411765</v>
       </c>
       <c r="Z46" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="AA46" t="n">
-        <v>44.68085106382978</v>
+        <v>40.38461538461539</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.70810393479271</v>
+        <v>12.30093833412674</v>
       </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.768283960461309</v>
+        <v>7.014838772418852</v>
       </c>
       <c r="AE46" t="n">
         <v>43</v>
@@ -5555,7 +5565,7 @@
         <v>46286</v>
       </c>
       <c r="C47" t="n">
-        <v>31.76499939</v>
+        <v>31.71999931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5654,7 +5664,7 @@
         <v>46286</v>
       </c>
       <c r="C48" t="n">
-        <v>87.89499664</v>
+        <v>87.12000275</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5753,7 +5763,7 @@
         <v>46286</v>
       </c>
       <c r="C49" t="n">
-        <v>458.5</v>
+        <v>457.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5862,7 @@
         <v>46286</v>
       </c>
       <c r="C50" t="n">
-        <v>1157.23999023</v>
+        <v>1164.89001465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5880,16 +5890,16 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>3.947753921081421</v>
+        <v>4.634908584430364</v>
       </c>
       <c r="L50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M50" t="n">
-        <v>57.69230769230769</v>
+        <v>52</v>
       </c>
       <c r="N50" t="n">
-        <v>9.226715679892591</v>
+        <v>9.181646458077708</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5961,7 +5971,7 @@
         <v>46286</v>
       </c>
       <c r="C51" t="n">
-        <v>536.9450073199999</v>
+        <v>535.40002441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,16 +5999,16 @@
         <v>15.06813824398204</v>
       </c>
       <c r="K51" t="n">
-        <v>3.175324728615903</v>
+        <v>2.878452402276532</v>
       </c>
       <c r="L51" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M51" t="n">
-        <v>35.29411764705883</v>
+        <v>35</v>
       </c>
       <c r="N51" t="n">
-        <v>11.2031956956144</v>
+        <v>13.89235137713702</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
@@ -6070,7 +6080,7 @@
         <v>46286</v>
       </c>
       <c r="C52" t="n">
-        <v>192</v>
+        <v>190.97999573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6098,7 +6108,7 @@
         <v>16.63935213539153</v>
       </c>
       <c r="K52" t="n">
-        <v>2.008287512219153</v>
+        <v>1.466366216188697</v>
       </c>
       <c r="L52" t="n">
         <v>23</v>
@@ -6107,13 +6117,13 @@
         <v>47.82608695652174</v>
       </c>
       <c r="N52" t="n">
-        <v>9.770564092829414</v>
+        <v>9.449383235200241</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>0.97218815447917</v>
+        <v>1.511470096941947</v>
       </c>
       <c r="Q52" t="n">
         <v>24</v>
@@ -6179,7 +6189,7 @@
         <v>46286</v>
       </c>
       <c r="C53" t="n">
-        <v>299.76998901</v>
+        <v>302.27999878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,13 +6217,13 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>12.96303068266793</v>
+        <v>13.90888357340827</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N53" t="n">
         <v>11.79551441110968</v>
@@ -6246,25 +6256,25 @@
         <v>68.75</v>
       </c>
       <c r="X53" t="n">
-        <v>12.96303068266793</v>
+        <v>15.19388328049949</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.115510364350003</v>
       </c>
       <c r="Z53" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AA53" t="n">
-        <v>50</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB53" t="n">
-        <v>12.54970589597803</v>
+        <v>12.35727639039834</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
       <c r="AD53" t="n">
-        <v>9.999999999999998</v>
+        <v>8.984715063389414</v>
       </c>
       <c r="AE53" t="n">
         <v>35</v>
@@ -6298,7 +6308,7 @@
         <v>46286</v>
       </c>
       <c r="C54" t="n">
-        <v>564.47998047</v>
+        <v>567.65002441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6397,7 +6407,7 @@
         <v>46286</v>
       </c>
       <c r="C55" t="n">
-        <v>248.42999268</v>
+        <v>247.88000488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6425,22 +6435,22 @@
         <v>11.44128000083862</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7744122728911229</v>
+        <v>0.5513124100108513</v>
       </c>
       <c r="L55" t="n">
         <v>14</v>
       </c>
       <c r="M55" t="n">
-        <v>35.71428571428572</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>7.525232615082142</v>
+        <v>6.866334451539212</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>2.208484948621803</v>
+        <v>2.43526169007553</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6506,7 +6516,7 @@
         <v>46286</v>
       </c>
       <c r="C56" t="n">
-        <v>91.70999908</v>
+        <v>91.75</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6576,7 @@
         <v>10.02075913024301</v>
       </c>
       <c r="Y56" t="n">
-        <v>3.878004861193818</v>
+        <v>3.836079571952089</v>
       </c>
       <c r="Z56" t="n">
         <v>12</v>
@@ -6581,7 +6591,7 @@
         <v>4</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.1269169856805585</v>
+        <v>0.1704593857220771</v>
       </c>
       <c r="AE56" t="n">
         <v>19</v>
@@ -6615,7 +6625,7 @@
         <v>46286</v>
       </c>
       <c r="C57" t="n">
-        <v>726.6295166</v>
+        <v>741.24499512</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,25 +6682,25 @@
         <v>60.52631578947368</v>
       </c>
       <c r="X57" t="n">
-        <v>35.57429187044519</v>
+        <v>40.15299060586315</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.2430680602233837</v>
+        <v>1.561089625498013</v>
       </c>
       <c r="Z57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA57" t="n">
-        <v>27.27272727272727</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.23736859190473</v>
+        <v>6.492481763604726</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.770959298600009</v>
+        <v>4.509304661758806</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6724,7 +6734,7 @@
         <v>46286</v>
       </c>
       <c r="C58" t="n">
-        <v>50.16949844</v>
+        <v>50</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6752,22 +6762,22 @@
         <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>6.15636949519045</v>
+        <v>5.797718530261675</v>
       </c>
       <c r="L58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M58" t="n">
-        <v>68.75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>16.43157808826553</v>
+        <v>16.13686905611211</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>1.736712091395587</v>
+        <v>2.081596371200023</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6833,7 +6843,7 @@
         <v>46286</v>
       </c>
       <c r="C59" t="n">
-        <v>148.86999512</v>
+        <v>149.5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6893,22 +6903,22 @@
         <v>22.36431024033017</v>
       </c>
       <c r="Y59" t="n">
-        <v>5.130004552561241</v>
+        <v>4.728522977652294</v>
       </c>
       <c r="Z59" t="n">
         <v>7</v>
       </c>
       <c r="AA59" t="n">
-        <v>14.28571428571429</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB59" t="n">
-        <v>14.09380874649435</v>
+        <v>9.256718738842906</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>5.133335808092143</v>
+        <v>5.533111469565211</v>
       </c>
       <c r="AE59" t="n">
         <v>19</v>
@@ -6942,7 +6952,7 @@
         <v>46286</v>
       </c>
       <c r="C60" t="n">
-        <v>254.72999573</v>
+        <v>257.38000488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6999,25 +7009,25 @@
         <v>69.47368421052632</v>
       </c>
       <c r="X60" t="n">
-        <v>27.33027772092391</v>
+        <v>30.18642160955904</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.2818560299849726</v>
+        <v>1.454930663335985</v>
       </c>
       <c r="Z60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA60" t="n">
-        <v>48</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB60" t="n">
-        <v>12.92183659638986</v>
+        <v>14.61354858877807</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.731479931509519</v>
+        <v>3.597409145406183</v>
       </c>
       <c r="AE60" t="n">
         <v>53</v>
@@ -7051,7 +7061,7 @@
         <v>46286</v>
       </c>
       <c r="C61" t="n">
-        <v>204.96499634</v>
+        <v>206.11999512</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         <v>46286</v>
       </c>
       <c r="C62" t="n">
-        <v>494.38000488</v>
+        <v>501.60998535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7249,7 +7259,7 @@
         <v>46286</v>
       </c>
       <c r="C63" t="n">
-        <v>1043.8449707</v>
+        <v>1043.95996094</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7309,7 +7319,7 @@
         <v>26.03182453415183</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.939428244462815</v>
+        <v>1.928625865759837</v>
       </c>
       <c r="Z63" t="n">
         <v>36</v>
@@ -7324,7 +7334,7 @@
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.101325454917957</v>
+        <v>2.112108811083724</v>
       </c>
       <c r="AE63" t="n">
         <v>54</v>
@@ -7358,7 +7368,7 @@
         <v>46286</v>
       </c>
       <c r="C64" t="n">
-        <v>80.05999756</v>
+        <v>79.62999725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7457,7 +7467,7 @@
         <v>46286</v>
       </c>
       <c r="C65" t="n">
-        <v>122.06999969</v>
+        <v>123.05000305</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7485,22 +7495,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>1.724999741666666</v>
+        <v>2.541669208333341</v>
       </c>
       <c r="L65" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M65" t="n">
-        <v>55</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="N65" t="n">
-        <v>11.67895108850531</v>
+        <v>13.22916687459514</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>8.134677099383559</v>
+        <v>7.273463411750813</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7527,13 +7537,13 @@
         <v>19.61980116727053</v>
       </c>
       <c r="Y65" t="n">
-        <v>9.771597498465667</v>
+        <v>9.047225106858459</v>
       </c>
       <c r="Z65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA65" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB65" t="n">
         <v>9.67392877385792</v>
@@ -7576,7 +7586,7 @@
         <v>46286</v>
       </c>
       <c r="C66" t="n">
-        <v>73.625</v>
+        <v>73.36000061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7604,22 +7614,22 @@
         <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>5.013549221819069</v>
+        <v>4.63557263118386</v>
       </c>
       <c r="L66" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M66" t="n">
-        <v>58.33333333333334</v>
+        <v>62.16216216216216</v>
       </c>
       <c r="N66" t="n">
-        <v>14.72246063738556</v>
+        <v>14.20425549117039</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>4.748388008149407</v>
+        <v>5.126772123400625</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7685,7 +7695,7 @@
         <v>46286</v>
       </c>
       <c r="C67" t="n">
-        <v>36.23500061</v>
+        <v>36.09999847</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7713,22 +7723,22 @@
         <v>16.29173844409661</v>
       </c>
       <c r="K67" t="n">
-        <v>2.503542229997713</v>
+        <v>2.121640827329863</v>
       </c>
       <c r="L67" t="n">
         <v>22</v>
       </c>
       <c r="M67" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>11.76148344880915</v>
+        <v>13.43262190542956</v>
       </c>
       <c r="O67" t="n">
         <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>7.313364598836714</v>
+        <v>7.714681343586216</v>
       </c>
       <c r="Q67" t="n">
         <v>33</v>
@@ -7794,7 +7804,7 @@
         <v>46286</v>
       </c>
       <c r="C68" t="n">
-        <v>137.24499512</v>
+        <v>137.67999268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7822,22 +7832,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>5.257301757856836</v>
+        <v>5.590914429100824</v>
       </c>
       <c r="L68" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M68" t="n">
-        <v>64.58333333333333</v>
+        <v>70.21276595744681</v>
       </c>
       <c r="N68" t="n">
-        <v>12.72095128489728</v>
+        <v>12.08139546847258</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>4.505814003339825</v>
+        <v>4.175629688158145</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7864,7 +7874,7 @@
         <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>8.258696842392709</v>
+        <v>7.967923084195649</v>
       </c>
       <c r="Z68" t="n">
         <v>12</v>
@@ -7873,7 +7883,7 @@
         <v>50</v>
       </c>
       <c r="AB68" t="n">
-        <v>11.28626210482051</v>
+        <v>11.2904366432055</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7913,7 +7923,7 @@
         <v>46286</v>
       </c>
       <c r="C69" t="n">
-        <v>225.60499573</v>
+        <v>227.38000488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7941,16 +7951,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>7.981143748729114</v>
+        <v>8.830714998520239</v>
       </c>
       <c r="L69" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M69" t="n">
-        <v>63.1578947368421</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N69" t="n">
-        <v>11.35964129165207</v>
+        <v>11.6521145174821</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -7983,22 +7993,22 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.899726952672944</v>
+        <v>3.143631710080674</v>
       </c>
       <c r="Z69" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AA69" t="n">
-        <v>40.42553191489362</v>
+        <v>37.73584905660378</v>
       </c>
       <c r="AB69" t="n">
-        <v>12.61345573411901</v>
+        <v>12.52971075558355</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.185501643988808</v>
+        <v>2.949076390485128</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8032,7 +8042,7 @@
         <v>46286</v>
       </c>
       <c r="C70" t="n">
-        <v>229.94000244</v>
+        <v>232.41000366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8060,22 +8070,22 @@
         <v>10.65198616240091</v>
       </c>
       <c r="K70" t="n">
-        <v>6.129418700112277</v>
+        <v>7.269454321950519</v>
       </c>
       <c r="L70" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M70" t="n">
-        <v>40</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N70" t="n">
-        <v>11.72424633069284</v>
+        <v>10.5418328963978</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>3.647039008877218</v>
+        <v>2.545501601839262</v>
       </c>
       <c r="Q70" t="n">
         <v>32</v>
@@ -8141,7 +8151,7 @@
         <v>46286</v>
       </c>
       <c r="C71" t="n">
-        <v>148.99000549</v>
+        <v>148.55999756</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8173,22 +8183,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K71" t="n">
-        <v>7.187054309352514</v>
+        <v>6.877696086330931</v>
       </c>
       <c r="L71" t="n">
         <v>16</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
       <c r="N71" t="n">
-        <v>10.88869311955713</v>
+        <v>12.50905150582083</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>0.7584364510113684</v>
+        <v>1.05008243512521</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8215,7 +8225,7 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y71" t="n">
-        <v>12.71821432214737</v>
+        <v>12.97012289724004</v>
       </c>
       <c r="Z71" t="n">
         <v>4</v>
@@ -8264,7 +8274,7 @@
         <v>46286</v>
       </c>
       <c r="C72" t="n">
-        <v>57.13000107</v>
+        <v>57.25</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8292,22 +8302,22 @@
         <v>10.6162778911167</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2280720526315783</v>
+        <v>0.4385964912280604</v>
       </c>
       <c r="L72" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M72" t="n">
-        <v>51.72413793103448</v>
+        <v>50.84745762711864</v>
       </c>
       <c r="N72" t="n">
-        <v>17.2639723534175</v>
+        <v>17.5069797488751</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>2.765620340290331</v>
+        <v>2.550218340611377</v>
       </c>
       <c r="Q72" t="n">
         <v>30</v>
@@ -8334,16 +8344,16 @@
         <v>12.66784838130402</v>
       </c>
       <c r="Y72" t="n">
-        <v>10.41241860138447</v>
+        <v>10.22424402221809</v>
       </c>
       <c r="Z72" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA72" t="n">
-        <v>56</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB72" t="n">
-        <v>11.82984176474623</v>
+        <v>11.98205950032272</v>
       </c>
       <c r="AC72" t="n">
         <v>10</v>
@@ -8383,7 +8393,7 @@
         <v>46286</v>
       </c>
       <c r="C73" t="n">
-        <v>129.41070557</v>
+        <v>129.58999634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8411,22 +8421,22 @@
         <v>12.28237922496582</v>
       </c>
       <c r="K73" t="n">
-        <v>1.117910745771367</v>
+        <v>1.258003545656416</v>
       </c>
       <c r="L73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M73" t="n">
-        <v>52.63157894736842</v>
+        <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>8.176251134453048</v>
+        <v>7.789120604197176</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>0.8723373017925251</v>
+        <v>0.7327780801139605</v>
       </c>
       <c r="Q73" t="n">
         <v>16</v>
@@ -8492,7 +8502,7 @@
         <v>46286</v>
       </c>
       <c r="C74" t="n">
-        <v>27.60499954</v>
+        <v>27.73999977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8552,22 +8562,22 @@
         <v>11.57371556196134</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.494692196340867</v>
+        <v>5.032520904824345</v>
       </c>
       <c r="Z74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA74" t="n">
-        <v>35.71428571428572</v>
+        <v>40</v>
       </c>
       <c r="AB74" t="n">
-        <v>9.635841473093306</v>
+        <v>9.169300480286273</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>4.767253721895914</v>
+        <v>5.230715969829303</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8601,7 +8611,7 @@
         <v>46286</v>
       </c>
       <c r="C75" t="n">
-        <v>182.8999939</v>
+        <v>183.08999634</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8629,16 +8639,16 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K75" t="n">
-        <v>11.1516198783808</v>
+        <v>11.26708778265197</v>
       </c>
       <c r="L75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N75" t="n">
-        <v>17.76304101843429</v>
+        <v>16.62719012983499</v>
       </c>
       <c r="O75" t="n">
         <v>10</v>
@@ -8671,7 +8681,7 @@
         <v>11.44333119476051</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.2617575347509171</v>
+        <v>0.1581462167534409</v>
       </c>
       <c r="Z75" t="n">
         <v>50</v>
@@ -8686,7 +8696,7 @@
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.745428832078278</v>
+        <v>2.84635518628904</v>
       </c>
       <c r="AE75" t="n">
         <v>19</v>
@@ -8720,7 +8730,7 @@
         <v>46286</v>
       </c>
       <c r="C76" t="n">
-        <v>187.77999878</v>
+        <v>187.47999573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8819,7 +8829,7 @@
         <v>46286</v>
       </c>
       <c r="C77" t="n">
-        <v>192.55000305</v>
+        <v>194.22999573</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8876,25 +8886,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>23.29898876327645</v>
+        <v>25.01440369846701</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.04153134401354563</v>
+        <v>0.5529680218587907</v>
       </c>
       <c r="Z77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA77" t="n">
-        <v>41.1764705882353</v>
+        <v>37.5</v>
       </c>
       <c r="AB77" t="n">
-        <v>8.03450545973401</v>
+        <v>7.69349818478715</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>9.962606260265117</v>
+        <v>9.499561515538947</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8928,7 +8938,7 @@
         <v>46286</v>
       </c>
       <c r="C78" t="n">
-        <v>194.83000183</v>
+        <v>194.33999634</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8947,7 +8957,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -8960,22 +8970,22 @@
         <v>15.7351954478678</v>
       </c>
       <c r="K78" t="n">
-        <v>1.909200381710141</v>
+        <v>1.65289453969657</v>
       </c>
       <c r="L78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M78" t="n">
-        <v>75</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N78" t="n">
-        <v>13.08999219944563</v>
+        <v>11.25415779326658</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>0.08909854846250731</v>
+        <v>0.3414614624356549</v>
       </c>
       <c r="Q78" t="n">
         <v>12</v>
@@ -9041,7 +9051,7 @@
         <v>46286</v>
       </c>
       <c r="C79" t="n">
-        <v>106.81999969</v>
+        <v>106.87999725</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9140,7 +9150,7 @@
         <v>46286</v>
       </c>
       <c r="C80" t="n">
-        <v>51.36999893</v>
+        <v>51.75999832</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9168,22 +9178,22 @@
         <v>16.51637120732817</v>
       </c>
       <c r="K80" t="n">
-        <v>1.774763559804482</v>
+        <v>2.547434311848007</v>
       </c>
       <c r="L80" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M80" t="n">
-        <v>66.66666666666667</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N80" t="n">
-        <v>14.06499869375114</v>
+        <v>14.02395794534022</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>2.186432434095442</v>
+        <v>1.416481746130027</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9249,7 +9259,7 @@
         <v>46286</v>
       </c>
       <c r="C81" t="n">
-        <v>40.91500092</v>
+        <v>41.20000076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9277,10 +9287,10 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K81" t="n">
-        <v>20.02053605153766</v>
+        <v>20.85655787244107</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
@@ -9315,22 +9325,22 @@
         <v>36.83700278308666</v>
       </c>
       <c r="Y81" t="n">
-        <v>3.297093842660881</v>
+        <v>2.623494620794431</v>
       </c>
       <c r="Z81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA81" t="n">
-        <v>31.57894736842105</v>
+        <v>40</v>
       </c>
       <c r="AB81" t="n">
-        <v>13.78032059620465</v>
+        <v>14.79127707394377</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.863252144343333</v>
+        <v>5.52135790688757</v>
       </c>
       <c r="AE81" t="n">
         <v>76</v>
@@ -9364,7 +9374,7 @@
         <v>46286</v>
       </c>
       <c r="C82" t="n">
-        <v>406.48001099</v>
+        <v>404.47000122</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9392,22 +9402,22 @@
         <v>11.8900081911483</v>
       </c>
       <c r="K82" t="n">
-        <v>1.409581271188975</v>
+        <v>0.9081193453484904</v>
       </c>
       <c r="L82" t="n">
         <v>22</v>
       </c>
       <c r="M82" t="n">
-        <v>40.90909090909091</v>
+        <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>10.64662700539032</v>
+        <v>10.68747122516058</v>
       </c>
       <c r="O82" t="n">
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>8.471012917249476</v>
+        <v>9.010058569752367</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -9473,7 +9483,7 @@
         <v>46286</v>
       </c>
       <c r="C83" t="n">
-        <v>273.73999023</v>
+        <v>274.19000244</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9501,7 +9511,7 @@
         <v>23.66411973888177</v>
       </c>
       <c r="K83" t="n">
-        <v>2.524340910112355</v>
+        <v>2.692884808988771</v>
       </c>
       <c r="L83" t="n">
         <v>3</v>
@@ -9582,7 +9592,7 @@
         <v>46286</v>
       </c>
       <c r="C84" t="n">
-        <v>25.69000053</v>
+        <v>25.45000076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9642,16 +9652,16 @@
         <v>14.74222881006126</v>
       </c>
       <c r="Y84" t="n">
-        <v>4.604529393709466</v>
+        <v>5.495727935251549</v>
       </c>
       <c r="Z84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA84" t="n">
-        <v>20</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.83959366477939</v>
+        <v>11.41021637006637</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9691,7 +9701,7 @@
         <v>46286</v>
       </c>
       <c r="C85" t="n">
-        <v>129.77999878</v>
+        <v>130.96000671</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9719,10 +9729,10 @@
         <v>23.66801733058809</v>
       </c>
       <c r="K85" t="n">
-        <v>5.701254332591055</v>
+        <v>6.662329378791676</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
@@ -9796,7 +9806,7 @@
         <v>46286</v>
       </c>
       <c r="C86" t="n">
-        <v>374.79998779</v>
+        <v>375.29998779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9856,22 +9866,22 @@
         <v>18.66270892223245</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.406004724645139</v>
+        <v>2.275809956162334</v>
       </c>
       <c r="Z86" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AA86" t="n">
-        <v>43.10344827586207</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="AB86" t="n">
-        <v>13.51480539732798</v>
+        <v>14.18015519051553</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.6086391623572163</v>
+        <v>0.7410550484100331</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9905,11 +9915,11 @@
         <v>46286</v>
       </c>
       <c r="C87" t="n">
-        <v>441.42001343</v>
+        <v>445.14001465</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9919,7 +9929,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9961,17 +9971,27 @@
       <c r="W87" t="n">
         <v>55.26315789473684</v>
       </c>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
+      <c r="X87" t="n">
+        <v>10.01357717655884</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0.1301235233806985</v>
+      </c>
       <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>11.77096045075639</v>
+      </c>
       <c r="AC87" t="n">
         <v>6</v>
       </c>
-      <c r="AD87" t="inlineStr"/>
+      <c r="AD87" t="n">
+        <v>5.877524518610489</v>
+      </c>
       <c r="AE87" t="n">
         <v>36</v>
       </c>
@@ -10004,11 +10024,11 @@
         <v>46286</v>
       </c>
       <c r="C88" t="n">
-        <v>268.91500854</v>
+        <v>270.86999512</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10032,7 +10052,7 @@
         <v>14.3256649882924</v>
       </c>
       <c r="K88" t="n">
-        <v>8.37665870762061</v>
+        <v>9.16454672662319</v>
       </c>
       <c r="L88" t="n">
         <v>20</v>
@@ -10041,13 +10061,13 @@
         <v>30</v>
       </c>
       <c r="N88" t="n">
-        <v>6.999718865000822</v>
+        <v>7.186011681620726</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>1.497869847380007</v>
+        <v>0.7653155703279957</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10074,22 +10094,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.615255642237912</v>
+        <v>0.9000078918783405</v>
       </c>
       <c r="Z88" t="n">
         <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>23.33333333333333</v>
+        <v>30</v>
       </c>
       <c r="AB88" t="n">
-        <v>11.25813856665627</v>
+        <v>10.41208368857444</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.423896482456989</v>
+        <v>3.128145665984983</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10123,7 +10143,7 @@
         <v>46286</v>
       </c>
       <c r="C89" t="n">
-        <v>70.85500336</v>
+        <v>70.83999634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10155,7 +10175,7 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K89" t="n">
-        <v>2.332474797681905</v>
+        <v>2.310800880200947</v>
       </c>
       <c r="L89" t="n">
         <v>37</v>
@@ -10170,7 +10190,7 @@
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>1.629517126029545</v>
+        <v>1.651046717713611</v>
       </c>
       <c r="Q89" t="n">
         <v>28</v>
@@ -10236,7 +10256,7 @@
         <v>46286</v>
       </c>
       <c r="C90" t="n">
-        <v>374.5</v>
+        <v>377.55999756</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10335,7 +10355,7 @@
         <v>46286</v>
       </c>
       <c r="C91" t="n">
-        <v>272.3999939</v>
+        <v>269.63000488</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10360,10 +10380,10 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>13.62406131818169</v>
+        <v>14.60766672642613</v>
       </c>
       <c r="K91" t="n">
-        <v>0.3869496135603834</v>
+        <v>0.5106967345503977</v>
       </c>
       <c r="L91" t="n">
         <v>20</v>
@@ -10372,13 +10392,13 @@
         <v>60</v>
       </c>
       <c r="N91" t="n">
-        <v>9.297602702674224</v>
+        <v>9.573441490935112</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>1.606832753310128</v>
+        <v>1.481736087635399</v>
       </c>
       <c r="Q91" t="n">
         <v>17</v>
@@ -10444,7 +10464,7 @@
         <v>46286</v>
       </c>
       <c r="C92" t="n">
-        <v>367.66000366</v>
+        <v>369.95001221</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10543,7 +10563,7 @@
         <v>46286</v>
       </c>
       <c r="C93" t="n">
-        <v>254.57000732</v>
+        <v>250.86000061</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10571,16 +10591,16 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>12.17502625492612</v>
+        <v>10.54022997832835</v>
       </c>
       <c r="L93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M93" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N93" t="n">
-        <v>11.87404846679999</v>
+        <v>11.73748496034269</v>
       </c>
       <c r="O93" t="n">
         <v>10</v>
@@ -10613,22 +10633,22 @@
         <v>12.3097290736065</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.1199386907897337</v>
+        <v>1.575552812631609</v>
       </c>
       <c r="Z93" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AA93" t="n">
-        <v>45.45454545454545</v>
+        <v>43.39622641509434</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.23592640207823</v>
+        <v>14.77795812566167</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.884720592229429</v>
+        <v>2.463257103952055</v>
       </c>
       <c r="AE93" t="n">
         <v>31</v>
@@ -10662,7 +10682,7 @@
         <v>46286</v>
       </c>
       <c r="C94" t="n">
-        <v>48.11500168</v>
+        <v>47.68000031</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10722,16 +10742,16 @@
         <v>12.08242925132574</v>
       </c>
       <c r="Y94" t="n">
-        <v>6.880194727903167</v>
+        <v>7.722078578118907</v>
       </c>
       <c r="Z94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA94" t="n">
-        <v>33.33333333333334</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB94" t="n">
-        <v>8.721012058594662</v>
+        <v>8.473516272682568</v>
       </c>
       <c r="AC94" t="n">
         <v>2</v>
@@ -10771,7 +10791,7 @@
         <v>46286</v>
       </c>
       <c r="C95" t="n">
-        <v>30.64999962</v>
+        <v>30.79999924</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10828,25 +10848,25 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X95" t="n">
-        <v>15.71428665520944</v>
+        <v>16.24060014393127</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.4223556435534404</v>
+        <v>0.3881010339247148</v>
       </c>
       <c r="Z95" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA95" t="n">
-        <v>48.97959183673469</v>
+        <v>48.93617021276596</v>
       </c>
       <c r="AB95" t="n">
-        <v>13.00064432445259</v>
+        <v>12.3026627979828</v>
       </c>
       <c r="AC95" t="n">
         <v>8</v>
       </c>
       <c r="AD95" t="n">
-        <v>7.609784711638423</v>
+        <v>7.6415559236228</v>
       </c>
       <c r="AE95" t="n">
         <v>51</v>
@@ -10880,7 +10900,7 @@
         <v>46286</v>
       </c>
       <c r="C96" t="n">
-        <v>86.52500153</v>
+        <v>86.54000092</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10940,7 +10960,7 @@
         <v>10.19405145840906</v>
       </c>
       <c r="Y96" t="n">
-        <v>5.940859285938027</v>
+        <v>5.924553828443802</v>
       </c>
       <c r="Z96" t="n">
         <v>18</v>
@@ -10955,7 +10975,7 @@
         <v>6</v>
       </c>
       <c r="AD96" t="n">
-        <v>0.06287609435191577</v>
+        <v>0.08019751659601448</v>
       </c>
       <c r="AE96" t="n">
         <v>29</v>
@@ -10989,7 +11009,7 @@
         <v>46286</v>
       </c>
       <c r="C97" t="n">
-        <v>107.57499695</v>
+        <v>107.44000244</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11017,7 +11037,7 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>5.310812862207115</v>
+        <v>5.178659648327466</v>
       </c>
       <c r="L97" t="n">
         <v>12</v>
@@ -11026,7 +11046,7 @@
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>9.865823559457239</v>
+        <v>9.549824708064946</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -11098,7 +11118,7 @@
         <v>46286</v>
       </c>
       <c r="C98" t="n">
-        <v>158.46499634</v>
+        <v>158.30000305</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11197,7 +11217,7 @@
         <v>46286</v>
       </c>
       <c r="C99" t="n">
-        <v>30375.44726562</v>
+        <v>30482.3515625</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -436,7 +436,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C2" t="n">
-        <v>338.98001099</v>
+        <v>342.49099731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,25 +727,25 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>12.9986380472102</v>
+        <v>14.89502875525965</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1943244704780023</v>
+        <v>0.8249838015273125</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.13793103448276</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.52967967438215</v>
+        <v>13.13625423883436</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.820873400343964</v>
+        <v>7.234701312388769</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3" t="n">
-        <v>264.48001099</v>
+        <v>266.05999756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C4" t="n">
-        <v>102.98000336</v>
+        <v>104.0625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>2.641285240371261</v>
+        <v>3.720221371394339</v>
       </c>
       <c r="L4" t="n">
         <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>52.94117647058823</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N4" t="n">
-        <v>7.395298426209745</v>
+        <v>8.162860539846717</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.272284394883718</v>
+        <v>2.198007870078089</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -930,10 +930,10 @@
         <v>17.64705882352941</v>
       </c>
       <c r="S4" t="n">
-        <v>18.00079491255962</v>
+        <v>18.14785373608903</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3537360890302068</v>
+        <v>-0.5007949125596198</v>
       </c>
       <c r="U4" t="n">
         <v>6.191126637620997</v>
@@ -962,10 +962,10 @@
         <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.81372549019608</v>
+        <v>12.68872549019608</v>
       </c>
       <c r="AH4" t="n">
-        <v>27.18627450980392</v>
+        <v>27.31127450980392</v>
       </c>
       <c r="AI4" t="n">
         <v>21.88065323728171</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C5" t="n">
-        <v>186.11000061</v>
+        <v>183.71499634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.829076549886702</v>
+        <v>7.040939228053523</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.876429880880892</v>
+        <v>8.742587687421709</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C6" t="n">
-        <v>383</v>
+        <v>384.85501099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,16 +1124,16 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>10.05747126436782</v>
+        <v>10.59052039942527</v>
       </c>
       <c r="L6" t="n">
         <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>39.1304347826087</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="N6" t="n">
-        <v>8.762970374522952</v>
+        <v>8.306221714859321</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -1148,10 +1148,10 @@
         <v>41.1764705882353</v>
       </c>
       <c r="S6" t="n">
-        <v>35.74958660151358</v>
+        <v>35.82311601327829</v>
       </c>
       <c r="T6" t="n">
-        <v>5.426883986721712</v>
+        <v>5.35335457495701</v>
       </c>
       <c r="U6" t="n">
         <v>26.36596836387115</v>
@@ -1163,25 +1163,25 @@
         <v>42.5</v>
       </c>
       <c r="X6" t="n">
-        <v>10.37930894252874</v>
+        <v>11.52684003448274</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2915742825754464</v>
+        <v>0.8395464578463518</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>44.82758620689656</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.745915768792873</v>
+        <v>9.609781599357904</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.719270152689302</v>
+        <v>3.187211664789458</v>
       </c>
       <c r="AE6" t="n">
         <v>29</v>
@@ -1190,10 +1190,10 @@
         <v>31.03448275862069</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.0031342919274</v>
+        <v>15.34310103351686</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.0313484666933</v>
+        <v>15.69138172510383</v>
       </c>
       <c r="AI6" t="n">
         <v>17.27561674448322</v>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C7" t="n">
-        <v>269.94000244</v>
+        <v>268.8500061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C8" t="n">
-        <v>464.23999023</v>
+        <v>465.42001343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,16 +1342,16 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>12.81377833056154</v>
+        <v>13.10053276471481</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N8" t="n">
-        <v>9.043238964344949</v>
+        <v>9.870996799924031</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
@@ -1381,10 +1381,10 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X8" t="n">
-        <v>13.85142490989666</v>
+        <v>14.26939802820826</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9114041217809343</v>
+        <v>1.022903142628706</v>
       </c>
       <c r="Z8" t="n">
         <v>56</v>
@@ -1393,13 +1393,13 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.3937646430881</v>
+        <v>13.33533409392914</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.172191610615865</v>
+        <v>9.06987287201153</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C9" t="n">
-        <v>615.52001953</v>
+        <v>613.45001221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,50 +1465,50 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>71.42857142857143</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="S9" t="n">
-        <v>69.18688170195094</v>
+        <v>68.36920858157229</v>
       </c>
       <c r="T9" t="n">
-        <v>2.241689726620493</v>
+        <v>3.425663213299501</v>
       </c>
       <c r="U9" t="n">
-        <v>56.43279073180463</v>
+        <v>56.22468051697918</v>
       </c>
       <c r="V9" t="n">
         <v>92</v>
       </c>
       <c r="W9" t="n">
-        <v>67.39130434782609</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="X9" t="n">
-        <v>39.99545804313283</v>
+        <v>41.20317820658344</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.188099689266541</v>
+        <v>1.374596107717052</v>
       </c>
       <c r="Z9" t="n">
         <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.15384615384615</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.29358770374292</v>
+        <v>13.59452842311039</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.822853079282043</v>
+        <v>4.689870671997188</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C10" t="n">
-        <v>258.45001221</v>
+        <v>254.39030457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,25 +1567,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>12.7936066701423</v>
+        <v>12.38702974586333</v>
       </c>
       <c r="K10" t="n">
-        <v>5.792062621097882</v>
+        <v>4.130291196899782</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>43.33333333333334</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="N10" t="n">
-        <v>11.39134211987505</v>
+        <v>12.68876942864811</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.087053909526282</v>
+        <v>3.716218171120822</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C11" t="n">
-        <v>205.41999817</v>
+        <v>204.41999817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,16 +1679,16 @@
         <v>14.2728744929405</v>
       </c>
       <c r="K11" t="n">
-        <v>13.32266416457344</v>
+        <v>12.77100091282524</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M11" t="n">
-        <v>64.70588235294117</v>
+        <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>14.60517234197607</v>
+        <v>12.70642957614508</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1718,25 +1718,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X11" t="n">
-        <v>13.61504501497082</v>
+        <v>14.88938578045085</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2573434269720676</v>
+        <v>1.843847326047832</v>
       </c>
       <c r="Z11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA11" t="n">
-        <v>44.82758620689656</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.75711369972829</v>
+        <v>11.45614554197544</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.762633199326341</v>
+        <v>6.271794998323966</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1745,10 +1745,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.19664013076596</v>
+        <v>16.88563774898843</v>
       </c>
       <c r="AH11" t="n">
-        <v>36.74453633982227</v>
+        <v>36.0555387215998</v>
       </c>
       <c r="AI11" t="n">
         <v>39.52330421009647</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C12" t="n">
-        <v>80.72000122</v>
+        <v>82.18000031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,16 +1798,16 @@
         <v>12.33653883634149</v>
       </c>
       <c r="K12" t="n">
-        <v>6.561057716171614</v>
+        <v>8.488449254125419</v>
       </c>
       <c r="L12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N12" t="n">
-        <v>9.577328043969082</v>
+        <v>8.758927394816478</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1840,22 +1840,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.450759931882653</v>
+        <v>2.722541380826948</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>25</v>
+        <v>13.63636363636364</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.787538517092495</v>
+        <v>10.83869362026744</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.807728103500642</v>
+        <v>7.481135632524316</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C13" t="n">
-        <v>322.8999939</v>
+        <v>329.30499268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>5</v>
       </c>
@@ -1946,25 +1950,25 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>43.77716402579273</v>
+        <v>47.76549707040503</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.388699946252935</v>
+        <v>1.15475992332138</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.627526536685187</v>
+        <v>15.18567789929377</v>
       </c>
       <c r="AC13" t="n">
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.621489783125097</v>
+        <v>1.866797101455964</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -1995,10 +1999,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C14" t="n">
-        <v>1711.31994629</v>
+        <v>1717.85998535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,7 +2016,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2026,22 +2030,22 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>8.804454584023969</v>
+        <v>9.220265423150909</v>
       </c>
       <c r="L14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>53.33333333333334</v>
+        <v>56.25</v>
       </c>
       <c r="N14" t="n">
-        <v>8.992220128437165</v>
+        <v>9.89370104261983</v>
       </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>1.098801901582802</v>
+        <v>0.7139101647740675</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2064,17 +2068,27 @@
       <c r="W14" t="n">
         <v>57.4468085106383</v>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>10.6622464385669</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.30304693951474</v>
+      </c>
       <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>35.41666666666666</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>14.10990500089401</v>
+      </c>
       <c r="AC14" t="n">
         <v>6</v>
       </c>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>4.758964603098526</v>
+      </c>
       <c r="AE14" t="n">
         <v>35</v>
       </c>
@@ -2104,10 +2118,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C15" t="n">
-        <v>362.66000366</v>
+        <v>362.42999268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,19 +2146,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>22.3973403666333</v>
+        <v>21.311746679127</v>
       </c>
       <c r="K15" t="n">
-        <v>7.995594620497459</v>
+        <v>7.927100239248763</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>61.53846153846154</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N15" t="n">
-        <v>14.47003005101384</v>
+        <v>14.92018308377776</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -2185,19 +2199,19 @@
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF15" t="n">
-        <v>41.66666666666666</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AG15" t="n">
-        <v>9.665483904862988</v>
+        <v>12.80514236111959</v>
       </c>
       <c r="AH15" t="n">
-        <v>32.00118276180368</v>
+        <v>27.73539817942095</v>
       </c>
       <c r="AI15" t="n">
-        <v>27.14056205144606</v>
+        <v>26.34651819201428</v>
       </c>
       <c r="AJ15" t="n">
         <v>47</v>
@@ -2213,10 +2227,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C16" t="n">
-        <v>313.58999634</v>
+        <v>307.69711304</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,25 +2255,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>11.07429159124881</v>
+        <v>11.84062035511823</v>
       </c>
       <c r="K16" t="n">
-        <v>1.593929664669491</v>
+        <v>0.5513229032174438</v>
       </c>
       <c r="L16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>54.83870967741935</v>
+        <v>60</v>
       </c>
       <c r="N16" t="n">
-        <v>9.294492093603905</v>
+        <v>10.52910447439699</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3996994078985017</v>
+        <v>1.440734000264654</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2322,10 +2336,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C17" t="n">
-        <v>201.1499939</v>
+        <v>198.42999268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,22 +2367,22 @@
         <v>17.56568419419229</v>
       </c>
       <c r="K17" t="n">
-        <v>2.911074897506838</v>
+        <v>1.519485249177599</v>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M17" t="n">
-        <v>58.8235294117647</v>
+        <v>62.16216216216216</v>
       </c>
       <c r="N17" t="n">
-        <v>13.46609029588345</v>
+        <v>12.44577820104661</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.001547798008675</v>
+        <v>4.413452983754862</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2431,10 +2445,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C18" t="n">
-        <v>57.95999908</v>
+        <v>56.52500153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,25 +2473,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>12.34095145691251</v>
+        <v>14.05029013936877</v>
       </c>
       <c r="K18" t="n">
-        <v>1.364111167840609</v>
+        <v>0.8204814255606818</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M18" t="n">
-        <v>52.63157894736842</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="N18" t="n">
-        <v>11.12502980176296</v>
+        <v>12.22840581705775</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.613873799426568</v>
+        <v>2.161781558292342</v>
       </c>
       <c r="Q18" t="n">
         <v>24</v>
@@ -2540,10 +2554,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C19" t="n">
-        <v>168.52000427</v>
+        <v>161.61000061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,11 +2574,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2572,25 +2582,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>23.56732248521627</v>
+        <v>25.99852664131597</v>
       </c>
       <c r="K19" t="n">
-        <v>1.454818167357796</v>
+        <v>0.4912282390511669</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N19" t="n">
-        <v>8.341748246093617</v>
+        <v>8.125463674653508</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>6.451326758917864</v>
+        <v>7.472066858499105</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2631,10 +2641,10 @@
         <v>48.38709677419355</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.99738448125545</v>
+        <v>14.07802964254577</v>
       </c>
       <c r="AH19" t="n">
-        <v>34.3897122929381</v>
+        <v>34.30906713164778</v>
       </c>
       <c r="AI19" t="n">
         <v>31.97025156241731</v>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C20" t="n">
-        <v>62.61999893</v>
+        <v>62.76499939</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,10 +2762,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C21" t="n">
-        <v>135.05000305</v>
+        <v>132.02999878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,10 +2861,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C22" t="n">
-        <v>816.5</v>
+        <v>805.7789917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,22 +2892,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>5.847882976611718</v>
+        <v>4.458053176330412</v>
       </c>
       <c r="L22" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M22" t="n">
-        <v>48.14814814814815</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N22" t="n">
-        <v>9.752072580897003</v>
+        <v>10.24875148673902</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>3.922720895897136</v>
+        <v>5.305428021250314</v>
       </c>
       <c r="Q22" t="n">
         <v>27</v>
@@ -2906,19 +2916,19 @@
         <v>51.85185185185185</v>
       </c>
       <c r="S22" t="n">
-        <v>33.92710170487948</v>
+        <v>34.11228689006467</v>
       </c>
       <c r="T22" t="n">
-        <v>17.92475014697237</v>
+        <v>17.73956496178719</v>
       </c>
       <c r="U22" t="n">
         <v>33.98561575495229</v>
       </c>
       <c r="V22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W22" t="n">
-        <v>55.88235294117647</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2960,10 +2970,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C23" t="n">
-        <v>22.93000031</v>
+        <v>22.62319946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,22 +3001,22 @@
         <v>18.24497148325086</v>
       </c>
       <c r="K23" t="n">
-        <v>2.549193579829701</v>
+        <v>1.177096792574717</v>
       </c>
       <c r="L23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>47.05882352941177</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N23" t="n">
-        <v>7.912202245602368</v>
+        <v>8.617763477575568</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4396001610869504</v>
+        <v>1.801695507395773</v>
       </c>
       <c r="Q23" t="n">
         <v>27</v>
@@ -3069,24 +3079,24 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C24" t="n">
-        <v>127.52999878</v>
+        <v>126.77999878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -3097,25 +3107,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>10.13804453095366</v>
+        <v>12.09391062009804</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2101969051456765</v>
+        <v>1.837377723150313</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="N24" t="n">
-        <v>12.27862100052214</v>
+        <v>11.99863686240228</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.769268395032604</v>
+        <v>8.015350021128942</v>
       </c>
       <c r="Q24" t="n">
         <v>35</v>
@@ -3139,25 +3149,25 @@
         <v>55.10204081632653</v>
       </c>
       <c r="X24" t="n">
-        <v>18.83863161428796</v>
+        <v>15.54213549659837</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.949157481654346</v>
+        <v>10.47874371653912</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.51331360108521</v>
+        <v>19.84634450039293</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.05645979196173823</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>36</v>
@@ -3188,10 +3198,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C25" t="n">
-        <v>898.47998047</v>
+        <v>901.01000977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,14 +3297,14 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C26" t="n">
-        <v>236.41999817</v>
+        <v>232.41749573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3304,7 +3314,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3315,25 +3325,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>11.92082492641692</v>
+        <v>14.3363003785587</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05501920677632999</v>
+        <v>1.134632173397598</v>
       </c>
       <c r="L26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>57.14285714285715</v>
+        <v>67.5</v>
       </c>
       <c r="N26" t="n">
-        <v>11.21256438173759</v>
+        <v>11.85821358775109</v>
       </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>7.940611931525754</v>
+        <v>6.788345079291513</v>
       </c>
       <c r="Q26" t="n">
         <v>35</v>
@@ -3356,27 +3366,17 @@
       <c r="W26" t="n">
         <v>60.8695652173913</v>
       </c>
-      <c r="X26" t="n">
-        <v>16.61377328984133</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>11.8723644629563</v>
-      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>8.021609374416245</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
         <v>28</v>
       </c>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C27" t="n">
-        <v>111.45999908</v>
+        <v>105.08999634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,25 +3434,25 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>13.9122753572231</v>
+        <v>15.78143822525823</v>
       </c>
       <c r="K27" t="n">
-        <v>3.818925527854478</v>
+        <v>0.2671489233073476</v>
       </c>
       <c r="L27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M27" t="n">
-        <v>45</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N27" t="n">
-        <v>12.1620108159896</v>
+        <v>10.75180168665076</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>4.027275808227992</v>
+        <v>7.712247889493096</v>
       </c>
       <c r="Q27" t="n">
         <v>16</v>
@@ -3493,10 +3493,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AG27" t="n">
-        <v>7.709617180205415</v>
+        <v>7.542950513538748</v>
       </c>
       <c r="AH27" t="n">
-        <v>25.62371615312792</v>
+        <v>25.79038281979459</v>
       </c>
       <c r="AI27" t="n">
         <v>15.17632443971473</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C28" t="n">
-        <v>87.59999847</v>
+        <v>87.55000305</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,25 +3543,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>11.48223102538071</v>
+        <v>11.99999968527919</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4702328461134497</v>
+        <v>1.003694897194918</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>54.28571428571428</v>
+        <v>62.16216216216216</v>
       </c>
       <c r="N28" t="n">
-        <v>9.955292196253463</v>
+        <v>10.4172646835197</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.522607353990746</v>
+        <v>0.9864046100681367</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C29" t="n">
-        <v>203.66999817</v>
+        <v>203.97999573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,19 +3684,19 @@
         <v>48.38709677419355</v>
       </c>
       <c r="X29" t="n">
-        <v>15.3007164090031</v>
+        <v>12.40258001548387</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.479015836644308</v>
+        <v>6.336671469973087</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>38.46153846153846</v>
+        <v>25</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.109641567169778</v>
+        <v>7.366843789063391</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
@@ -3711,10 +3711,10 @@
         <v>47.61904761904762</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.03835978835979</v>
+        <v>11.15740740740741</v>
       </c>
       <c r="AH29" t="n">
-        <v>36.58068783068784</v>
+        <v>36.46164021164022</v>
       </c>
       <c r="AI29" t="n">
         <v>28.34400610153417</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C30" t="n">
-        <v>684.72998047</v>
+        <v>693.4400024399999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,22 +3796,22 @@
         <v>21.84840721774197</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.996263424913914</v>
+        <v>1.76233954128151</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>26.31578947368421</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.428164700328242</v>
+        <v>9.243365095367428</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.06562823849068</v>
+        <v>3.29574263434238</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3842,14 +3842,14 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C31" t="n">
-        <v>215.83999634</v>
+        <v>222.17500305</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3901,17 +3901,27 @@
       <c r="W31" t="n">
         <v>44.44444444444444</v>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>11.62288403003544</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.02474584037108762</v>
+      </c>
       <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>11.92845557722451</v>
+      </c>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
-      <c r="AD31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>2.975990593510647</v>
+      </c>
       <c r="AE31" t="n">
         <v>26</v>
       </c>
@@ -3941,10 +3951,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C32" t="n">
-        <v>104.23000336</v>
+        <v>103.60500336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4040,10 +4050,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C33" t="n">
-        <v>13.17000008</v>
+        <v>13.07999992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,37 +4081,37 @@
         <v>11.61202677950211</v>
       </c>
       <c r="K33" t="n">
-        <v>1.777438233889028</v>
+        <v>1.081919200495052</v>
       </c>
       <c r="L33" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M33" t="n">
-        <v>56.86274509803921</v>
+        <v>63.26530612244898</v>
       </c>
       <c r="N33" t="n">
-        <v>12.55058230874586</v>
+        <v>11.5566999540909</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.148819069711052</v>
+        <v>4.865440662785581</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R33" t="n">
-        <v>54.76190476190476</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="S33" t="n">
-        <v>43.22931921323939</v>
+        <v>44.2836928525867</v>
       </c>
       <c r="T33" t="n">
-        <v>11.53258554866537</v>
+        <v>11.81386812302306</v>
       </c>
       <c r="U33" t="n">
-        <v>39.94911903473349</v>
+        <v>41.04052722210609</v>
       </c>
       <c r="V33" t="n">
         <v>48</v>
@@ -4149,10 +4159,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C34" t="n">
-        <v>319.01000977</v>
+        <v>318.17001343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,7 +4190,7 @@
         <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>3.979798717709726</v>
+        <v>3.706005897165365</v>
       </c>
       <c r="L34" t="n">
         <v>25</v>
@@ -4189,13 +4199,13 @@
         <v>48</v>
       </c>
       <c r="N34" t="n">
-        <v>12.69421011751322</v>
+        <v>12.65339506121833</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.86632916380667</v>
+        <v>4.140545251634276</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4258,10 +4268,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C35" t="n">
-        <v>83.94999695</v>
+        <v>83.55999756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,10 +4345,10 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AG35" t="n">
-        <v>28.81071063127341</v>
+        <v>28.81490034134547</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.24811289813836</v>
+        <v>18.24392318806629</v>
       </c>
       <c r="AI35" t="n">
         <v>31.45150447508847</v>
@@ -4357,14 +4367,14 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C36" t="n">
-        <v>354.97000122</v>
+        <v>352.1000061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4374,7 +4384,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4416,17 +4426,27 @@
       <c r="W36" t="n">
         <v>48.14814814814815</v>
       </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+      <c r="X36" t="n">
+        <v>11.11552580886888</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.314388028908943</v>
+      </c>
       <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>9.611540673019196</v>
+      </c>
       <c r="AC36" t="n">
         <v>3</v>
       </c>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
       <c r="AE36" t="n">
         <v>20</v>
       </c>
@@ -4434,10 +4454,10 @@
         <v>55</v>
       </c>
       <c r="AG36" t="n">
-        <v>21.162034451735</v>
+        <v>21.35251064221119</v>
       </c>
       <c r="AH36" t="n">
-        <v>33.837965548265</v>
+        <v>33.64748935778881</v>
       </c>
       <c r="AI36" t="n">
         <v>34.20853424503424</v>
@@ -4456,10 +4476,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C37" t="n">
-        <v>959.39001465</v>
+        <v>949.08001709</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,7 +4507,7 @@
         <v>13.30675651903024</v>
       </c>
       <c r="K37" t="n">
-        <v>4.055316122559649</v>
+        <v>2.937095129067235</v>
       </c>
       <c r="L37" t="n">
         <v>38</v>
@@ -4496,13 +4516,13 @@
         <v>55.26315789473684</v>
       </c>
       <c r="N37" t="n">
-        <v>9.954193227163939</v>
+        <v>10.53629816537831</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>5.71300352443167</v>
+        <v>6.861379624203479</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4565,10 +4585,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C38" t="n">
-        <v>33.38999939</v>
+        <v>33.27000046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,25 +4613,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>13.72832922207538</v>
+        <v>14.06988793284954</v>
       </c>
       <c r="K38" t="n">
-        <v>1.690270520939507</v>
+        <v>1.72756030694281</v>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M38" t="n">
-        <v>50.90909090909091</v>
+        <v>50.9433962264151</v>
       </c>
       <c r="N38" t="n">
-        <v>15.3206344232693</v>
+        <v>14.9493074826842</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>6.204850716530674</v>
+        <v>6.165919711562284</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4620,10 +4640,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S38" t="n">
-        <v>32.69616050844603</v>
+        <v>32.49430562574008</v>
       </c>
       <c r="T38" t="n">
-        <v>29.00596715112844</v>
+        <v>29.20782203383438</v>
       </c>
       <c r="U38" t="n">
         <v>47.42656695641357</v>
@@ -4635,19 +4655,19 @@
         <v>71.23287671232876</v>
       </c>
       <c r="X38" t="n">
-        <v>18.08874313747508</v>
+        <v>16.46267138606403</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.27010460299414</v>
+        <v>12.58539342506598</v>
       </c>
       <c r="Z38" t="n">
         <v>11</v>
       </c>
       <c r="AA38" t="n">
-        <v>45.45454545454545</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.11727802990801</v>
+        <v>8.585608626655416</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
@@ -4684,10 +4704,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C39" t="n">
-        <v>297.20001221</v>
+        <v>301.93499756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,7 +4735,7 @@
         <v>17.57170813546579</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6127483903423769</v>
+        <v>2.215708922237924</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -4724,13 +4744,13 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>6.997009141765651</v>
+        <v>6.32375530636368</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>9.330081684319346</v>
+        <v>7.615552599340769</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4771,10 +4791,10 @@
         <v>50</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.06130268199234</v>
+        <v>13.18630268199234</v>
       </c>
       <c r="AH39" t="n">
-        <v>36.93869731800766</v>
+        <v>36.81369731800766</v>
       </c>
       <c r="AI39" t="n">
         <v>29.92980081982123</v>
@@ -4793,10 +4813,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C40" t="n">
-        <v>206.47999573</v>
+        <v>211.27000427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,25 +4841,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>20.00812356142131</v>
+        <v>19.53760153045933</v>
       </c>
       <c r="K40" t="n">
-        <v>4.822824756794919</v>
+        <v>7.25454810121291</v>
       </c>
       <c r="L40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M40" t="n">
-        <v>71.42857142857143</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N40" t="n">
-        <v>8.436049077843947</v>
+        <v>9.073791769367094</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>3.030995635327161</v>
+        <v>0.6950305716487026</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4902,10 +4922,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C41" t="n">
-        <v>231.92999268</v>
+        <v>231.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4965,7 +4985,7 @@
         <v>10.73879246924641</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.898504511885262</v>
+        <v>8.069258489925456</v>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
@@ -4974,7 +4994,7 @@
         <v>50</v>
       </c>
       <c r="AB41" t="n">
-        <v>10.80125222495703</v>
+        <v>10.74405165423873</v>
       </c>
       <c r="AC41" t="n">
         <v>4</v>
@@ -5011,10 +5031,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C42" t="n">
-        <v>121.77999878</v>
+        <v>121.16000366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,19 +5091,19 @@
         <v>69.49152542372882</v>
       </c>
       <c r="X42" t="n">
-        <v>46.49635691053297</v>
+        <v>46.49988754245867</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.362759195606634</v>
+        <v>2.862181996176283</v>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>16.46136610268062</v>
+        <v>7.804571570745455</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
@@ -5098,10 +5118,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG42" t="n">
-        <v>18.370996174305</v>
+        <v>18.32291925122808</v>
       </c>
       <c r="AH42" t="n">
-        <v>27.46233715902834</v>
+        <v>27.51041408210526</v>
       </c>
       <c r="AI42" t="n">
         <v>32.57524229286744</v>
@@ -5120,10 +5140,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C43" t="n">
-        <v>401.6499939</v>
+        <v>402.39001465</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5151,7 +5171,7 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>16.335986647357</v>
+        <v>16.55033009413469</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5186,10 +5206,10 @@
         <v>50</v>
       </c>
       <c r="X43" t="n">
-        <v>16.86604228530051</v>
+        <v>17.00796559594495</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.4535583028040802</v>
+        <v>0.391114826652561</v>
       </c>
       <c r="Z43" t="n">
         <v>19</v>
@@ -5204,7 +5224,7 @@
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>7.580825159126192</v>
+        <v>7.638761502154989</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5235,10 +5255,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C44" t="n">
-        <v>269.47000122</v>
+        <v>268.20001221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5298,22 +5318,22 @@
         <v>10.11126434424055</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.127087842137978</v>
+        <v>4.578928656499237</v>
       </c>
       <c r="Z44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="n">
-        <v>9.090909090909092</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.290252104904014</v>
+        <v>6.300018693230369</v>
       </c>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.953536317722504</v>
+        <v>1.489263664191254</v>
       </c>
       <c r="AE44" t="n">
         <v>14</v>
@@ -5344,10 +5364,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C45" t="n">
-        <v>352.04000854</v>
+        <v>340.07998657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5430,10 +5450,10 @@
         <v>20.75101136856449</v>
       </c>
       <c r="AJ45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK45" t="n">
-        <v>41.37931034482759</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="46">
@@ -5443,10 +5463,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C46" t="n">
-        <v>183.97000122</v>
+        <v>184.92999268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5474,16 +5494,16 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>10.89878949694532</v>
+        <v>11.47748107783027</v>
       </c>
       <c r="L46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M46" t="n">
-        <v>58.33333333333334</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N46" t="n">
-        <v>9.298386782800609</v>
+        <v>9.468877562053361</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5498,10 +5518,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S46" t="n">
-        <v>40.6864804710499</v>
+        <v>40.73127330419659</v>
       </c>
       <c r="T46" t="n">
-        <v>25.27096633746074</v>
+        <v>25.22617350431405</v>
       </c>
       <c r="U46" t="n">
         <v>51.67092456194193</v>
@@ -5516,22 +5536,22 @@
         <v>12.08632414475048</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.059482195411765</v>
+        <v>0.5431912158471164</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA46" t="n">
-        <v>40.38461538461539</v>
+        <v>45.09803921568628</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.30093833412674</v>
+        <v>12.41154959563775</v>
       </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.014838772418852</v>
+        <v>7.497534734234323</v>
       </c>
       <c r="AE46" t="n">
         <v>43</v>
@@ -5562,10 +5582,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C47" t="n">
-        <v>31.71999931</v>
+        <v>31.54500008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5661,10 +5681,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C48" t="n">
-        <v>87.12000275</v>
+        <v>88.30500031</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5760,10 +5780,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C49" t="n">
-        <v>457.5</v>
+        <v>463.21499634</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5859,10 +5879,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C50" t="n">
-        <v>1164.89001465</v>
+        <v>1168.19506836</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5890,16 +5910,16 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>4.634908584430364</v>
+        <v>4.931781240615307</v>
       </c>
       <c r="L50" t="n">
         <v>25</v>
       </c>
       <c r="M50" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N50" t="n">
-        <v>9.181646458077708</v>
+        <v>9.309194714168672</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5946,10 +5966,10 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AG50" t="n">
-        <v>16.93866459627329</v>
+        <v>16.80771221532091</v>
       </c>
       <c r="AH50" t="n">
-        <v>22.34704968944099</v>
+        <v>22.47800207039337</v>
       </c>
       <c r="AI50" t="n">
         <v>23.56568654157959</v>
@@ -5968,19 +5988,19 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C51" t="n">
-        <v>535.40002441</v>
+        <v>521.42498779</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5996,46 +6016,46 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>15.06813824398204</v>
+        <v>15.85507589392084</v>
       </c>
       <c r="K51" t="n">
-        <v>2.878452402276532</v>
+        <v>1.130137253474839</v>
       </c>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M51" t="n">
-        <v>35</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N51" t="n">
-        <v>13.89235137713702</v>
+        <v>9.829818071831747</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.8601419617823014</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R51" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="S51" t="n">
-        <v>18.90078037904125</v>
+        <v>19.90698160535117</v>
       </c>
       <c r="T51" t="n">
-        <v>21.09921962095875</v>
+        <v>17.59301839464883</v>
       </c>
       <c r="U51" t="n">
-        <v>19.82449614134158</v>
+        <v>18.48123255886363</v>
       </c>
       <c r="V51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W51" t="n">
-        <v>45.45454545454545</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -6077,19 +6097,19 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C52" t="n">
-        <v>190.97999573</v>
+        <v>194.88499451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6108,22 +6128,22 @@
         <v>16.63935213539153</v>
       </c>
       <c r="K52" t="n">
-        <v>1.466366216188697</v>
+        <v>3.541065373923602</v>
       </c>
       <c r="L52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M52" t="n">
-        <v>47.82608695652174</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N52" t="n">
-        <v>9.449383235200241</v>
+        <v>8.969975430330191</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>1.511470096941947</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>24</v>
@@ -6186,10 +6206,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C53" t="n">
-        <v>302.27999878</v>
+        <v>305.42999268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,17 +6237,13 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>13.90888357340827</v>
+        <v>15.09590319051892</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>60</v>
-      </c>
-      <c r="N53" t="n">
-        <v>11.79551441110968</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>4</v>
       </c>
@@ -6256,25 +6272,25 @@
         <v>68.75</v>
       </c>
       <c r="X53" t="n">
-        <v>15.19388328049949</v>
+        <v>15.45767052957543</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.115510364350003</v>
+        <v>0.3133333085599044</v>
       </c>
       <c r="Z53" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA53" t="n">
-        <v>39.1304347826087</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB53" t="n">
-        <v>12.35727639039834</v>
+        <v>13.25185352009791</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.984715063389414</v>
+        <v>9.717113645120879</v>
       </c>
       <c r="AE53" t="n">
         <v>35</v>
@@ -6305,10 +6321,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C54" t="n">
-        <v>567.65002441</v>
+        <v>558.59997559</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6404,10 +6420,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C55" t="n">
-        <v>247.88000488</v>
+        <v>251.16000366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6432,25 +6448,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>11.44128000083862</v>
+        <v>11.44160340853909</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5513124100108513</v>
+        <v>1.882199947115892</v>
       </c>
       <c r="L55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>31.25</v>
       </c>
       <c r="N55" t="n">
-        <v>6.866334451539212</v>
+        <v>7.552551706909805</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>2.43526169007553</v>
+        <v>1.097149505472328</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6513,14 +6529,14 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C56" t="n">
-        <v>91.75</v>
+        <v>91.59999847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6530,7 +6546,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6572,27 +6588,17 @@
       <c r="W56" t="n">
         <v>36.8421052631579</v>
       </c>
-      <c r="X56" t="n">
-        <v>10.02075913024301</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>3.836079571952089</v>
-      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>8.784158376605012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>4</v>
       </c>
-      <c r="AD56" t="n">
-        <v>0.1704593857220771</v>
-      </c>
+      <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="n">
         <v>19</v>
       </c>
@@ -6600,10 +6606,10 @@
         <v>31.57894736842105</v>
       </c>
       <c r="AG56" t="n">
-        <v>14.53960756592336</v>
+        <v>14.67118651329178</v>
       </c>
       <c r="AH56" t="n">
-        <v>17.03933980249769</v>
+        <v>16.90776085512928</v>
       </c>
       <c r="AI56" t="n">
         <v>15.36437908779228</v>
@@ -6622,10 +6628,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C57" t="n">
-        <v>741.24499512</v>
+        <v>749.31750488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6682,25 +6688,25 @@
         <v>60.52631578947368</v>
       </c>
       <c r="X57" t="n">
-        <v>40.15299060586315</v>
+        <v>40.94775289945536</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.561089625498013</v>
+        <v>1.050155749587944</v>
       </c>
       <c r="Z57" t="n">
         <v>9</v>
       </c>
       <c r="AA57" t="n">
-        <v>33.33333333333334</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB57" t="n">
-        <v>6.492481763604726</v>
+        <v>10.93029431764743</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>4.509304661758806</v>
+        <v>5.002377000094615</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6731,10 +6737,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>49.72999954</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6751,7 +6757,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6762,22 +6772,22 @@
         <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>5.797718530261675</v>
+        <v>5.22640987685925</v>
       </c>
       <c r="L58" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M58" t="n">
-        <v>66.66666666666667</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N58" t="n">
-        <v>16.13686905611211</v>
+        <v>15.636887868917</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.081596371200023</v>
+        <v>2.635830801779271</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6840,10 +6850,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C59" t="n">
-        <v>149.5</v>
+        <v>152.00999451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,25 +6910,25 @@
         <v>40.90909090909091</v>
       </c>
       <c r="X59" t="n">
-        <v>22.36431024033017</v>
+        <v>21.72833272418202</v>
       </c>
       <c r="Y59" t="n">
-        <v>4.728522977652294</v>
+        <v>3.128985290122632</v>
       </c>
       <c r="Z59" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="n">
-        <v>28.57142857142857</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB59" t="n">
-        <v>9.256718738842906</v>
+        <v>7.568269764282801</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>5.533111469565211</v>
+        <v>7.092952138940245</v>
       </c>
       <c r="AE59" t="n">
         <v>19</v>
@@ -6927,10 +6937,10 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AG59" t="n">
-        <v>11.70412920412921</v>
+        <v>11.20546581765418</v>
       </c>
       <c r="AH59" t="n">
-        <v>14.611660269555</v>
+        <v>15.11032365603003</v>
       </c>
       <c r="AI59" t="n">
         <v>11.80641234678251</v>
@@ -6949,10 +6959,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C60" t="n">
-        <v>257.38000488</v>
+        <v>262.26000977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,25 +7019,25 @@
         <v>69.47368421052632</v>
       </c>
       <c r="X60" t="n">
-        <v>30.18642160955904</v>
+        <v>31.89611792768943</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.454930663335985</v>
+        <v>0.8880902876328145</v>
       </c>
       <c r="Z60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA60" t="n">
-        <v>33.33333333333334</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB60" t="n">
-        <v>14.61354858877807</v>
+        <v>11.4876316801165</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.597409145406183</v>
+        <v>4.148754397226694</v>
       </c>
       <c r="AE60" t="n">
         <v>53</v>
@@ -7058,19 +7068,19 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C61" t="n">
-        <v>206.11999512</v>
+        <v>200.41000366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7085,17 +7095,27 @@
       <c r="I61" t="n">
         <v>10</v>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>10.7162131936937</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.109932332134389</v>
+      </c>
       <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="M61" t="n">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="N61" t="n">
+        <v>10.28712249536336</v>
+      </c>
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>1.869319486494136</v>
+      </c>
       <c r="Q61" t="n">
         <v>32</v>
       </c>
@@ -7103,10 +7123,10 @@
         <v>40.625</v>
       </c>
       <c r="S61" t="n">
-        <v>40.76035648890225</v>
+        <v>40.91660648890225</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.1353564889022465</v>
+        <v>-0.2916064889022465</v>
       </c>
       <c r="U61" t="n">
         <v>25.51963484266544</v>
@@ -7157,10 +7177,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C62" t="n">
-        <v>501.60998535</v>
+        <v>495.51000977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7256,10 +7276,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C63" t="n">
-        <v>1043.95996094</v>
+        <v>1078.07995605</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7316,25 +7336,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X63" t="n">
-        <v>26.03182453415183</v>
+        <v>28.22334378268323</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.928625865759837</v>
+        <v>0.4542976869806092</v>
       </c>
       <c r="Z63" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA63" t="n">
-        <v>55.55555555555556</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.76137818193657</v>
+        <v>13.94670307957604</v>
       </c>
       <c r="AC63" t="n">
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.112108811083724</v>
+        <v>3.56188386904942</v>
       </c>
       <c r="AE63" t="n">
         <v>54</v>
@@ -7365,10 +7385,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C64" t="n">
-        <v>79.62999725</v>
+        <v>79.71499634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7442,10 +7462,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AG64" t="n">
-        <v>9.685220935220935</v>
+        <v>9.824109824109824</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.6481123981124</v>
+        <v>23.50922350922351</v>
       </c>
       <c r="AI64" t="n">
         <v>16.27877475083369</v>
@@ -7464,10 +7484,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C65" t="n">
-        <v>123.05000305</v>
+        <v>124.42849731</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7495,22 +7515,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>2.541669208333341</v>
+        <v>3.690414424999999</v>
       </c>
       <c r="L65" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M65" t="n">
-        <v>48.83720930232558</v>
+        <v>60</v>
       </c>
       <c r="N65" t="n">
-        <v>13.22916687459514</v>
+        <v>12.31882085729384</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.273463411750813</v>
+        <v>6.085023008142931</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7534,19 +7554,19 @@
         <v>67.44186046511628</v>
       </c>
       <c r="X65" t="n">
-        <v>19.61980116727053</v>
+        <v>19.42972700127354</v>
       </c>
       <c r="Y65" t="n">
-        <v>9.047225106858459</v>
+        <v>8.028306984033861</v>
       </c>
       <c r="Z65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA65" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.67392877385792</v>
+        <v>11.63888788218732</v>
       </c>
       <c r="AC65" t="n">
         <v>6</v>
@@ -7583,10 +7603,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C66" t="n">
-        <v>73.36000061</v>
+        <v>72.07499695</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7614,22 +7634,22 @@
         <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>4.63557263118386</v>
+        <v>2.802733308947825</v>
       </c>
       <c r="L66" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M66" t="n">
-        <v>62.16216216216216</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="N66" t="n">
-        <v>14.20425549117039</v>
+        <v>12.71496556991628</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>5.126772123400625</v>
+        <v>7.001046041667602</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7638,19 +7658,19 @@
         <v>59.375</v>
       </c>
       <c r="S66" t="n">
-        <v>41.63020375686206</v>
+        <v>41.24945663042527</v>
       </c>
       <c r="T66" t="n">
-        <v>17.74479624313794</v>
+        <v>18.12554336957473</v>
       </c>
       <c r="U66" t="n">
         <v>42.26002487538288</v>
       </c>
       <c r="V66" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W66" t="n">
-        <v>65.11627906976744</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
@@ -7692,10 +7712,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C67" t="n">
-        <v>36.09999847</v>
+        <v>36.01499939</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7720,25 +7740,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>16.29173844409661</v>
+        <v>14.88081023728842</v>
       </c>
       <c r="K67" t="n">
-        <v>2.121640827329863</v>
+        <v>1.881190802778554</v>
       </c>
       <c r="L67" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M67" t="n">
-        <v>50</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N67" t="n">
-        <v>13.43262190542956</v>
+        <v>11.75877558440893</v>
       </c>
       <c r="O67" t="n">
         <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>7.714681343586216</v>
+        <v>7.968899002111041</v>
       </c>
       <c r="Q67" t="n">
         <v>33</v>
@@ -7801,10 +7821,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C68" t="n">
-        <v>137.67999268</v>
+        <v>136.16000366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7832,22 +7852,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>5.590914429100824</v>
+        <v>4.425189276013231</v>
       </c>
       <c r="L68" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M68" t="n">
-        <v>70.21276595744681</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="N68" t="n">
-        <v>12.08139546847258</v>
+        <v>12.73973496534695</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>4.175629688158145</v>
+        <v>5.33856894360194</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7856,10 +7876,10 @@
         <v>48.93617021276596</v>
       </c>
       <c r="S68" t="n">
-        <v>52.54195353519956</v>
+        <v>53.11675643043801</v>
       </c>
       <c r="T68" t="n">
-        <v>-3.605783322433602</v>
+        <v>-4.180586217672051</v>
       </c>
       <c r="U68" t="n">
         <v>35.27555503368215</v>
@@ -7874,7 +7894,7 @@
         <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>7.967923084195649</v>
+        <v>8.983958483942867</v>
       </c>
       <c r="Z68" t="n">
         <v>12</v>
@@ -7883,7 +7903,7 @@
         <v>50</v>
       </c>
       <c r="AB68" t="n">
-        <v>11.2904366432055</v>
+        <v>11.41220375899009</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7920,10 +7940,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C69" t="n">
-        <v>227.38000488</v>
+        <v>228.72000122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7951,16 +7971,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>8.830714998520239</v>
+        <v>9.472076405186414</v>
       </c>
       <c r="L69" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M69" t="n">
-        <v>66.66666666666667</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N69" t="n">
-        <v>11.6521145174821</v>
+        <v>10.42466721111809</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -7975,10 +7995,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S69" t="n">
-        <v>68.9327301854474</v>
+        <v>68.77179183301969</v>
       </c>
       <c r="T69" t="n">
-        <v>-7.230602525872932</v>
+        <v>-7.069664173445226</v>
       </c>
       <c r="U69" t="n">
         <v>47.42656695641357</v>
@@ -7993,22 +8013,22 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.143631710080674</v>
+        <v>2.572837549518148</v>
       </c>
       <c r="Z69" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA69" t="n">
-        <v>37.73584905660378</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AB69" t="n">
-        <v>12.52971075558355</v>
+        <v>12.75482378585914</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.949076390485128</v>
+        <v>3.51766628964868</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8039,10 +8059,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C70" t="n">
-        <v>232.41000366</v>
+        <v>234.52000427</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8070,22 +8090,22 @@
         <v>10.65198616240091</v>
       </c>
       <c r="K70" t="n">
-        <v>7.269454321950519</v>
+        <v>8.243330706311314</v>
       </c>
       <c r="L70" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M70" t="n">
-        <v>40.90909090909091</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N70" t="n">
-        <v>10.5418328963978</v>
+        <v>9.960987323754711</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>2.545501601839262</v>
+        <v>1.622889172225239</v>
       </c>
       <c r="Q70" t="n">
         <v>32</v>
@@ -8094,10 +8114,10 @@
         <v>59.375</v>
       </c>
       <c r="S70" t="n">
-        <v>41.93110795454545</v>
+        <v>42.10037878787879</v>
       </c>
       <c r="T70" t="n">
-        <v>17.44389204545455</v>
+        <v>17.27462121212121</v>
       </c>
       <c r="U70" t="n">
         <v>42.26002487538288</v>
@@ -8148,10 +8168,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C71" t="n">
-        <v>148.55999756</v>
+        <v>149.05000305</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8183,22 +8203,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K71" t="n">
-        <v>6.877696086330931</v>
+        <v>7.230218021582724</v>
       </c>
       <c r="L71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>43.75</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N71" t="n">
-        <v>12.50905150582083</v>
+        <v>10.88869311955713</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>1.05008243512521</v>
+        <v>0.7178778450887213</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8207,10 +8227,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="S71" t="n">
-        <v>25.18709732468611</v>
+        <v>25.26062673645081</v>
       </c>
       <c r="T71" t="n">
-        <v>39.51878502825507</v>
+        <v>39.44525561649036</v>
       </c>
       <c r="U71" t="n">
         <v>47.91396311978173</v>
@@ -8225,7 +8245,7 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y71" t="n">
-        <v>12.97012289724004</v>
+        <v>12.68306636604192</v>
       </c>
       <c r="Z71" t="n">
         <v>4</v>
@@ -8271,14 +8291,14 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C72" t="n">
-        <v>57.25</v>
+        <v>57.13000107</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8288,7 +8308,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8299,40 +8319,40 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>10.6162778911167</v>
+        <v>11.90214849498216</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4385964912280604</v>
+        <v>1.690994579490779</v>
       </c>
       <c r="L72" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M72" t="n">
-        <v>50.84745762711864</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N72" t="n">
-        <v>17.5069797488751</v>
+        <v>19.01078477972821</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>2.550218340611377</v>
+        <v>1.287238290786896</v>
       </c>
       <c r="Q72" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R72" t="n">
-        <v>43.33333333333334</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="S72" t="n">
-        <v>28.8033342474519</v>
+        <v>27.29450326125777</v>
       </c>
       <c r="T72" t="n">
-        <v>14.52999908588144</v>
+        <v>17.86678706132287</v>
       </c>
       <c r="U72" t="n">
-        <v>27.37748557646652</v>
+        <v>29.16173598052001</v>
       </c>
       <c r="V72" t="n">
         <v>79</v>
@@ -8340,27 +8360,17 @@
       <c r="W72" t="n">
         <v>69.62025316455696</v>
       </c>
-      <c r="X72" t="n">
-        <v>12.66784838130402</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>10.22424402221809</v>
-      </c>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>55.55555555555556</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>11.98205950032272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
         <v>10</v>
       </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="n">
         <v>33</v>
       </c>
@@ -8390,19 +8400,19 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C73" t="n">
-        <v>129.58999634</v>
+        <v>131.13000488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8421,22 +8431,22 @@
         <v>12.28237922496582</v>
       </c>
       <c r="K73" t="n">
-        <v>1.258003545656416</v>
+        <v>2.461323204640986</v>
       </c>
       <c r="L73" t="n">
         <v>20</v>
       </c>
       <c r="M73" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N73" t="n">
-        <v>7.789120604197176</v>
+        <v>7.722513865648351</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>0.7327780801139605</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>16</v>
@@ -8499,10 +8509,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C74" t="n">
-        <v>27.73999977</v>
+        <v>27.80999947</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8562,22 +8572,22 @@
         <v>11.57371556196134</v>
       </c>
       <c r="Y74" t="n">
-        <v>5.032520904824345</v>
+        <v>4.792877966773279</v>
       </c>
       <c r="Z74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA74" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AB74" t="n">
-        <v>9.169300480286273</v>
+        <v>10.03441324978687</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.230715969829303</v>
+        <v>5.469256839219927</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8608,10 +8618,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C75" t="n">
-        <v>183.08999634</v>
+        <v>183.6499939</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8639,16 +8649,16 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K75" t="n">
-        <v>11.26708778265197</v>
+        <v>11.60740838406202</v>
       </c>
       <c r="L75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M75" t="n">
-        <v>71.42857142857143</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>16.62719012983499</v>
+        <v>16.38045520777747</v>
       </c>
       <c r="O75" t="n">
         <v>10</v>
@@ -8678,25 +8688,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X75" t="n">
-        <v>11.44333119476051</v>
+        <v>12.75599504767073</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.1581462167534409</v>
+        <v>1.018647977983878</v>
       </c>
       <c r="Z75" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="AA75" t="n">
-        <v>42</v>
+        <v>49.18032786885246</v>
       </c>
       <c r="AB75" t="n">
-        <v>14.9208019071865</v>
+        <v>14.64926999144619</v>
       </c>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.84635518628904</v>
+        <v>2.001742733899425</v>
       </c>
       <c r="AE75" t="n">
         <v>19</v>
@@ -8727,10 +8737,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C76" t="n">
-        <v>187.47999573</v>
+        <v>188.53500366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8772,10 +8782,10 @@
         <v>39.1304347826087</v>
       </c>
       <c r="S76" t="n">
-        <v>19.44263526357348</v>
+        <v>19.45242766467023</v>
       </c>
       <c r="T76" t="n">
-        <v>19.68779951903522</v>
+        <v>19.67800711793847</v>
       </c>
       <c r="U76" t="n">
         <v>22.15762279247795</v>
@@ -8804,10 +8814,10 @@
         <v>30</v>
       </c>
       <c r="AG76" t="n">
-        <v>12.19345238095238</v>
+        <v>12.21446078431373</v>
       </c>
       <c r="AH76" t="n">
-        <v>17.80654761904762</v>
+        <v>17.78553921568627</v>
       </c>
       <c r="AI76" t="n">
         <v>14.54772448676043</v>
@@ -8826,10 +8836,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C77" t="n">
-        <v>194.22999573</v>
+        <v>196.44000244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8871,10 +8881,10 @@
         <v>45.94594594594594</v>
       </c>
       <c r="S77" t="n">
-        <v>43.74503262661158</v>
+        <v>43.84527867635976</v>
       </c>
       <c r="T77" t="n">
-        <v>2.200913319334369</v>
+        <v>2.100667269586182</v>
       </c>
       <c r="U77" t="n">
         <v>31.03856980437303</v>
@@ -8886,25 +8896,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>25.01440369846701</v>
+        <v>26.35217262704843</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.5529680218587907</v>
+        <v>0.4863178772367749</v>
       </c>
       <c r="Z77" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA77" t="n">
-        <v>37.5</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB77" t="n">
-        <v>7.69349818478715</v>
+        <v>8.822785207291803</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>9.499561515538947</v>
+        <v>9.560174962701961</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8935,10 +8945,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C78" t="n">
-        <v>194.33999634</v>
+        <v>190.46000671</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8957,7 +8967,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -8967,25 +8977,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>15.7351954478678</v>
+        <v>17.38881221393466</v>
       </c>
       <c r="K78" t="n">
-        <v>1.65289453969657</v>
+        <v>1.82849312590454</v>
       </c>
       <c r="L78" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M78" t="n">
-        <v>78.94736842105263</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N78" t="n">
-        <v>11.25415779326658</v>
+        <v>14.09576159547897</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>0.3414614624356549</v>
+        <v>0.1684271944232707</v>
       </c>
       <c r="Q78" t="n">
         <v>12</v>
@@ -9048,19 +9058,19 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C79" t="n">
-        <v>106.87999725</v>
+        <v>101.02500153</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9075,17 +9085,27 @@
       <c r="I79" t="n">
         <v>10</v>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>13.29782231051553</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.737158536774075</v>
+      </c>
       <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="M79" t="n">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="N79" t="n">
+        <v>10.59077997077294</v>
+      </c>
       <c r="O79" t="n">
         <v>6</v>
       </c>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>4.190053589598808</v>
+      </c>
       <c r="Q79" t="n">
         <v>27</v>
       </c>
@@ -9147,10 +9167,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C80" t="n">
-        <v>51.75999832</v>
+        <v>52.27999878</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9175,25 +9195,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>16.51637120732817</v>
+        <v>16.52331791600153</v>
       </c>
       <c r="K80" t="n">
-        <v>2.547434311848007</v>
+        <v>3.586283963240211</v>
       </c>
       <c r="L80" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M80" t="n">
-        <v>57.57575757575758</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N80" t="n">
-        <v>14.02395794534022</v>
+        <v>16.04957400277359</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>1.416481746130027</v>
+        <v>0.3993926810875958</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9202,10 +9222,10 @@
         <v>51.16279069767442</v>
       </c>
       <c r="S80" t="n">
-        <v>37.13031022624946</v>
+        <v>37.2465892960169</v>
       </c>
       <c r="T80" t="n">
-        <v>14.03248047142496</v>
+        <v>13.91620140165752</v>
       </c>
       <c r="U80" t="n">
         <v>36.75230846944931</v>
@@ -9256,10 +9276,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C81" t="n">
-        <v>41.20000076</v>
+        <v>40.59000015</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9276,7 +9296,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>5</v>
       </c>
@@ -9287,13 +9311,17 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K81" t="n">
-        <v>20.85655787244107</v>
+        <v>19.06717504077218</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M81" t="n">
+        <v>100</v>
+      </c>
+      <c r="N81" t="n">
+        <v>13.44989647840349</v>
+      </c>
       <c r="O81" t="n">
         <v>6</v>
       </c>
@@ -9325,22 +9353,22 @@
         <v>36.83700278308666</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.623494620794431</v>
+        <v>4.065235557329883</v>
       </c>
       <c r="Z81" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA81" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB81" t="n">
-        <v>14.79127707394377</v>
+        <v>15.61237027176215</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.52135790688757</v>
+        <v>4.101500082403908</v>
       </c>
       <c r="AE81" t="n">
         <v>76</v>
@@ -9371,10 +9399,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C82" t="n">
-        <v>404.47000122</v>
+        <v>404.2749939</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9402,22 +9430,22 @@
         <v>11.8900081911483</v>
       </c>
       <c r="K82" t="n">
-        <v>0.9081193453484904</v>
+        <v>0.859468464293256</v>
       </c>
       <c r="L82" t="n">
         <v>22</v>
       </c>
       <c r="M82" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N82" t="n">
-        <v>10.68747122516058</v>
+        <v>10.24481670081885</v>
       </c>
       <c r="O82" t="n">
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>9.010058569752367</v>
+        <v>9.062640994328387</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -9480,10 +9508,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C83" t="n">
-        <v>274.19000244</v>
+        <v>276.91500854</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9511,17 +9539,13 @@
         <v>23.66411973888177</v>
       </c>
       <c r="K83" t="n">
-        <v>2.692884808988771</v>
+        <v>3.713486344569272</v>
       </c>
       <c r="L83" t="n">
-        <v>3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N83" t="n">
-        <v>7.952586279424212</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>2</v>
       </c>
@@ -9589,10 +9613,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C84" t="n">
-        <v>25.45000076</v>
+        <v>25.16500092</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9649,19 +9673,19 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X84" t="n">
-        <v>14.74222881006126</v>
+        <v>12.30192171221367</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.495727935251549</v>
+        <v>6.554026623403331</v>
       </c>
       <c r="Z84" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AA84" t="n">
-        <v>21.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.41021637006637</v>
+        <v>10.3555874022774</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9670,19 +9694,19 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF84" t="n">
-        <v>25</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="AG84" t="n">
-        <v>12.20678275972394</v>
+        <v>12.19135027339362</v>
       </c>
       <c r="AH84" t="n">
-        <v>12.79321724027606</v>
+        <v>14.12443920029059</v>
       </c>
       <c r="AI84" t="n">
-        <v>11.18617014076657</v>
+        <v>11.80641234678251</v>
       </c>
       <c r="AJ84" t="n">
         <v>19</v>
@@ -9698,10 +9722,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C85" t="n">
-        <v>130.96000671</v>
+        <v>130.6000061</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9726,10 +9750,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>23.66801733058809</v>
+        <v>22.77987498113207</v>
       </c>
       <c r="K85" t="n">
-        <v>6.662329378791676</v>
+        <v>6.369121516291965</v>
       </c>
       <c r="L85" t="n">
         <v>1</v>
@@ -9803,10 +9827,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C86" t="n">
-        <v>375.29998779</v>
+        <v>376.90499878</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9866,22 +9890,22 @@
         <v>18.66270892223245</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.275809956162334</v>
+        <v>1.857881887651502</v>
       </c>
       <c r="Z86" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AA86" t="n">
-        <v>43.54838709677419</v>
+        <v>44.61538461538461</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.18015519051553</v>
+        <v>14.33758974622789</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.7410550484100331</v>
+        <v>1.163739008608977</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9912,10 +9936,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C87" t="n">
-        <v>445.14001465</v>
+        <v>446.66500854</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9957,10 +9981,10 @@
         <v>62.85714285714285</v>
       </c>
       <c r="S87" t="n">
-        <v>38.53446374414116</v>
+        <v>38.53963972757801</v>
       </c>
       <c r="T87" t="n">
-        <v>24.32267911300169</v>
+        <v>24.31750312956484</v>
       </c>
       <c r="U87" t="n">
         <v>46.33693684359532</v>
@@ -9972,25 +9996,25 @@
         <v>55.26315789473684</v>
       </c>
       <c r="X87" t="n">
-        <v>10.01357717655884</v>
+        <v>10.65035245950179</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.1301235233806985</v>
+        <v>0.3646861651569022</v>
       </c>
       <c r="Z87" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA87" t="n">
-        <v>36.36363636363637</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.77096045075639</v>
+        <v>11.81374338316508</v>
       </c>
       <c r="AC87" t="n">
         <v>6</v>
       </c>
       <c r="AD87" t="n">
-        <v>5.877524518610489</v>
+        <v>5.655940266504588</v>
       </c>
       <c r="AE87" t="n">
         <v>36</v>
@@ -10021,14 +10045,14 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C88" t="n">
-        <v>270.86999512</v>
+        <v>269.26000977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10052,7 +10076,7 @@
         <v>14.3256649882924</v>
       </c>
       <c r="K88" t="n">
-        <v>9.16454672662319</v>
+        <v>8.515699219938689</v>
       </c>
       <c r="L88" t="n">
         <v>20</v>
@@ -10061,13 +10085,13 @@
         <v>30</v>
       </c>
       <c r="N88" t="n">
-        <v>7.186011681620726</v>
+        <v>7.301238111646442</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>0.7653155703279957</v>
+        <v>1.367821237600797</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10094,22 +10118,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.9000078918783405</v>
+        <v>1.489034134554312</v>
       </c>
       <c r="Z88" t="n">
         <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>30</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.41208368857444</v>
+        <v>10.90209910753714</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.128145665984983</v>
+        <v>2.548920156640611</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10140,10 +10164,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C89" t="n">
-        <v>70.83999634</v>
+        <v>70.33000183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10160,11 +10184,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.68: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10175,22 +10195,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K89" t="n">
-        <v>2.310800880200947</v>
+        <v>1.574240328839882</v>
       </c>
       <c r="L89" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M89" t="n">
-        <v>75.67567567567568</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N89" t="n">
-        <v>14.04258870465226</v>
+        <v>14.20605006089529</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>1.651046717713611</v>
+        <v>2.388164226783163</v>
       </c>
       <c r="Q89" t="n">
         <v>28</v>
@@ -10253,10 +10273,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C90" t="n">
-        <v>377.55999756</v>
+        <v>374.23999023</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10352,10 +10372,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C91" t="n">
-        <v>269.63000488</v>
+        <v>271.625</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10383,7 +10403,7 @@
         <v>14.60766672642613</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5106967345503977</v>
+        <v>1.254376391354439</v>
       </c>
       <c r="L91" t="n">
         <v>20</v>
@@ -10392,13 +10412,13 @@
         <v>60</v>
       </c>
       <c r="N91" t="n">
-        <v>9.573441490935112</v>
+        <v>9.67454013150881</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>1.481736087635399</v>
+        <v>0.7363865496180511</v>
       </c>
       <c r="Q91" t="n">
         <v>17</v>
@@ -10439,10 +10459,10 @@
         <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>18.37197931276879</v>
+        <v>18.24697931276879</v>
       </c>
       <c r="AH91" t="n">
-        <v>21.62802068723121</v>
+        <v>21.75302068723121</v>
       </c>
       <c r="AI91" t="n">
         <v>21.88065323728171</v>
@@ -10461,10 +10481,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C92" t="n">
-        <v>369.95001221</v>
+        <v>362.79998779</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10560,10 +10580,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C93" t="n">
-        <v>250.86000061</v>
+        <v>253.09010315</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10591,16 +10611,16 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>10.54022997832835</v>
+        <v>11.52291373439716</v>
       </c>
       <c r="L93" t="n">
         <v>8</v>
       </c>
       <c r="M93" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N93" t="n">
-        <v>11.73748496034269</v>
+        <v>11.84691764092608</v>
       </c>
       <c r="O93" t="n">
         <v>10</v>
@@ -10630,25 +10650,25 @@
         <v>74.39024390243902</v>
       </c>
       <c r="X93" t="n">
-        <v>12.3097290736065</v>
+        <v>12.53635174236054</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.575552812631609</v>
+        <v>0.9005427955257939</v>
       </c>
       <c r="Z93" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA93" t="n">
-        <v>43.39622641509434</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="AB93" t="n">
-        <v>14.77795812566167</v>
+        <v>15.25721401882834</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.463257103952055</v>
+        <v>3.127622786146067</v>
       </c>
       <c r="AE93" t="n">
         <v>31</v>
@@ -10679,10 +10699,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C94" t="n">
-        <v>47.68000031</v>
+        <v>47.06999969</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10739,19 +10759,19 @@
         <v>35</v>
       </c>
       <c r="X94" t="n">
-        <v>12.08242925132574</v>
+        <v>10.85603409950266</v>
       </c>
       <c r="Y94" t="n">
-        <v>7.722078578118907</v>
+        <v>8.902648815402491</v>
       </c>
       <c r="Z94" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AA94" t="n">
-        <v>42.85714285714285</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB94" t="n">
-        <v>8.473516272682568</v>
+        <v>7.083717613832559</v>
       </c>
       <c r="AC94" t="n">
         <v>2</v>
@@ -10788,7 +10808,7 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C95" t="n">
         <v>30.79999924</v>
@@ -10842,25 +10862,25 @@
         <v>51.67092456194193</v>
       </c>
       <c r="V95" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W95" t="n">
-        <v>61.19402985074627</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="X95" t="n">
-        <v>16.24060014393127</v>
+        <v>15.02976579706115</v>
       </c>
       <c r="Y95" t="n">
         <v>0.3881010339247148</v>
       </c>
       <c r="Z95" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AA95" t="n">
-        <v>48.93617021276596</v>
+        <v>48</v>
       </c>
       <c r="AB95" t="n">
-        <v>12.3026627979828</v>
+        <v>12.63847080611493</v>
       </c>
       <c r="AC95" t="n">
         <v>8</v>
@@ -10897,14 +10917,14 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C96" t="n">
-        <v>86.54000092</v>
+        <v>83.62010193</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10914,7 +10934,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -10932,51 +10952,41 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R96" t="n">
-        <v>44.82758620689656</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="S96" t="n">
-        <v>38.67873801802249</v>
+        <v>36.31816540221713</v>
       </c>
       <c r="T96" t="n">
-        <v>6.148848188874069</v>
+        <v>6.538977454925728</v>
       </c>
       <c r="U96" t="n">
-        <v>28.41316802303719</v>
+        <v>26.50854712412369</v>
       </c>
       <c r="V96" t="n">
         <v>36</v>
       </c>
       <c r="W96" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="X96" t="n">
-        <v>10.19405145840906</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>5.924553828443802</v>
-      </c>
+        <v>52.77777777777778</v>
+      </c>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>27.77777777777778</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>8.444925214768407</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
         <v>6</v>
       </c>
-      <c r="AD96" t="n">
-        <v>0.08019751659601448</v>
-      </c>
+      <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="n">
         <v>29</v>
       </c>
@@ -10993,10 +11003,10 @@
         <v>34.43102188199472</v>
       </c>
       <c r="AJ96" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AK96" t="n">
-        <v>56.75675675675676</v>
+        <v>55.55555555555556</v>
       </c>
     </row>
     <row r="97">
@@ -11006,10 +11016,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C97" t="n">
-        <v>107.44000244</v>
+        <v>109.19999695</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11037,16 +11047,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>5.178659648327466</v>
+        <v>6.901610684684645</v>
       </c>
       <c r="L97" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N97" t="n">
-        <v>9.549824708064946</v>
+        <v>7.786884223287527</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -11115,10 +11125,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C98" t="n">
-        <v>158.30000305</v>
+        <v>159.71000671</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11160,10 +11170,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="S98" t="n">
-        <v>25.93218294182662</v>
+        <v>26.05123056087423</v>
       </c>
       <c r="T98" t="n">
-        <v>31.21067420103053</v>
+        <v>31.09162658198291</v>
       </c>
       <c r="U98" t="n">
         <v>36.54655436930671</v>
@@ -11192,10 +11202,10 @@
         <v>50</v>
       </c>
       <c r="AG98" t="n">
-        <v>23.29596222204581</v>
+        <v>23.30158525398464</v>
       </c>
       <c r="AH98" t="n">
-        <v>26.70403777795419</v>
+        <v>26.69841474601536</v>
       </c>
       <c r="AI98" t="n">
         <v>31.42742581957335</v>
@@ -11214,10 +11224,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C99" t="n">
-        <v>30482.3515625</v>
+        <v>30595.95703125</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -670,7 +670,7 @@
         <v>46287</v>
       </c>
       <c r="C2" t="n">
-        <v>342.49099731</v>
+        <v>339.75</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,22 +730,22 @@
         <v>14.89502875525965</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8249838015273125</v>
+        <v>1.618693577125219</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>28.57142857142857</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.13625423883436</v>
+        <v>13.58815897675221</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.234701312388769</v>
+        <v>6.486299740161872</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -779,7 +779,7 @@
         <v>46287</v>
       </c>
       <c r="C3" t="n">
-        <v>266.05999756</v>
+        <v>265.20999146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46287</v>
       </c>
       <c r="C4" t="n">
-        <v>104.0625</v>
+        <v>103.69000244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>3.720221371394339</v>
+        <v>3.34894901695828</v>
       </c>
       <c r="L4" t="n">
         <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>47.05882352941177</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N4" t="n">
-        <v>8.162860539846717</v>
+        <v>7.890725191224749</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.198007870078089</v>
+        <v>2.565145565831273</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -987,7 +987,7 @@
         <v>46287</v>
       </c>
       <c r="C5" t="n">
-        <v>183.71499634</v>
+        <v>183.72000122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.040939228053523</v>
+        <v>7.038406778589157</v>
       </c>
       <c r="Z5" t="n">
         <v>12</v>
@@ -1096,7 +1096,7 @@
         <v>46287</v>
       </c>
       <c r="C6" t="n">
-        <v>384.85501099</v>
+        <v>390.36999512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,16 +1124,16 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>10.59052039942527</v>
+        <v>12.175285954023</v>
       </c>
       <c r="L6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M6" t="n">
-        <v>34.78260869565217</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="N6" t="n">
-        <v>8.306221714859321</v>
+        <v>9.304681100542773</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
@@ -1163,10 +1163,10 @@
         <v>42.5</v>
       </c>
       <c r="X6" t="n">
-        <v>11.52684003448274</v>
+        <v>12.22557857183908</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8395464578463518</v>
+        <v>0.04481386369854512</v>
       </c>
       <c r="Z6" t="n">
         <v>30</v>
@@ -1175,13 +1175,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.609781599357904</v>
+        <v>11.83396486958489</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.187211664789458</v>
+        <v>3.956959402694793</v>
       </c>
       <c r="AE6" t="n">
         <v>29</v>
@@ -1215,7 +1215,7 @@
         <v>46287</v>
       </c>
       <c r="C7" t="n">
-        <v>268.8500061</v>
+        <v>269.64001465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>46287</v>
       </c>
       <c r="C8" t="n">
-        <v>465.42001343</v>
+        <v>472.45999146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,17 +1342,13 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>13.10053276471481</v>
+        <v>14.81129990594057</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="N8" t="n">
-        <v>9.870996799924031</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>5</v>
       </c>
@@ -1381,25 +1377,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X8" t="n">
-        <v>14.26939802820826</v>
+        <v>14.81616480096733</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.022903142628706</v>
+        <v>0.004237116816441233</v>
       </c>
       <c r="Z8" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.28571428571428</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.33533409392914</v>
+        <v>12.11302435876111</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.06987287201153</v>
+        <v>9.996186433279918</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -1433,7 +1429,7 @@
         <v>46287</v>
       </c>
       <c r="C9" t="n">
-        <v>613.45001221</v>
+        <v>623.77001953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,25 +1486,25 @@
         <v>69.56521739130434</v>
       </c>
       <c r="X9" t="n">
-        <v>41.20317820658344</v>
+        <v>41.77525982519865</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.374596107717052</v>
+        <v>0.1200922270777505</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>53.84615384615385</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.59452842311039</v>
+        <v>14.3701493681632</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.689870671997188</v>
+        <v>5.88697757540012</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1542,7 +1538,7 @@
         <v>46287</v>
       </c>
       <c r="C10" t="n">
-        <v>254.39030457</v>
+        <v>254.97999573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,22 +1566,22 @@
         <v>12.38702974586333</v>
       </c>
       <c r="K10" t="n">
-        <v>4.130291196899782</v>
+        <v>4.371671120206333</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M10" t="n">
-        <v>32.35294117647059</v>
+        <v>43.75</v>
       </c>
       <c r="N10" t="n">
-        <v>12.68876942864811</v>
+        <v>11.60730936984054</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.716218171120822</v>
+        <v>3.476354111083335</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
@@ -1651,7 +1647,7 @@
         <v>46287</v>
       </c>
       <c r="C11" t="n">
-        <v>204.41999817</v>
+        <v>205.19000244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,16 +1675,16 @@
         <v>14.2728744929405</v>
       </c>
       <c r="K11" t="n">
-        <v>12.77100091282524</v>
+        <v>13.19578397227343</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>70</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N11" t="n">
-        <v>12.70642957614508</v>
+        <v>14.60517234197607</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1721,22 +1717,22 @@
         <v>14.88938578045085</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.843847326047832</v>
+        <v>1.474115120968467</v>
       </c>
       <c r="Z11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA11" t="n">
-        <v>42.10526315789474</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.45614554197544</v>
+        <v>11.68272682296382</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.271794998323966</v>
+        <v>6.623523236603157</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1770,7 +1766,7 @@
         <v>46287</v>
       </c>
       <c r="C12" t="n">
-        <v>82.18000031</v>
+        <v>82.83999634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,16 +1794,16 @@
         <v>12.33653883634149</v>
       </c>
       <c r="K12" t="n">
-        <v>8.488449254125419</v>
+        <v>9.359731141914196</v>
       </c>
       <c r="L12" t="n">
         <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>47.05882352941177</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="N12" t="n">
-        <v>8.758927394816478</v>
+        <v>9.968600531219094</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1840,22 +1836,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.722541380826948</v>
+        <v>1.941296111236324</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.63636363636364</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.83869362026744</v>
+        <v>9.54377757206133</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>7.481135632524316</v>
+        <v>8.218244346677627</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1889,7 +1885,7 @@
         <v>46287</v>
       </c>
       <c r="C13" t="n">
-        <v>329.30499268</v>
+        <v>333.20001221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,11 +1902,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>5</v>
       </c>
@@ -1950,25 +1942,25 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>47.76549707040503</v>
+        <v>48.43430927883343</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15475992332138</v>
+        <v>0.436261110988112</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.18567789929377</v>
+        <v>14.02555810861999</v>
       </c>
       <c r="AC13" t="n">
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.866797101455964</v>
+        <v>2.574972492615812</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -2002,16 +1994,16 @@
         <v>46287</v>
       </c>
       <c r="C14" t="n">
-        <v>1717.85998535</v>
+        <v>1747.90002441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2030,22 +2022,22 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>9.220265423150909</v>
+        <v>11.13018885546517</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>56.25</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>9.89370104261983</v>
+        <v>9.638543004103335</v>
       </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7139101647740675</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2069,25 +2061,25 @@
         <v>57.4468085106383</v>
       </c>
       <c r="X14" t="n">
-        <v>10.6622464385669</v>
+        <v>11.24462686563246</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.30304693951474</v>
+        <v>0.1028705955439135</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>35.41666666666666</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.10990500089401</v>
+        <v>12.86001943665113</v>
       </c>
       <c r="AC14" t="n">
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.758964603098526</v>
+        <v>5.903202063575053</v>
       </c>
       <c r="AE14" t="n">
         <v>35</v>
@@ -2121,7 +2113,7 @@
         <v>46287</v>
       </c>
       <c r="C15" t="n">
-        <v>362.42999268</v>
+        <v>364.54000854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,13 +2141,13 @@
         <v>21.311746679127</v>
       </c>
       <c r="K15" t="n">
-        <v>7.927100239248763</v>
+        <v>8.555436463700495</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M15" t="n">
-        <v>57.14285714285715</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N15" t="n">
         <v>14.92018308377776</v>
@@ -2230,7 +2222,7 @@
         <v>46287</v>
       </c>
       <c r="C16" t="n">
-        <v>307.69711304</v>
+        <v>305.07000732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,25 +2247,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>11.84062035511823</v>
+        <v>12.11142859736806</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5513229032174438</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N16" t="n">
-        <v>10.52910447439699</v>
+        <v>10.42456807465101</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.440734000264654</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2339,7 +2331,7 @@
         <v>46287</v>
       </c>
       <c r="C17" t="n">
-        <v>198.42999268</v>
+        <v>197.72000122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,22 +2359,22 @@
         <v>17.56568419419229</v>
       </c>
       <c r="K17" t="n">
-        <v>1.519485249177599</v>
+        <v>1.156243953962988</v>
       </c>
       <c r="L17" t="n">
         <v>37</v>
       </c>
       <c r="M17" t="n">
-        <v>62.16216216216216</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N17" t="n">
-        <v>12.44577820104661</v>
+        <v>12.34001860995113</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.413452983754862</v>
+        <v>4.788390569584067</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2448,7 +2440,7 @@
         <v>46287</v>
       </c>
       <c r="C18" t="n">
-        <v>56.52500153</v>
+        <v>56.20000076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,22 +2468,22 @@
         <v>14.05029013936877</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8204814255606818</v>
+        <v>0.240795742974953</v>
       </c>
       <c r="L18" t="n">
         <v>27</v>
       </c>
       <c r="M18" t="n">
-        <v>37.03703703703704</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="N18" t="n">
-        <v>12.22840581705775</v>
+        <v>11.58798642514625</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.161781558292342</v>
+        <v>2.75257617078366</v>
       </c>
       <c r="Q18" t="n">
         <v>24</v>
@@ -2557,7 +2549,7 @@
         <v>46287</v>
       </c>
       <c r="C19" t="n">
-        <v>161.61000061</v>
+        <v>164.22000122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,25 +2574,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>25.99852664131597</v>
+        <v>26.10436640399428</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4912282390511669</v>
+        <v>2.260417811028881</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N19" t="n">
-        <v>8.125463674653508</v>
+        <v>9.06462653177455</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>7.472066858499105</v>
+        <v>5.612711459459829</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2666,7 +2658,7 @@
         <v>46287</v>
       </c>
       <c r="C20" t="n">
-        <v>62.76499939</v>
+        <v>62.25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2757,7 @@
         <v>46287</v>
       </c>
       <c r="C21" t="n">
-        <v>132.02999878</v>
+        <v>132.47000122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2856,7 @@
         <v>46287</v>
       </c>
       <c r="C22" t="n">
-        <v>805.7789917</v>
+        <v>808.01000977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,22 +2884,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>4.458053176330412</v>
+        <v>4.747273677974095</v>
       </c>
       <c r="L22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>48.38709677419355</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N22" t="n">
-        <v>10.24875148673902</v>
+        <v>9.831739442004206</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>5.305428021250314</v>
+        <v>5.014666384706534</v>
       </c>
       <c r="Q22" t="n">
         <v>27</v>
@@ -2973,7 +2965,7 @@
         <v>46287</v>
       </c>
       <c r="C23" t="n">
-        <v>22.62319946</v>
+        <v>22.42000008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2998,25 +2990,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>18.24497148325086</v>
+        <v>18.28153539499147</v>
       </c>
       <c r="K23" t="n">
-        <v>1.177096792574717</v>
+        <v>0.3131977575384637</v>
       </c>
       <c r="L23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>46.66666666666666</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N23" t="n">
-        <v>8.617763477575568</v>
+        <v>8.082740010852966</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.801695507395773</v>
+        <v>2.678413511406208</v>
       </c>
       <c r="Q23" t="n">
         <v>27</v>
@@ -3082,7 +3074,7 @@
         <v>46287</v>
       </c>
       <c r="C24" t="n">
-        <v>126.77999878</v>
+        <v>125.26999664</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,22 +3102,22 @@
         <v>12.09391062009804</v>
       </c>
       <c r="K24" t="n">
-        <v>1.837377723150313</v>
+        <v>0.6244525001363188</v>
       </c>
       <c r="L24" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M24" t="n">
-        <v>46.80851063829788</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="N24" t="n">
-        <v>11.99863686240228</v>
+        <v>11.21798687594374</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>8.015350021128942</v>
+        <v>9.317364981291188</v>
       </c>
       <c r="Q24" t="n">
         <v>35</v>
@@ -3152,7 +3144,7 @@
         <v>15.54213549659837</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.47874371653912</v>
+        <v>11.54497884719317</v>
       </c>
       <c r="Z24" t="n">
         <v>15</v>
@@ -3161,7 +3153,7 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB24" t="n">
-        <v>19.84634450039293</v>
+        <v>23.26287165872696</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
@@ -3201,7 +3193,7 @@
         <v>46287</v>
       </c>
       <c r="C25" t="n">
-        <v>901.01000977</v>
+        <v>899.40997314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,7 +3292,7 @@
         <v>46287</v>
       </c>
       <c r="C26" t="n">
-        <v>232.41749573</v>
+        <v>233.27999878</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3328,22 +3320,22 @@
         <v>14.3363003785587</v>
       </c>
       <c r="K26" t="n">
-        <v>1.134632173397598</v>
+        <v>1.509943543293435</v>
       </c>
       <c r="L26" t="n">
         <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="N26" t="n">
-        <v>11.85821358775109</v>
+        <v>12.3463803058366</v>
       </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>6.788345079291513</v>
+        <v>6.393517945302185</v>
       </c>
       <c r="Q26" t="n">
         <v>35</v>
@@ -3409,7 +3401,7 @@
         <v>46287</v>
       </c>
       <c r="C27" t="n">
-        <v>105.08999634</v>
+        <v>106.44000244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,25 +3426,25 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>15.78143822525823</v>
+        <v>16.02249521790768</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2671489233073476</v>
+        <v>1.846713482423046</v>
       </c>
       <c r="L27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M27" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="N27" t="n">
-        <v>10.75180168665076</v>
+        <v>11.99970971428389</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>7.712247889493096</v>
+        <v>6.041713381982539</v>
       </c>
       <c r="Q27" t="n">
         <v>16</v>
@@ -3518,7 +3510,7 @@
         <v>46287</v>
       </c>
       <c r="C28" t="n">
-        <v>87.55000305</v>
+        <v>87.09999847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,22 +3538,22 @@
         <v>11.99999968527919</v>
       </c>
       <c r="K28" t="n">
-        <v>1.003694897194918</v>
+        <v>0.4845387153875613</v>
       </c>
       <c r="L28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>62.16216216216216</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N28" t="n">
-        <v>10.4172646835197</v>
+        <v>10.4975408863062</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9864046100681367</v>
+        <v>1.508153696067449</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3627,7 +3619,7 @@
         <v>46287</v>
       </c>
       <c r="C29" t="n">
-        <v>203.97999573</v>
+        <v>202.41000366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,16 +3679,16 @@
         <v>12.40258001548387</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.336671469973087</v>
+        <v>7.057578843834356</v>
       </c>
       <c r="Z29" t="n">
         <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.366843789063391</v>
+        <v>6.398777077334111</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
@@ -3736,7 +3728,7 @@
         <v>46287</v>
       </c>
       <c r="C30" t="n">
-        <v>693.4400024399999</v>
+        <v>703.11999512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,22 +3788,22 @@
         <v>21.84840721774197</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.76233954128151</v>
+        <v>0.3910026833058078</v>
       </c>
       <c r="Z30" t="n">
         <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>39.1304347826087</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.243365095367428</v>
+        <v>9.29158783186034</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.29574263434238</v>
+        <v>4.627089360251735</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3845,7 +3837,7 @@
         <v>46287</v>
       </c>
       <c r="C31" t="n">
-        <v>222.17500305</v>
+        <v>221.08999634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,25 +3894,25 @@
         <v>44.44444444444444</v>
       </c>
       <c r="X31" t="n">
-        <v>11.62288403003544</v>
+        <v>11.71831948309332</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.02474584037108762</v>
+        <v>0.5979686363379422</v>
       </c>
       <c r="Z31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA31" t="n">
-        <v>50</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.92845557722451</v>
+        <v>11.86672979181411</v>
       </c>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.975990593510647</v>
+        <v>2.416481163120532</v>
       </c>
       <c r="AE31" t="n">
         <v>26</v>
@@ -3954,7 +3946,7 @@
         <v>46287</v>
       </c>
       <c r="C32" t="n">
-        <v>103.60500336</v>
+        <v>103.81999969</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,7 +4045,7 @@
         <v>46287</v>
       </c>
       <c r="C33" t="n">
-        <v>13.07999992</v>
+        <v>13.10000038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,22 +4073,22 @@
         <v>11.61202677950211</v>
       </c>
       <c r="K33" t="n">
-        <v>1.081919200495052</v>
+        <v>1.236482265790007</v>
       </c>
       <c r="L33" t="n">
         <v>49</v>
       </c>
       <c r="M33" t="n">
-        <v>63.26530612244898</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N33" t="n">
-        <v>11.5566999540909</v>
+        <v>11.63053169281733</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.865440662785581</v>
+        <v>4.705337075723048</v>
       </c>
       <c r="Q33" t="n">
         <v>41</v>
@@ -4162,7 +4154,7 @@
         <v>46287</v>
       </c>
       <c r="C34" t="n">
-        <v>318.17001343</v>
+        <v>319.22000122</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,22 +4182,22 @@
         <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>3.706005897165365</v>
+        <v>4.0482444342538</v>
       </c>
       <c r="L34" t="n">
         <v>25</v>
       </c>
       <c r="M34" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N34" t="n">
-        <v>12.65339506121833</v>
+        <v>12.14395554637762</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>4.140545251634276</v>
+        <v>3.798003115990345</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4271,7 +4263,7 @@
         <v>46287</v>
       </c>
       <c r="C35" t="n">
-        <v>83.55999756</v>
+        <v>83.44999695</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,7 +4362,7 @@
         <v>46287</v>
       </c>
       <c r="C36" t="n">
-        <v>352.1000061</v>
+        <v>351.16000366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,16 +4422,16 @@
         <v>11.11552580886888</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.314388028908943</v>
+        <v>3.572509896535114</v>
       </c>
       <c r="Z36" t="n">
         <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>33.33333333333334</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.611540673019196</v>
+        <v>9.636819790475995</v>
       </c>
       <c r="AC36" t="n">
         <v>3</v>
@@ -4479,7 +4471,7 @@
         <v>46287</v>
       </c>
       <c r="C37" t="n">
-        <v>949.08001709</v>
+        <v>949.48999023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4507,22 +4499,22 @@
         <v>13.30675651903024</v>
       </c>
       <c r="K37" t="n">
-        <v>2.937095129067235</v>
+        <v>2.98156076247289</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>55.26315789473684</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N37" t="n">
-        <v>10.53629816537831</v>
+        <v>10.79622705585686</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>6.861379624203479</v>
+        <v>6.815238752998853</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4588,7 +4580,7 @@
         <v>46287</v>
       </c>
       <c r="C38" t="n">
-        <v>33.27000046</v>
+        <v>32.84999847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,22 +4608,22 @@
         <v>14.06988793284954</v>
       </c>
       <c r="K38" t="n">
-        <v>1.72756030694281</v>
+        <v>0.4433469863530215</v>
       </c>
       <c r="L38" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M38" t="n">
-        <v>50.9433962264151</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="N38" t="n">
-        <v>14.9493074826842</v>
+        <v>14.5384872035971</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>6.165919711562284</v>
+        <v>7.523298695605685</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4658,16 +4650,16 @@
         <v>16.46267138606403</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.58539342506598</v>
+        <v>13.68891937063007</v>
       </c>
       <c r="Z38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>18.18181818181818</v>
+        <v>40</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.585608626655416</v>
+        <v>7.415092393240514</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
@@ -4707,7 +4699,7 @@
         <v>46287</v>
       </c>
       <c r="C39" t="n">
-        <v>301.93499756</v>
+        <v>305.3500061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4735,22 +4727,22 @@
         <v>17.57170813546579</v>
       </c>
       <c r="K39" t="n">
-        <v>2.215708922237924</v>
+        <v>3.371810472944148</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
       </c>
       <c r="M39" t="n">
-        <v>50</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N39" t="n">
-        <v>6.32375530636368</v>
+        <v>6.80547840454862</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>7.615552599340769</v>
+        <v>6.411989397042328</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4816,7 +4808,7 @@
         <v>46287</v>
       </c>
       <c r="C40" t="n">
-        <v>211.27000427</v>
+        <v>211.8500061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4833,7 +4825,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4844,22 +4840,22 @@
         <v>19.53760153045933</v>
       </c>
       <c r="K40" t="n">
-        <v>7.25454810121291</v>
+        <v>7.548995173287687</v>
       </c>
       <c r="L40" t="n">
         <v>9</v>
       </c>
       <c r="M40" t="n">
-        <v>55.55555555555556</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N40" t="n">
-        <v>9.073791769367094</v>
+        <v>10.13810346320369</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6950305716487026</v>
+        <v>0.4193482477317767</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4925,7 +4921,7 @@
         <v>46287</v>
       </c>
       <c r="C41" t="n">
-        <v>231.5</v>
+        <v>231.38000488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4985,7 +4981,7 @@
         <v>10.73879246924641</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.069258489925456</v>
+        <v>8.116909636185454</v>
       </c>
       <c r="Z41" t="n">
         <v>6</v>
@@ -5034,11 +5030,11 @@
         <v>46287</v>
       </c>
       <c r="C42" t="n">
-        <v>121.16000366</v>
+        <v>123.86000061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5048,7 +5044,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5094,22 +5090,22 @@
         <v>46.49988754245867</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.862181996176283</v>
+        <v>0.6975088002595276</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>33.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.804571570745455</v>
+        <v>16.93665027209175</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.311640004197479</v>
       </c>
       <c r="AE42" t="n">
         <v>48</v>
@@ -5143,7 +5139,7 @@
         <v>46287</v>
       </c>
       <c r="C43" t="n">
-        <v>402.39001465</v>
+        <v>402.08999634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5171,7 +5167,7 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>16.55033009413469</v>
+        <v>16.46343123533671</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5209,7 +5205,7 @@
         <v>17.00796559594495</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.391114826652561</v>
+        <v>0.4653822992604084</v>
       </c>
       <c r="Z43" t="n">
         <v>19</v>
@@ -5224,7 +5220,7 @@
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>7.638761502154989</v>
+        <v>7.569846426087801</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5258,7 +5254,7 @@
         <v>46287</v>
       </c>
       <c r="C44" t="n">
-        <v>268.20001221</v>
+        <v>269.19000244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5318,22 +5314,22 @@
         <v>10.11126434424055</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.578928656499237</v>
+        <v>4.226706717403161</v>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.11111111111111</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="AB44" t="n">
-        <v>6.300018693230369</v>
+        <v>5.290252104904014</v>
       </c>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.489263664191254</v>
+        <v>1.851552997519268</v>
       </c>
       <c r="AE44" t="n">
         <v>14</v>
@@ -5367,7 +5363,7 @@
         <v>46287</v>
       </c>
       <c r="C45" t="n">
-        <v>340.07998657</v>
+        <v>340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,7 +5462,7 @@
         <v>46287</v>
       </c>
       <c r="C46" t="n">
-        <v>184.92999268</v>
+        <v>188.32000732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5494,16 +5490,16 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>11.47748107783027</v>
+        <v>13.52101272679376</v>
       </c>
       <c r="L46" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M46" t="n">
-        <v>53.84615384615385</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N46" t="n">
-        <v>9.468877562053361</v>
+        <v>8.672056058212824</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5533,25 +5529,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X46" t="n">
-        <v>12.08632414475048</v>
+        <v>13.68979853728842</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.5431912158471164</v>
+        <v>0.1484617025152901</v>
       </c>
       <c r="Z46" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA46" t="n">
-        <v>45.09803921568628</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.41154959563775</v>
+        <v>12.20932868619317</v>
       </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.497534734234323</v>
+        <v>7.863212156124078</v>
       </c>
       <c r="AE46" t="n">
         <v>43</v>
@@ -5585,7 +5581,7 @@
         <v>46287</v>
       </c>
       <c r="C47" t="n">
-        <v>31.54500008</v>
+        <v>31.27000046</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5680,7 @@
         <v>46287</v>
       </c>
       <c r="C48" t="n">
-        <v>88.30500031</v>
+        <v>88.61000061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5783,7 +5779,7 @@
         <v>46287</v>
       </c>
       <c r="C49" t="n">
-        <v>463.21499634</v>
+        <v>464.91000366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5882,7 +5878,7 @@
         <v>46287</v>
       </c>
       <c r="C50" t="n">
-        <v>1168.19506836</v>
+        <v>1170.14001465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,7 +5906,7 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>4.931781240615307</v>
+        <v>5.106483808837536</v>
       </c>
       <c r="L50" t="n">
         <v>25</v>
@@ -5919,7 +5915,7 @@
         <v>56</v>
       </c>
       <c r="N50" t="n">
-        <v>9.309194714168672</v>
+        <v>10.05458656298896</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5991,7 +5987,7 @@
         <v>46287</v>
       </c>
       <c r="C51" t="n">
-        <v>521.42498779</v>
+        <v>522.34002686</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6019,7 +6015,7 @@
         <v>15.85507589392084</v>
       </c>
       <c r="K51" t="n">
-        <v>1.130137253474839</v>
+        <v>1.307608661459314</v>
       </c>
       <c r="L51" t="n">
         <v>19</v>
@@ -6034,7 +6030,7 @@
         <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>0.8601419617823014</v>
+        <v>0.6834544292269928</v>
       </c>
       <c r="Q51" t="n">
         <v>16</v>
@@ -6100,7 +6096,7 @@
         <v>46287</v>
       </c>
       <c r="C52" t="n">
-        <v>194.88499451</v>
+        <v>196.08000183</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6128,16 +6124,16 @@
         <v>16.63935213539153</v>
       </c>
       <c r="K52" t="n">
-        <v>3.541065373923602</v>
+        <v>4.175964594120285</v>
       </c>
       <c r="L52" t="n">
         <v>21</v>
       </c>
       <c r="M52" t="n">
-        <v>38.09523809523809</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N52" t="n">
-        <v>8.969975430330191</v>
+        <v>9.802110805836252</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -6209,7 +6205,7 @@
         <v>46287</v>
       </c>
       <c r="C53" t="n">
-        <v>305.42999268</v>
+        <v>310.95999146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,10 +6233,10 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>15.09590319051892</v>
+        <v>17.17978564961131</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6272,25 +6268,25 @@
         <v>68.75</v>
       </c>
       <c r="X53" t="n">
-        <v>15.45767052957543</v>
+        <v>17.31167927226511</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.3133333085599044</v>
+        <v>0.1124300866477967</v>
       </c>
       <c r="Z53" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AA53" t="n">
-        <v>39.58333333333334</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="AB53" t="n">
-        <v>13.25185352009791</v>
+        <v>11.1254549960324</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
       <c r="AD53" t="n">
-        <v>9.717113645120879</v>
+        <v>9.898699029247792</v>
       </c>
       <c r="AE53" t="n">
         <v>35</v>
@@ -6324,7 +6320,7 @@
         <v>46287</v>
       </c>
       <c r="C54" t="n">
-        <v>558.59997559</v>
+        <v>555.89001465</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6423,7 +6419,7 @@
         <v>46287</v>
       </c>
       <c r="C55" t="n">
-        <v>251.16000366</v>
+        <v>250.3500061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6451,7 +6447,7 @@
         <v>11.44160340853909</v>
       </c>
       <c r="K55" t="n">
-        <v>1.882199947115892</v>
+        <v>1.553627196032825</v>
       </c>
       <c r="L55" t="n">
         <v>16</v>
@@ -6466,7 +6462,7 @@
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>1.097149505472328</v>
+        <v>1.424245341010999</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6532,7 +6528,7 @@
         <v>46287</v>
       </c>
       <c r="C56" t="n">
-        <v>91.59999847</v>
+        <v>90.76999664</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6627,7 @@
         <v>46287</v>
       </c>
       <c r="C57" t="n">
-        <v>749.31750488</v>
+        <v>736.5949707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,22 +6687,22 @@
         <v>40.94775289945536</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.050155749587944</v>
+        <v>2.730208287241054</v>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
-        <v>44.44444444444444</v>
+        <v>37.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>10.93029431764743</v>
+        <v>6.26800817540273</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.002377000094615</v>
+        <v>3.36156956356477</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6740,7 +6736,7 @@
         <v>46287</v>
       </c>
       <c r="C58" t="n">
-        <v>49.72999954</v>
+        <v>51.04000092</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6759,7 +6755,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6772,22 +6768,22 @@
         <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>5.22640987685925</v>
+        <v>7.99831302236913</v>
       </c>
       <c r="L58" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M58" t="n">
-        <v>81.81818181818181</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>15.636887868917</v>
+        <v>13.46314839236823</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.635830801779271</v>
+        <v>0.001562040724212288</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6853,7 +6849,7 @@
         <v>46287</v>
       </c>
       <c r="C59" t="n">
-        <v>152.00999451</v>
+        <v>150.91000366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6913,22 +6909,22 @@
         <v>21.72833272418202</v>
       </c>
       <c r="Y59" t="n">
-        <v>3.128985290122632</v>
+        <v>3.829973604440817</v>
       </c>
       <c r="Z59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="n">
-        <v>27.27272727272727</v>
+        <v>20</v>
       </c>
       <c r="AB59" t="n">
-        <v>7.568269764282801</v>
+        <v>6.277605227315403</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>7.092952138940245</v>
+        <v>6.415747844532249</v>
       </c>
       <c r="AE59" t="n">
         <v>19</v>
@@ -6962,7 +6958,7 @@
         <v>46287</v>
       </c>
       <c r="C60" t="n">
-        <v>262.26000977</v>
+        <v>262.35998535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7019,25 +7015,25 @@
         <v>69.47368421052632</v>
       </c>
       <c r="X60" t="n">
-        <v>31.89611792768943</v>
+        <v>32.58897740521489</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.8880902876328145</v>
+        <v>1.368426560150382</v>
       </c>
       <c r="Z60" t="n">
         <v>23</v>
       </c>
       <c r="AA60" t="n">
-        <v>39.1304347826087</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB60" t="n">
-        <v>11.4876316801165</v>
+        <v>11.79745384878262</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.148754397226694</v>
+        <v>3.681958335648305</v>
       </c>
       <c r="AE60" t="n">
         <v>53</v>
@@ -7071,7 +7067,7 @@
         <v>46287</v>
       </c>
       <c r="C61" t="n">
-        <v>200.41000366</v>
+        <v>200.17999268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7099,7 +7095,7 @@
         <v>10.7162131936937</v>
       </c>
       <c r="K61" t="n">
-        <v>1.109932332134389</v>
+        <v>0.9938882515060365</v>
       </c>
       <c r="L61" t="n">
         <v>39</v>
@@ -7108,13 +7104,13 @@
         <v>64.1025641025641</v>
       </c>
       <c r="N61" t="n">
-        <v>10.28712249536336</v>
+        <v>9.608809794895119</v>
       </c>
       <c r="O61" t="n">
         <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>1.869319486494136</v>
+        <v>1.986369455840853</v>
       </c>
       <c r="Q61" t="n">
         <v>32</v>
@@ -7180,7 +7176,7 @@
         <v>46287</v>
       </c>
       <c r="C62" t="n">
-        <v>495.51000977</v>
+        <v>498</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7279,7 +7275,7 @@
         <v>46287</v>
       </c>
       <c r="C63" t="n">
-        <v>1078.07995605</v>
+        <v>1096.16003418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7336,25 +7332,25 @@
         <v>66.26506024096386</v>
       </c>
       <c r="X63" t="n">
-        <v>28.22334378268323</v>
+        <v>29.9104930429817</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.4542976869806092</v>
+        <v>0.09933614217362274</v>
       </c>
       <c r="Z63" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA63" t="n">
-        <v>51.85185185185185</v>
+        <v>50</v>
       </c>
       <c r="AB63" t="n">
-        <v>13.94670307957604</v>
+        <v>13.0475416644662</v>
       </c>
       <c r="AC63" t="n">
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.56188386904942</v>
+        <v>3.904542479695239</v>
       </c>
       <c r="AE63" t="n">
         <v>54</v>
@@ -7388,7 +7384,7 @@
         <v>46287</v>
       </c>
       <c r="C64" t="n">
-        <v>79.71499634</v>
+        <v>79.26000214</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7487,11 +7483,11 @@
         <v>46287</v>
       </c>
       <c r="C65" t="n">
-        <v>124.42849731</v>
+        <v>127.26000214</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7501,7 +7497,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7515,22 +7511,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>3.690414424999999</v>
+        <v>6.050001783333325</v>
       </c>
       <c r="L65" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="M65" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N65" t="n">
-        <v>12.31882085729384</v>
+        <v>12.31419423330883</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.085023008142931</v>
+        <v>3.724656435873319</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7557,22 +7553,22 @@
         <v>19.42972700127354</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.028306984033861</v>
+        <v>5.935391786728362</v>
       </c>
       <c r="Z65" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AA65" t="n">
-        <v>20</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="AB65" t="n">
-        <v>11.63888788218732</v>
+        <v>12.78863992159546</v>
       </c>
       <c r="AC65" t="n">
         <v>6</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>0.06868493315270729</v>
       </c>
       <c r="AE65" t="n">
         <v>30</v>
@@ -7606,7 +7602,7 @@
         <v>46287</v>
       </c>
       <c r="C66" t="n">
-        <v>72.07499695</v>
+        <v>72.16000366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7634,22 +7630,22 @@
         <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>2.802733308947825</v>
+        <v>2.923980933053372</v>
       </c>
       <c r="L66" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M66" t="n">
-        <v>71.05263157894737</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N66" t="n">
-        <v>12.71496556991628</v>
+        <v>13.18130511333543</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>7.001046041667602</v>
+        <v>6.874995509111925</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7715,7 +7711,7 @@
         <v>46287</v>
       </c>
       <c r="C67" t="n">
-        <v>36.01499939</v>
+        <v>36.09999847</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,7 +7739,7 @@
         <v>14.88081023728842</v>
       </c>
       <c r="K67" t="n">
-        <v>1.881190802778554</v>
+        <v>2.121640827329863</v>
       </c>
       <c r="L67" t="n">
         <v>29</v>
@@ -7752,13 +7748,13 @@
         <v>48.27586206896552</v>
       </c>
       <c r="N67" t="n">
-        <v>11.75877558440893</v>
+        <v>11.70357981730552</v>
       </c>
       <c r="O67" t="n">
         <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>7.968899002111041</v>
+        <v>7.714681343586216</v>
       </c>
       <c r="Q67" t="n">
         <v>33</v>
@@ -7824,7 +7820,7 @@
         <v>46287</v>
       </c>
       <c r="C68" t="n">
-        <v>136.16000366</v>
+        <v>137</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7852,22 +7848,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>4.425189276013231</v>
+        <v>5.069407654669345</v>
       </c>
       <c r="L68" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M68" t="n">
-        <v>60.78431372549019</v>
+        <v>62.5</v>
       </c>
       <c r="N68" t="n">
-        <v>12.73973496534695</v>
+        <v>13.04632496509233</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>5.33856894360194</v>
+        <v>4.692700240146008</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7894,16 +7890,16 @@
         <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>8.983958483942867</v>
+        <v>8.422463627158905</v>
       </c>
       <c r="Z68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA68" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB68" t="n">
-        <v>11.41220375899009</v>
+        <v>11.5215949254118</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7943,7 +7939,7 @@
         <v>46287</v>
       </c>
       <c r="C69" t="n">
-        <v>228.72000122</v>
+        <v>228.86999512</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7971,13 +7967,13 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>9.472076405186414</v>
+        <v>9.543867868956646</v>
       </c>
       <c r="L69" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M69" t="n">
-        <v>62.85714285714285</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N69" t="n">
         <v>10.42466721111809</v>
@@ -8013,13 +8009,13 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.572837549518148</v>
+        <v>2.508945104677585</v>
       </c>
       <c r="Z69" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA69" t="n">
-        <v>48.14814814814815</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="AB69" t="n">
         <v>12.75482378585914</v>
@@ -8028,7 +8024,7 @@
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>3.51766628964868</v>
+        <v>3.580897651657189</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8062,7 +8058,7 @@
         <v>46287</v>
       </c>
       <c r="C70" t="n">
-        <v>234.52000427</v>
+        <v>237.57000732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8076,7 +8072,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -8090,22 +8086,22 @@
         <v>10.65198616240091</v>
       </c>
       <c r="K70" t="n">
-        <v>8.243330706311314</v>
+        <v>9.651067712900829</v>
       </c>
       <c r="L70" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>42.10526315789474</v>
+        <v>40</v>
       </c>
       <c r="N70" t="n">
-        <v>9.960987323754711</v>
+        <v>8.1132552331543</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>1.622889172225239</v>
+        <v>0.31822060138329</v>
       </c>
       <c r="Q70" t="n">
         <v>32</v>
@@ -8128,17 +8124,27 @@
       <c r="W70" t="n">
         <v>61.70212765957447</v>
       </c>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
+      <c r="X70" t="n">
+        <v>10.28339259836972</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.573363650292924</v>
+      </c>
       <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>12.52204960322272</v>
+      </c>
       <c r="AC70" t="n">
         <v>2</v>
       </c>
-      <c r="AD70" t="inlineStr"/>
+      <c r="AD70" t="n">
+        <v>1.434863334498471</v>
+      </c>
       <c r="AE70" t="n">
         <v>35</v>
       </c>
@@ -8171,7 +8177,7 @@
         <v>46287</v>
       </c>
       <c r="C71" t="n">
-        <v>149.05000305</v>
+        <v>149.19999695</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8203,22 +8209,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K71" t="n">
-        <v>7.230218021582724</v>
+        <v>7.338127302158282</v>
       </c>
       <c r="L71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M71" t="n">
-        <v>53.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N71" t="n">
-        <v>10.88869311955713</v>
+        <v>10.66431037743974</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>0.7178778450887213</v>
+        <v>0.6166240407553758</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8245,7 +8251,7 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y71" t="n">
-        <v>12.68306636604192</v>
+        <v>12.59519647577826</v>
       </c>
       <c r="Z71" t="n">
         <v>4</v>
@@ -8294,7 +8300,7 @@
         <v>46287</v>
       </c>
       <c r="C72" t="n">
-        <v>57.13000107</v>
+        <v>56.31000137</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8322,22 +8328,22 @@
         <v>11.90214849498216</v>
       </c>
       <c r="K72" t="n">
-        <v>1.690994579490779</v>
+        <v>0.2314009599192923</v>
       </c>
       <c r="L72" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M72" t="n">
-        <v>52.38095238095238</v>
+        <v>50.84745762711864</v>
       </c>
       <c r="N72" t="n">
-        <v>19.01078477972821</v>
+        <v>17.66998127897994</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>1.287238290786896</v>
+        <v>2.762207265952332</v>
       </c>
       <c r="Q72" t="n">
         <v>31</v>
@@ -8403,7 +8409,7 @@
         <v>46287</v>
       </c>
       <c r="C73" t="n">
-        <v>131.13000488</v>
+        <v>131.19000244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8431,7 +8437,7 @@
         <v>12.28237922496582</v>
       </c>
       <c r="K73" t="n">
-        <v>2.461323204640986</v>
+        <v>2.508203622225635</v>
       </c>
       <c r="L73" t="n">
         <v>20</v>
@@ -8512,7 +8518,7 @@
         <v>46287</v>
       </c>
       <c r="C74" t="n">
-        <v>27.80999947</v>
+        <v>27.93000031</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,22 +8578,22 @@
         <v>11.57371556196134</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.792877966773279</v>
+        <v>4.382056865165773</v>
       </c>
       <c r="Z74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA74" t="n">
-        <v>25</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="AB74" t="n">
-        <v>10.03441324978687</v>
+        <v>10.45947430997677</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.469256839219927</v>
+        <v>5.875406801955741</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8621,7 +8627,7 @@
         <v>46287</v>
       </c>
       <c r="C75" t="n">
-        <v>183.6499939</v>
+        <v>184.99000549</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8638,7 +8644,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8649,16 +8659,16 @@
         <v>12.64532180659963</v>
       </c>
       <c r="K75" t="n">
-        <v>11.60740838406202</v>
+        <v>12.42175755766417</v>
       </c>
       <c r="L75" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="N75" t="n">
-        <v>16.38045520777747</v>
+        <v>16.26850272100832</v>
       </c>
       <c r="O75" t="n">
         <v>10</v>
@@ -8691,22 +8701,22 @@
         <v>12.75599504767073</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.018647977983878</v>
+        <v>0.2964254715372316</v>
       </c>
       <c r="Z75" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AA75" t="n">
-        <v>49.18032786885246</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB75" t="n">
-        <v>14.64926999144619</v>
+        <v>15.79253798589024</v>
       </c>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.001742733899425</v>
+        <v>2.711612438419619</v>
       </c>
       <c r="AE75" t="n">
         <v>19</v>
@@ -8740,7 +8750,7 @@
         <v>46287</v>
       </c>
       <c r="C76" t="n">
-        <v>188.53500366</v>
+        <v>190.22999573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8839,7 +8849,7 @@
         <v>46287</v>
       </c>
       <c r="C77" t="n">
-        <v>196.44000244</v>
+        <v>198.27000427</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8896,25 +8906,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>26.35217262704843</v>
+        <v>27.47231603601605</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.4863178772367749</v>
+        <v>0.4418727878253814</v>
       </c>
       <c r="Z77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA77" t="n">
-        <v>28.57142857142857</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB77" t="n">
-        <v>8.822785207291803</v>
+        <v>8.513637572162638</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>9.560174962701961</v>
+        <v>9.600549427576798</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8948,16 +8958,16 @@
         <v>46287</v>
       </c>
       <c r="C78" t="n">
-        <v>190.46000671</v>
+        <v>190.99000549</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8965,11 +8975,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>5</v>
       </c>
@@ -8980,22 +8986,22 @@
         <v>17.38881221393466</v>
       </c>
       <c r="K78" t="n">
-        <v>1.82849312590454</v>
+        <v>2.111854331536245</v>
       </c>
       <c r="L78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M78" t="n">
-        <v>76.47058823529412</v>
+        <v>68.75</v>
       </c>
       <c r="N78" t="n">
-        <v>14.09576159547897</v>
+        <v>15.54385872887818</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1684271944232707</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>12</v>
@@ -9061,7 +9067,7 @@
         <v>46287</v>
       </c>
       <c r="C79" t="n">
-        <v>101.02500153</v>
+        <v>100.34999847</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9089,22 +9095,22 @@
         <v>13.29782231051553</v>
       </c>
       <c r="K79" t="n">
-        <v>1.737158536774075</v>
+        <v>1.057397167924856</v>
       </c>
       <c r="L79" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M79" t="n">
-        <v>55.55555555555556</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N79" t="n">
-        <v>10.59077997077294</v>
+        <v>10.70284978590574</v>
       </c>
       <c r="O79" t="n">
         <v>6</v>
       </c>
       <c r="P79" t="n">
-        <v>4.190053589598808</v>
+        <v>4.890886734260658</v>
       </c>
       <c r="Q79" t="n">
         <v>27</v>
@@ -9170,7 +9176,7 @@
         <v>46287</v>
       </c>
       <c r="C80" t="n">
-        <v>52.27999878</v>
+        <v>52.11999893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9198,22 +9204,22 @@
         <v>16.52331791600153</v>
       </c>
       <c r="K80" t="n">
-        <v>3.586283963240211</v>
+        <v>3.269264256221471</v>
       </c>
       <c r="L80" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M80" t="n">
-        <v>57.14285714285715</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N80" t="n">
-        <v>16.04957400277359</v>
+        <v>14.46703039554393</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>0.3993926810875958</v>
+        <v>0.7076023529764885</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9279,7 +9285,7 @@
         <v>46287</v>
       </c>
       <c r="C81" t="n">
-        <v>40.59000015</v>
+        <v>41.54000092</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9296,11 +9302,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>5</v>
       </c>
@@ -9311,17 +9313,13 @@
         <v>19.42803345269662</v>
       </c>
       <c r="K81" t="n">
-        <v>19.06717504077218</v>
+        <v>21.85391826699654</v>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" t="n">
-        <v>100</v>
-      </c>
-      <c r="N81" t="n">
-        <v>13.44989647840349</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>6</v>
       </c>
@@ -9353,22 +9351,22 @@
         <v>36.83700278308666</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.065235557329883</v>
+        <v>1.81990173733716</v>
       </c>
       <c r="Z81" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA81" t="n">
-        <v>33.33333333333334</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="AB81" t="n">
-        <v>15.61237027176215</v>
+        <v>15.1991249268936</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.101500082403908</v>
+        <v>6.294654794629684</v>
       </c>
       <c r="AE81" t="n">
         <v>76</v>
@@ -9402,7 +9400,7 @@
         <v>46287</v>
       </c>
       <c r="C82" t="n">
-        <v>404.2749939</v>
+        <v>402.44000244</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9430,22 +9428,22 @@
         <v>11.8900081911483</v>
       </c>
       <c r="K82" t="n">
-        <v>0.859468464293256</v>
+        <v>0.401670514668151</v>
       </c>
       <c r="L82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M82" t="n">
-        <v>54.54545454545455</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N82" t="n">
-        <v>10.24481670081885</v>
+        <v>10.22920997752422</v>
       </c>
       <c r="O82" t="n">
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>9.062640994328387</v>
+        <v>9.559930065037703</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -9511,7 +9509,7 @@
         <v>46287</v>
       </c>
       <c r="C83" t="n">
-        <v>276.91500854</v>
+        <v>275.08999634</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9539,13 +9537,17 @@
         <v>23.66411973888177</v>
       </c>
       <c r="K83" t="n">
-        <v>3.713486344569272</v>
+        <v>3.029961176029983</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
-      </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N83" t="n">
+        <v>7.952586279424212</v>
+      </c>
       <c r="O83" t="n">
         <v>2</v>
       </c>
@@ -9616,7 +9618,7 @@
         <v>46287</v>
       </c>
       <c r="C84" t="n">
-        <v>25.16500092</v>
+        <v>25.10000038</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9676,16 +9678,16 @@
         <v>12.30192171221367</v>
       </c>
       <c r="Y84" t="n">
-        <v>6.554026623403331</v>
+        <v>6.795395131579185</v>
       </c>
       <c r="Z84" t="n">
         <v>9</v>
       </c>
       <c r="AA84" t="n">
-        <v>66.66666666666667</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB84" t="n">
-        <v>10.3555874022774</v>
+        <v>8.083997451240061</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9725,7 +9727,7 @@
         <v>46287</v>
       </c>
       <c r="C85" t="n">
-        <v>130.6000061</v>
+        <v>130.78999329</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9753,7 +9755,7 @@
         <v>22.77987498113207</v>
       </c>
       <c r="K85" t="n">
-        <v>6.369121516291965</v>
+        <v>6.523859414881161</v>
       </c>
       <c r="L85" t="n">
         <v>1</v>
@@ -9830,7 +9832,7 @@
         <v>46287</v>
       </c>
       <c r="C86" t="n">
-        <v>376.90499878</v>
+        <v>378.8999939</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9890,22 +9892,22 @@
         <v>18.66270892223245</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.857881887651502</v>
+        <v>1.338406032106054</v>
       </c>
       <c r="Z86" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA86" t="n">
-        <v>44.61538461538461</v>
+        <v>46.875</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.33758974622789</v>
+        <v>14.08544139687812</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.163739008608977</v>
+        <v>1.68413452597842</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9939,7 +9941,7 @@
         <v>46287</v>
       </c>
       <c r="C87" t="n">
-        <v>446.66500854</v>
+        <v>452</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9996,25 +9998,25 @@
         <v>55.26315789473684</v>
       </c>
       <c r="X87" t="n">
-        <v>10.65035245950179</v>
+        <v>11.78082480528946</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.3646861651569022</v>
+        <v>0.19431303447216</v>
       </c>
       <c r="Z87" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AA87" t="n">
-        <v>35.29411764705883</v>
+        <v>35.13513513513514</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.81374338316508</v>
+        <v>11.43142672574399</v>
       </c>
       <c r="AC87" t="n">
         <v>6</v>
       </c>
       <c r="AD87" t="n">
-        <v>5.655940266504588</v>
+        <v>5.816990135575228</v>
       </c>
       <c r="AE87" t="n">
         <v>36</v>
@@ -10048,11 +10050,11 @@
         <v>46287</v>
       </c>
       <c r="C88" t="n">
-        <v>269.26000977</v>
+        <v>271.41000366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10076,22 +10078,22 @@
         <v>14.3256649882924</v>
       </c>
       <c r="K88" t="n">
-        <v>8.515699219938689</v>
+        <v>9.382178020452869</v>
       </c>
       <c r="L88" t="n">
         <v>20</v>
       </c>
       <c r="M88" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N88" t="n">
-        <v>7.301238111646442</v>
+        <v>7.329832686730091</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>1.367821237600797</v>
+        <v>0.564828741508161</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10118,22 +10120,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.489034134554312</v>
+        <v>0.7024413728232926</v>
       </c>
       <c r="Z88" t="n">
         <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>26.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.90209910753714</v>
+        <v>10.01342480579197</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.548920156640611</v>
+        <v>3.320885903708615</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10167,7 +10169,7 @@
         <v>46287</v>
       </c>
       <c r="C89" t="n">
-        <v>70.33000183</v>
+        <v>69.88999939</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10195,22 +10197,22 @@
         <v>15.93516705034004</v>
       </c>
       <c r="K89" t="n">
-        <v>1.574240328839882</v>
+        <v>0.9387659591126418</v>
       </c>
       <c r="L89" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M89" t="n">
-        <v>64.1025641025641</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N89" t="n">
-        <v>14.20605006089529</v>
+        <v>13.73633787362494</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>2.388164226783163</v>
+        <v>3.032763489626356</v>
       </c>
       <c r="Q89" t="n">
         <v>28</v>
@@ -10276,7 +10278,7 @@
         <v>46287</v>
       </c>
       <c r="C90" t="n">
-        <v>374.23999023</v>
+        <v>372.95001221</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10375,16 +10377,16 @@
         <v>46287</v>
       </c>
       <c r="C91" t="n">
-        <v>271.625</v>
+        <v>274.41000366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10403,22 +10405,22 @@
         <v>14.60766672642613</v>
       </c>
       <c r="K91" t="n">
-        <v>1.254376391354439</v>
+        <v>2.292549640653796</v>
       </c>
       <c r="L91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M91" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N91" t="n">
-        <v>9.67454013150881</v>
+        <v>11.04549553119507</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0.7363865496180511</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>17</v>
@@ -10484,7 +10486,7 @@
         <v>46287</v>
       </c>
       <c r="C92" t="n">
-        <v>362.79998779</v>
+        <v>362.04000854</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10583,7 +10585,7 @@
         <v>46287</v>
       </c>
       <c r="C93" t="n">
-        <v>253.09010315</v>
+        <v>253.46000671</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10611,7 +10613,7 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>11.52291373439716</v>
+        <v>11.68590992547096</v>
       </c>
       <c r="L93" t="n">
         <v>8</v>
@@ -10653,22 +10655,22 @@
         <v>12.53635174236054</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.9005427955257939</v>
+        <v>0.7557040935862069</v>
       </c>
       <c r="Z93" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA93" t="n">
-        <v>44.23076923076923</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.25721401882834</v>
+        <v>15.00928929785776</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.127622786146067</v>
+        <v>3.268999872267853</v>
       </c>
       <c r="AE93" t="n">
         <v>31</v>
@@ -10702,21 +10704,21 @@
         <v>46287</v>
       </c>
       <c r="C94" t="n">
-        <v>47.06999969</v>
+        <v>46.45000076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10726,17 +10728,27 @@
       <c r="I94" t="n">
         <v>10</v>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>10.64427558504014</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.60623560032802</v>
+      </c>
       <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="M94" t="n">
+        <v>40.90909090909091</v>
+      </c>
+      <c r="N94" t="n">
+        <v>7.569977336443118</v>
+      </c>
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>1.385365818883133</v>
+      </c>
       <c r="Q94" t="n">
         <v>19</v>
       </c>
@@ -10758,27 +10770,17 @@
       <c r="W94" t="n">
         <v>35</v>
       </c>
-      <c r="X94" t="n">
-        <v>10.85603409950266</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>8.902648815402491</v>
-      </c>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>7.083717613832559</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>2</v>
       </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="n">
         <v>18</v>
       </c>
@@ -10811,7 +10813,7 @@
         <v>46287</v>
       </c>
       <c r="C95" t="n">
-        <v>30.79999924</v>
+        <v>30.82999992</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10871,13 +10873,13 @@
         <v>15.02976579706115</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.3881010339247148</v>
+        <v>0.2910742553917989</v>
       </c>
       <c r="Z95" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA95" t="n">
-        <v>48</v>
+        <v>48.97959183673469</v>
       </c>
       <c r="AB95" t="n">
         <v>12.63847080611493</v>
@@ -10886,7 +10888,7 @@
         <v>8</v>
       </c>
       <c r="AD95" t="n">
-        <v>7.6415559236228</v>
+        <v>7.731429946756863</v>
       </c>
       <c r="AE95" t="n">
         <v>51</v>
@@ -10920,7 +10922,7 @@
         <v>46287</v>
       </c>
       <c r="C96" t="n">
-        <v>83.62010193</v>
+        <v>83.15000153</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11019,7 +11021,7 @@
         <v>46287</v>
       </c>
       <c r="C97" t="n">
-        <v>109.19999695</v>
+        <v>110.12000275</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11047,16 +11049,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>6.901610684684645</v>
+        <v>7.802252668257981</v>
       </c>
       <c r="L97" t="n">
         <v>10</v>
       </c>
       <c r="M97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N97" t="n">
-        <v>7.786884223287527</v>
+        <v>5.520930121865053</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -11128,7 +11130,7 @@
         <v>46287</v>
       </c>
       <c r="C98" t="n">
-        <v>159.71000671</v>
+        <v>158.71000671</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11227,7 +11229,7 @@
         <v>46287</v>
       </c>
       <c r="C99" t="n">
-        <v>30595.95703125</v>
+        <v>30732.39648438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -440,7 +440,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C2" t="n">
-        <v>339.75</v>
+        <v>336.8500061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,22 +730,22 @@
         <v>14.89502875525965</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.618693577125219</v>
+        <v>2.458443947987232</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.42857142857143</v>
+        <v>25.92592592592593</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.58815897675221</v>
+        <v>13.63464783109587</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.486299740161872</v>
+        <v>5.681225803961754</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -754,10 +754,10 @@
         <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.79340213879687</v>
+        <v>17.00173547213021</v>
       </c>
       <c r="AH2" t="n">
-        <v>33.20659786120312</v>
+        <v>32.99826452786979</v>
       </c>
       <c r="AI2" t="n">
         <v>31.42742581957335</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3" t="n">
-        <v>265.20999146</v>
+        <v>264.09500122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C4" t="n">
-        <v>103.69000244</v>
+        <v>104.04000092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>3.34894901695828</v>
+        <v>3.697796294558287</v>
       </c>
       <c r="L4" t="n">
         <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>64.70588235294117</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N4" t="n">
-        <v>7.890725191224749</v>
+        <v>8.162860539846717</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.565145565831273</v>
+        <v>2.22010861147155</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -962,10 +962,10 @@
         <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.68872549019608</v>
+        <v>12.93872549019608</v>
       </c>
       <c r="AH4" t="n">
-        <v>27.31127450980392</v>
+        <v>27.06127450980392</v>
       </c>
       <c r="AI4" t="n">
         <v>21.88065323728171</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C5" t="n">
-        <v>183.72000122</v>
+        <v>184.80999756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.038406778589157</v>
+        <v>6.48687294613196</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.742587687421709</v>
+        <v>9.282538324923399</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C6" t="n">
-        <v>390.36999512</v>
+        <v>380.44750977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1124,22 +1124,22 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>12.175285954023</v>
+        <v>9.323997060344835</v>
       </c>
       <c r="L6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>23.52941176470588</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="N6" t="n">
-        <v>9.304681100542773</v>
+        <v>8.293871144373249</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6183481740811514</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1148,10 +1148,10 @@
         <v>41.1764705882353</v>
       </c>
       <c r="S6" t="n">
-        <v>35.82311601327829</v>
+        <v>35.896645425043</v>
       </c>
       <c r="T6" t="n">
-        <v>5.35335457495701</v>
+        <v>5.279825163192299</v>
       </c>
       <c r="U6" t="n">
         <v>26.36596836387115</v>
@@ -1166,22 +1166,22 @@
         <v>12.22557857183908</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04481386369854512</v>
+        <v>2.58549035649378</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.33333333333334</v>
+        <v>31.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.83396486958489</v>
+        <v>11.12079488636523</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.956959402694793</v>
+        <v>1.452052316110508</v>
       </c>
       <c r="AE6" t="n">
         <v>29</v>
@@ -1190,10 +1190,10 @@
         <v>31.03448275862069</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.34310103351686</v>
+        <v>15.42930793006858</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.69138172510383</v>
+        <v>15.60517482855211</v>
       </c>
       <c r="AI6" t="n">
         <v>17.27561674448322</v>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C7" t="n">
-        <v>269.64001465</v>
+        <v>266.55999756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C8" t="n">
-        <v>472.45999146</v>
+        <v>470.66500854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,13 +1342,17 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>14.81129990594057</v>
+        <v>14.37510567557341</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.71697227940768</v>
+      </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
@@ -1377,25 +1381,25 @@
         <v>65.71428571428571</v>
       </c>
       <c r="X8" t="n">
-        <v>14.81616480096733</v>
+        <v>15.40423868800416</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004237116816441233</v>
+        <v>0.8917636164240128</v>
       </c>
       <c r="Z8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA8" t="n">
-        <v>42.85714285714285</v>
+        <v>49.01960784313726</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.11302435876111</v>
+        <v>12.47723654808551</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.996186433279918</v>
+        <v>9.190191164662254</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -1426,10 +1430,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C9" t="n">
-        <v>623.77001953</v>
+        <v>612.29998779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1490,10 @@
         <v>69.56521739130434</v>
       </c>
       <c r="X9" t="n">
-        <v>41.77525982519865</v>
+        <v>41.81382074233824</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1200922270777505</v>
+        <v>1.983366942435738</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
@@ -1498,13 +1502,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.3701493681632</v>
+        <v>15.39615186886673</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.88697757540012</v>
+        <v>4.097909642749443</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1535,10 +1539,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C10" t="n">
-        <v>254.97999573</v>
+        <v>248.08000183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,25 +1567,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>12.38702974586333</v>
+        <v>10.66334722469461</v>
       </c>
       <c r="K10" t="n">
-        <v>4.371671120206333</v>
+        <v>1.547277418259529</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>43.75</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="N10" t="n">
-        <v>11.60730936984054</v>
+        <v>10.89344440638165</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.476354111083335</v>
+        <v>6.354402349127075</v>
       </c>
       <c r="Q10" t="n">
         <v>23</v>
@@ -1644,10 +1648,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C11" t="n">
-        <v>205.19000244</v>
+        <v>202.55000305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,16 +1679,16 @@
         <v>14.2728744929405</v>
       </c>
       <c r="K11" t="n">
-        <v>13.19578397227343</v>
+        <v>11.73939332417273</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>64.70588235294117</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N11" t="n">
-        <v>14.60517234197607</v>
+        <v>13.46029151457658</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1717,22 +1721,22 @@
         <v>14.88938578045085</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.474115120968467</v>
+        <v>2.741761072948579</v>
       </c>
       <c r="Z11" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
-        <v>42.85714285714285</v>
+        <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.68272682296382</v>
+        <v>10.69867830841566</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.623523236603157</v>
+        <v>5.406471456876128</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1741,10 +1745,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.88563774898843</v>
+        <v>16.5190487178349</v>
       </c>
       <c r="AH11" t="n">
-        <v>36.0555387215998</v>
+        <v>36.42212775275333</v>
       </c>
       <c r="AI11" t="n">
         <v>39.52330421009647</v>
@@ -1763,10 +1767,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C12" t="n">
-        <v>82.83999634</v>
+        <v>82.27999878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,16 +1798,16 @@
         <v>12.33653883634149</v>
       </c>
       <c r="K12" t="n">
-        <v>9.359731141914196</v>
+        <v>8.620460435643572</v>
       </c>
       <c r="L12" t="n">
         <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>35.29411764705883</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N12" t="n">
-        <v>9.968600531219094</v>
+        <v>8.368489809226187</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1836,22 +1840,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.941296111236324</v>
+        <v>2.604171984493153</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.83333333333333</v>
+        <v>13.63636363636364</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.54377757206133</v>
+        <v>10.83869362026744</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>8.218244346677627</v>
+        <v>7.593577842296617</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1882,10 +1886,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C13" t="n">
-        <v>333.20001221</v>
+        <v>330.29998779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,25 +1946,25 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>48.43430927883343</v>
+        <v>49.46326571942468</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.436261110988112</v>
+        <v>1.982284803822776</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.02555810861999</v>
+        <v>25.9014832189109</v>
       </c>
       <c r="AC13" t="n">
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.574972492615812</v>
+        <v>1.038297203868022</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -1978,10 +1982,10 @@
         <v>28.0091537409322</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
-        <v>47.36842105263158</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1991,19 +1995,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C14" t="n">
-        <v>1747.90002441</v>
+        <v>1725.32995605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2022,22 +2026,22 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>11.13018885546517</v>
+        <v>9.695200627134316</v>
       </c>
       <c r="L14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="N14" t="n">
-        <v>9.638543004103335</v>
+        <v>9.629461273126402</v>
       </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.2778602629131877</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2064,22 +2068,22 @@
         <v>11.24462686563246</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1028705955439135</v>
+        <v>1.392809955998697</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>40.90909090909091</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.86001943665113</v>
+        <v>14.10990500089401</v>
       </c>
       <c r="AC14" t="n">
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.903202063575053</v>
+        <v>4.672265827619116</v>
       </c>
       <c r="AE14" t="n">
         <v>35</v>
@@ -2110,10 +2114,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C15" t="n">
-        <v>364.54000854</v>
+        <v>354.66500854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,19 +2142,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>21.311746679127</v>
+        <v>21.26377548417351</v>
       </c>
       <c r="K15" t="n">
-        <v>8.555436463700495</v>
+        <v>5.614785478991324</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>61.53846153846154</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>14.92018308377776</v>
+        <v>12.97794550771273</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -2165,10 +2169,10 @@
         <v>56.81818181818182</v>
       </c>
       <c r="S15" t="n">
-        <v>44.30251814592512</v>
+        <v>44.35933632774331</v>
       </c>
       <c r="T15" t="n">
-        <v>12.5156636722567</v>
+        <v>12.45884549043851</v>
       </c>
       <c r="U15" t="n">
         <v>42.22414699362943</v>
@@ -2197,10 +2201,10 @@
         <v>40.54054054054054</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.80514236111959</v>
+        <v>12.89595898419428</v>
       </c>
       <c r="AH15" t="n">
-        <v>27.73539817942095</v>
+        <v>27.64458155634626</v>
       </c>
       <c r="AI15" t="n">
         <v>26.34651819201428</v>
@@ -2219,10 +2223,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C16" t="n">
-        <v>305.07000732</v>
+        <v>303.73999023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,25 +2251,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>12.11142859736806</v>
+        <v>12.84030384924218</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.3966357030896095</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M16" t="n">
-        <v>63.33333333333334</v>
+        <v>65.625</v>
       </c>
       <c r="N16" t="n">
-        <v>10.42456807465101</v>
+        <v>10.60661575543022</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.000000000000002</v>
+        <v>1.597029906113723</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2306,10 +2310,10 @@
         <v>31.81818181818182</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.553493417337811</v>
+        <v>7.667129780974175</v>
       </c>
       <c r="AH16" t="n">
-        <v>24.264688400844</v>
+        <v>24.15105203720764</v>
       </c>
       <c r="AI16" t="n">
         <v>16.36059318135624</v>
@@ -2328,10 +2332,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C17" t="n">
-        <v>197.72000122</v>
+        <v>201.41000366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,25 +2360,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>17.56568419419229</v>
+        <v>16.68016123470477</v>
       </c>
       <c r="K17" t="n">
-        <v>1.156243953962988</v>
+        <v>3.04409942992987</v>
       </c>
       <c r="L17" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>70.27027027027027</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N17" t="n">
-        <v>12.34001860995113</v>
+        <v>11.60093981164182</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.788390569584067</v>
+        <v>2.868578197512561</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2437,10 +2441,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C18" t="n">
-        <v>56.20000076</v>
+        <v>55.86500168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>14.05029013936877</v>
+        <v>14.55618927013956</v>
       </c>
       <c r="K18" t="n">
-        <v>0.240795742974953</v>
+        <v>0.2332485306848264</v>
       </c>
       <c r="L18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>40.74074074074074</v>
+        <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>11.58798642514625</v>
+        <v>12.08063464273946</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75257617078366</v>
+        <v>2.760313079614685</v>
       </c>
       <c r="Q18" t="n">
         <v>24</v>
@@ -2492,10 +2496,10 @@
         <v>50</v>
       </c>
       <c r="S18" t="n">
-        <v>38.92361111111111</v>
+        <v>39.02777777777778</v>
       </c>
       <c r="T18" t="n">
-        <v>11.07638888888889</v>
+        <v>10.97222222222222</v>
       </c>
       <c r="U18" t="n">
         <v>31.42742581957335</v>
@@ -2546,10 +2550,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C19" t="n">
-        <v>164.22000122</v>
+        <v>156.60510254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,25 +2578,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>26.10436640399428</v>
+        <v>28.50865071929265</v>
       </c>
       <c r="K19" t="n">
-        <v>2.260417811028881</v>
+        <v>0.7981829924241346</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N19" t="n">
-        <v>9.06462653177455</v>
+        <v>13.56441314681235</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>5.612711459459829</v>
+        <v>7.144788520758505</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2655,19 +2659,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C20" t="n">
-        <v>62.25</v>
+        <v>61.50999832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2682,17 +2686,27 @@
       <c r="I20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>10.46037350496544</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.08135249064178396</v>
+      </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42.10526315789474</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.347066422818166</v>
+      </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>9.910585001622231</v>
+      </c>
       <c r="Q20" t="n">
         <v>18</v>
       </c>
@@ -2754,10 +2768,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C21" t="n">
-        <v>132.47000122</v>
+        <v>132.6499939</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,10 +2867,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C22" t="n">
-        <v>808.01000977</v>
+        <v>809.54998779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,22 +2898,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>4.747273677974095</v>
+        <v>4.94691043639115</v>
       </c>
       <c r="L22" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M22" t="n">
-        <v>56.66666666666666</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N22" t="n">
-        <v>9.831739442004206</v>
+        <v>9.839575323488956</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>5.014666384706534</v>
+        <v>4.814900736569627</v>
       </c>
       <c r="Q22" t="n">
         <v>27</v>
@@ -2962,19 +2976,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C23" t="n">
-        <v>22.42000008</v>
+        <v>22.79000092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2990,25 +3004,25 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>18.28153539499147</v>
+        <v>19.43327406271869</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3131977575384637</v>
+        <v>3.42637202241689</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M23" t="n">
-        <v>57.14285714285715</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="N23" t="n">
-        <v>8.082740010852966</v>
+        <v>9.158437146117038</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.678413511406208</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>27</v>
@@ -3043,25 +3057,25 @@
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>45.45454545454545</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="AG23" t="n">
-        <v>20.3713172349536</v>
+        <v>20.24647735517301</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.08322821959186</v>
+        <v>27.57960960134874</v>
       </c>
       <c r="AI23" t="n">
-        <v>26.92029418081331</v>
+        <v>29.23715741664665</v>
       </c>
       <c r="AJ23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>46.42857142857143</v>
+        <v>48.27586206896552</v>
       </c>
     </row>
     <row r="24">
@@ -3071,14 +3085,14 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C24" t="n">
-        <v>125.26999664</v>
+        <v>128.41999817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3088,7 +3102,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -3102,22 +3116,22 @@
         <v>12.09391062009804</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6244525001363188</v>
+        <v>3.154724615028615</v>
       </c>
       <c r="L24" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>51.16279069767442</v>
+        <v>48.71794871794872</v>
       </c>
       <c r="N24" t="n">
-        <v>11.21798687594374</v>
+        <v>12.03677738110602</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.317364981291188</v>
+        <v>6.63593006575105</v>
       </c>
       <c r="Q24" t="n">
         <v>35</v>
@@ -3141,25 +3155,25 @@
         <v>55.10204081632653</v>
       </c>
       <c r="X24" t="n">
-        <v>15.54213549659837</v>
+        <v>14.09925232216449</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.54497884719317</v>
+        <v>9.320715580321215</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB24" t="n">
-        <v>23.26287165872696</v>
+        <v>15.11588024088992</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.7491065065477809</v>
       </c>
       <c r="AE24" t="n">
         <v>36</v>
@@ -3190,10 +3204,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C25" t="n">
-        <v>899.40997314</v>
+        <v>900.6799926800001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,10 +3303,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C26" t="n">
-        <v>233.27999878</v>
+        <v>239.66000366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,22 +3334,22 @@
         <v>14.3363003785587</v>
       </c>
       <c r="K26" t="n">
-        <v>1.509943543293435</v>
+        <v>4.286152127662901</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M26" t="n">
-        <v>65</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N26" t="n">
-        <v>12.3463803058366</v>
+        <v>10.37768672476844</v>
       </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>6.393517945302185</v>
+        <v>3.561209035491841</v>
       </c>
       <c r="Q26" t="n">
         <v>35</v>
@@ -3398,10 +3412,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C27" t="n">
-        <v>106.44000244</v>
+        <v>106.37999725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,22 +3443,22 @@
         <v>16.02249521790768</v>
       </c>
       <c r="K27" t="n">
-        <v>1.846713482423046</v>
+        <v>1.789297743478158</v>
       </c>
       <c r="L27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N27" t="n">
-        <v>11.99970971428389</v>
+        <v>11.37046284508763</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.041713381982539</v>
+        <v>6.101527758029723</v>
       </c>
       <c r="Q27" t="n">
         <v>16</v>
@@ -3453,10 +3467,10 @@
         <v>31.25</v>
       </c>
       <c r="S27" t="n">
-        <v>18.49808412308412</v>
+        <v>18.65433412308412</v>
       </c>
       <c r="T27" t="n">
-        <v>12.75191587691588</v>
+        <v>12.59566587691588</v>
       </c>
       <c r="U27" t="n">
         <v>14.16464385478204</v>
@@ -3507,10 +3521,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C28" t="n">
-        <v>87.09999847</v>
+        <v>85.95999908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,25 +3549,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>11.99999968527919</v>
+        <v>13.02538256852792</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4845387153875613</v>
+        <v>0.3385092986981642</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>55.55555555555556</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N28" t="n">
-        <v>10.4975408863062</v>
+        <v>9.878793241215995</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.508153696067449</v>
+        <v>1.655885375330568</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3616,10 +3630,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C29" t="n">
-        <v>202.41000366</v>
+        <v>205.8500061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,16 +3693,16 @@
         <v>12.40258001548387</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.057578843834356</v>
+        <v>5.478001995973747</v>
       </c>
       <c r="Z29" t="n">
         <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.398777077334111</v>
+        <v>7.689250324535682</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
@@ -3725,10 +3739,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C30" t="n">
-        <v>703.11999512</v>
+        <v>708.11999512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,25 +3799,25 @@
         <v>48.48484848484848</v>
       </c>
       <c r="X30" t="n">
-        <v>21.84840721774197</v>
+        <v>24.47652957953899</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.3910026833058078</v>
+        <v>1.800706651829898</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="n">
-        <v>47.82608695652174</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.29158783186034</v>
+        <v>13.44675914756516</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.627089360251735</v>
+        <v>3.257959644197095</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3834,10 +3848,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C31" t="n">
-        <v>221.08999634</v>
+        <v>220.96499634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,25 +3908,25 @@
         <v>44.44444444444444</v>
       </c>
       <c r="X31" t="n">
-        <v>11.71831948309332</v>
+        <v>12.15781921491597</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5979686363379422</v>
+        <v>1.043463511988807</v>
       </c>
       <c r="Z31" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AA31" t="n">
-        <v>48.27586206896552</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.86672979181411</v>
+        <v>11.821060333009</v>
       </c>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.416481163120532</v>
+        <v>1.977167509544187</v>
       </c>
       <c r="AE31" t="n">
         <v>26</v>
@@ -3943,10 +3957,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C32" t="n">
-        <v>103.81999969</v>
+        <v>104.06999969</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,10 +4056,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C33" t="n">
-        <v>13.10000038</v>
+        <v>13.03680038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,25 +4084,25 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>11.61202677950211</v>
+        <v>12.09016672741415</v>
       </c>
       <c r="K33" t="n">
-        <v>1.236482265790007</v>
+        <v>1.296041114418367</v>
       </c>
       <c r="L33" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>61.22448979591837</v>
+        <v>66</v>
       </c>
       <c r="N33" t="n">
-        <v>11.63053169281733</v>
+        <v>11.30618932481016</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.705337075723048</v>
+        <v>4.643773669563567</v>
       </c>
       <c r="Q33" t="n">
         <v>41</v>
@@ -4097,10 +4111,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="S33" t="n">
-        <v>44.2836928525867</v>
+        <v>44.28681980693316</v>
       </c>
       <c r="T33" t="n">
-        <v>11.81386812302306</v>
+        <v>11.81074116867659</v>
       </c>
       <c r="U33" t="n">
         <v>41.04052722210609</v>
@@ -4151,10 +4165,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C34" t="n">
-        <v>319.22000122</v>
+        <v>321.3500061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4182,22 +4196,22 @@
         <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>4.0482444342538</v>
+        <v>4.742509416251761</v>
       </c>
       <c r="L34" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M34" t="n">
-        <v>52</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N34" t="n">
-        <v>12.14395554637762</v>
+        <v>12.21257287371713</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.798003115990345</v>
+        <v>3.109998606967523</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4260,10 +4274,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C35" t="n">
-        <v>83.44999695</v>
+        <v>84.01999664</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4337,10 +4351,10 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AG35" t="n">
-        <v>28.81490034134547</v>
+        <v>28.81942522822331</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.24392318806629</v>
+        <v>18.23939830118846</v>
       </c>
       <c r="AI35" t="n">
         <v>31.45150447508847</v>
@@ -4359,10 +4373,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C36" t="n">
-        <v>351.16000366</v>
+        <v>338.32000732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,16 +4436,16 @@
         <v>11.11552580886888</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.572509896535114</v>
+        <v>7.098334612047575</v>
       </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AA36" t="n">
-        <v>38.88888888888889</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.636819790475995</v>
+        <v>10.62804754079361</v>
       </c>
       <c r="AC36" t="n">
         <v>3</v>
@@ -4446,10 +4460,10 @@
         <v>55</v>
       </c>
       <c r="AG36" t="n">
-        <v>21.35251064221119</v>
+        <v>21.57229086199141</v>
       </c>
       <c r="AH36" t="n">
-        <v>33.64748935778881</v>
+        <v>33.42770913800859</v>
       </c>
       <c r="AI36" t="n">
         <v>34.20853424503424</v>
@@ -4468,10 +4482,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C37" t="n">
-        <v>949.48999023</v>
+        <v>937.3150024399999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,22 +4513,22 @@
         <v>13.30675651903024</v>
       </c>
       <c r="K37" t="n">
-        <v>2.98156076247289</v>
+        <v>1.661063171366584</v>
       </c>
       <c r="L37" t="n">
         <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>53.84615384615385</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N37" t="n">
-        <v>10.79622705585686</v>
+        <v>11.24751725733877</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>6.815238752998853</v>
+        <v>8.202685048234027</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4577,10 +4591,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C38" t="n">
-        <v>32.84999847</v>
+        <v>33.11000061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4608,22 +4622,22 @@
         <v>14.06988793284954</v>
       </c>
       <c r="K38" t="n">
-        <v>0.4433469863530215</v>
+        <v>1.238338961438301</v>
       </c>
       <c r="L38" t="n">
         <v>51</v>
       </c>
       <c r="M38" t="n">
-        <v>54.90196078431372</v>
+        <v>49.01960784313726</v>
       </c>
       <c r="N38" t="n">
-        <v>14.5384872035971</v>
+        <v>15.21024155886768</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>7.523298695605685</v>
+        <v>6.678952961819351</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4632,10 +4646,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S38" t="n">
-        <v>32.49430562574008</v>
+        <v>32.02426801124558</v>
       </c>
       <c r="T38" t="n">
-        <v>29.20782203383438</v>
+        <v>29.67785964832888</v>
       </c>
       <c r="U38" t="n">
         <v>47.42656695641357</v>
@@ -4650,13 +4664,13 @@
         <v>16.46267138606403</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.68891937063007</v>
+        <v>13.00578187551442</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="n">
-        <v>40</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB38" t="n">
         <v>7.415092393240514</v>
@@ -4696,10 +4710,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C39" t="n">
-        <v>305.3500061</v>
+        <v>299.60501099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,25 +4738,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>17.57170813546579</v>
+        <v>16.5258375325574</v>
       </c>
       <c r="K39" t="n">
-        <v>3.371810472944148</v>
+        <v>1.42692580349888</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M39" t="n">
-        <v>41.66666666666666</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N39" t="n">
-        <v>6.80547840454862</v>
+        <v>8.505794505893762</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>6.411989397042328</v>
+        <v>8.452463809373768</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4805,10 +4819,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C40" t="n">
-        <v>211.8500061</v>
+        <v>211.97999573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,11 +4839,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5</v>
       </c>
@@ -4837,25 +4847,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>19.53760153045933</v>
+        <v>16.65750342876763</v>
       </c>
       <c r="K40" t="n">
-        <v>7.548995173287687</v>
+        <v>7.614986458097239</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>77.77777777777777</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N40" t="n">
-        <v>10.13810346320369</v>
+        <v>8.110141750390678</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4193482477317767</v>
+        <v>0.3577694469651505</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4918,10 +4928,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C41" t="n">
-        <v>231.38000488</v>
+        <v>234.86500549</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4981,16 +4991,16 @@
         <v>10.73879246924641</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.116909636185454</v>
+        <v>6.732984408365327</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB41" t="n">
-        <v>10.74405165423873</v>
+        <v>14.45595395278494</v>
       </c>
       <c r="AC41" t="n">
         <v>4</v>
@@ -5027,14 +5037,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C42" t="n">
-        <v>123.86000061</v>
+        <v>120.18990326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5044,7 +5054,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5090,7 +5100,7 @@
         <v>46.49988754245867</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.6975088002595276</v>
+        <v>3.639942257434414</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
@@ -5099,13 +5109,13 @@
         <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>16.93665027209175</v>
+        <v>15.57342437292846</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.311640004197479</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>48</v>
@@ -5114,10 +5124,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG42" t="n">
-        <v>18.32291925122808</v>
+        <v>18.21875258456141</v>
       </c>
       <c r="AH42" t="n">
-        <v>27.51041408210526</v>
+        <v>27.61458074877193</v>
       </c>
       <c r="AI42" t="n">
         <v>32.57524229286744</v>
@@ -5136,10 +5146,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C43" t="n">
-        <v>402.08999634</v>
+        <v>397.25</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5167,7 +5177,7 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>16.46343123533671</v>
+        <v>15.06154960173787</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5202,25 +5212,25 @@
         <v>50</v>
       </c>
       <c r="X43" t="n">
-        <v>17.00796559594495</v>
+        <v>17.14409918609703</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.4653822992604084</v>
+        <v>1.777767381224027</v>
       </c>
       <c r="Z43" t="n">
         <v>19</v>
       </c>
       <c r="AA43" t="n">
-        <v>52.63157894736842</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.415358728982806</v>
+        <v>9.755121205036906</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>7.569846426087801</v>
+        <v>6.334851543159226</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C44" t="n">
-        <v>269.19000244</v>
+        <v>267.23999023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,22 +5324,22 @@
         <v>10.11126434424055</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.226706717403161</v>
+        <v>4.920488394286215</v>
       </c>
       <c r="Z44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="n">
-        <v>9.090909090909092</v>
+        <v>12.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.290252104904014</v>
+        <v>5.966186301970189</v>
       </c>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.851552997519268</v>
+        <v>1.135377735416254</v>
       </c>
       <c r="AE44" t="n">
         <v>14</v>
@@ -5360,10 +5370,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C45" t="n">
-        <v>340</v>
+        <v>338.55999756</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5459,10 +5469,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C46" t="n">
-        <v>188.32000732</v>
+        <v>186.30000305</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5490,16 +5500,16 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>13.52101272679376</v>
+        <v>12.30333578579199</v>
       </c>
       <c r="L46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>8.672056058212824</v>
+        <v>7.815794300539654</v>
       </c>
       <c r="O46" t="n">
         <v>10</v>
@@ -5514,10 +5524,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S46" t="n">
-        <v>40.73127330419659</v>
+        <v>40.78104311880403</v>
       </c>
       <c r="T46" t="n">
-        <v>25.22617350431405</v>
+        <v>25.17640368970661</v>
       </c>
       <c r="U46" t="n">
         <v>51.67092456194193</v>
@@ -5532,22 +5542,22 @@
         <v>13.68979853728842</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1484617025152901</v>
+        <v>1.219513772857728</v>
       </c>
       <c r="Z46" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA46" t="n">
-        <v>46.15384615384615</v>
+        <v>42.5925925925926</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.20932868619317</v>
+        <v>12.389491273043</v>
       </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.863212156124078</v>
+        <v>6.864196043286097</v>
       </c>
       <c r="AE46" t="n">
         <v>43</v>
@@ -5578,10 +5588,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C47" t="n">
-        <v>31.27000046</v>
+        <v>31.76000023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5677,10 +5687,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C48" t="n">
-        <v>88.61000061</v>
+        <v>87.91500092</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,10 +5786,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C49" t="n">
-        <v>464.91000366</v>
+        <v>470.51998901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5875,10 +5885,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C50" t="n">
-        <v>1170.14001465</v>
+        <v>1148.30004883</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5906,16 +5916,16 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>5.106483808837536</v>
+        <v>3.144733945482914</v>
       </c>
       <c r="L50" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M50" t="n">
-        <v>56</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N50" t="n">
-        <v>10.05458656298896</v>
+        <v>10.19612979167614</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5962,10 +5972,10 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AG50" t="n">
-        <v>16.80771221532091</v>
+        <v>16.57608695652174</v>
       </c>
       <c r="AH50" t="n">
-        <v>22.47800207039337</v>
+        <v>22.70962732919254</v>
       </c>
       <c r="AI50" t="n">
         <v>23.56568654157959</v>
@@ -5984,19 +5994,19 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C51" t="n">
-        <v>522.34002686</v>
+        <v>528.98999023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6015,22 +6025,22 @@
         <v>15.85507589392084</v>
       </c>
       <c r="K51" t="n">
-        <v>1.307608661459314</v>
+        <v>2.597366007360691</v>
       </c>
       <c r="L51" t="n">
         <v>19</v>
       </c>
       <c r="M51" t="n">
-        <v>47.36842105263158</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N51" t="n">
-        <v>9.829818071831747</v>
+        <v>12.94308443033863</v>
       </c>
       <c r="O51" t="n">
         <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>0.6834544292269928</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>16</v>
@@ -6093,19 +6103,19 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C52" t="n">
-        <v>196.08000183</v>
+        <v>192.89590454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6124,22 +6134,22 @@
         <v>16.63935213539153</v>
       </c>
       <c r="K52" t="n">
-        <v>4.175964594120285</v>
+        <v>2.484275470030739</v>
       </c>
       <c r="L52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M52" t="n">
-        <v>33.33333333333334</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="N52" t="n">
-        <v>9.802110805836252</v>
+        <v>9.308901439506009</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.5032230823743156</v>
       </c>
       <c r="Q52" t="n">
         <v>24</v>
@@ -6202,10 +6212,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C53" t="n">
-        <v>310.95999146</v>
+        <v>305.51998901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6233,10 +6243,10 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>17.17978564961131</v>
+        <v>15.12981671942386</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6271,22 +6281,22 @@
         <v>17.31167927226511</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1124300866477967</v>
+        <v>1.859885193338207</v>
       </c>
       <c r="Z53" t="n">
         <v>41</v>
       </c>
       <c r="AA53" t="n">
-        <v>41.46341463414634</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="AB53" t="n">
-        <v>11.1254549960324</v>
+        <v>10.60505770631941</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
       <c r="AD53" t="n">
-        <v>9.898699029247792</v>
+        <v>8.294380766415443</v>
       </c>
       <c r="AE53" t="n">
         <v>35</v>
@@ -6317,10 +6327,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C54" t="n">
-        <v>555.89001465</v>
+        <v>559.77502441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6416,10 +6426,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C55" t="n">
-        <v>250.3500061</v>
+        <v>236.48500061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6444,25 +6454,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>11.44160340853909</v>
+        <v>15.92484916015828</v>
       </c>
       <c r="K55" t="n">
-        <v>1.553627196032825</v>
+        <v>1.044696372457321</v>
       </c>
       <c r="L55" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>31.25</v>
+        <v>70</v>
       </c>
       <c r="N55" t="n">
-        <v>7.552551706909805</v>
+        <v>10.73472617816773</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>1.424245341010999</v>
+        <v>1.93508783512526</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6525,10 +6535,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C56" t="n">
-        <v>90.76999664</v>
+        <v>89.55999756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6624,10 +6634,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C57" t="n">
-        <v>736.5949707</v>
+        <v>747.13000488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6684,25 +6694,25 @@
         <v>60.52631578947368</v>
       </c>
       <c r="X57" t="n">
-        <v>40.94775289945536</v>
+        <v>42.18177017922093</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.730208287241054</v>
+        <v>2.195316009179649</v>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="AB57" t="n">
-        <v>6.26800817540273</v>
+        <v>6.459860413815332</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.36156956356477</v>
+        <v>3.890083619285001</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C58" t="n">
-        <v>51.04000092</v>
+        <v>49.06000137</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6753,11 +6763,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6768,22 +6774,22 @@
         <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>7.99831302236913</v>
+        <v>3.808724320750256</v>
       </c>
       <c r="L58" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="N58" t="n">
-        <v>13.46314839236823</v>
+        <v>15.38447108883103</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>0.001562040724212288</v>
+        <v>4.037498492226388</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6846,10 +6852,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C59" t="n">
-        <v>150.91000366</v>
+        <v>147.43499756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6909,22 +6915,22 @@
         <v>21.72833272418202</v>
       </c>
       <c r="Y59" t="n">
-        <v>3.829973604440817</v>
+        <v>6.044481723562345</v>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA59" t="n">
-        <v>20</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB59" t="n">
-        <v>6.277605227315403</v>
+        <v>10.20473306791089</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>6.415747844532249</v>
+        <v>4.209990375232309</v>
       </c>
       <c r="AE59" t="n">
         <v>19</v>
@@ -6933,10 +6939,10 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AG59" t="n">
-        <v>11.20546581765418</v>
+        <v>11.45218697850277</v>
       </c>
       <c r="AH59" t="n">
-        <v>15.11032365603003</v>
+        <v>14.86360249518144</v>
       </c>
       <c r="AI59" t="n">
         <v>11.80641234678251</v>
@@ -6955,10 +6961,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C60" t="n">
-        <v>262.35998535</v>
+        <v>257.57998657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7018,22 +7024,22 @@
         <v>32.58897740521489</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.368426560150382</v>
+        <v>3.165418582706758</v>
       </c>
       <c r="Z60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA60" t="n">
-        <v>34.78260869565217</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB60" t="n">
-        <v>11.79745384878262</v>
+        <v>13.18378199417288</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.681958335648305</v>
+        <v>1.894551915691578</v>
       </c>
       <c r="AE60" t="n">
         <v>53</v>
@@ -7064,10 +7070,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C61" t="n">
-        <v>200.17999268</v>
+        <v>198.81500244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7092,25 +7098,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>10.7162131936937</v>
+        <v>10.83783673873874</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9938882515060365</v>
+        <v>0.4420531419692342</v>
       </c>
       <c r="L61" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M61" t="n">
-        <v>64.1025641025641</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N61" t="n">
-        <v>9.608809794895119</v>
+        <v>9.232286451878743</v>
       </c>
       <c r="O61" t="n">
         <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>1.986369455840853</v>
+        <v>2.546689138677061</v>
       </c>
       <c r="Q61" t="n">
         <v>32</v>
@@ -7119,10 +7125,10 @@
         <v>40.625</v>
       </c>
       <c r="S61" t="n">
-        <v>40.91660648890225</v>
+        <v>41.07285648890225</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.2916064889022465</v>
+        <v>-0.4478564889022465</v>
       </c>
       <c r="U61" t="n">
         <v>25.51963484266544</v>
@@ -7145,19 +7151,19 @@
       </c>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF61" t="n">
-        <v>46.42857142857143</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="AG61" t="n">
-        <v>14.20701175206925</v>
+        <v>14.73319737251626</v>
       </c>
       <c r="AH61" t="n">
-        <v>32.22155967650218</v>
+        <v>33.41495077563189</v>
       </c>
       <c r="AI61" t="n">
-        <v>29.53156998279538</v>
+        <v>30.74322697621846</v>
       </c>
       <c r="AJ61" t="n">
         <v>35</v>
@@ -7173,10 +7179,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C62" t="n">
-        <v>498</v>
+        <v>499.27999878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7272,10 +7278,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C63" t="n">
-        <v>1096.16003418</v>
+        <v>1069.80004883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7326,31 +7332,31 @@
         <v>56.85367346805482</v>
       </c>
       <c r="V63" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W63" t="n">
-        <v>66.26506024096386</v>
+        <v>65.85365853658537</v>
       </c>
       <c r="X63" t="n">
-        <v>29.9104930429817</v>
+        <v>24.54793165650138</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.09933614217362274</v>
+        <v>3.229292902939651</v>
       </c>
       <c r="Z63" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AA63" t="n">
-        <v>50</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="AB63" t="n">
-        <v>13.0475416644662</v>
+        <v>15.17606609794329</v>
       </c>
       <c r="AC63" t="n">
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.904542479695239</v>
+        <v>0.7964260262016465</v>
       </c>
       <c r="AE63" t="n">
         <v>54</v>
@@ -7381,19 +7387,19 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C64" t="n">
-        <v>79.26000214</v>
+        <v>77.74500275</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7408,17 +7414,27 @@
       <c r="I64" t="n">
         <v>10</v>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>11.54021807329905</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.4197940941387701</v>
+      </c>
       <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="M64" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10.52797185138249</v>
+      </c>
       <c r="O64" t="n">
         <v>10</v>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>9.540156890662654</v>
+      </c>
       <c r="Q64" t="n">
         <v>21</v>
       </c>
@@ -7480,24 +7496,24 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C65" t="n">
-        <v>127.26000214</v>
+        <v>123.30500031</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7511,22 +7527,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>6.050001783333325</v>
+        <v>2.75416692499999</v>
       </c>
       <c r="L65" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M65" t="n">
-        <v>50</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="N65" t="n">
-        <v>12.31419423330883</v>
+        <v>13.22595954855335</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>3.724656435873319</v>
+        <v>7.051619697611611</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7553,22 +7569,22 @@
         <v>19.42972700127354</v>
       </c>
       <c r="Y65" t="n">
-        <v>5.935391786728362</v>
+        <v>8.858743125450275</v>
       </c>
       <c r="Z65" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA65" t="n">
-        <v>13.33333333333333</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB65" t="n">
-        <v>12.78863992159546</v>
+        <v>8.855675284029097</v>
       </c>
       <c r="AC65" t="n">
         <v>6</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.06868493315270729</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>30</v>
@@ -7599,10 +7615,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C66" t="n">
-        <v>72.16000366</v>
+        <v>71.66000366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7630,22 +7646,22 @@
         <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>2.923980933053372</v>
+        <v>2.210815912871245</v>
       </c>
       <c r="L66" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M66" t="n">
-        <v>70.27027027027027</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N66" t="n">
-        <v>13.18130511333543</v>
+        <v>13.11142197008968</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>6.874995509111925</v>
+        <v>7.620704342844298</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7654,10 +7670,10 @@
         <v>59.375</v>
       </c>
       <c r="S66" t="n">
-        <v>41.24945663042527</v>
+        <v>41.02008470924301</v>
       </c>
       <c r="T66" t="n">
-        <v>18.12554336957473</v>
+        <v>18.35491529075699</v>
       </c>
       <c r="U66" t="n">
         <v>42.26002487538288</v>
@@ -7708,10 +7724,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C67" t="n">
-        <v>36.09999847</v>
+        <v>35.83499908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7736,25 +7752,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>14.88081023728842</v>
+        <v>14.75766233411265</v>
       </c>
       <c r="K67" t="n">
-        <v>2.121640827329863</v>
+        <v>1.371996127274522</v>
       </c>
       <c r="L67" t="n">
         <v>29</v>
       </c>
       <c r="M67" t="n">
-        <v>48.27586206896552</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="N67" t="n">
-        <v>11.70357981730552</v>
+        <v>10.36043911443285</v>
       </c>
       <c r="O67" t="n">
         <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>7.714681343586216</v>
+        <v>8.511230125026703</v>
       </c>
       <c r="Q67" t="n">
         <v>33</v>
@@ -7817,10 +7833,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C68" t="n">
-        <v>137</v>
+        <v>140.01499939</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7848,22 +7864,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>5.069407654669345</v>
+        <v>7.381701085227688</v>
       </c>
       <c r="L68" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M68" t="n">
-        <v>62.5</v>
+        <v>67.44186046511628</v>
       </c>
       <c r="N68" t="n">
-        <v>13.04632496509233</v>
+        <v>10.92845754480795</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>4.692700240146008</v>
+        <v>2.438310148108203</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7872,10 +7888,10 @@
         <v>48.93617021276596</v>
       </c>
       <c r="S68" t="n">
-        <v>53.11675643043801</v>
+        <v>53.81917476863463</v>
       </c>
       <c r="T68" t="n">
-        <v>-4.180586217672051</v>
+        <v>-4.883004555868673</v>
       </c>
       <c r="U68" t="n">
         <v>35.27555503368215</v>
@@ -7890,16 +7906,16 @@
         <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>8.422463627158905</v>
+        <v>6.407089785539776</v>
       </c>
       <c r="Z68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA68" t="n">
-        <v>54.54545454545455</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB68" t="n">
-        <v>11.5215949254118</v>
+        <v>10.42035820542849</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7936,10 +7952,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C69" t="n">
-        <v>228.86999512</v>
+        <v>224.47489929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7967,16 +7983,16 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>9.543867868956646</v>
+        <v>7.440246568049602</v>
       </c>
       <c r="L69" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M69" t="n">
-        <v>61.11111111111111</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N69" t="n">
-        <v>10.42466721111809</v>
+        <v>11.75501853230481</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -7991,10 +8007,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S69" t="n">
-        <v>68.77179183301969</v>
+        <v>68.60611577708606</v>
       </c>
       <c r="T69" t="n">
-        <v>-7.069664173445226</v>
+        <v>-6.903988117511595</v>
       </c>
       <c r="U69" t="n">
         <v>47.42656695641357</v>
@@ -8009,22 +8025,22 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.508945104677585</v>
+        <v>4.381110691993095</v>
       </c>
       <c r="Z69" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AA69" t="n">
-        <v>46.42857142857143</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="AB69" t="n">
-        <v>12.75482378585914</v>
+        <v>12.77735056160086</v>
       </c>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>3.580897651657189</v>
+        <v>1.693064330408767</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8055,10 +8071,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C70" t="n">
-        <v>237.57000732</v>
+        <v>233.41499329</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8072,7 +8088,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -8086,22 +8102,22 @@
         <v>10.65198616240091</v>
       </c>
       <c r="K70" t="n">
-        <v>9.651067712900829</v>
+        <v>7.733309954288226</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M70" t="n">
-        <v>40</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N70" t="n">
-        <v>8.1132552331543</v>
+        <v>10.32124274020965</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>0.31822060138329</v>
+        <v>2.103982553467953</v>
       </c>
       <c r="Q70" t="n">
         <v>32</v>
@@ -8110,10 +8126,10 @@
         <v>59.375</v>
       </c>
       <c r="S70" t="n">
-        <v>42.10037878787879</v>
+        <v>41.90320616883117</v>
       </c>
       <c r="T70" t="n">
-        <v>17.27462121212121</v>
+        <v>17.47179383116883</v>
       </c>
       <c r="U70" t="n">
         <v>42.26002487538288</v>
@@ -8128,22 +8144,22 @@
         <v>10.28339259836972</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.573363650292924</v>
+        <v>2.312299779685223</v>
       </c>
       <c r="Z70" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA70" t="n">
-        <v>33.33333333333334</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="AB70" t="n">
-        <v>12.52204960322272</v>
+        <v>12.97555081273557</v>
       </c>
       <c r="AC70" t="n">
         <v>2</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.434863334498471</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
         <v>35</v>
@@ -8174,10 +8190,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C71" t="n">
-        <v>149.19999695</v>
+        <v>146.56500244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8194,11 +8210,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -8209,22 +8221,22 @@
         <v>18.57059022636381</v>
       </c>
       <c r="K71" t="n">
-        <v>7.338127302158282</v>
+        <v>5.442447798561156</v>
       </c>
       <c r="L71" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M71" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>10.66431037743974</v>
+        <v>11.66304203341437</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>0.6166240407553758</v>
+        <v>2.42554327487241</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8233,10 +8245,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="S71" t="n">
-        <v>25.26062673645081</v>
+        <v>25.33415614821552</v>
       </c>
       <c r="T71" t="n">
-        <v>39.44525561649036</v>
+        <v>39.37172620472565</v>
       </c>
       <c r="U71" t="n">
         <v>47.91396311978173</v>
@@ -8251,17 +8263,13 @@
         <v>24.2086924558512</v>
       </c>
       <c r="Y71" t="n">
-        <v>12.59519647577826</v>
+        <v>14.1388371067572</v>
       </c>
       <c r="Z71" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>10.31728732748828</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>10</v>
       </c>
@@ -8275,10 +8283,10 @@
         <v>58.06451612903226</v>
       </c>
       <c r="AG71" t="n">
-        <v>7.748286659576983</v>
+        <v>7.754490133522391</v>
       </c>
       <c r="AH71" t="n">
-        <v>50.31622946945527</v>
+        <v>50.31002599550987</v>
       </c>
       <c r="AI71" t="n">
         <v>40.76626249536972</v>
@@ -8297,10 +8305,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C72" t="n">
-        <v>56.31000137</v>
+        <v>57.52500153</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8328,22 +8336,22 @@
         <v>11.90214849498216</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2314009599192923</v>
+        <v>2.394092582019081</v>
       </c>
       <c r="L72" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M72" t="n">
-        <v>50.84745762711864</v>
+        <v>55</v>
       </c>
       <c r="N72" t="n">
-        <v>17.66998127897994</v>
+        <v>18.73908866401763</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>2.762207265952332</v>
+        <v>0.5917406001675118</v>
       </c>
       <c r="Q72" t="n">
         <v>31</v>
@@ -8406,19 +8414,19 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C73" t="n">
-        <v>131.19000244</v>
+        <v>129.6401062</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8437,22 +8445,22 @@
         <v>12.28237922496582</v>
       </c>
       <c r="K73" t="n">
-        <v>2.508203622225635</v>
+        <v>1.297157990635633</v>
       </c>
       <c r="L73" t="n">
         <v>20</v>
       </c>
       <c r="M73" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>7.722513865648351</v>
+        <v>7.789120604197176</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.6938417852052181</v>
       </c>
       <c r="Q73" t="n">
         <v>16</v>
@@ -8515,10 +8523,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C74" t="n">
-        <v>27.93000031</v>
+        <v>28.05990028</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8578,22 +8586,22 @@
         <v>11.57371556196134</v>
       </c>
       <c r="Y74" t="n">
-        <v>4.382056865165773</v>
+        <v>3.937346238355299</v>
       </c>
       <c r="Z74" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA74" t="n">
-        <v>17.64705882352941</v>
+        <v>20</v>
       </c>
       <c r="AB74" t="n">
-        <v>10.45947430997677</v>
+        <v>10.42033107051223</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>5.875406801955741</v>
+        <v>6.311145407962238</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8624,10 +8632,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C75" t="n">
-        <v>184.99000549</v>
+        <v>191.01499939</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8636,7 +8644,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8644,38 +8652,24 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.62: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
       <c r="I75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>12.64532180659963</v>
-      </c>
-      <c r="K75" t="n">
-        <v>12.42175755766417</v>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>13</v>
-      </c>
-      <c r="M75" t="n">
-        <v>84.61538461538461</v>
-      </c>
-      <c r="N75" t="n">
-        <v>16.26850272100832</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>10</v>
       </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
         <v>31</v>
       </c>
@@ -8698,25 +8692,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X75" t="n">
-        <v>12.75599504767073</v>
+        <v>17.76966861016416</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.2964254715372316</v>
+        <v>1.431959335406607</v>
       </c>
       <c r="Z75" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AA75" t="n">
-        <v>42.85714285714285</v>
+        <v>48.88888888888889</v>
       </c>
       <c r="AB75" t="n">
-        <v>15.79253798589024</v>
+        <v>15.08098172122898</v>
       </c>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.711612438419619</v>
+        <v>1.590820568229734</v>
       </c>
       <c r="AE75" t="n">
         <v>19</v>
@@ -8747,10 +8741,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C76" t="n">
-        <v>190.22999573</v>
+        <v>191.22999573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8846,10 +8840,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C77" t="n">
-        <v>198.27000427</v>
+        <v>196.2749939</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8891,10 +8885,10 @@
         <v>45.94594594594594</v>
       </c>
       <c r="S77" t="n">
-        <v>43.84527867635976</v>
+        <v>43.60199485199485</v>
       </c>
       <c r="T77" t="n">
-        <v>2.100667269586182</v>
+        <v>2.343951093951091</v>
       </c>
       <c r="U77" t="n">
         <v>31.03856980437303</v>
@@ -8906,25 +8900,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>27.47231603601605</v>
+        <v>27.7686821005714</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.4418727878253814</v>
+        <v>1.672242078321173</v>
       </c>
       <c r="Z77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA77" t="n">
-        <v>41.66666666666666</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB77" t="n">
-        <v>8.513637572162638</v>
+        <v>7.779644426519988</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>9.600549427576798</v>
+        <v>8.469386567638558</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8955,10 +8949,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C78" t="n">
-        <v>190.99000549</v>
+        <v>194.11999512</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8986,16 +8980,16 @@
         <v>17.38881221393466</v>
       </c>
       <c r="K78" t="n">
-        <v>2.111854331536245</v>
+        <v>3.785287683914018</v>
       </c>
       <c r="L78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M78" t="n">
-        <v>68.75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N78" t="n">
-        <v>15.54385872887818</v>
+        <v>13.87857020882609</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
@@ -9064,10 +9058,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C79" t="n">
-        <v>100.34999847</v>
+        <v>100.4701004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9095,22 +9089,22 @@
         <v>13.29782231051553</v>
       </c>
       <c r="K79" t="n">
-        <v>1.057397167924856</v>
+        <v>1.178345734199859</v>
       </c>
       <c r="L79" t="n">
         <v>34</v>
       </c>
       <c r="M79" t="n">
-        <v>52.94117647058823</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N79" t="n">
-        <v>10.70284978590574</v>
+        <v>10.16814465225778</v>
       </c>
       <c r="O79" t="n">
         <v>6</v>
       </c>
       <c r="P79" t="n">
-        <v>4.890886734260658</v>
+        <v>4.765500197509498</v>
       </c>
       <c r="Q79" t="n">
         <v>27</v>
@@ -9173,10 +9167,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C80" t="n">
-        <v>52.11999893</v>
+        <v>52.18999863</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9204,22 +9198,22 @@
         <v>16.52331791600153</v>
       </c>
       <c r="K80" t="n">
-        <v>3.269264256221471</v>
+        <v>3.407959913657388</v>
       </c>
       <c r="L80" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M80" t="n">
-        <v>57.57575757575758</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N80" t="n">
-        <v>14.46703039554393</v>
+        <v>15.08050453966852</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>0.7076023529764885</v>
+        <v>0.5725285430995264</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9282,19 +9276,19 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C81" t="n">
-        <v>41.54000092</v>
+        <v>41.5320015</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9309,12 +9303,8 @@
       <c r="I81" t="n">
         <v>10</v>
       </c>
-      <c r="J81" t="n">
-        <v>19.42803345269662</v>
-      </c>
-      <c r="K81" t="n">
-        <v>21.85391826699654</v>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>0</v>
       </c>
@@ -9323,9 +9313,7 @@
       <c r="O81" t="n">
         <v>6</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
         <v>75</v>
       </c>
@@ -9348,25 +9336,25 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X81" t="n">
-        <v>36.83700278308666</v>
+        <v>25.81026070595338</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.81990173733716</v>
+        <v>2.735361215951426</v>
       </c>
       <c r="Z81" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA81" t="n">
-        <v>34.78260869565217</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="AB81" t="n">
-        <v>15.1991249268936</v>
+        <v>15.38614866662838</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>6.294654794629684</v>
+        <v>5.412695559109992</v>
       </c>
       <c r="AE81" t="n">
         <v>76</v>
@@ -9397,10 +9385,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C82" t="n">
-        <v>402.44000244</v>
+        <v>406.68499756</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9428,22 +9416,22 @@
         <v>11.8900081911483</v>
       </c>
       <c r="K82" t="n">
-        <v>0.401670514668151</v>
+        <v>1.460721798811204</v>
       </c>
       <c r="L82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M82" t="n">
-        <v>61.90476190476191</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N82" t="n">
-        <v>10.22920997752422</v>
+        <v>10.64662700539032</v>
       </c>
       <c r="O82" t="n">
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>9.559930065037703</v>
+        <v>8.416338904154008</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -9452,10 +9440,10 @@
         <v>23.80952380952381</v>
       </c>
       <c r="S82" t="n">
-        <v>24.69287715086034</v>
+        <v>24.81192476990796</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.8833533413365302</v>
+        <v>-1.002400960384151</v>
       </c>
       <c r="U82" t="n">
         <v>10.62801302263647</v>
@@ -9478,25 +9466,25 @@
       </c>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF82" t="n">
-        <v>35</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AG82" t="n">
-        <v>13.17822214017867</v>
+        <v>13.86021156207492</v>
       </c>
       <c r="AH82" t="n">
-        <v>21.82177785982133</v>
+        <v>19.47312177125842</v>
       </c>
       <c r="AI82" t="n">
-        <v>18.11918241010821</v>
+        <v>17.19475260508348</v>
       </c>
       <c r="AJ82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK82" t="n">
-        <v>39.1304347826087</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="83">
@@ -9506,10 +9494,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C83" t="n">
-        <v>275.08999634</v>
+        <v>272.6000061</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9534,19 +9522,19 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>23.66411973888177</v>
+        <v>23.15662045633322</v>
       </c>
       <c r="K83" t="n">
-        <v>3.029961176029983</v>
+        <v>2.097380561797735</v>
       </c>
       <c r="L83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>33.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N83" t="n">
-        <v>7.952586279424212</v>
+        <v>16.19377238813152</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
@@ -9615,10 +9603,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C84" t="n">
-        <v>25.10000038</v>
+        <v>25.51469994</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9675,19 +9663,19 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X84" t="n">
-        <v>12.30192171221367</v>
+        <v>11.74273811359998</v>
       </c>
       <c r="Y84" t="n">
-        <v>6.795395131579185</v>
+        <v>5.255478476450115</v>
       </c>
       <c r="Z84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA84" t="n">
-        <v>44.44444444444444</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB84" t="n">
-        <v>8.083997451240061</v>
+        <v>13.80679724257406</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9702,10 +9690,10 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AG84" t="n">
-        <v>12.19135027339362</v>
+        <v>12.0597713260252</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.12443920029059</v>
+        <v>14.25601814765901</v>
       </c>
       <c r="AI84" t="n">
         <v>11.80641234678251</v>
@@ -9724,10 +9712,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C85" t="n">
-        <v>130.78999329</v>
+        <v>132.06500244</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9752,13 +9740,13 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>22.77987498113207</v>
+        <v>20.94520590500485</v>
       </c>
       <c r="K85" t="n">
-        <v>6.523859414881161</v>
+        <v>7.562309620671259</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
@@ -9829,10 +9817,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C86" t="n">
-        <v>378.8999939</v>
+        <v>378.61999512</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9889,25 +9877,25 @@
         <v>75</v>
       </c>
       <c r="X86" t="n">
-        <v>18.66270892223245</v>
+        <v>19.48461089652223</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.338406032106054</v>
+        <v>2.089479398726291</v>
       </c>
       <c r="Z86" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="AA86" t="n">
-        <v>46.875</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.08544139687812</v>
+        <v>12.96908160209497</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.68413452597842</v>
+        <v>0.9299517515402367</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9938,10 +9926,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C87" t="n">
-        <v>452</v>
+        <v>445.29000854</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9983,10 +9971,10 @@
         <v>62.85714285714285</v>
       </c>
       <c r="S87" t="n">
-        <v>38.53963972757801</v>
+        <v>38.54528625496368</v>
       </c>
       <c r="T87" t="n">
-        <v>24.31750312956484</v>
+        <v>24.31185660217918</v>
       </c>
       <c r="U87" t="n">
         <v>46.33693684359532</v>
@@ -10001,22 +9989,22 @@
         <v>11.78082480528946</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.19431303447216</v>
+        <v>1.675939820308725</v>
       </c>
       <c r="Z87" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA87" t="n">
-        <v>35.13513513513514</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.43142672574399</v>
+        <v>10.73880085154371</v>
       </c>
       <c r="AC87" t="n">
         <v>6</v>
       </c>
       <c r="AD87" t="n">
-        <v>5.816990135575228</v>
+        <v>4.397764058755183</v>
       </c>
       <c r="AE87" t="n">
         <v>36</v>
@@ -10047,14 +10035,14 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C88" t="n">
-        <v>271.41000366</v>
+        <v>269.42001343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10078,22 +10066,22 @@
         <v>14.3256649882924</v>
       </c>
       <c r="K88" t="n">
-        <v>9.382178020452869</v>
+        <v>8.580183021515753</v>
       </c>
       <c r="L88" t="n">
         <v>20</v>
       </c>
       <c r="M88" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N88" t="n">
-        <v>7.329832686730091</v>
+        <v>7.301238111646442</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>0.564828741508161</v>
+        <v>1.307620726889835</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10120,22 +10108,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.7024413728232926</v>
+        <v>1.430495493401962</v>
       </c>
       <c r="Z88" t="n">
         <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.01342480579197</v>
+        <v>10.90209910753714</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.320885903708615</v>
+        <v>2.606794585668271</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10144,10 +10132,10 @@
         <v>37.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>14.49900793650794</v>
+        <v>14.62527056277056</v>
       </c>
       <c r="AH88" t="n">
-        <v>23.00099206349206</v>
+        <v>22.87472943722944</v>
       </c>
       <c r="AI88" t="n">
         <v>21.15936755954878</v>
@@ -10166,10 +10154,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C89" t="n">
-        <v>69.88999939</v>
+        <v>69.59999847</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10194,25 +10182,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>15.93516705034004</v>
+        <v>16.77289524548043</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9387659591126418</v>
+        <v>1.531721915802309</v>
       </c>
       <c r="L89" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M89" t="n">
-        <v>68.42105263157895</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N89" t="n">
-        <v>13.73633787362494</v>
+        <v>15.81842140182667</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>3.032763489626356</v>
+        <v>2.431041291946734</v>
       </c>
       <c r="Q89" t="n">
         <v>28</v>
@@ -10275,19 +10263,19 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C90" t="n">
-        <v>372.95001221</v>
+        <v>370.66000366</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10302,17 +10290,27 @@
       <c r="I90" t="n">
         <v>10</v>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>10.14435985893962</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.273225043715831</v>
+      </c>
       <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="M90" t="n">
+        <v>48</v>
+      </c>
+      <c r="N90" t="n">
+        <v>11.04170859565737</v>
+      </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="P90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>6.642204742053481</v>
+      </c>
       <c r="Q90" t="n">
         <v>26</v>
       </c>
@@ -10320,10 +10318,10 @@
         <v>46.15384615384615</v>
       </c>
       <c r="S90" t="n">
-        <v>39.62711650529987</v>
+        <v>39.53096265914602</v>
       </c>
       <c r="T90" t="n">
-        <v>6.526729648546286</v>
+        <v>6.622883494700133</v>
       </c>
       <c r="U90" t="n">
         <v>28.75585353039122</v>
@@ -10374,10 +10372,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C91" t="n">
-        <v>274.41000366</v>
+        <v>276.66500854</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10405,16 +10403,16 @@
         <v>14.60766672642613</v>
       </c>
       <c r="K91" t="n">
-        <v>2.292549640653796</v>
+        <v>3.133153829825863</v>
       </c>
       <c r="L91" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M91" t="n">
-        <v>57.14285714285715</v>
+        <v>70</v>
       </c>
       <c r="N91" t="n">
-        <v>11.04549553119507</v>
+        <v>10.94289877833009</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
@@ -10461,10 +10459,10 @@
         <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>18.24697931276879</v>
+        <v>17.99697931276879</v>
       </c>
       <c r="AH91" t="n">
-        <v>21.75302068723121</v>
+        <v>22.00302068723121</v>
       </c>
       <c r="AI91" t="n">
         <v>21.88065323728171</v>
@@ -10483,10 +10481,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C92" t="n">
-        <v>362.04000854</v>
+        <v>362.45001221</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10582,10 +10580,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C93" t="n">
-        <v>253.46000671</v>
+        <v>249.97999573</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10613,16 +10611,16 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>11.68590992547096</v>
+        <v>10.15246014024851</v>
       </c>
       <c r="L93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M93" t="n">
-        <v>62.5</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N93" t="n">
-        <v>11.84691764092608</v>
+        <v>10.43413306745</v>
       </c>
       <c r="O93" t="n">
         <v>10</v>
@@ -10655,43 +10653,43 @@
         <v>12.53635174236054</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.7557040935862069</v>
+        <v>2.118330268578184</v>
       </c>
       <c r="Z93" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA93" t="n">
-        <v>43.13725490196079</v>
+        <v>42.5925925925926</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.00928929785776</v>
+        <v>15.01588432498114</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.268999872267853</v>
+        <v>1.922392350462498</v>
       </c>
       <c r="AE93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF93" t="n">
-        <v>51.61290322580645</v>
+        <v>53.125</v>
       </c>
       <c r="AG93" t="n">
-        <v>36.3664466271118</v>
+        <v>36.95413310104903</v>
       </c>
       <c r="AH93" t="n">
-        <v>15.24645659869465</v>
+        <v>16.17086689895097</v>
       </c>
       <c r="AI93" t="n">
-        <v>34.8403954480288</v>
+        <v>36.44951711897464</v>
       </c>
       <c r="AJ93" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AK93" t="n">
-        <v>46.26865671641791</v>
+        <v>47.05882352941177</v>
       </c>
     </row>
     <row r="94">
@@ -10701,10 +10699,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C94" t="n">
-        <v>46.45000076</v>
+        <v>46.93500137</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10729,25 +10727,25 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>10.64427558504014</v>
+        <v>10.65414640017589</v>
       </c>
       <c r="K94" t="n">
-        <v>0.60623560032802</v>
+        <v>1.667931191714578</v>
       </c>
       <c r="L94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M94" t="n">
-        <v>40.90909090909091</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="N94" t="n">
-        <v>7.569977336443118</v>
+        <v>9.529258611612029</v>
       </c>
       <c r="O94" t="n">
         <v>2</v>
       </c>
       <c r="P94" t="n">
-        <v>1.385365818883133</v>
+        <v>0.3266209948338927</v>
       </c>
       <c r="Q94" t="n">
         <v>19</v>
@@ -10810,10 +10808,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C95" t="n">
-        <v>30.82999992</v>
+        <v>30.70999908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10870,25 +10868,25 @@
         <v>60.60606060606061</v>
       </c>
       <c r="X95" t="n">
-        <v>15.02976579706115</v>
+        <v>13.09436689962857</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.2910742553917989</v>
+        <v>0.6791752893165026</v>
       </c>
       <c r="Z95" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AA95" t="n">
-        <v>48.97959183673469</v>
+        <v>52.54237288135593</v>
       </c>
       <c r="AB95" t="n">
-        <v>12.63847080611493</v>
+        <v>12.58792141161612</v>
       </c>
       <c r="AC95" t="n">
         <v>8</v>
       </c>
       <c r="AD95" t="n">
-        <v>7.731429946756863</v>
+        <v>7.370885946636752</v>
       </c>
       <c r="AE95" t="n">
         <v>51</v>
@@ -10919,19 +10917,19 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C96" t="n">
-        <v>83.15000153</v>
+        <v>82.45500183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10946,17 +10944,27 @@
       <c r="I96" t="n">
         <v>10</v>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>10.56995037090656</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.2288910194601312</v>
+      </c>
       <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="M96" t="n">
+        <v>25.80645161290322</v>
+      </c>
+      <c r="N96" t="n">
+        <v>9.725336025229296</v>
+      </c>
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="P96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>1.767064328982748</v>
+      </c>
       <c r="Q96" t="n">
         <v>28</v>
       </c>
@@ -10964,10 +10972,10 @@
         <v>42.85714285714285</v>
       </c>
       <c r="S96" t="n">
-        <v>36.31816540221713</v>
+        <v>36.34084113917858</v>
       </c>
       <c r="T96" t="n">
-        <v>6.538977454925728</v>
+        <v>6.516301717964275</v>
       </c>
       <c r="U96" t="n">
         <v>26.50854712412369</v>
@@ -11018,10 +11026,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C97" t="n">
-        <v>110.12000275</v>
+        <v>110.37000275</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11049,13 +11057,13 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>7.802252668257981</v>
+        <v>8.046990794792986</v>
       </c>
       <c r="L97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M97" t="n">
-        <v>20</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="N97" t="n">
         <v>5.520930121865053</v>
@@ -11127,10 +11135,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C98" t="n">
-        <v>158.71000671</v>
+        <v>160.8500061</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11204,10 +11212,10 @@
         <v>50</v>
       </c>
       <c r="AG98" t="n">
-        <v>23.30158525398464</v>
+        <v>23.30751223359583</v>
       </c>
       <c r="AH98" t="n">
-        <v>26.69841474601536</v>
+        <v>26.69248776640417</v>
       </c>
       <c r="AI98" t="n">
         <v>31.42742581957335</v>
@@ -11226,10 +11234,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C99" t="n">
-        <v>30732.39648438</v>
+        <v>30393.90234375</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/TDA_usa.xlsx
+++ b/TDA_usa.xlsx
@@ -440,7 +440,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C2" t="n">
-        <v>336.8500061</v>
+        <v>337.98999023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         <v>55.17241379310344</v>
       </c>
       <c r="X2" t="n">
-        <v>14.89502875525965</v>
+        <v>14.33206763779027</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.458443947987232</v>
+        <v>2.12833908261344</v>
       </c>
       <c r="Z2" t="n">
         <v>27</v>
@@ -739,13 +739,13 @@
         <v>25.92592592592593</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.63464783109587</v>
+        <v>11.22728593043887</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.681225803961754</v>
+        <v>5.999347372211073</v>
       </c>
       <c r="AE2" t="n">
         <v>24</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C3" t="n">
-        <v>264.09500122</v>
+        <v>263.94500732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C4" t="n">
-        <v>104.04000092</v>
+        <v>101.79000092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>14.49633120893619</v>
       </c>
       <c r="K4" t="n">
-        <v>3.697796294558287</v>
+        <v>1.455196913555157</v>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M4" t="n">
-        <v>47.05882352941177</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N4" t="n">
-        <v>8.162860539846717</v>
+        <v>8.655039844254842</v>
       </c>
       <c r="O4" t="n">
         <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22010861147155</v>
+        <v>4.479615854786867</v>
       </c>
       <c r="Q4" t="n">
         <v>17</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C5" t="n">
-        <v>184.80999756</v>
+        <v>179.50999451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         <v>16.4241560412371</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.48687294613196</v>
+        <v>9.168653505322922</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>57.14285714285715</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.282538324923399</v>
+        <v>9.979199909871117</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C6" t="n">
-        <v>380.44750977</v>
+        <v>382.48001099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
         <v>12.33153059688125</v>
       </c>
       <c r="K6" t="n">
-        <v>9.323997060344835</v>
+        <v>9.908049135057473</v>
       </c>
       <c r="L6" t="n">
         <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>47.82608695652174</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="N6" t="n">
-        <v>8.293871144373249</v>
+        <v>8.792023371649595</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6183481740811514</v>
+        <v>0.08366162957686996</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1148,10 +1148,10 @@
         <v>41.1764705882353</v>
       </c>
       <c r="S6" t="n">
-        <v>35.896645425043</v>
+        <v>35.74958660151358</v>
       </c>
       <c r="T6" t="n">
-        <v>5.279825163192299</v>
+        <v>5.426883986721712</v>
       </c>
       <c r="U6" t="n">
         <v>26.36596836387115</v>
@@ -1166,22 +1166,22 @@
         <v>12.22557857183908</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.58549035649378</v>
+        <v>2.065063478641893</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.25</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.12079488636523</v>
+        <v>11.6727343382273</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.452052316110508</v>
+        <v>1.975736739193301</v>
       </c>
       <c r="AE6" t="n">
         <v>29</v>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C7" t="n">
-        <v>266.55999756</v>
+        <v>262.13500977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C8" t="n">
-        <v>470.66500854</v>
+        <v>470.69000244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>27.00617237148732</v>
       </c>
       <c r="K8" t="n">
-        <v>14.37510567557341</v>
+        <v>14.38117937959193</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1384,7 +1384,7 @@
         <v>15.40423868800416</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8917636164240128</v>
+        <v>0.8865006346760462</v>
       </c>
       <c r="Z8" t="n">
         <v>51</v>
@@ -1399,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.190191164662254</v>
+        <v>9.19501321584093</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C9" t="n">
-        <v>612.29998779</v>
+        <v>624.48901367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>69.56521739130434</v>
       </c>
       <c r="X9" t="n">
-        <v>41.81382074233824</v>
+        <v>42.76276847219069</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.983366942435738</v>
+        <v>0.6966434213742434</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
@@ -1502,13 +1502,13 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.39615186886673</v>
+        <v>12.22811867012128</v>
       </c>
       <c r="AC9" t="n">
         <v>6</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.097909642749443</v>
+        <v>5.340561247218978</v>
       </c>
       <c r="AE9" t="n">
         <v>53</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C10" t="n">
-        <v>248.08000183</v>
+        <v>249.39480591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1566,27 +1566,17 @@
       <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>10.66334722469461</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.547277418259529</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>37</v>
-      </c>
-      <c r="M10" t="n">
-        <v>43.24324324324324</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10.89344440638165</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="P10" t="n">
-        <v>6.354402349127075</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>23</v>
       </c>
@@ -1594,10 +1584,10 @@
         <v>39.1304347826087</v>
       </c>
       <c r="S10" t="n">
-        <v>44.91320488081318</v>
+        <v>45.0219005329871</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.782770098204487</v>
+        <v>-5.891465750378401</v>
       </c>
       <c r="U10" t="n">
         <v>22.15762279247795</v>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C11" t="n">
-        <v>202.55000305</v>
+        <v>205.29499817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,19 +1666,19 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>14.2728744929405</v>
+        <v>13.72614166687475</v>
       </c>
       <c r="K11" t="n">
-        <v>11.73939332417273</v>
+        <v>13.25370625810491</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>62.96296296296296</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N11" t="n">
-        <v>13.46029151457658</v>
+        <v>14.60517234197607</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
@@ -1721,22 +1711,22 @@
         <v>14.88938578045085</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.741761072948579</v>
+        <v>1.423699422914193</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>34</v>
+        <v>41.81818181818182</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.69867830841566</v>
+        <v>11.72485443115941</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.406471456876128</v>
+        <v>6.671279545475739</v>
       </c>
       <c r="AE11" t="n">
         <v>51</v>
@@ -1745,10 +1735,10 @@
         <v>52.94117647058823</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.5190487178349</v>
+        <v>16.59563041412189</v>
       </c>
       <c r="AH11" t="n">
-        <v>36.42212775275333</v>
+        <v>36.34554605646635</v>
       </c>
       <c r="AI11" t="n">
         <v>39.52330421009647</v>
@@ -1767,10 +1757,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C12" t="n">
-        <v>82.27999878</v>
+        <v>83.30500031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,19 +1785,19 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>12.33653883634149</v>
+        <v>11.94931875599405</v>
       </c>
       <c r="K12" t="n">
-        <v>8.620460435643572</v>
+        <v>9.973597768976884</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>47.05882352941177</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="N12" t="n">
-        <v>8.368489809226187</v>
+        <v>11.16892037353304</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -1840,22 +1830,22 @@
         <v>11.52475691089108</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.604171984493153</v>
+        <v>1.390865297427712</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>13.63636363636364</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.83869362026744</v>
+        <v>8.660294208015948</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>7.593577842296617</v>
+        <v>8.730565102857257</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -1886,14 +1876,14 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C13" t="n">
-        <v>330.29998779</v>
+        <v>313.8500061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1903,7 +1893,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1946,25 +1936,21 @@
         <v>89.47368421052632</v>
       </c>
       <c r="X13" t="n">
-        <v>49.46326571942468</v>
+        <v>49.46331986206478</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.982284803822776</v>
+        <v>6.863910064590273</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>25.9014832189109</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.038297203868022</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>11</v>
@@ -1995,10 +1981,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C14" t="n">
-        <v>1725.32995605</v>
+        <v>1725.60498047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2012,7 @@
         <v>17.05961525742885</v>
       </c>
       <c r="K14" t="n">
-        <v>9.695200627134316</v>
+        <v>9.712686476043086</v>
       </c>
       <c r="L14" t="n">
         <v>16</v>
@@ -2041,7 +2027,7 @@
         <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2778602629131877</v>
+        <v>0.2618781229276168</v>
       </c>
       <c r="Q14" t="n">
         <v>35</v>
@@ -2068,7 +2054,7 @@
         <v>11.24462686563246</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.392809955998697</v>
+        <v>1.377091579838474</v>
       </c>
       <c r="Z14" t="n">
         <v>48</v>
@@ -2083,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.672265827619116</v>
+        <v>4.687459023685081</v>
       </c>
       <c r="AE14" t="n">
         <v>35</v>
@@ -2092,10 +2078,10 @@
         <v>48.57142857142857</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.6521791880231</v>
+        <v>14.65584219168611</v>
       </c>
       <c r="AH14" t="n">
-        <v>33.91924938340546</v>
+        <v>33.91558637974246</v>
       </c>
       <c r="AI14" t="n">
         <v>32.99423600250972</v>
@@ -2114,10 +2100,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C15" t="n">
-        <v>354.66500854</v>
+        <v>349.92498779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,19 +2128,19 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>21.26377548417351</v>
+        <v>20.97100937908157</v>
       </c>
       <c r="K15" t="n">
-        <v>5.614785478991324</v>
+        <v>4.203266827241503</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>73.33333333333333</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N15" t="n">
-        <v>12.97794550771273</v>
+        <v>14.16399542271508</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -2169,10 +2155,10 @@
         <v>56.81818181818182</v>
       </c>
       <c r="S15" t="n">
-        <v>44.35933632774331</v>
+        <v>44.41615450956149</v>
       </c>
       <c r="T15" t="n">
-        <v>12.45884549043851</v>
+        <v>12.40202730862033</v>
       </c>
       <c r="U15" t="n">
         <v>42.22414699362943</v>
@@ -2201,10 +2187,10 @@
         <v>40.54054054054054</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.89595898419428</v>
+        <v>12.92081142283982</v>
       </c>
       <c r="AH15" t="n">
-        <v>27.64458155634626</v>
+        <v>27.61972911770072</v>
       </c>
       <c r="AI15" t="n">
         <v>26.34651819201428</v>
@@ -2223,10 +2209,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C16" t="n">
-        <v>303.73999023</v>
+        <v>302.17001343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,25 +2237,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>12.84030384924218</v>
+        <v>13.59799017086963</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3966357030896095</v>
+        <v>0.7535626496014247</v>
       </c>
       <c r="L16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>65.625</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N16" t="n">
-        <v>10.60661575543022</v>
+        <v>12.35940608177617</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.597029906113723</v>
+        <v>1.237114914470472</v>
       </c>
       <c r="Q16" t="n">
         <v>21</v>
@@ -2332,10 +2318,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C17" t="n">
-        <v>201.41000366</v>
+        <v>197.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,25 +2346,25 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>16.68016123470477</v>
+        <v>16.77369964168221</v>
       </c>
       <c r="K17" t="n">
-        <v>3.04409942992987</v>
+        <v>1.594653393659384</v>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M17" t="n">
-        <v>58.8235294117647</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N17" t="n">
-        <v>11.60093981164182</v>
+        <v>11.6287587119756</v>
       </c>
       <c r="O17" t="n">
         <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.868578197512561</v>
+        <v>4.336199257721529</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -2441,10 +2427,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C18" t="n">
-        <v>55.86500168</v>
+        <v>55.99000168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,25 +2455,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>14.55618927013956</v>
+        <v>14.548522445454</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2332485306848264</v>
+        <v>0.4485109301489265</v>
       </c>
       <c r="L18" t="n">
         <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N18" t="n">
-        <v>12.08063464273946</v>
+        <v>13.01269330692513</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.760313079614685</v>
+        <v>2.540096459593477</v>
       </c>
       <c r="Q18" t="n">
         <v>24</v>
@@ -2496,10 +2482,10 @@
         <v>50</v>
       </c>
       <c r="S18" t="n">
-        <v>39.02777777777778</v>
+        <v>38.92361111111111</v>
       </c>
       <c r="T18" t="n">
-        <v>10.97222222222222</v>
+        <v>11.07638888888889</v>
       </c>
       <c r="U18" t="n">
         <v>31.42742581957335</v>
@@ -2550,10 +2536,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C19" t="n">
-        <v>156.60510254</v>
+        <v>156.25999451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,10 +2564,10 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>28.50865071929265</v>
+        <v>28.50635473648759</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7981829924241346</v>
+        <v>0.5728257822964045</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -2596,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>7.144788520758505</v>
+        <v>7.384871768225687</v>
       </c>
       <c r="Q19" t="n">
         <v>31</v>
@@ -2659,10 +2645,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C20" t="n">
-        <v>61.50999832</v>
+        <v>60.81000137</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,25 +2673,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>10.46037350496544</v>
+        <v>11.72056853364725</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08135249064178396</v>
+        <v>0.3548149940939993</v>
       </c>
       <c r="L20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M20" t="n">
-        <v>42.10526315789474</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N20" t="n">
-        <v>9.347066422818166</v>
+        <v>9.151548028955576</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>9.910585001622231</v>
+        <v>9.611083440763291</v>
       </c>
       <c r="Q20" t="n">
         <v>18</v>
@@ -2768,10 +2754,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C21" t="n">
-        <v>132.6499939</v>
+        <v>132.03999329</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,10 +2853,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C22" t="n">
-        <v>809.54998779</v>
+        <v>804.98608398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,22 +2884,22 @@
         <v>13.12294737246159</v>
       </c>
       <c r="K22" t="n">
-        <v>4.94691043639115</v>
+        <v>4.355263704734802</v>
       </c>
       <c r="L22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M22" t="n">
-        <v>61.53846153846154</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="N22" t="n">
-        <v>9.839575323488956</v>
+        <v>11.08131653353117</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>4.814900736569627</v>
+        <v>5.409153400480649</v>
       </c>
       <c r="Q22" t="n">
         <v>27</v>
@@ -2922,10 +2908,10 @@
         <v>51.85185185185185</v>
       </c>
       <c r="S22" t="n">
-        <v>34.11228689006467</v>
+        <v>34.20487948265726</v>
       </c>
       <c r="T22" t="n">
-        <v>17.73956496178719</v>
+        <v>17.64697236919459</v>
       </c>
       <c r="U22" t="n">
         <v>33.98561575495229</v>
@@ -2976,19 +2962,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C23" t="n">
-        <v>22.79000092</v>
+        <v>22.17499924</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3004,46 +2990,46 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>19.43327406271869</v>
+        <v>19.50640188619991</v>
       </c>
       <c r="K23" t="n">
-        <v>3.42637202241689</v>
+        <v>0.7267765361496092</v>
       </c>
       <c r="L23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>36.36363636363637</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="N23" t="n">
-        <v>9.158437146117038</v>
+        <v>7.809376468462354</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>7.220744785017641</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R23" t="n">
-        <v>48.14814814814815</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="S23" t="n">
-        <v>22.6501407602756</v>
+        <v>22.48473748473749</v>
       </c>
       <c r="T23" t="n">
-        <v>25.49800738787254</v>
+        <v>23.66910866910867</v>
       </c>
       <c r="U23" t="n">
-        <v>30.74322697621846</v>
+        <v>28.75585353039122</v>
       </c>
       <c r="V23" t="n">
         <v>29</v>
       </c>
       <c r="W23" t="n">
-        <v>58.62068965517241</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -3085,10 +3071,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C24" t="n">
-        <v>128.41999817</v>
+        <v>129.41000366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,22 +3102,22 @@
         <v>12.09391062009804</v>
       </c>
       <c r="K24" t="n">
-        <v>3.154724615028615</v>
+        <v>3.949957017641825</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>48.71794871794872</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N24" t="n">
-        <v>12.03677738110602</v>
+        <v>11.10942165651704</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>6.63593006575105</v>
+        <v>5.820149575753453</v>
       </c>
       <c r="Q24" t="n">
         <v>35</v>
@@ -3158,22 +3144,22 @@
         <v>14.09925232216449</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.320715580321215</v>
+        <v>8.621657873702093</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.11588024088992</v>
+        <v>16.56026942025002</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.7491065065477809</v>
+        <v>1.508390384663405</v>
       </c>
       <c r="AE24" t="n">
         <v>36</v>
@@ -3204,10 +3190,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C25" t="n">
-        <v>900.6799926800001</v>
+        <v>897.92840576</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,10 +3289,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C26" t="n">
-        <v>239.66000366</v>
+        <v>238.81500244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3334,7 +3320,7 @@
         <v>14.3363003785587</v>
       </c>
       <c r="K26" t="n">
-        <v>4.286152127662901</v>
+        <v>3.918456540450954</v>
       </c>
       <c r="L26" t="n">
         <v>34</v>
@@ -3343,13 +3329,13 @@
         <v>52.94117647058823</v>
       </c>
       <c r="N26" t="n">
-        <v>10.37768672476844</v>
+        <v>10.2668491421958</v>
       </c>
       <c r="O26" t="n">
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>3.561209035491841</v>
+        <v>3.927640570720259</v>
       </c>
       <c r="Q26" t="n">
         <v>35</v>
@@ -3412,19 +3398,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C27" t="n">
-        <v>106.37999725</v>
+        <v>105.64499664</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3439,27 +3425,17 @@
       <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
-        <v>16.02249521790768</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.789297743478158</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>46.66666666666666</v>
-      </c>
-      <c r="N27" t="n">
-        <v>11.37046284508763</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" t="n">
-        <v>6.101527758029723</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
         <v>16</v>
       </c>
@@ -3521,10 +3497,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C28" t="n">
-        <v>85.95999908</v>
+        <v>84.55619812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,25 +3525,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>13.02538256852792</v>
+        <v>14.21319796954315</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3385092986981642</v>
+        <v>0.06650665088758778</v>
       </c>
       <c r="L28" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M28" t="n">
-        <v>54.05405405405406</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="N28" t="n">
-        <v>9.878793241215995</v>
+        <v>10.2823373466755</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.655885375330568</v>
+        <v>1.932208302082516</v>
       </c>
       <c r="Q28" t="n">
         <v>36</v>
@@ -3630,10 +3606,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C29" t="n">
-        <v>205.8500061</v>
+        <v>206.36999512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3693,16 +3669,16 @@
         <v>12.40258001548387</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.478001995973747</v>
+        <v>5.239233962677314</v>
       </c>
       <c r="Z29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>40</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.689250324535682</v>
+        <v>7.373282762675609</v>
       </c>
       <c r="AC29" t="n">
         <v>3</v>
@@ -3739,10 +3715,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C30" t="n">
-        <v>708.11999512</v>
+        <v>695.09997559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,25 +3775,25 @@
         <v>48.48484848484848</v>
       </c>
       <c r="X30" t="n">
-        <v>24.47652957953899</v>
+        <v>24.49637909542586</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.800706651829898</v>
+        <v>3.621640577235885</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA30" t="n">
-        <v>38.88888888888889</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.44675914756516</v>
+        <v>11.44356745640347</v>
       </c>
       <c r="AC30" t="n">
         <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.257959644197095</v>
+        <v>1.430154477643619</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -3848,10 +3824,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C31" t="n">
-        <v>220.96499634</v>
+        <v>222.15499878</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,25 +3884,25 @@
         <v>44.44444444444444</v>
       </c>
       <c r="X31" t="n">
-        <v>12.15781921491597</v>
+        <v>13.83796451678614</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.043463511988807</v>
+        <v>1.978909557920649</v>
       </c>
       <c r="Z31" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AA31" t="n">
-        <v>48.38709677419355</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.821060333009</v>
+        <v>9.438273591895756</v>
       </c>
       <c r="AC31" t="n">
         <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.977167509544187</v>
+        <v>1.041704838697666</v>
       </c>
       <c r="AE31" t="n">
         <v>26</v>
@@ -3957,10 +3933,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C32" t="n">
-        <v>104.06999969</v>
+        <v>105.02999878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,10 +4032,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C33" t="n">
-        <v>13.03680038</v>
+        <v>12.78499985</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,25 +4060,25 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>12.09016672741415</v>
+        <v>13.38797803607155</v>
       </c>
       <c r="K33" t="n">
-        <v>1.296041114418367</v>
+        <v>0.8280720617742654</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M33" t="n">
-        <v>66</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N33" t="n">
-        <v>11.30618932481016</v>
+        <v>13.04571358977554</v>
       </c>
       <c r="O33" t="n">
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.643773669563567</v>
+        <v>5.129452376176613</v>
       </c>
       <c r="Q33" t="n">
         <v>41</v>
@@ -4111,10 +4087,10 @@
         <v>56.09756097560975</v>
       </c>
       <c r="S33" t="n">
-        <v>44.28681980693316</v>
+        <v>44.29011133782419</v>
       </c>
       <c r="T33" t="n">
-        <v>11.81074116867659</v>
+        <v>11.80744963778557</v>
       </c>
       <c r="U33" t="n">
         <v>41.04052722210609</v>
@@ -4165,10 +4141,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C34" t="n">
-        <v>321.3500061</v>
+        <v>321.5249939</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,13 +4172,13 @@
         <v>18.31300954242431</v>
       </c>
       <c r="K34" t="n">
-        <v>4.742509416251761</v>
+        <v>4.799545859199661</v>
       </c>
       <c r="L34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M34" t="n">
-        <v>57.14285714285715</v>
+        <v>60</v>
       </c>
       <c r="N34" t="n">
         <v>12.21257287371713</v>
@@ -4211,7 +4187,7 @@
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.109998606967523</v>
+        <v>3.053881688667071</v>
       </c>
       <c r="Q34" t="n">
         <v>32</v>
@@ -4274,10 +4250,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C35" t="n">
-        <v>84.01999664</v>
+        <v>81.34999847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4351,10 +4327,10 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AG35" t="n">
-        <v>28.81942522822331</v>
+        <v>28.82432718900762</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.23939830118846</v>
+        <v>18.23449634040415</v>
       </c>
       <c r="AI35" t="n">
         <v>31.45150447508847</v>
@@ -4373,10 +4349,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C36" t="n">
-        <v>338.32000732</v>
+        <v>341.55999756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,16 +4412,16 @@
         <v>11.11552580886888</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.098334612047575</v>
+        <v>6.208642951418087</v>
       </c>
       <c r="Z36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="n">
-        <v>66.66666666666667</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.62804754079361</v>
+        <v>10.64080225337827</v>
       </c>
       <c r="AC36" t="n">
         <v>3</v>
@@ -4460,10 +4436,10 @@
         <v>55</v>
       </c>
       <c r="AG36" t="n">
-        <v>21.57229086199141</v>
+        <v>21.82870111840166</v>
       </c>
       <c r="AH36" t="n">
-        <v>33.42770913800859</v>
+        <v>33.17129888159834</v>
       </c>
       <c r="AI36" t="n">
         <v>34.20853424503424</v>
@@ -4482,10 +4458,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C37" t="n">
-        <v>937.3150024399999</v>
+        <v>921.35498047</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4510,25 +4486,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>13.30675651903024</v>
+        <v>13.99503762193179</v>
       </c>
       <c r="K37" t="n">
-        <v>1.661063171366584</v>
+        <v>0.7297620854745501</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
-        <v>61.53846153846154</v>
+        <v>59.375</v>
       </c>
       <c r="N37" t="n">
-        <v>11.24751725733877</v>
+        <v>11.83462101954172</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.202685048234027</v>
+        <v>9.203077345362098</v>
       </c>
       <c r="Q37" t="n">
         <v>31</v>
@@ -4591,10 +4567,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C38" t="n">
-        <v>33.11000061</v>
+        <v>32.88499832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,22 +4598,22 @@
         <v>14.06988793284954</v>
       </c>
       <c r="K38" t="n">
-        <v>1.238338961438301</v>
+        <v>0.5503637973653719</v>
       </c>
       <c r="L38" t="n">
         <v>51</v>
       </c>
       <c r="M38" t="n">
-        <v>49.01960784313726</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N38" t="n">
-        <v>15.21024155886768</v>
+        <v>14.67104130409128</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>6.678952961819351</v>
+        <v>7.408860516554228</v>
       </c>
       <c r="Q38" t="n">
         <v>47</v>
@@ -4646,31 +4622,31 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S38" t="n">
-        <v>32.02426801124558</v>
+        <v>31.81778213006765</v>
       </c>
       <c r="T38" t="n">
-        <v>29.67785964832888</v>
+        <v>29.88434552950682</v>
       </c>
       <c r="U38" t="n">
         <v>47.42656695641357</v>
       </c>
       <c r="V38" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W38" t="n">
-        <v>71.23287671232876</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="X38" t="n">
         <v>16.46267138606403</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.00578187551442</v>
+        <v>13.59695970499646</v>
       </c>
       <c r="Z38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>22.22222222222222</v>
+        <v>40</v>
       </c>
       <c r="AB38" t="n">
         <v>7.415092393240514</v>
@@ -4710,10 +4686,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C39" t="n">
-        <v>299.60501099</v>
+        <v>292.23498535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4738,25 +4714,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>16.5258375325574</v>
+        <v>16.91780816552121</v>
       </c>
       <c r="K39" t="n">
-        <v>1.42692580349888</v>
+        <v>0.3830002228257801</v>
       </c>
       <c r="L39" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M39" t="n">
-        <v>38.88888888888889</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N39" t="n">
-        <v>8.505794505893762</v>
+        <v>7.087456070434586</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
       <c r="P39" t="n">
-        <v>8.452463809373768</v>
+        <v>9.580307179330006</v>
       </c>
       <c r="Q39" t="n">
         <v>23</v>
@@ -4819,10 +4795,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C40" t="n">
-        <v>211.97999573</v>
+        <v>212.41999817</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,22 +4826,22 @@
         <v>16.65750342876763</v>
       </c>
       <c r="K40" t="n">
-        <v>7.614986458097239</v>
+        <v>7.838360632905883</v>
       </c>
       <c r="L40" t="n">
         <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>58.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>8.110141750390678</v>
+        <v>8.277597911045294</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3577694469651505</v>
+        <v>0.1498904157532177</v>
       </c>
       <c r="Q40" t="n">
         <v>15</v>
@@ -4928,24 +4904,24 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C41" t="n">
-        <v>234.86500549</v>
+        <v>228.04499817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4955,17 +4931,27 @@
       <c r="I41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>10.23747648344719</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8870133337102182</v>
+      </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="M41" t="n">
+        <v>34.48275862068966</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10.74521687400087</v>
+      </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>9.032863958561443</v>
+      </c>
       <c r="Q41" t="n">
         <v>28</v>
       </c>
@@ -4987,27 +4973,17 @@
       <c r="W41" t="n">
         <v>53.125</v>
       </c>
-      <c r="X41" t="n">
-        <v>10.73879246924641</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>6.732984408365327</v>
-      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>14.45595395278494</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>4</v>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
         <v>26</v>
       </c>
@@ -5037,14 +5013,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C42" t="n">
-        <v>120.18990326</v>
+        <v>125.83499908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5054,7 +5030,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5097,25 +5073,25 @@
         <v>69.49152542372882</v>
       </c>
       <c r="X42" t="n">
-        <v>46.49988754245867</v>
+        <v>48.37385646591557</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.639942257434414</v>
+        <v>0.3882837654293092</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>15.57342437292846</v>
+        <v>24.20591203963515</v>
       </c>
       <c r="AC42" t="n">
         <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.61799866069503</v>
       </c>
       <c r="AE42" t="n">
         <v>48</v>
@@ -5124,10 +5100,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG42" t="n">
-        <v>18.21875258456141</v>
+        <v>18.11005693238749</v>
       </c>
       <c r="AH42" t="n">
-        <v>27.61458074877193</v>
+        <v>27.72327640094584</v>
       </c>
       <c r="AI42" t="n">
         <v>32.57524229286744</v>
@@ -5146,10 +5122,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C43" t="n">
-        <v>397.25</v>
+        <v>400.92001343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5153,7 @@
         <v>14.82459093170673</v>
       </c>
       <c r="K43" t="n">
-        <v>15.06154960173787</v>
+        <v>16.12455131933381</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5215,22 +5191,22 @@
         <v>17.14409918609703</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.777767381224027</v>
+        <v>0.8703365119087647</v>
       </c>
       <c r="Z43" t="n">
         <v>19</v>
       </c>
       <c r="AA43" t="n">
-        <v>47.36842105263158</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.755121205036906</v>
+        <v>9.492455284116355</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.334851543159226</v>
+        <v>7.192260356001046</v>
       </c>
       <c r="AE43" t="n">
         <v>20</v>
@@ -5261,14 +5237,14 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C44" t="n">
-        <v>267.23999023</v>
+        <v>270.82998657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5278,7 +5254,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5320,27 +5296,17 @@
       <c r="W44" t="n">
         <v>40</v>
       </c>
-      <c r="X44" t="n">
-        <v>10.11126434424055</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>4.920488394286215</v>
-      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>5.966186301970189</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>6</v>
       </c>
-      <c r="AD44" t="n">
-        <v>1.135377735416254</v>
-      </c>
+      <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
         <v>14</v>
       </c>
@@ -5370,10 +5336,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C45" t="n">
-        <v>338.55999756</v>
+        <v>336.86999512</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5469,10 +5435,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C46" t="n">
-        <v>186.30000305</v>
+        <v>186.38000488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5500,7 +5466,7 @@
         <v>22.7700200025672</v>
       </c>
       <c r="K46" t="n">
-        <v>12.30333578579199</v>
+        <v>12.35156161633883</v>
       </c>
       <c r="L46" t="n">
         <v>12</v>
@@ -5524,10 +5490,10 @@
         <v>65.95744680851064</v>
       </c>
       <c r="S46" t="n">
-        <v>40.78104311880403</v>
+        <v>40.83666820571823</v>
       </c>
       <c r="T46" t="n">
-        <v>25.17640368970661</v>
+        <v>25.12077860279241</v>
       </c>
       <c r="U46" t="n">
         <v>51.67092456194193</v>
@@ -5542,7 +5508,7 @@
         <v>13.68979853728842</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.219513772857728</v>
+        <v>1.177094988439664</v>
       </c>
       <c r="Z46" t="n">
         <v>54</v>
@@ -5551,13 +5517,13 @@
         <v>42.5925925925926</v>
       </c>
       <c r="AB46" t="n">
-        <v>12.389491273043</v>
+        <v>12.41420915723557</v>
       </c>
       <c r="AC46" t="n">
         <v>8</v>
       </c>
       <c r="AD46" t="n">
-        <v>6.864196043286097</v>
+        <v>6.90417369410683</v>
       </c>
       <c r="AE46" t="n">
         <v>43</v>
@@ -5588,10 +5554,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C47" t="n">
-        <v>31.76000023</v>
+        <v>31.26499939</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5687,10 +5653,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C48" t="n">
-        <v>87.91500092</v>
+        <v>88.53500366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5786,10 +5752,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C49" t="n">
-        <v>470.51998901</v>
+        <v>469.17999268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5885,10 +5851,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C50" t="n">
-        <v>1148.30004883</v>
+        <v>1186.89001465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5916,16 +5882,16 @@
         <v>13.87537090186995</v>
       </c>
       <c r="K50" t="n">
-        <v>3.144733945482914</v>
+        <v>6.61103333432711</v>
       </c>
       <c r="L50" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M50" t="n">
-        <v>53.57142857142857</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N50" t="n">
-        <v>10.19612979167614</v>
+        <v>11.00631344302492</v>
       </c>
       <c r="O50" t="n">
         <v>2</v>
@@ -5972,10 +5938,10 @@
         <v>39.28571428571428</v>
       </c>
       <c r="AG50" t="n">
-        <v>16.57608695652174</v>
+        <v>16.33152173913043</v>
       </c>
       <c r="AH50" t="n">
-        <v>22.70962732919254</v>
+        <v>22.95419254658385</v>
       </c>
       <c r="AI50" t="n">
         <v>23.56568654157959</v>
@@ -5994,10 +5960,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C51" t="n">
-        <v>528.98999023</v>
+        <v>528.23999023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6025,7 +5991,7 @@
         <v>15.85507589392084</v>
       </c>
       <c r="K51" t="n">
-        <v>2.597366007360691</v>
+        <v>2.451903851314841</v>
       </c>
       <c r="L51" t="n">
         <v>19</v>
@@ -6103,10 +6069,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C52" t="n">
-        <v>192.89590454</v>
+        <v>188.16999817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6131,25 +6097,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>16.63935213539153</v>
+        <v>16.95823306076329</v>
       </c>
       <c r="K52" t="n">
-        <v>2.484275470030739</v>
+        <v>0.3573323573333509</v>
       </c>
       <c r="L52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M52" t="n">
-        <v>43.47826086956522</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N52" t="n">
-        <v>9.308901439506009</v>
+        <v>9.847427296221635</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>0.5032230823743156</v>
+        <v>2.633258159211671</v>
       </c>
       <c r="Q52" t="n">
         <v>24</v>
@@ -6212,10 +6178,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C53" t="n">
-        <v>305.51998901</v>
+        <v>303.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6243,13 +6209,17 @@
         <v>23.1435368229701</v>
       </c>
       <c r="K53" t="n">
-        <v>15.12981671942386</v>
+        <v>14.3686195052902</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N53" t="n">
+        <v>14.6445693615431</v>
+      </c>
       <c r="O53" t="n">
         <v>4</v>
       </c>
@@ -6263,10 +6233,10 @@
         <v>62.5</v>
       </c>
       <c r="S53" t="n">
-        <v>61.5021706108263</v>
+        <v>61.55425394415963</v>
       </c>
       <c r="T53" t="n">
-        <v>0.9978293891736953</v>
+        <v>0.9457460558403668</v>
       </c>
       <c r="U53" t="n">
         <v>48.36276351921527</v>
@@ -6278,25 +6248,25 @@
         <v>68.75</v>
       </c>
       <c r="X53" t="n">
-        <v>17.31167927226511</v>
+        <v>17.34183230066753</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.859885193338207</v>
+        <v>2.533804643308268</v>
       </c>
       <c r="Z53" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA53" t="n">
-        <v>34.14634146341464</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB53" t="n">
-        <v>10.60505770631941</v>
+        <v>11.40260002168185</v>
       </c>
       <c r="AC53" t="n">
         <v>10</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.294380766415443</v>
+        <v>7.660292196046125</v>
       </c>
       <c r="AE53" t="n">
         <v>35</v>
@@ -6327,10 +6297,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C54" t="n">
-        <v>559.77502441</v>
+        <v>561.10998535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6426,10 +6396,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C55" t="n">
-        <v>236.48500061</v>
+        <v>239.66999817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,25 +6424,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>15.92484916015828</v>
+        <v>15.92843952915467</v>
       </c>
       <c r="K55" t="n">
-        <v>1.044696372457321</v>
+        <v>2.409947194548301</v>
       </c>
       <c r="L55" t="n">
         <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="N55" t="n">
-        <v>10.73472617816773</v>
+        <v>14.76702107404096</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>1.93508783512526</v>
+        <v>0.5761674735861089</v>
       </c>
       <c r="Q55" t="n">
         <v>16</v>
@@ -6535,10 +6505,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C56" t="n">
-        <v>89.55999756</v>
+        <v>88.94499969</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6634,10 +6604,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C57" t="n">
-        <v>747.13000488</v>
+        <v>771.61499023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6694,25 +6664,25 @@
         <v>60.52631578947368</v>
       </c>
       <c r="X57" t="n">
-        <v>42.18177017922093</v>
+        <v>44.10817128365145</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.195316009179649</v>
+        <v>0.3403306128511474</v>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="n">
-        <v>30</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB57" t="n">
-        <v>6.459860413815332</v>
+        <v>13.55329255158906</v>
       </c>
       <c r="AC57" t="n">
         <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.890083619285001</v>
+        <v>5.678996751597365</v>
       </c>
       <c r="AE57" t="n">
         <v>31</v>
@@ -6743,10 +6713,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C58" t="n">
-        <v>49.06000137</v>
+        <v>49.52999878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6763,7 +6733,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %79.17: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6774,22 +6748,22 @@
         <v>24.34769105644016</v>
       </c>
       <c r="K58" t="n">
-        <v>3.808724320750256</v>
+        <v>4.803217394612891</v>
       </c>
       <c r="L58" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M58" t="n">
-        <v>73.07692307692308</v>
+        <v>79.16666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>15.38447108883103</v>
+        <v>15.44066906643997</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>4.037498492226388</v>
+        <v>3.050271437135699</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -6839,10 +6813,10 @@
         <v>23.14189128245424</v>
       </c>
       <c r="AJ58" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AK58" t="n">
-        <v>48.33333333333334</v>
+        <v>49.18032786885246</v>
       </c>
     </row>
     <row r="59">
@@ -6852,10 +6826,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C59" t="n">
-        <v>147.43499756</v>
+        <v>148.32000732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6912,40 +6886,40 @@
         <v>40.90909090909091</v>
       </c>
       <c r="X59" t="n">
-        <v>21.72833272418202</v>
+        <v>17.93176089548698</v>
       </c>
       <c r="Y59" t="n">
-        <v>6.044481723562345</v>
+        <v>5.480493850556368</v>
       </c>
       <c r="Z59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>22.22222222222222</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB59" t="n">
-        <v>10.20473306791089</v>
+        <v>9.678472286119888</v>
       </c>
       <c r="AC59" t="n">
         <v>10</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.209990375232309</v>
+        <v>4.781559207787112</v>
       </c>
       <c r="AE59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF59" t="n">
-        <v>26.31578947368421</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AG59" t="n">
-        <v>11.45218697850277</v>
+        <v>9.318983485650152</v>
       </c>
       <c r="AH59" t="n">
-        <v>14.86360249518144</v>
+        <v>18.45879429212763</v>
       </c>
       <c r="AI59" t="n">
-        <v>11.80641234678251</v>
+        <v>12.49975337955399</v>
       </c>
       <c r="AJ59" t="n">
         <v>21</v>
@@ -6961,10 +6935,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C60" t="n">
-        <v>257.57998657</v>
+        <v>259.23001099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7006,10 +6980,10 @@
         <v>62.5</v>
       </c>
       <c r="S60" t="n">
-        <v>45.04068152807469</v>
+        <v>45.19693152807469</v>
       </c>
       <c r="T60" t="n">
-        <v>17.45931847192531</v>
+        <v>17.30306847192531</v>
       </c>
       <c r="U60" t="n">
         <v>48.36276351921527</v>
@@ -7024,43 +6998,43 @@
         <v>32.58897740521489</v>
       </c>
       <c r="Y60" t="n">
-        <v>3.165418582706758</v>
+        <v>2.545108650375949</v>
       </c>
       <c r="Z60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA60" t="n">
-        <v>45.45454545454545</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB60" t="n">
-        <v>13.18378199417288</v>
+        <v>15.00649963668617</v>
       </c>
       <c r="AC60" t="n">
         <v>5</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.894551915691578</v>
+        <v>2.519002705381934</v>
       </c>
       <c r="AE60" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AF60" t="n">
-        <v>52.83018867924528</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AG60" t="n">
-        <v>35.59427459808616</v>
+        <v>34.49280838144433</v>
       </c>
       <c r="AH60" t="n">
-        <v>17.23591408115912</v>
+        <v>18.44836808914391</v>
       </c>
       <c r="AI60" t="n">
-        <v>39.66008127870629</v>
+        <v>39.52330421009647</v>
       </c>
       <c r="AJ60" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK60" t="n">
-        <v>51.72413793103448</v>
+        <v>51.13636363636363</v>
       </c>
     </row>
     <row r="61">
@@ -7070,10 +7044,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C61" t="n">
-        <v>198.81500244</v>
+        <v>196.25999451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,25 +7072,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>10.83783673873874</v>
+        <v>12.27477477477478</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4420531419692342</v>
+        <v>0.7753501976893507</v>
       </c>
       <c r="L61" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M61" t="n">
-        <v>59.45945945945946</v>
+        <v>68.29268292682927</v>
       </c>
       <c r="N61" t="n">
-        <v>9.232286451878743</v>
+        <v>10.60251497273278</v>
       </c>
       <c r="O61" t="n">
         <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>2.546689138677061</v>
+        <v>2.207533685515939</v>
       </c>
       <c r="Q61" t="n">
         <v>32</v>
@@ -7125,10 +7099,10 @@
         <v>40.625</v>
       </c>
       <c r="S61" t="n">
-        <v>41.07285648890225</v>
+        <v>40.83848148890225</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.4478564889022465</v>
+        <v>-0.2134814889022465</v>
       </c>
       <c r="U61" t="n">
         <v>25.51963484266544</v>
@@ -7179,10 +7153,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C62" t="n">
-        <v>499.27999878</v>
+        <v>496.21499634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7278,10 +7252,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C63" t="n">
-        <v>1069.80004883</v>
+        <v>1075.25952148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7338,46 +7312,46 @@
         <v>65.85365853658537</v>
       </c>
       <c r="X63" t="n">
-        <v>24.54793165650138</v>
+        <v>24.54794540916325</v>
       </c>
       <c r="Y63" t="n">
-        <v>3.229292902939651</v>
+        <v>2.73545712528267</v>
       </c>
       <c r="Z63" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AA63" t="n">
-        <v>30.55555555555556</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB63" t="n">
-        <v>15.17606609794329</v>
+        <v>13.30013704667113</v>
       </c>
       <c r="AC63" t="n">
         <v>4</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.7964260262016465</v>
+        <v>1.300106737093432</v>
       </c>
       <c r="AE63" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AF63" t="n">
-        <v>51.85185185185185</v>
+        <v>52.72727272727273</v>
       </c>
       <c r="AG63" t="n">
-        <v>18.43095848557299</v>
+        <v>17.75057461650021</v>
       </c>
       <c r="AH63" t="n">
-        <v>33.42089336627886</v>
+        <v>34.97669811077252</v>
       </c>
       <c r="AI63" t="n">
-        <v>38.85170019812708</v>
+        <v>39.79154435522611</v>
       </c>
       <c r="AJ63" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK63" t="n">
-        <v>50</v>
+        <v>50.66666666666666</v>
       </c>
     </row>
     <row r="64">
@@ -7387,10 +7361,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C64" t="n">
-        <v>77.74500275</v>
+        <v>76.14499664</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7415,25 +7389,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>11.54021807329905</v>
+        <v>13.4140748522771</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4197940941387701</v>
+        <v>0.4816546131910737</v>
       </c>
       <c r="L64" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M64" t="n">
-        <v>28.57142857142857</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="N64" t="n">
-        <v>10.52797185138249</v>
+        <v>11.65536109147039</v>
       </c>
       <c r="O64" t="n">
         <v>10</v>
       </c>
       <c r="P64" t="n">
-        <v>9.540156890662654</v>
+        <v>9.472719595880719</v>
       </c>
       <c r="Q64" t="n">
         <v>21</v>
@@ -7474,10 +7448,10 @@
         <v>33.33333333333334</v>
       </c>
       <c r="AG64" t="n">
-        <v>9.824109824109824</v>
+        <v>9.962998712998713</v>
       </c>
       <c r="AH64" t="n">
-        <v>23.50922350922351</v>
+        <v>23.37033462033462</v>
       </c>
       <c r="AI64" t="n">
         <v>16.27877475083369</v>
@@ -7496,10 +7470,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C65" t="n">
-        <v>123.30500031</v>
+        <v>120.91000366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7527,22 +7501,22 @@
         <v>11.30164391184886</v>
       </c>
       <c r="K65" t="n">
-        <v>2.75416692499999</v>
+        <v>0.7583363833333356</v>
       </c>
       <c r="L65" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M65" t="n">
-        <v>51.21951219512195</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N65" t="n">
-        <v>13.22595954855335</v>
+        <v>11.51559057951757</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.051619697611611</v>
+        <v>9.172108183194805</v>
       </c>
       <c r="Q65" t="n">
         <v>35</v>
@@ -7569,16 +7543,16 @@
         <v>19.42972700127354</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.858743125450275</v>
+        <v>10.62901200621384</v>
       </c>
       <c r="Z65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA65" t="n">
-        <v>44.44444444444444</v>
+        <v>62.5</v>
       </c>
       <c r="AB65" t="n">
-        <v>8.855675284029097</v>
+        <v>9.67392877385792</v>
       </c>
       <c r="AC65" t="n">
         <v>6</v>
@@ -7615,10 +7589,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C66" t="n">
-        <v>71.66000366</v>
+        <v>71.85990142999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7646,22 +7620,22 @@
         <v>16.1363613718736</v>
       </c>
       <c r="K66" t="n">
-        <v>2.210815912871245</v>
+        <v>2.49593610722405</v>
       </c>
       <c r="L66" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M66" t="n">
-        <v>69.23076923076923</v>
+        <v>65.78947368421052</v>
       </c>
       <c r="N66" t="n">
-        <v>13.11142197008968</v>
+        <v>13.03913093242597</v>
       </c>
       <c r="O66" t="n">
         <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>7.620704342844298</v>
+        <v>7.321328218248313</v>
       </c>
       <c r="Q66" t="n">
         <v>32</v>
@@ -7670,10 +7644,10 @@
         <v>59.375</v>
       </c>
       <c r="S66" t="n">
-        <v>41.02008470924301</v>
+        <v>40.55092134945465</v>
       </c>
       <c r="T66" t="n">
-        <v>18.35491529075699</v>
+        <v>18.82407865054535</v>
       </c>
       <c r="U66" t="n">
         <v>42.26002487538288</v>
@@ -7724,10 +7698,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C67" t="n">
-        <v>35.83499908</v>
+        <v>35.80770111</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7755,7 +7729,7 @@
         <v>14.75766233411265</v>
       </c>
       <c r="K67" t="n">
-        <v>1.371996127274522</v>
+        <v>1.294774143734223</v>
       </c>
       <c r="L67" t="n">
         <v>29</v>
@@ -7764,34 +7738,34 @@
         <v>51.72413793103448</v>
       </c>
       <c r="N67" t="n">
-        <v>10.36043911443285</v>
+        <v>10.44289043416823</v>
       </c>
       <c r="O67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P67" t="n">
-        <v>8.511230125026703</v>
+        <v>0.6962114899087268</v>
       </c>
       <c r="Q67" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R67" t="n">
-        <v>33.33333333333334</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="S67" t="n">
-        <v>24.18883404177522</v>
+        <v>28.85095070439898</v>
       </c>
       <c r="T67" t="n">
-        <v>9.144499291558116</v>
+        <v>9.080083778359644</v>
       </c>
       <c r="U67" t="n">
-        <v>19.75022767922068</v>
+        <v>22.68802210080984</v>
       </c>
       <c r="V67" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W67" t="n">
-        <v>41.66666666666666</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -7811,10 +7785,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="AG67" t="n">
-        <v>15.32491511193337</v>
+        <v>15.42271285171894</v>
       </c>
       <c r="AH67" t="n">
-        <v>36.39922281910111</v>
+        <v>36.30142507931555</v>
       </c>
       <c r="AI67" t="n">
         <v>34.43102188199472</v>
@@ -7833,10 +7807,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C68" t="n">
-        <v>140.01499939</v>
+        <v>138.7749939</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7864,22 +7838,22 @@
         <v>12.84091305260983</v>
       </c>
       <c r="K68" t="n">
-        <v>7.381701085227688</v>
+        <v>6.430703696009865</v>
       </c>
       <c r="L68" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M68" t="n">
-        <v>67.44186046511628</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N68" t="n">
-        <v>10.92845754480795</v>
+        <v>11.87175174027434</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>2.438310148108203</v>
+        <v>3.353634036081221</v>
       </c>
       <c r="Q68" t="n">
         <v>47</v>
@@ -7888,10 +7862,10 @@
         <v>48.93617021276596</v>
       </c>
       <c r="S68" t="n">
-        <v>53.81917476863463</v>
+        <v>53.4246733904281</v>
       </c>
       <c r="T68" t="n">
-        <v>-4.883004555868673</v>
+        <v>-4.488503177662146</v>
       </c>
       <c r="U68" t="n">
         <v>35.27555503368215</v>
@@ -7906,16 +7880,16 @@
         <v>27.22171167302887</v>
       </c>
       <c r="Y68" t="n">
-        <v>6.407089785539776</v>
+        <v>7.235970426875538</v>
       </c>
       <c r="Z68" t="n">
         <v>12</v>
       </c>
       <c r="AA68" t="n">
-        <v>58.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB68" t="n">
-        <v>10.42035820542849</v>
+        <v>11.59574080845966</v>
       </c>
       <c r="AC68" t="n">
         <v>2</v>
@@ -7952,10 +7926,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C69" t="n">
-        <v>224.47489929</v>
+        <v>224.28500366</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7983,7 +7957,7 @@
         <v>11.0027272252725</v>
       </c>
       <c r="K69" t="n">
-        <v>7.440246568049602</v>
+        <v>7.349356970264176</v>
       </c>
       <c r="L69" t="n">
         <v>44</v>
@@ -7992,7 +7966,7 @@
         <v>63.63636363636363</v>
       </c>
       <c r="N69" t="n">
-        <v>11.75501853230481</v>
+        <v>11.19447909849975</v>
       </c>
       <c r="O69" t="n">
         <v>2</v>
@@ -8007,10 +7981,10 @@
         <v>61.70212765957447</v>
       </c>
       <c r="S69" t="n">
-        <v>68.60611577708606</v>
+        <v>68.35316535056342</v>
       </c>
       <c r="T69" t="n">
-        <v>-6.903988117511595</v>
+        <v>-6.65103769098895</v>
       </c>
       <c r="U69" t="n">
         <v>47.42656695641357</v>
@@ -8025,7 +7999,7 @@
         <v>13.27382123522316</v>
       </c>
       <c r="Y69" t="n">
-        <v>4.381110691993095</v>
+        <v>4.461999955258056</v>
       </c>
       <c r="Z69" t="n">
         <v>45</v>
@@ -8040,7 +8014,7 @@
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.693064330408767</v>
+        <v>1.609830689381897</v>
       </c>
       <c r="AE69" t="n">
         <v>34</v>
@@ -8071,19 +8045,19 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C70" t="n">
-        <v>233.41499329</v>
+        <v>230.74499512</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8098,27 +8072,17 @@
       <c r="I70" t="n">
         <v>10</v>
       </c>
-      <c r="J70" t="n">
-        <v>10.65198616240091</v>
-      </c>
-      <c r="K70" t="n">
-        <v>7.733309954288226</v>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>21</v>
-      </c>
-      <c r="M70" t="n">
-        <v>38.09523809523809</v>
-      </c>
-      <c r="N70" t="n">
-        <v>10.32124274020965</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
         <v>10</v>
       </c>
-      <c r="P70" t="n">
-        <v>2.103982553467953</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
         <v>32</v>
       </c>
@@ -8126,10 +8090,10 @@
         <v>59.375</v>
       </c>
       <c r="S70" t="n">
-        <v>41.90320616883117</v>
+        <v>42.00622814685315</v>
       </c>
       <c r="T70" t="n">
-        <v>17.47179383116883</v>
+        <v>17.36877185314685</v>
       </c>
       <c r="U70" t="n">
         <v>42.26002487538288</v>
@@ -8144,16 +8108,16 @@
         <v>10.28339259836972</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.312299779685223</v>
+        <v>3.429734341807356</v>
       </c>
       <c r="Z70" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA70" t="n">
-        <v>32.35294117647059</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AB70" t="n">
-        <v>12.97555081273557</v>
+        <v>12.103896387302</v>
       </c>
       <c r="AC70" t="n">
         <v>2</v>
@@ -8190,14 +8154,14 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C71" t="n">
-        <v>146.56500244</v>
+        <v>138.59939575</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8207,7 +8171,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -8218,25 +8182,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>18.57059022636381</v>
+        <v>21.80433619509799</v>
       </c>
       <c r="K71" t="n">
-        <v>5.442447798561156</v>
+        <v>3.835331273425724</v>
       </c>
       <c r="L71" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N71" t="n">
-        <v>11.66304203341437</v>
+        <v>13.97672339699281</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>2.42554327487241</v>
+        <v>4.010839735857941</v>
       </c>
       <c r="Q71" t="n">
         <v>34</v>
@@ -8245,10 +8209,10 @@
         <v>64.70588235294117</v>
       </c>
       <c r="S71" t="n">
-        <v>25.33415614821552</v>
+        <v>25.40768555998023</v>
       </c>
       <c r="T71" t="n">
-        <v>39.37172620472565</v>
+        <v>39.29819679296095</v>
       </c>
       <c r="U71" t="n">
         <v>47.91396311978173</v>
@@ -8259,43 +8223,37 @@
       <c r="W71" t="n">
         <v>65.78947368421052</v>
       </c>
-      <c r="X71" t="n">
-        <v>24.2086924558512</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>14.1388371067572</v>
-      </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>10</v>
       </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF71" t="n">
-        <v>58.06451612903226</v>
+        <v>56.25</v>
       </c>
       <c r="AG71" t="n">
-        <v>7.754490133522391</v>
+        <v>8.53411322778099</v>
       </c>
       <c r="AH71" t="n">
-        <v>50.31002599550987</v>
+        <v>47.71588677221901</v>
       </c>
       <c r="AI71" t="n">
-        <v>40.76626249536972</v>
+        <v>39.32559113685198</v>
       </c>
       <c r="AJ71" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK71" t="n">
-        <v>50</v>
+        <v>48.64864864864865</v>
       </c>
     </row>
     <row r="72">
@@ -8305,19 +8263,19 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C72" t="n">
-        <v>57.52500153</v>
+        <v>57.97499847</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8336,37 +8294,37 @@
         <v>11.90214849498216</v>
       </c>
       <c r="K72" t="n">
-        <v>2.394092582019081</v>
+        <v>3.19508392683383</v>
       </c>
       <c r="L72" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M72" t="n">
-        <v>55</v>
+        <v>50.90909090909091</v>
       </c>
       <c r="N72" t="n">
-        <v>18.73908866401763</v>
+        <v>16.92447247597807</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>0.5917406001675118</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R72" t="n">
-        <v>45.16129032258065</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="S72" t="n">
-        <v>27.29450326125777</v>
+        <v>28.20432003663303</v>
       </c>
       <c r="T72" t="n">
-        <v>17.86678706132287</v>
+        <v>15.12901329670031</v>
       </c>
       <c r="U72" t="n">
-        <v>29.16173598052001</v>
+        <v>27.37748557646652</v>
       </c>
       <c r="V72" t="n">
         <v>79</v>
@@ -8414,10 +8372,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C73" t="n">
-        <v>129.6401062</v>
+        <v>128.83999634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8445,22 +8403,22 @@
         <v>12.28237922496582</v>
       </c>
       <c r="K73" t="n">
-        <v>1.297157990635633</v>
+        <v>0.6719744940003602</v>
       </c>
       <c r="L73" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M73" t="n">
-        <v>60</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N73" t="n">
-        <v>7.789120604197176</v>
+        <v>8.156469565824043</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>0.6938417852052181</v>
+        <v>1.319161080007203</v>
       </c>
       <c r="Q73" t="n">
         <v>16</v>
@@ -8523,10 +8481,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C74" t="n">
-        <v>28.05990028</v>
+        <v>28.48999977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8583,25 +8541,25 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X74" t="n">
-        <v>11.57371556196134</v>
+        <v>10.60204182469922</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.937346238355299</v>
+        <v>2.464906993074778</v>
       </c>
       <c r="Z74" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA74" t="n">
-        <v>20</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB74" t="n">
-        <v>10.42033107051223</v>
+        <v>11.56142715499327</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>6.311145407962238</v>
+        <v>7.725519886868016</v>
       </c>
       <c r="AE74" t="n">
         <v>17</v>
@@ -8632,10 +8590,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C75" t="n">
-        <v>191.01499939</v>
+        <v>193.04859924</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8692,25 +8650,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X75" t="n">
-        <v>17.76966861016416</v>
+        <v>18.31053726619789</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.431959335406607</v>
+        <v>0.8379872104688046</v>
       </c>
       <c r="Z75" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AA75" t="n">
-        <v>48.88888888888889</v>
+        <v>50</v>
       </c>
       <c r="AB75" t="n">
-        <v>15.08098172122898</v>
+        <v>15.12944719185882</v>
       </c>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.590820568229734</v>
+        <v>2.180283284608209</v>
       </c>
       <c r="AE75" t="n">
         <v>19</v>
@@ -8741,10 +8699,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C76" t="n">
-        <v>191.22999573</v>
+        <v>191.64360046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,10 +8744,10 @@
         <v>39.1304347826087</v>
       </c>
       <c r="S76" t="n">
-        <v>19.45242766467023</v>
+        <v>19.46277963154393</v>
       </c>
       <c r="T76" t="n">
-        <v>19.67800711793847</v>
+        <v>19.66765515106476</v>
       </c>
       <c r="U76" t="n">
         <v>22.15762279247795</v>
@@ -8818,10 +8776,10 @@
         <v>30</v>
       </c>
       <c r="AG76" t="n">
-        <v>12.21446078431373</v>
+        <v>12.48674242424243</v>
       </c>
       <c r="AH76" t="n">
-        <v>17.78553921568627</v>
+        <v>17.51325757575757</v>
       </c>
       <c r="AI76" t="n">
         <v>14.54772448676043</v>
@@ -8840,10 +8798,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C77" t="n">
-        <v>196.2749939</v>
+        <v>193.625</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8885,10 +8843,10 @@
         <v>45.94594594594594</v>
       </c>
       <c r="S77" t="n">
-        <v>43.60199485199485</v>
+        <v>43.42395967395967</v>
       </c>
       <c r="T77" t="n">
-        <v>2.343951093951091</v>
+        <v>2.521986271986272</v>
       </c>
       <c r="U77" t="n">
         <v>31.03856980437303</v>
@@ -8900,25 +8858,25 @@
         <v>46.93877551020408</v>
       </c>
       <c r="X77" t="n">
-        <v>27.7686821005714</v>
+        <v>27.76675802703741</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.672242078321173</v>
+        <v>2.998347072646701</v>
       </c>
       <c r="Z77" t="n">
         <v>14</v>
       </c>
       <c r="AA77" t="n">
-        <v>28.57142857142857</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="AB77" t="n">
-        <v>7.779644426519988</v>
+        <v>6.323504890604125</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>8.469386567638558</v>
+        <v>7.218075894641707</v>
       </c>
       <c r="AE77" t="n">
         <v>37</v>
@@ -8949,10 +8907,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C78" t="n">
-        <v>194.11999512</v>
+        <v>191.38999939</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8980,16 +8938,16 @@
         <v>17.38881221393466</v>
       </c>
       <c r="K78" t="n">
-        <v>3.785287683914018</v>
+        <v>2.325709076162896</v>
       </c>
       <c r="L78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M78" t="n">
-        <v>66.66666666666667</v>
+        <v>56.25</v>
       </c>
       <c r="N78" t="n">
-        <v>13.87857020882609</v>
+        <v>15.82680926559527</v>
       </c>
       <c r="O78" t="n">
         <v>2</v>
@@ -9058,10 +9016,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C79" t="n">
-        <v>100.4701004</v>
+        <v>98.90499878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9086,25 +9044,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>13.29782231051553</v>
+        <v>14.37614294541949</v>
       </c>
       <c r="K79" t="n">
-        <v>1.178345734199859</v>
+        <v>0.8565709673172606</v>
       </c>
       <c r="L79" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M79" t="n">
-        <v>58.8235294117647</v>
+        <v>62.5</v>
       </c>
       <c r="N79" t="n">
-        <v>10.16814465225778</v>
+        <v>10.65094992334666</v>
       </c>
       <c r="O79" t="n">
         <v>6</v>
       </c>
       <c r="P79" t="n">
-        <v>4.765500197509498</v>
+        <v>5.099746088283608</v>
       </c>
       <c r="Q79" t="n">
         <v>27</v>
@@ -9167,10 +9125,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C80" t="n">
-        <v>52.18999863</v>
+        <v>51.61999893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9198,22 +9156,22 @@
         <v>16.52331791600153</v>
       </c>
       <c r="K80" t="n">
-        <v>3.407959913657388</v>
+        <v>2.278576743018368</v>
       </c>
       <c r="L80" t="n">
         <v>34</v>
       </c>
       <c r="M80" t="n">
-        <v>55.88235294117647</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N80" t="n">
-        <v>15.08050453966852</v>
+        <v>13.91777750315925</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>0.5725285430995264</v>
+        <v>1.683073143759928</v>
       </c>
       <c r="Q80" t="n">
         <v>43</v>
@@ -9276,10 +9234,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C81" t="n">
-        <v>41.5320015</v>
+        <v>41.51010132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9336,10 +9294,10 @@
         <v>73.80952380952381</v>
       </c>
       <c r="X81" t="n">
-        <v>25.81026070595338</v>
+        <v>25.25667518954236</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.735361215951426</v>
+        <v>2.786649692790322</v>
       </c>
       <c r="Z81" t="n">
         <v>30</v>
@@ -9348,34 +9306,34 @@
         <v>36.66666666666666</v>
       </c>
       <c r="AB81" t="n">
-        <v>15.38614866662838</v>
+        <v>15.47020730874735</v>
       </c>
       <c r="AC81" t="n">
         <v>8</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.412695559109992</v>
+        <v>5.362792549310003</v>
       </c>
       <c r="AE81" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF81" t="n">
-        <v>48.68421052631579</v>
+        <v>48.05194805194805</v>
       </c>
       <c r="AG81" t="n">
-        <v>22.53688630216007</v>
+        <v>22.40653712940474</v>
       </c>
       <c r="AH81" t="n">
-        <v>26.14732422415572</v>
+        <v>25.64541092254331</v>
       </c>
       <c r="AI81" t="n">
-        <v>37.78372877915117</v>
+        <v>37.25303790298501</v>
       </c>
       <c r="AJ81" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK81" t="n">
-        <v>46.21848739495798</v>
+        <v>45.83333333333334</v>
       </c>
     </row>
     <row r="82">
@@ -9385,10 +9343,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C82" t="n">
-        <v>406.68499756</v>
+        <v>404.30499268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9413,25 +9371,25 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>11.8900081911483</v>
+        <v>11.93836860913503</v>
       </c>
       <c r="K82" t="n">
-        <v>1.460721798811204</v>
+        <v>0.9223452897140882</v>
       </c>
       <c r="L82" t="n">
         <v>22</v>
       </c>
       <c r="M82" t="n">
-        <v>40.90909090909091</v>
+        <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>10.64662700539032</v>
+        <v>10.68747122516058</v>
       </c>
       <c r="O82" t="n">
         <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>8.416338904154008</v>
+        <v>8.994692586886522</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -9494,19 +9452,19 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C83" t="n">
-        <v>272.6000061</v>
+        <v>270.67498779</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9514,7 +9472,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>5</v>
       </c>
@@ -9522,25 +9484,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>23.15662045633322</v>
+        <v>22.97484747408979</v>
       </c>
       <c r="K83" t="n">
-        <v>2.097380561797735</v>
+        <v>1.376399921348304</v>
       </c>
       <c r="L83" t="n">
         <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N83" t="n">
-        <v>16.19377238813152</v>
+        <v>14.20682329074149</v>
       </c>
       <c r="O83" t="n">
         <v>2</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>0.6151333832484784</v>
       </c>
       <c r="Q83" t="n">
         <v>19</v>
@@ -9549,10 +9511,10 @@
         <v>47.36842105263158</v>
       </c>
       <c r="S83" t="n">
-        <v>26.69755729035507</v>
+        <v>26.8291362377235</v>
       </c>
       <c r="T83" t="n">
-        <v>20.67086376227651</v>
+        <v>20.53928481490809</v>
       </c>
       <c r="U83" t="n">
         <v>27.32980516117956</v>
@@ -9603,10 +9565,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C84" t="n">
-        <v>25.51469994</v>
+        <v>25.57500076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9642,19 +9604,19 @@
       </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R84" t="n">
-        <v>45.45454545454545</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="S84" t="n">
-        <v>12.81565656565657</v>
+        <v>13.42592592592593</v>
       </c>
       <c r="T84" t="n">
-        <v>32.63888888888889</v>
+        <v>29.43121693121693</v>
       </c>
       <c r="U84" t="n">
-        <v>26.92029418081331</v>
+        <v>24.46996892537596</v>
       </c>
       <c r="V84" t="n">
         <v>23</v>
@@ -9663,19 +9625,19 @@
         <v>39.1304347826087</v>
       </c>
       <c r="X84" t="n">
-        <v>11.74273811359998</v>
+        <v>11.18910436500753</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.255478476450115</v>
+        <v>5.031561583372291</v>
       </c>
       <c r="Z84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA84" t="n">
-        <v>36.36363636363637</v>
+        <v>40</v>
       </c>
       <c r="AB84" t="n">
-        <v>13.80679724257406</v>
+        <v>11.95541884884477</v>
       </c>
       <c r="AC84" t="n">
         <v>4</v>
@@ -9690,10 +9652,10 @@
         <v>26.31578947368421</v>
       </c>
       <c r="AG84" t="n">
-        <v>12.0597713260252</v>
+        <v>11.92819237865677</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.25601814765901</v>
+        <v>14.38759709502743</v>
       </c>
       <c r="AI84" t="n">
         <v>11.80641234678251</v>
@@ -9712,10 +9674,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C85" t="n">
-        <v>132.06500244</v>
+        <v>131.63000488</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9740,16 +9702,20 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>20.94520590500485</v>
+        <v>20.29342759782459</v>
       </c>
       <c r="K85" t="n">
-        <v>7.562309620671259</v>
+        <v>7.208019374440333</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M85" t="n">
+        <v>40</v>
+      </c>
+      <c r="N85" t="n">
+        <v>16.73056940998959</v>
+      </c>
       <c r="O85" t="n">
         <v>2</v>
       </c>
@@ -9817,10 +9783,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C86" t="n">
-        <v>378.61999512</v>
+        <v>380.98498535</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9877,25 +9843,25 @@
         <v>75</v>
       </c>
       <c r="X86" t="n">
-        <v>19.48461089652223</v>
+        <v>18.89682198567812</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.089479398726291</v>
+        <v>1.477896736371564</v>
       </c>
       <c r="Z86" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AA86" t="n">
-        <v>46.55172413793103</v>
+        <v>46.03174603174603</v>
       </c>
       <c r="AB86" t="n">
-        <v>12.96908160209497</v>
+        <v>13.76401771694373</v>
       </c>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.9299517515402367</v>
+        <v>1.544935819686621</v>
       </c>
       <c r="AE86" t="n">
         <v>54</v>
@@ -9926,10 +9892,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C87" t="n">
-        <v>445.29000854</v>
+        <v>450.54019165</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,10 +9937,10 @@
         <v>62.85714285714285</v>
       </c>
       <c r="S87" t="n">
-        <v>38.54528625496368</v>
+        <v>38.62289911829082</v>
       </c>
       <c r="T87" t="n">
-        <v>24.31185660217918</v>
+        <v>24.23424373885203</v>
       </c>
       <c r="U87" t="n">
         <v>46.33693684359532</v>
@@ -9989,22 +9955,22 @@
         <v>11.78082480528946</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.675939820308725</v>
+        <v>0.5166519176796003</v>
       </c>
       <c r="Z87" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA87" t="n">
-        <v>34.21052631578947</v>
+        <v>32.43243243243244</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.73880085154371</v>
+        <v>12.16748227202618</v>
       </c>
       <c r="AC87" t="n">
         <v>6</v>
       </c>
       <c r="AD87" t="n">
-        <v>4.397764058755183</v>
+        <v>5.511825032047623</v>
       </c>
       <c r="AE87" t="n">
         <v>36</v>
@@ -10035,10 +10001,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C88" t="n">
-        <v>269.42001343</v>
+        <v>270.88000488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10063,25 +10029,25 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3256649882924</v>
+        <v>13.3049116789209</v>
       </c>
       <c r="K88" t="n">
-        <v>8.580183021515753</v>
+        <v>9.168580805454107</v>
       </c>
       <c r="L88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M88" t="n">
-        <v>30</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="N88" t="n">
-        <v>7.301238111646442</v>
+        <v>7.05570383617107</v>
       </c>
       <c r="O88" t="n">
         <v>10</v>
       </c>
       <c r="P88" t="n">
-        <v>1.307620726889835</v>
+        <v>0.7615920152223454</v>
       </c>
       <c r="Q88" t="n">
         <v>25</v>
@@ -10108,22 +10074,22 @@
         <v>10.15595905146061</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.430495493401962</v>
+        <v>0.8963457397209385</v>
       </c>
       <c r="Z88" t="n">
         <v>30</v>
       </c>
       <c r="AA88" t="n">
-        <v>26.66666666666667</v>
+        <v>30</v>
       </c>
       <c r="AB88" t="n">
-        <v>10.90209910753714</v>
+        <v>10.41208368857444</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.606794585668271</v>
+        <v>3.13172534700672</v>
       </c>
       <c r="AE88" t="n">
         <v>24</v>
@@ -10132,10 +10098,10 @@
         <v>37.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>14.62527056277056</v>
+        <v>14.77678571428571</v>
       </c>
       <c r="AH88" t="n">
-        <v>22.87472943722944</v>
+        <v>22.72321428571428</v>
       </c>
       <c r="AI88" t="n">
         <v>21.15936755954878</v>
@@ -10154,10 +10120,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C89" t="n">
-        <v>69.59999847</v>
+        <v>69.20500183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,43 +10151,43 @@
         <v>16.77289524548043</v>
       </c>
       <c r="K89" t="n">
-        <v>1.531721915802309</v>
+        <v>0.9555051070125442</v>
       </c>
       <c r="L89" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M89" t="n">
-        <v>64.1025641025641</v>
+        <v>62.16216216216216</v>
       </c>
       <c r="N89" t="n">
-        <v>15.81842140182667</v>
+        <v>14.56043805466842</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>2.431041291946734</v>
+        <v>3.015679917365888</v>
       </c>
       <c r="Q89" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R89" t="n">
-        <v>50</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="S89" t="n">
-        <v>51.42050322886025</v>
+        <v>51.48646288763518</v>
       </c>
       <c r="T89" t="n">
-        <v>-1.420503228860248</v>
+        <v>-3.210600818669661</v>
       </c>
       <c r="U89" t="n">
-        <v>32.63312745729346</v>
+        <v>31.38609015268349</v>
       </c>
       <c r="V89" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W89" t="n">
-        <v>57.89473684210526</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
@@ -10263,10 +10229,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C90" t="n">
-        <v>370.66000366</v>
+        <v>372.17999268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10294,22 +10260,22 @@
         <v>10.14435985893962</v>
       </c>
       <c r="K90" t="n">
-        <v>1.273225043715831</v>
+        <v>1.688522590163943</v>
       </c>
       <c r="L90" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M90" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>11.04170859565737</v>
+        <v>11.29721583383503</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>6.642204742053481</v>
+        <v>6.206676278770673</v>
       </c>
       <c r="Q90" t="n">
         <v>26</v>
@@ -10372,19 +10338,19 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C91" t="n">
-        <v>276.66500854</v>
+        <v>273.51000977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10403,22 +10369,22 @@
         <v>14.60766672642613</v>
       </c>
       <c r="K91" t="n">
-        <v>3.133153829825863</v>
+        <v>1.957056515617528</v>
       </c>
       <c r="L91" t="n">
         <v>20</v>
       </c>
       <c r="M91" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="N91" t="n">
-        <v>10.94289877833009</v>
+        <v>9.324408966333976</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.04211918806806825</v>
       </c>
       <c r="Q91" t="n">
         <v>17</v>
@@ -10459,10 +10425,10 @@
         <v>40</v>
       </c>
       <c r="AG91" t="n">
-        <v>17.99697931276879</v>
+        <v>17.87197931276879</v>
       </c>
       <c r="AH91" t="n">
-        <v>22.00302068723121</v>
+        <v>22.12802068723121</v>
       </c>
       <c r="AI91" t="n">
         <v>21.88065323728171</v>
@@ -10481,10 +10447,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C92" t="n">
-        <v>362.45001221</v>
+        <v>365.77999878</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10580,27 +10546,31 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C93" t="n">
-        <v>249.97999573</v>
+        <v>244.88000488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>5</v>
       </c>
@@ -10611,22 +10581,22 @@
         <v>24.42890054371254</v>
       </c>
       <c r="K93" t="n">
-        <v>10.15246014024851</v>
+        <v>7.905174163705708</v>
       </c>
       <c r="L93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M93" t="n">
-        <v>57.14285714285715</v>
+        <v>75</v>
       </c>
       <c r="N93" t="n">
-        <v>10.43413306745</v>
+        <v>12.04804885617308</v>
       </c>
       <c r="O93" t="n">
         <v>10</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.941358097542367</v>
       </c>
       <c r="Q93" t="n">
         <v>35</v>
@@ -10653,22 +10623,22 @@
         <v>12.53635174236054</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.118330268578184</v>
+        <v>4.115272538119418</v>
       </c>
       <c r="Z93" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AA93" t="n">
-        <v>42.5925925925926</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.01588432498114</v>
+        <v>13.48319595978856</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.922392350462498</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>32</v>
@@ -10699,10 +10669,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C94" t="n">
-        <v>46.93500137</v>
+        <v>47.51499939</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10727,40 +10697,40 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>10.65414640017589</v>
+        <v>10.66382526639831</v>
       </c>
       <c r="K94" t="n">
-        <v>1.667931191714578</v>
+        <v>2.935440954079649</v>
       </c>
       <c r="L94" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M94" t="n">
-        <v>17.39130434782609</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="N94" t="n">
-        <v>9.529258611612029</v>
+        <v>7.488848857552793</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P94" t="n">
-        <v>0.3266209948338927</v>
+        <v>0.06271799617505458</v>
       </c>
       <c r="Q94" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R94" t="n">
-        <v>36.8421052631579</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="S94" t="n">
-        <v>13.82874800637959</v>
+        <v>14.42624777183601</v>
       </c>
       <c r="T94" t="n">
-        <v>23.01335725677831</v>
+        <v>20.86786987522282</v>
       </c>
       <c r="U94" t="n">
-        <v>19.14951274513507</v>
+        <v>17.30972039724374</v>
       </c>
       <c r="V94" t="n">
         <v>20</v>
@@ -10786,10 +10756,10 @@
         <v>44.44444444444444</v>
       </c>
       <c r="AG94" t="n">
-        <v>9.67106967106967</v>
+        <v>9.532180782180781</v>
       </c>
       <c r="AH94" t="n">
-        <v>34.77337477337477</v>
+        <v>34.91226366226366</v>
       </c>
       <c r="AI94" t="n">
         <v>24.55951812700564</v>
@@ -10808,10 +10778,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C95" t="n">
-        <v>30.70999908</v>
+        <v>30.76499939</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10868,25 +10838,25 @@
         <v>60.60606060606061</v>
       </c>
       <c r="X95" t="n">
-        <v>13.09436689962857</v>
+        <v>11.86686238201107</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.6791752893165026</v>
+        <v>0.5012958913291232</v>
       </c>
       <c r="Z95" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AA95" t="n">
-        <v>52.54237288135593</v>
+        <v>44</v>
       </c>
       <c r="AB95" t="n">
-        <v>12.58792141161612</v>
+        <v>13.07387352214588</v>
       </c>
       <c r="AC95" t="n">
         <v>8</v>
       </c>
       <c r="AD95" t="n">
-        <v>7.370885946636752</v>
+        <v>7.536484194287507</v>
       </c>
       <c r="AE95" t="n">
         <v>51</v>
@@ -10917,10 +10887,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C96" t="n">
-        <v>82.45500183</v>
+        <v>81.54000092</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10945,25 +10915,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>10.56995037090656</v>
+        <v>12.00673815299945</v>
       </c>
       <c r="K96" t="n">
-        <v>0.2288910194601312</v>
+        <v>0.7350685431820381</v>
       </c>
       <c r="L96" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M96" t="n">
-        <v>25.80645161290322</v>
+        <v>37.14285714285715</v>
       </c>
       <c r="N96" t="n">
-        <v>9.725336025229296</v>
+        <v>9.94351526814239</v>
       </c>
       <c r="O96" t="n">
         <v>2</v>
       </c>
       <c r="P96" t="n">
-        <v>1.767064328982748</v>
+        <v>1.255701192356584</v>
       </c>
       <c r="Q96" t="n">
         <v>28</v>
@@ -10972,10 +10942,10 @@
         <v>42.85714285714285</v>
       </c>
       <c r="S96" t="n">
-        <v>36.34084113917858</v>
+        <v>36.36485074302011</v>
       </c>
       <c r="T96" t="n">
-        <v>6.516301717964275</v>
+        <v>6.492292114122741</v>
       </c>
       <c r="U96" t="n">
         <v>26.50854712412369</v>
@@ -11004,10 +10974,10 @@
         <v>51.72413793103448</v>
       </c>
       <c r="AG96" t="n">
-        <v>10.9644059117274</v>
+        <v>11.05061280827912</v>
       </c>
       <c r="AH96" t="n">
-        <v>40.75973201930709</v>
+        <v>40.67352512275536</v>
       </c>
       <c r="AI96" t="n">
         <v>34.43102188199472</v>
@@ -11026,10 +10996,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C97" t="n">
-        <v>110.37000275</v>
+        <v>108.47499847</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11057,16 +11027,16 @@
         <v>12.59519198565262</v>
       </c>
       <c r="K97" t="n">
-        <v>8.046990794792986</v>
+        <v>6.191871605740951</v>
       </c>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M97" t="n">
-        <v>22.22222222222222</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N97" t="n">
-        <v>5.520930121865053</v>
+        <v>9.139762072655046</v>
       </c>
       <c r="O97" t="n">
         <v>2</v>
@@ -11135,10 +11105,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C98" t="n">
-        <v>160.8500061</v>
+        <v>162.30000305</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11212,10 +11182,10 @@
         <v>50</v>
       </c>
       <c r="AG98" t="n">
-        <v>23.30751223359583</v>
+        <v>23.31376848985208</v>
       </c>
       <c r="AH98" t="n">
-        <v>26.69248776640417</v>
+        <v>26.68623151014792</v>
       </c>
       <c r="AI98" t="n">
         <v>31.42742581957335</v>
@@ -11234,10 +11204,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C99" t="n">
-        <v>30393.90234375</v>
+        <v>30461.33398438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
